--- a/unit12_Uboot/unit12_Uboot.xlsx
+++ b/unit12_Uboot/unit12_Uboot.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E8A02B-439D-4E80-9A73-A4897A1925E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{397A4370-2DA9-47D6-89C9-CB902F4B581E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -891,7 +891,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -960,7 +960,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2228,12 +2227,12 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2280,13 +2279,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2333,13 +2332,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2386,13 +2385,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>40</xdr:col>
+      <xdr:col>39</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2439,13 +2438,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2539,13 +2538,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>57</xdr:col>
+      <xdr:col>56</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2598,7 +2597,7 @@
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
@@ -2681,13 +2680,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>42</xdr:col>
+      <xdr:col>41</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>133349</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>49</xdr:col>
+      <xdr:col>48</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
@@ -2750,13 +2749,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>50</xdr:col>
+      <xdr:col>49</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>123824</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>56</xdr:col>
+      <xdr:col>55</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
@@ -2823,13 +2822,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>47</xdr:col>
+      <xdr:col>46</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>38099</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>53</xdr:col>
+      <xdr:col>52</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2896,13 +2895,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>59</xdr:col>
+      <xdr:col>58</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>68</xdr:col>
+      <xdr:col>67</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
@@ -2949,13 +2948,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>71</xdr:col>
+      <xdr:col>70</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>104774</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>77</xdr:col>
+      <xdr:col>76</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
@@ -3022,13 +3021,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>59</xdr:col>
+      <xdr:col>58</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>70</xdr:col>
+      <xdr:col>69</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -4541,11 +4540,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:BZ44"/>
+  <dimension ref="A1:BS44"/>
   <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:71" ht="15" thickBot="1"/>
-    <row r="2" spans="1:71" ht="15" thickBot="1">
+    <row r="1" spans="1:70" ht="15" thickBot="1"/>
+    <row r="2" spans="1:70" ht="15" thickBot="1">
       <c r="B2" s="32" t="s">
         <v>83</v>
       </c>
@@ -4555,29 +4554,28 @@
       <c r="F2" s="33"/>
       <c r="G2" s="33"/>
       <c r="H2" s="33"/>
-      <c r="I2" s="34"/>
-    </row>
-    <row r="3" spans="1:71">
+    </row>
+    <row r="3" spans="1:70">
       <c r="C3" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:71">
+    <row r="4" spans="1:70">
       <c r="C4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:71">
+    <row r="5" spans="1:70">
       <c r="C5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:71">
+    <row r="6" spans="1:70">
       <c r="C6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:71" ht="15">
+    <row r="8" spans="1:70" ht="15">
       <c r="D8" s="39" t="s">
         <v>115</v>
       </c>
@@ -4625,25 +4623,25 @@
       <c r="AT8" s="37"/>
       <c r="AU8" s="37"/>
       <c r="AV8" s="37"/>
-      <c r="AW8" s="37"/>
-      <c r="AX8" s="36"/>
+      <c r="AW8" s="36"/>
+      <c r="AX8" s="37"/>
       <c r="AY8" s="37"/>
       <c r="AZ8" s="37"/>
       <c r="BA8" s="37"/>
       <c r="BB8" s="37"/>
       <c r="BC8" s="37"/>
       <c r="BD8" s="37"/>
-      <c r="BE8" s="37"/>
-      <c r="BF8" s="38"/>
-    </row>
-    <row r="9" spans="1:71" ht="15" thickBot="1"/>
-    <row r="10" spans="1:71" s="30" customFormat="1" ht="15" thickBot="1">
+      <c r="BE8" s="38"/>
+    </row>
+    <row r="9" spans="1:70" ht="15" thickBot="1"/>
+    <row r="10" spans="1:70" s="30" customFormat="1" ht="15" thickBot="1">
       <c r="A10" s="29"/>
     </row>
-    <row r="13" spans="1:71">
-      <c r="L13" s="41" t="s">
+    <row r="13" spans="1:70">
+      <c r="K13" s="41" t="s">
         <v>89</v>
       </c>
+      <c r="L13" s="42"/>
       <c r="M13" s="42"/>
       <c r="N13" s="42"/>
       <c r="O13" s="42"/>
@@ -4651,52 +4649,51 @@
       <c r="Q13" s="42"/>
       <c r="R13" s="42"/>
       <c r="S13" s="42"/>
-      <c r="T13" s="42"/>
-      <c r="U13" s="43"/>
-      <c r="X13" s="41" t="s">
+      <c r="T13" s="43"/>
+      <c r="W13" s="41" t="s">
         <v>96</v>
       </c>
+      <c r="X13" s="42"/>
       <c r="Y13" s="42"/>
       <c r="Z13" s="42"/>
       <c r="AA13" s="42"/>
       <c r="AB13" s="42"/>
       <c r="AC13" s="42"/>
-      <c r="AD13" s="42"/>
-      <c r="AE13" s="43"/>
-      <c r="AK13" s="8"/>
-      <c r="AL13" s="41" t="s">
+      <c r="AD13" s="43"/>
+      <c r="AJ13" s="8"/>
+      <c r="AK13" s="41" t="s">
         <v>116</v>
       </c>
+      <c r="AL13" s="42"/>
       <c r="AM13" s="42"/>
       <c r="AN13" s="42"/>
       <c r="AO13" s="42"/>
-      <c r="AP13" s="42"/>
-      <c r="AQ13" s="43"/>
-      <c r="BC13" s="41" t="s">
+      <c r="AP13" s="43"/>
+      <c r="BB13" s="41" t="s">
         <v>121</v>
       </c>
+      <c r="BC13" s="42"/>
       <c r="BD13" s="42"/>
       <c r="BE13" s="42"/>
       <c r="BF13" s="42"/>
-      <c r="BG13" s="42"/>
-      <c r="BH13" s="43"/>
-      <c r="BN13" s="41" t="s">
+      <c r="BG13" s="43"/>
+      <c r="BM13" s="41" t="s">
         <v>124</v>
       </c>
+      <c r="BN13" s="42"/>
       <c r="BO13" s="42"/>
       <c r="BP13" s="42"/>
       <c r="BQ13" s="42"/>
-      <c r="BR13" s="42"/>
-      <c r="BS13" s="43"/>
-    </row>
-    <row r="14" spans="1:71">
-      <c r="P14" s="8"/>
-      <c r="AA14" s="8"/>
-      <c r="AN14" s="8"/>
-      <c r="BE14" s="6"/>
-      <c r="BP14" s="6"/>
-    </row>
-    <row r="15" spans="1:71">
+      <c r="BR13" s="43"/>
+    </row>
+    <row r="14" spans="1:70">
+      <c r="O14" s="8"/>
+      <c r="Z14" s="8"/>
+      <c r="AM14" s="8"/>
+      <c r="BD14" s="6"/>
+      <c r="BO14" s="6"/>
+    </row>
+    <row r="15" spans="1:70">
       <c r="B15" s="36" t="s">
         <v>114</v>
       </c>
@@ -4706,381 +4703,341 @@
       <c r="F15" s="37"/>
       <c r="G15" s="37"/>
       <c r="H15" s="38"/>
-      <c r="J15" t="s">
+      <c r="I15" t="s">
         <v>91</v>
       </c>
-      <c r="P15" s="8"/>
-      <c r="AA15" s="8"/>
-      <c r="AN15" s="8"/>
-      <c r="BE15" s="8"/>
-      <c r="BP15" s="8"/>
-    </row>
-    <row r="16" spans="1:71">
-      <c r="J16" t="s">
+      <c r="O15" s="8"/>
+      <c r="Z15" s="8"/>
+      <c r="AM15" s="8"/>
+      <c r="BD15" s="8"/>
+      <c r="BO15" s="8"/>
+    </row>
+    <row r="16" spans="1:70">
+      <c r="I16" t="s">
         <v>90</v>
       </c>
-      <c r="P16" s="8"/>
-      <c r="Q16" t="s">
+      <c r="O16" s="8"/>
+      <c r="P16" t="s">
         <v>92</v>
       </c>
-      <c r="AA16" s="8"/>
-      <c r="AN16" s="8"/>
-      <c r="BE16" s="8"/>
-      <c r="BP16" s="8"/>
-    </row>
-    <row r="17" spans="16:68">
-      <c r="P17" s="8"/>
-      <c r="Q17" t="s">
+      <c r="Z16" s="8"/>
+      <c r="AM16" s="8"/>
+      <c r="BD16" s="8"/>
+      <c r="BO16" s="8"/>
+    </row>
+    <row r="17" spans="15:67">
+      <c r="O17" s="8"/>
+      <c r="P17" t="s">
         <v>95</v>
       </c>
-      <c r="AA17" s="8"/>
-      <c r="AN17" s="8"/>
-      <c r="BE17" s="8"/>
-      <c r="BP17" s="8"/>
-    </row>
-    <row r="18" spans="16:68">
-      <c r="P18" s="8"/>
-      <c r="Q18" t="s">
+      <c r="Z17" s="8"/>
+      <c r="AM17" s="8"/>
+      <c r="BD17" s="8"/>
+      <c r="BO17" s="8"/>
+    </row>
+    <row r="18" spans="15:67">
+      <c r="O18" s="8"/>
+      <c r="P18" t="s">
         <v>93</v>
       </c>
-      <c r="AA18" s="8"/>
-      <c r="AN18" s="8"/>
-      <c r="BE18" s="8"/>
-      <c r="BP18" s="8"/>
-    </row>
-    <row r="19" spans="16:68">
-      <c r="P19" s="8"/>
-      <c r="R19" t="s">
+      <c r="Z18" s="8"/>
+      <c r="AM18" s="8"/>
+      <c r="BD18" s="8"/>
+      <c r="BO18" s="8"/>
+    </row>
+    <row r="19" spans="15:67">
+      <c r="O19" s="8"/>
+      <c r="Q19" t="s">
         <v>94</v>
       </c>
-      <c r="AA19" s="8"/>
-      <c r="AB19" t="s">
+      <c r="Z19" s="8"/>
+      <c r="AA19" t="s">
         <v>97</v>
       </c>
-      <c r="AN19" s="8"/>
-      <c r="BE19" s="8"/>
-      <c r="BP19" s="8"/>
-    </row>
-    <row r="20" spans="16:68">
-      <c r="P20" s="8"/>
-      <c r="AA20" s="8"/>
-      <c r="AB20" s="12"/>
+      <c r="AM19" s="8"/>
+      <c r="BD19" s="8"/>
+      <c r="BO19" s="8"/>
+    </row>
+    <row r="20" spans="15:67">
+      <c r="O20" s="8"/>
+      <c r="Z20" s="8"/>
+      <c r="AA20" s="12"/>
+      <c r="AB20" s="13"/>
       <c r="AC20" s="13"/>
-      <c r="AD20" s="13"/>
-      <c r="AE20" s="14"/>
-      <c r="AN20" s="8"/>
-      <c r="BE20" s="8"/>
-      <c r="BP20" s="8"/>
-    </row>
-    <row r="21" spans="16:68">
-      <c r="P21" s="8"/>
-      <c r="AA21" s="8"/>
-      <c r="AC21" s="6"/>
-      <c r="AN21" s="8"/>
-      <c r="BE21" s="8"/>
-      <c r="BP21" s="8"/>
-    </row>
-    <row r="22" spans="16:68">
-      <c r="P22" s="8"/>
-      <c r="AA22" s="8"/>
-      <c r="AC22" t="s">
+      <c r="AD20" s="14"/>
+      <c r="AM20" s="8"/>
+      <c r="BD20" s="8"/>
+      <c r="BO20" s="8"/>
+    </row>
+    <row r="21" spans="15:67">
+      <c r="O21" s="8"/>
+      <c r="Z21" s="8"/>
+      <c r="AB21" s="6"/>
+      <c r="AM21" s="8"/>
+      <c r="BD21" s="8"/>
+      <c r="BO21" s="8"/>
+    </row>
+    <row r="22" spans="15:67">
+      <c r="O22" s="8"/>
+      <c r="Z22" s="8"/>
+      <c r="AB22" t="s">
         <v>98</v>
       </c>
-      <c r="AN22" s="8"/>
-      <c r="BE22" s="8"/>
-      <c r="BP22" s="8"/>
-    </row>
-    <row r="23" spans="16:68">
-      <c r="P23" s="8"/>
-      <c r="AA23" s="8"/>
-      <c r="AC23" t="s">
+      <c r="AM22" s="8"/>
+      <c r="BD22" s="8"/>
+      <c r="BO22" s="8"/>
+    </row>
+    <row r="23" spans="15:67">
+      <c r="O23" s="8"/>
+      <c r="Z23" s="8"/>
+      <c r="AB23" t="s">
         <v>99</v>
       </c>
-      <c r="AN23" s="8"/>
-      <c r="BE23" s="8"/>
-      <c r="BP23" s="8"/>
-    </row>
-    <row r="24" spans="16:68">
-      <c r="P24" s="8"/>
-      <c r="AA24" s="8"/>
-      <c r="AC24" t="s">
+      <c r="AM23" s="8"/>
+      <c r="BD23" s="8"/>
+      <c r="BO23" s="8"/>
+    </row>
+    <row r="24" spans="15:67">
+      <c r="O24" s="8"/>
+      <c r="Z24" s="8"/>
+      <c r="AB24" t="s">
         <v>100</v>
       </c>
-      <c r="AN24" s="8"/>
-      <c r="AO24" t="s">
+      <c r="AM24" s="8"/>
+      <c r="AN24" t="s">
         <v>117</v>
       </c>
-      <c r="BE24" s="8"/>
-      <c r="BP24" s="8"/>
-    </row>
-    <row r="25" spans="16:68">
-      <c r="P25" s="8"/>
-      <c r="AA25" s="8"/>
-      <c r="AC25" s="8"/>
-      <c r="AN25" s="8"/>
-      <c r="AO25" s="12"/>
+      <c r="BD24" s="8"/>
+      <c r="BO24" s="8"/>
+    </row>
+    <row r="25" spans="15:67">
+      <c r="O25" s="8"/>
+      <c r="Z25" s="8"/>
+      <c r="AB25" s="8"/>
+      <c r="AM25" s="8"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="13"/>
       <c r="AP25" s="13"/>
-      <c r="AQ25" s="13"/>
-      <c r="AR25" s="14"/>
-      <c r="BE25" s="8"/>
-      <c r="BP25" s="8"/>
-    </row>
-    <row r="26" spans="16:68">
-      <c r="P26" s="8"/>
-      <c r="AA26" s="8"/>
-      <c r="AC26" s="8"/>
-      <c r="AN26" s="8"/>
-      <c r="AO26" s="4"/>
-      <c r="AP26" s="6"/>
-      <c r="BE26" s="8"/>
-      <c r="BP26" s="8"/>
-    </row>
-    <row r="27" spans="16:68">
-      <c r="P27" s="8"/>
-      <c r="AA27" s="8"/>
-      <c r="AC27" t="s">
+      <c r="AQ25" s="14"/>
+      <c r="BD25" s="8"/>
+      <c r="BO25" s="8"/>
+    </row>
+    <row r="26" spans="15:67">
+      <c r="O26" s="8"/>
+      <c r="Z26" s="8"/>
+      <c r="AB26" s="8"/>
+      <c r="AM26" s="8"/>
+      <c r="AN26" s="4"/>
+      <c r="AO26" s="6"/>
+      <c r="BD26" s="8"/>
+      <c r="BO26" s="8"/>
+    </row>
+    <row r="27" spans="15:67">
+      <c r="O27" s="8"/>
+      <c r="Z27" s="8"/>
+      <c r="AB27" t="s">
         <v>103</v>
       </c>
-      <c r="AN27" s="8"/>
-      <c r="AO27" t="s">
+      <c r="AM27" s="8"/>
+      <c r="AN27" t="s">
         <v>118</v>
       </c>
-      <c r="AP27" s="8"/>
-      <c r="BE27" s="8"/>
-      <c r="BP27" s="8"/>
-    </row>
-    <row r="28" spans="16:68">
-      <c r="P28" s="8"/>
-      <c r="AA28" s="8"/>
-      <c r="AC28" s="8"/>
-      <c r="AN28" s="8"/>
-      <c r="AP28" s="40" t="s">
+      <c r="AO27" s="8"/>
+      <c r="BD27" s="8"/>
+      <c r="BO27" s="8"/>
+    </row>
+    <row r="28" spans="15:67">
+      <c r="O28" s="8"/>
+      <c r="Z28" s="8"/>
+      <c r="AB28" s="8"/>
+      <c r="AM28" s="8"/>
+      <c r="AO28" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="BE28" s="8"/>
-      <c r="BP28" s="8"/>
-    </row>
-    <row r="29" spans="16:68">
-      <c r="P29" s="8"/>
-      <c r="AA29" s="8"/>
-      <c r="AC29" s="8"/>
-      <c r="AN29" s="8"/>
-      <c r="AP29" s="8"/>
-      <c r="BE29" s="8"/>
-      <c r="BP29" s="8"/>
-    </row>
-    <row r="30" spans="16:68">
-      <c r="P30" s="8"/>
-      <c r="AA30" s="8"/>
-      <c r="AC30" s="8"/>
-      <c r="AN30" s="8"/>
-      <c r="AP30" s="8"/>
-      <c r="AQ30" t="s">
+      <c r="BD28" s="8"/>
+      <c r="BO28" s="8"/>
+    </row>
+    <row r="29" spans="15:67">
+      <c r="O29" s="8"/>
+      <c r="Z29" s="8"/>
+      <c r="AB29" s="8"/>
+      <c r="AM29" s="8"/>
+      <c r="AO29" s="8"/>
+      <c r="BD29" s="8"/>
+      <c r="BO29" s="8"/>
+    </row>
+    <row r="30" spans="15:67">
+      <c r="O30" s="8"/>
+      <c r="Z30" s="8"/>
+      <c r="AB30" s="8"/>
+      <c r="AM30" s="8"/>
+      <c r="AO30" s="8"/>
+      <c r="AP30" t="s">
         <v>120</v>
       </c>
-      <c r="BE30" s="8"/>
-      <c r="BP30" s="8"/>
-    </row>
-    <row r="31" spans="16:68">
-      <c r="P31" s="8"/>
-      <c r="AA31" s="8"/>
-      <c r="AC31" s="8"/>
-      <c r="AN31" s="8"/>
-      <c r="AP31" s="8"/>
-      <c r="AQ31" t="s">
+      <c r="BD30" s="8"/>
+      <c r="BO30" s="8"/>
+    </row>
+    <row r="31" spans="15:67">
+      <c r="O31" s="8"/>
+      <c r="Z31" s="8"/>
+      <c r="AB31" s="8"/>
+      <c r="AM31" s="8"/>
+      <c r="AO31" s="8"/>
+      <c r="AP31" t="s">
         <v>95</v>
       </c>
-      <c r="BE31" s="8"/>
-      <c r="BP31" s="8"/>
-    </row>
-    <row r="32" spans="16:68">
-      <c r="P32" s="8"/>
-      <c r="AA32" s="8"/>
-      <c r="AC32" s="8"/>
-      <c r="AN32" s="8"/>
-      <c r="AP32" s="8"/>
-      <c r="AQ32" s="12"/>
+      <c r="BD31" s="8"/>
+      <c r="BO31" s="8"/>
+    </row>
+    <row r="32" spans="15:67">
+      <c r="O32" s="8"/>
+      <c r="Z32" s="8"/>
+      <c r="AB32" s="8"/>
+      <c r="AM32" s="8"/>
+      <c r="AO32" s="8"/>
+      <c r="AP32" s="12"/>
+      <c r="AQ32" s="13"/>
       <c r="AR32" s="13"/>
-      <c r="AS32" s="13"/>
-      <c r="AT32" s="14"/>
-      <c r="BE32" s="8"/>
-      <c r="BP32" s="8"/>
-    </row>
-    <row r="33" spans="16:78">
-      <c r="P33" s="8"/>
-      <c r="AA33" s="8"/>
-      <c r="AC33" s="8"/>
-      <c r="AN33" s="8"/>
-      <c r="AO33" s="9"/>
-      <c r="AP33" s="11"/>
-      <c r="BE33" s="8"/>
-      <c r="BP33" s="8"/>
-    </row>
-    <row r="34" spans="16:78">
-      <c r="P34" s="8"/>
-      <c r="AA34" s="8"/>
-      <c r="AC34" s="8" t="s">
+      <c r="AS32" s="14"/>
+      <c r="BD32" s="8"/>
+      <c r="BO32" s="8"/>
+    </row>
+    <row r="33" spans="15:71">
+      <c r="O33" s="8"/>
+      <c r="Z33" s="8"/>
+      <c r="AB33" s="8"/>
+      <c r="AM33" s="8"/>
+      <c r="AN33" s="9"/>
+      <c r="AO33" s="11"/>
+      <c r="BD33" s="8"/>
+      <c r="BO33" s="8"/>
+    </row>
+    <row r="34" spans="15:71">
+      <c r="O34" s="8"/>
+      <c r="Z34" s="8"/>
+      <c r="AB34" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="AN34" s="8"/>
-      <c r="BC34" t="s">
+      <c r="AM34" s="8"/>
+      <c r="BB34" t="s">
         <v>122</v>
       </c>
-      <c r="BE34" s="8"/>
-      <c r="BP34" s="8"/>
-    </row>
-    <row r="35" spans="16:78">
-      <c r="P35" s="8"/>
-      <c r="AA35" s="8"/>
-      <c r="AC35" s="8"/>
-      <c r="AN35" s="8"/>
-      <c r="BE35" s="8"/>
-      <c r="BF35" s="12"/>
+      <c r="BD34" s="8"/>
+      <c r="BO34" s="8"/>
+    </row>
+    <row r="35" spans="15:71">
+      <c r="O35" s="8"/>
+      <c r="Z35" s="8"/>
+      <c r="AB35" s="8"/>
+      <c r="AM35" s="8"/>
+      <c r="BD35" s="8"/>
+      <c r="BE35" s="12"/>
+      <c r="BF35" s="13"/>
       <c r="BG35" s="13"/>
-      <c r="BH35" s="13"/>
-      <c r="BI35" s="14"/>
-      <c r="BP35" s="8"/>
-    </row>
-    <row r="36" spans="16:78">
-      <c r="P36" s="8"/>
-      <c r="AA36" s="8"/>
-      <c r="AN36" s="8"/>
-      <c r="BE36" s="8"/>
-      <c r="BF36" s="4"/>
-      <c r="BG36" s="6"/>
-      <c r="BP36" s="8"/>
-    </row>
-    <row r="37" spans="16:78">
-      <c r="P37" s="8"/>
-      <c r="AA37" s="8"/>
-      <c r="AN37" s="8"/>
-      <c r="BE37" s="8"/>
-      <c r="BF37" s="7"/>
-      <c r="BG37" t="s">
+      <c r="BH35" s="14"/>
+      <c r="BO35" s="8"/>
+    </row>
+    <row r="36" spans="15:71">
+      <c r="O36" s="8"/>
+      <c r="Z36" s="8"/>
+      <c r="AM36" s="8"/>
+      <c r="BD36" s="8"/>
+      <c r="BE36" s="4"/>
+      <c r="BF36" s="6"/>
+      <c r="BO36" s="8"/>
+    </row>
+    <row r="37" spans="15:71">
+      <c r="O37" s="8"/>
+      <c r="Z37" s="8"/>
+      <c r="AM37" s="8"/>
+      <c r="BD37" s="8"/>
+      <c r="BE37" s="7"/>
+      <c r="BF37" t="s">
         <v>123</v>
       </c>
-      <c r="BP37" s="8" t="s">
+      <c r="BO37" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="BR37" s="44"/>
-      <c r="BS37" s="44"/>
-      <c r="BT37" s="44"/>
-      <c r="BU37" s="44"/>
-      <c r="BV37" s="44"/>
-      <c r="BW37" s="44"/>
-      <c r="BX37" s="44"/>
-      <c r="BY37" s="44"/>
-      <c r="BZ37" s="44"/>
-    </row>
-    <row r="38" spans="16:78">
-      <c r="P38" s="8"/>
-      <c r="AA38" s="8"/>
-      <c r="AN38" s="8"/>
-      <c r="BE38" s="8"/>
-      <c r="BF38" s="7"/>
-      <c r="BG38" s="8"/>
-      <c r="BP38" s="8"/>
-      <c r="BQ38" t="s">
+    </row>
+    <row r="38" spans="15:71">
+      <c r="O38" s="8"/>
+      <c r="Z38" s="8"/>
+      <c r="AM38" s="8"/>
+      <c r="BD38" s="8"/>
+      <c r="BE38" s="7"/>
+      <c r="BF38" s="8"/>
+      <c r="BO38" s="8"/>
+      <c r="BP38" t="s">
         <v>126</v>
       </c>
-      <c r="BR38" s="44"/>
-      <c r="BS38" s="44"/>
-      <c r="BT38" s="44"/>
-      <c r="BU38" s="44"/>
-      <c r="BV38" s="44"/>
-      <c r="BW38" s="44"/>
-      <c r="BX38" s="44"/>
-      <c r="BY38" s="44"/>
-      <c r="BZ38" s="44"/>
-    </row>
-    <row r="39" spans="16:78">
-      <c r="P39" s="8"/>
-      <c r="AA39" s="8"/>
-      <c r="AN39" s="8"/>
-      <c r="BE39" s="8"/>
-      <c r="BF39" s="7"/>
-      <c r="BG39" s="8"/>
-      <c r="BP39" s="8"/>
-      <c r="BQ39" s="12"/>
+    </row>
+    <row r="39" spans="15:71">
+      <c r="O39" s="8"/>
+      <c r="Z39" s="8"/>
+      <c r="AM39" s="8"/>
+      <c r="BD39" s="8"/>
+      <c r="BE39" s="7"/>
+      <c r="BF39" s="8"/>
+      <c r="BO39" s="8"/>
+      <c r="BP39" s="12"/>
+      <c r="BQ39" s="13"/>
       <c r="BR39" s="13"/>
-      <c r="BS39" s="13"/>
-      <c r="BT39" s="14"/>
-      <c r="BU39" s="44"/>
-      <c r="BV39" s="44"/>
-      <c r="BW39" s="44"/>
-      <c r="BX39" s="44"/>
-      <c r="BY39" s="44"/>
-      <c r="BZ39" s="44"/>
-    </row>
-    <row r="40" spans="16:78">
-      <c r="P40" s="8"/>
-      <c r="AA40" s="8"/>
-      <c r="AN40" s="8"/>
-      <c r="BE40" s="8"/>
-      <c r="BF40" s="7"/>
-      <c r="BG40" s="8"/>
-      <c r="BP40" s="8"/>
-      <c r="BR40" s="6"/>
-      <c r="BS40" s="44"/>
-      <c r="BT40" s="44"/>
-      <c r="BU40" s="44"/>
-      <c r="BV40" s="44"/>
-      <c r="BW40" s="44"/>
-      <c r="BX40" s="44"/>
-      <c r="BY40" s="44"/>
-      <c r="BZ40" s="44"/>
-    </row>
-    <row r="41" spans="16:78">
-      <c r="P41" s="8"/>
-      <c r="AA41" s="8"/>
-      <c r="AN41" s="8"/>
-      <c r="BE41" s="8"/>
-      <c r="BF41" s="7"/>
-      <c r="BG41" s="8"/>
-      <c r="BP41" s="8"/>
-      <c r="BR41" s="8"/>
-      <c r="BS41" s="44"/>
-      <c r="BT41" s="44"/>
-      <c r="BU41" s="44"/>
-      <c r="BV41" s="44"/>
-      <c r="BW41" s="44"/>
-      <c r="BX41" s="44"/>
-      <c r="BY41" s="44"/>
-      <c r="BZ41" s="44"/>
-    </row>
-    <row r="42" spans="16:78">
-      <c r="P42" s="8"/>
-      <c r="AA42" s="8"/>
-      <c r="AN42" s="8"/>
-      <c r="BE42" s="8"/>
-      <c r="BF42" s="7"/>
-      <c r="BG42" s="8"/>
-      <c r="BP42" s="8"/>
-      <c r="BR42" s="8"/>
-    </row>
-    <row r="43" spans="16:78">
-      <c r="P43" s="8"/>
-      <c r="AA43" s="8"/>
-      <c r="AN43" s="8"/>
-      <c r="BE43" s="8"/>
-      <c r="BF43" s="9"/>
-      <c r="BG43" s="11"/>
-      <c r="BP43" s="8"/>
-    </row>
-    <row r="44" spans="16:78">
-      <c r="P44" s="8"/>
-      <c r="AA44" s="8"/>
-      <c r="AN44" s="8"/>
-      <c r="BE44" s="8"/>
-      <c r="BP44" s="8"/>
+      <c r="BS39" s="14"/>
+    </row>
+    <row r="40" spans="15:71">
+      <c r="O40" s="8"/>
+      <c r="Z40" s="8"/>
+      <c r="AM40" s="8"/>
+      <c r="BD40" s="8"/>
+      <c r="BE40" s="7"/>
+      <c r="BF40" s="8"/>
+      <c r="BO40" s="8"/>
+      <c r="BQ40" s="6"/>
+    </row>
+    <row r="41" spans="15:71">
+      <c r="O41" s="8"/>
+      <c r="Z41" s="8"/>
+      <c r="AM41" s="8"/>
+      <c r="BD41" s="8"/>
+      <c r="BE41" s="7"/>
+      <c r="BF41" s="8"/>
+      <c r="BO41" s="8"/>
+      <c r="BQ41" s="8"/>
+    </row>
+    <row r="42" spans="15:71">
+      <c r="O42" s="8"/>
+      <c r="Z42" s="8"/>
+      <c r="AM42" s="8"/>
+      <c r="BD42" s="8"/>
+      <c r="BE42" s="7"/>
+      <c r="BF42" s="8"/>
+      <c r="BO42" s="8"/>
+      <c r="BQ42" s="8"/>
+    </row>
+    <row r="43" spans="15:71">
+      <c r="O43" s="8"/>
+      <c r="Z43" s="8"/>
+      <c r="AM43" s="8"/>
+      <c r="BD43" s="8"/>
+      <c r="BE43" s="9"/>
+      <c r="BF43" s="11"/>
+      <c r="BO43" s="8"/>
+    </row>
+    <row r="44" spans="15:71">
+      <c r="O44" s="8"/>
+      <c r="Z44" s="8"/>
+      <c r="AM44" s="8"/>
+      <c r="BD44" s="8"/>
+      <c r="BO44" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="L13:U13"/>
-    <mergeCell ref="X13:AE13"/>
-    <mergeCell ref="BC13:BH13"/>
-    <mergeCell ref="AL13:AQ13"/>
-    <mergeCell ref="BN13:BS13"/>
+    <mergeCell ref="K13:T13"/>
+    <mergeCell ref="W13:AD13"/>
+    <mergeCell ref="BB13:BG13"/>
+    <mergeCell ref="AK13:AP13"/>
+    <mergeCell ref="BM13:BR13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/unit12_Uboot/unit12_Uboot.xlsx
+++ b/unit12_Uboot/unit12_Uboot.xlsx
@@ -3,15 +3,18 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{397A4370-2DA9-47D6-89C9-CB902F4B581E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720DC19B-37DC-4851-A63C-8A6B316EEADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="First stage boot loader" sheetId="2" r:id="rId2"/>
     <sheet name="Second stage boot loader." sheetId="3" r:id="rId3"/>
     <sheet name="Third stage boot loader" sheetId="4" r:id="rId4"/>
+    <sheet name="command line" sheetId="5" r:id="rId5"/>
+    <sheet name="load Linux kernel" sheetId="7" r:id="rId6"/>
+    <sheet name=" source code" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -23,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="229">
   <si>
     <t>protocall driver cho nokia 5110</t>
   </si>
@@ -628,12 +631,538 @@
   <si>
     <t>(const init_fnc_t init_sequence[])</t>
   </si>
+  <si>
+    <t>`</t>
+  </si>
+  <si>
+    <t>static int run_main_loop(void)</t>
+  </si>
+  <si>
+    <t>main_loop();</t>
+  </si>
+  <si>
+    <t>common\main.c</t>
+  </si>
+  <si>
+    <t>void main_loop(void)</t>
+  </si>
+  <si>
+    <t>common\autoboot.c</t>
+  </si>
+  <si>
+    <t>void autoboot_command(const char *s)</t>
+  </si>
+  <si>
+    <t>autoboot_command(s);</t>
+  </si>
+  <si>
+    <t>run_command_list(s, -1, 0);</t>
+  </si>
+  <si>
+    <t>for (;;)</t>
+  </si>
+  <si>
+    <t>1.2.3. Third stage boot loader</t>
+  </si>
+  <si>
+    <t>1.2.4. Hệ thống command line của u-boot</t>
+  </si>
+  <si>
+    <t>Trên Linux thì các command line bản chất là các file binary được đặt trong thư mục /bin hoặc /sbin của hệ thống.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuy nhiên do u-boot là một chương trình vi điều khiển, do vậy các command line của nó là các function trong source code. </t>
+  </si>
+  <si>
+    <t>Mỗi 1 function khi muốn đăng ký thành command line sẽ sử dụng macro U_BOOT_CMD giống như dưới:</t>
+  </si>
+  <si>
+    <t>      );</t>
+  </si>
+  <si>
+    <t>U_BOOT_CMD(</t>
+  </si>
+  <si>
+    <t>        hab_auth_img, 4, 0, do_authenticate_image,</t>
+  </si>
+  <si>
+    <t>        "authenticate image via HAB",</t>
+  </si>
+  <si>
+    <t>        "addr length ivt_offset\n"</t>
+  </si>
+  <si>
+    <t>        "addr - image hex address\n"</t>
+  </si>
+  <si>
+    <t>        "length - image hex length\n"SSGSSG</t>
+  </si>
+  <si>
+    <t>        "ivt_offset - hex offset of IVT in the image"</t>
+  </si>
+  <si>
+    <t>Hàm do_main_loop sẽ liên tục get input của user thông qua serial, từ đó detect được command line mà user gõ.</t>
+  </si>
+  <si>
+    <t>Nếu như quá trình boot không bị interrupt bởi input từ user thì hàm do_main_loop sẽ thực thi 1 loạt command line để execute Linux kernel. Quá trình này giống như chạy shell script.</t>
+  </si>
+  <si>
+    <t>1.2.5. Quá trình load Linux kernel</t>
+  </si>
+  <si>
+    <t>1.2.6. Tổ chức source code của u-boot.</t>
+  </si>
+  <si>
+    <t>s = bootdelay_process();</t>
+  </si>
+  <si>
+    <t>const char *bootdelay_process(void)</t>
+  </si>
+  <si>
+    <t>...</t>
+  </si>
+  <si>
+    <t>bootcount_inc();</t>
+  </si>
+  <si>
+    <t>s = env_get("bootdelay");</t>
+  </si>
+  <si>
+    <t>env\common.c</t>
+  </si>
+  <si>
+    <t>char *env_get(const char *name)</t>
+  </si>
+  <si>
+    <t>if (gd-&gt;flags &amp; GD_FLG_ENV_READY)</t>
+  </si>
+  <si>
+    <t>if (env_get_f(name, (char *)(gd-&gt;env_buf), sizeof(gd-&gt;env_buf)) &gt;= 0)</t>
+  </si>
+  <si>
+    <t>return (char *)(gd-&gt;env_buf);</t>
+  </si>
+  <si>
+    <r>
+      <t>hsearch_r(e, ENV_FIND, &amp;ep, &amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>env_htab</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 0);</t>
+    </r>
+  </si>
+  <si>
+    <t>return ep ? ep-&gt;data : NULL;</t>
+  </si>
+  <si>
+    <t>s = env_get("bootcmd");</t>
+  </si>
+  <si>
+    <t>bootdelay = s ? (int)simple_strtol(s, NULL, 10) : CONFIG_BOOTDELAY;</t>
+  </si>
+  <si>
+    <t>stored_bootdelay = bootdelay;</t>
+  </si>
+  <si>
+    <t>if (s &amp;&amp; (stored_bootdelay == -2 ||</t>
+  </si>
+  <si>
+    <t> (stored_bootdelay != -1 &amp;&amp; !abortboot(stored_bootdelay))))</t>
+  </si>
+  <si>
+    <t>common\cli.c</t>
+  </si>
+  <si>
+    <t>int run_command_list(const char *cmd, int len, int flag)</t>
+  </si>
+  <si>
+    <t>rcode = board_run_command(buff);</t>
+  </si>
+  <si>
+    <t>if (IS_ENABLED(CONFIG_AUTOBOOT_USE_MENUKEY) &amp;&amp;</t>
+  </si>
+  <si>
+    <t>menukey == AUTOBOOT_MENUKEY) {</t>
+  </si>
+  <si>
+    <t>s = env_get("menucmd");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. cmd: Chứa source code của tất cả các command line. Thông thường mỗi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">command line sẽ là 1 file source C. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. configs: Chứa file config để generate ra file .config khi build u-boot. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Documentation: Chứa hệ thống tài liệu của u-boot. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. env: Chứa source code để xây dựng ra hệ thống biến môi trương của u-boot. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. lib: Source code phần middler ware của u-boot. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. net: Source code liên quan đến tính năng network. U-boot cũng có thể sử dụng </t>
+  </si>
+  <si>
+    <t xml:space="preserve">được network như ping, sftp,… </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. arch: Source code specific cho từng platform. Device tree cũng được lưu trữ trong </t>
+  </si>
+  <si>
+    <t xml:space="preserve">folder này. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. common: Source code phần middler ware của u-boot. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. drivers: Chứa source code driver của từng board. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. spl: Chứa 1 phần code để build ra second stage boot loader. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11. tools: Chứa các loại tool dùng trong quá trình build u-boot. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12. fs: Chứa source code của các loại file system dùng trong u-boot. U-boot cũng </t>
+  </si>
+  <si>
+    <t>có tính năng đọc file theo file name như Linux.</t>
+  </si>
+  <si>
+    <t>load Linux kernel</t>
+  </si>
+  <si>
+    <t>initr_env</t>
+  </si>
+  <si>
+    <t>static int initr_env(void)</t>
+  </si>
+  <si>
+    <t>Quá trình Load Kernel Image</t>
+  </si>
+  <si>
+    <t>Đặc điểm chung:</t>
+  </si>
+  <si>
+    <t>Mỗi board có chuỗi command line riêng để load kernel image lên RAM</t>
+  </si>
+  <si>
+    <t>Các hãng sản xuất board tạo script riêng cho từng loại board</t>
+  </si>
+  <si>
+    <t>U-Boot thực thi script này mà không cần quan tâm chi tiết bên trong</t>
+  </si>
+  <si>
+    <t>Cấu hình Script:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Script được định nghĩa bằng macro </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>CONFIG_EXTRA_ENV_SETTINGS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nằm trong thư mục </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/include/configs</t>
+    </r>
+  </si>
+  <si>
+    <t>Quy trình cụ thể với Beagle Bone Black:</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Đọc cấu hình:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> U-Boot đọc file </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/boot/uEnv.txt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> từ SD card để lấy config hệ thống</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Load file:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Lựa chọn và load kernel image cùng DTB file từ MMC hoặc SD card lên RAM</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Giải nén:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Dựa vào định dạng kernel image (uImage hoặc zImage) để thực hiện giải nén</t>
+    </r>
+  </si>
+  <si>
+    <t>4. Khởi động kernel:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Gọi lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>bootm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> với địa chỉ RAM của kernel image và DTB file</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>bootm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> jump đến instruction đầu tiên của kernel</t>
+    </r>
+  </si>
+  <si>
+    <t>Chuyển toàn bộ quyền điều khiển hệ thống cho kernel</t>
+  </si>
+  <si>
+    <r>
+      <t>Kết quả:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> U-Boot hoàn thành nhiệm vụ khởi tạo và chuyển giao quyền điều khiển cho Linux kernel.</t>
+    </r>
+  </si>
+  <si>
+    <t>=&gt; quá trình lấy chuỗi cmd được diễn giải qua trong sheet thỉd stage boot loader và command line, đây là nhắc lại chi tiết:</t>
+  </si>
+  <si>
+    <t>Lấy các biến môi trường tương ứng với board:</t>
+  </si>
+  <si>
+    <t>env_relocate();</t>
+  </si>
+  <si>
+    <t>void env_relocate(void)</t>
+  </si>
+  <si>
+    <t>env_load();</t>
+  </si>
+  <si>
+    <t>env\env.c</t>
+  </si>
+  <si>
+    <t>int env_load(void)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">for (prio = 0; (drv = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>env_driver_lookup(ENVOP_LOAD, prio)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>); prio++)</t>
+    </r>
+  </si>
+  <si>
+    <t>static struct env_driver *env_driver_lookup(enum env_operation op, int prio)</t>
+  </si>
+  <si>
+    <t>__weak enum env_location env_get_location(enum env_operation op, int prio)</t>
+  </si>
+  <si>
+    <t>return env_locations[prio];</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">enum env_location loc = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>env_get_location</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(op, prio);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>drv =</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> _env_driver_lookup</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(loc);</t>
+    </r>
+  </si>
+  <si>
+    <t>= ENVL_MMC // nếu là BBB</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ví dụ: Beagle Bone có file riêng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>include/configs/omap3_beagle.h</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -698,8 +1227,84 @@
       <color rgb="FFFF0000"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF002060"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Arial Unicode MS"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -721,6 +1326,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -891,7 +1508,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -951,6 +1568,57 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -959,6 +1627,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2171,7 +2844,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>74</xdr:col>
+      <xdr:col>71</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>59</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2544,7 +3217,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>56</xdr:col>
+      <xdr:col>51</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2686,7 +3359,7 @@
       <xdr:rowOff>133349</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>48</xdr:col>
+      <xdr:col>47</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
@@ -2749,16 +3422,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>49</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123824</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>55</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2773,13 +3446,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12382500" y="5057774"/>
-          <a:ext cx="1485900" cy="571501"/>
+          <a:off x="7305675" y="5267324"/>
+          <a:ext cx="1666875" cy="571501"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRoundRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -119972"/>
-            <a:gd name="adj2" fmla="val -47959"/>
+            <a:gd name="adj1" fmla="val 78314"/>
+            <a:gd name="adj2" fmla="val -77959"/>
             <a:gd name="adj3" fmla="val 16667"/>
           </a:avLst>
         </a:prstGeom>
@@ -2822,13 +3495,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>38099</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>52</xdr:col>
+      <xdr:col>47</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2846,8 +3519,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11239500" y="6600824"/>
-          <a:ext cx="1552575" cy="685801"/>
+          <a:off x="10001250" y="6600824"/>
+          <a:ext cx="1362075" cy="685801"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRoundRectCallout">
           <a:avLst>
@@ -2895,13 +3568,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>58</xdr:col>
+      <xdr:col>53</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>67</xdr:col>
+      <xdr:col>62</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
@@ -2948,16 +3621,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>70</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>104774</xdr:rowOff>
+      <xdr:col>63</xdr:col>
+      <xdr:colOff>238124</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>76</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>70</xdr:col>
+      <xdr:colOff>19049</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2972,13 +3645,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17021175" y="5400674"/>
-          <a:ext cx="1485900" cy="571501"/>
+          <a:off x="15239999" y="5553074"/>
+          <a:ext cx="1447800" cy="571501"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRoundRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -67408"/>
-            <a:gd name="adj2" fmla="val 150374"/>
+            <a:gd name="adj1" fmla="val -70266"/>
+            <a:gd name="adj2" fmla="val 128708"/>
             <a:gd name="adj3" fmla="val 16667"/>
           </a:avLst>
         </a:prstGeom>
@@ -3021,15 +3694,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>58</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>69</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:col>63</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -3045,7 +3718,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="14049375" y="7467600"/>
+          <a:off x="13801725" y="7286625"/>
           <a:ext cx="2619375" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -3070,6 +3743,2928 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>55</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>72</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="Straight Arrow Connector 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{146CA192-9F71-BC1E-6CF0-6B55586CB436}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14287500" y="8010525"/>
+          <a:ext cx="3810000" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>74</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>80</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="20" name="Straight Arrow Connector 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7925CDF2-3C82-1DF2-5DE3-B57448820024}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18573750" y="8553450"/>
+          <a:ext cx="1666875" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>74</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>80</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="22" name="Straight Arrow Connector 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F75824A4-E0C1-83BC-9BCF-7AF87A72E458}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="18573750" y="9277350"/>
+          <a:ext cx="1428750" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>55</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>72</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="23" name="Straight Arrow Connector 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8979AE25-2F38-429C-8CAF-7A2ED240FB83}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="14287500" y="9458325"/>
+          <a:ext cx="3810000" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>70</xdr:col>
+      <xdr:colOff>19049</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>76</xdr:col>
+      <xdr:colOff>85724</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="Rounded Rectangular Callout 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A360713F-65EE-4164-8F7C-0BE52A97B155}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17164049" y="9905999"/>
+          <a:ext cx="1495425" cy="419101"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 108863"/>
+            <a:gd name="adj2" fmla="val -131292"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="1050"/>
+            <a:t>Nhận cmd và xử lý</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1050">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>74</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>80</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="Straight Arrow Connector 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15FC690B-A48F-46A3-B3CC-6FC6423B42CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18097500" y="8743950"/>
+          <a:ext cx="1428750" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>74</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>80</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="14" name="Straight Arrow Connector 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A493B3DA-BE52-436C-AC36-988E5A9573FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="18097500" y="9286875"/>
+          <a:ext cx="1428750" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>88</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>98</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="Rounded Rectangular Callout 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EE3DAFD-2DB3-4DAB-A2DD-398B84166BB8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22383750" y="9439274"/>
+          <a:ext cx="2447925" cy="619126"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -78798"/>
+            <a:gd name="adj2" fmla="val -99342"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="1050"/>
+            <a:t>đợi để nhận cmd, sau time line sẽ bắt đầu boot image</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>69</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>78</xdr:col>
+      <xdr:colOff>38099</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="Rounded Rectangular Callout 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D10ECAF9-F55F-4197-B5CE-186E0D65FA05}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16430625" y="7800974"/>
+          <a:ext cx="1943099" cy="209551"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -90265"/>
+            <a:gd name="adj2" fmla="val -128197"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="900"/>
+            <a:t>ví dụ khởi tạo các biến môi trường</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="900">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>118206</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAABA389-2BCB-3858-F14D-2E65CE494382}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="457201" y="180976"/>
+          <a:ext cx="5376005" cy="3133724"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="Straight Arrow Connector 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A26A6C8B-62C1-4C11-A1B7-1D5F9306FC7C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18097500" y="10010775"/>
+          <a:ext cx="1428750" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="Straight Arrow Connector 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A20437BF-F70F-4D81-834F-5FD4D39BC73D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2286000" y="11811000"/>
+          <a:ext cx="1371600" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="14" name="Straight Arrow Connector 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6A43351-E2FC-4645-9F69-75EBEC9DFA7D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18097500" y="8743950"/>
+          <a:ext cx="1428750" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="Straight Arrow Connector 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{644FA444-682B-4536-9FC5-8100F3E0DAC6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="18097500" y="9467850"/>
+          <a:ext cx="1428750" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="Straight Arrow Connector 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A208622-3FE5-EF8F-FB0E-20CC1C5DD0D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="914400" y="7286625"/>
+          <a:ext cx="914400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>152401</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="Rounded Rectangular Callout 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A738D9F5-39DE-4DC1-A459-3C8320D4266A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2057401" y="8524876"/>
+          <a:ext cx="1143000" cy="390524"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 111983"/>
+            <a:gd name="adj2" fmla="val -87181"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="900"/>
+            <a:t>đếm số lần boot</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>180974</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="Rounded Rectangular Callout 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5CAD16C-E64B-4DC1-9DF0-70538CC3CD5C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2057400" y="9029699"/>
+          <a:ext cx="1143000" cy="428625"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 114483"/>
+            <a:gd name="adj2" fmla="val -106693"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="900"/>
+            <a:t>lấy tham</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="900" baseline="0"/>
+            <a:t> số môi trường bootdelay</a:t>
+          </a:r>
+          <a:endParaRPr lang="vi-VN" sz="900"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="21" name="Straight Arrow Connector 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EC4C919-AC89-450F-245E-29F3408141B8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4114800" y="8734425"/>
+          <a:ext cx="2057400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>28574</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>228599</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="Rounded Rectangular Callout 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{308927B7-790E-468F-9406-0EA450BD26CC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4371974" y="8848725"/>
+          <a:ext cx="1343025" cy="428625"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 103135"/>
+            <a:gd name="adj2" fmla="val 31085"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="900"/>
+            <a:t>môi trường đã sẵn sàng (ENV_READY)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="Rounded Rectangular Callout 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{007EAAA8-AF4D-4B67-9544-6C0F897E1080}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4343400" y="9553575"/>
+          <a:ext cx="1343025" cy="428625"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 103135"/>
+            <a:gd name="adj2" fmla="val 31085"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="900"/>
+            <a:t>môi trường chưa sẵn sàng (!ENV_READY)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>78</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>84</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="25" name="Straight Arrow Connector 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36EC7B03-5689-4319-B269-E08DC690BF2C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="18097500" y="10734675"/>
+          <a:ext cx="1371600" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="26" name="Straight Arrow Connector 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B815200-79B5-40D8-AD7B-03EBFCBE7CFD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="4114800" y="10363200"/>
+          <a:ext cx="2057400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="Rounded Rectangular Callout 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1B65556-D6D1-41A6-BB31-60BB42E586CD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2057401" y="10544175"/>
+          <a:ext cx="1143000" cy="552450"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 108649"/>
+            <a:gd name="adj2" fmla="val 66718"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="900"/>
+            <a:t>Trả về chuỗi chứa lệnh boot phù hợp</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="Rounded Rectangular Callout 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DA5C327-9BDA-4B0E-B26D-65C20A5A02BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2057400" y="9991725"/>
+          <a:ext cx="1143000" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 108649"/>
+            <a:gd name="adj2" fmla="val 155395"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="900"/>
+            <a:t>lưu số s đợi lệnh từ user</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>19051</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>171449</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>19051</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>180974</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="Rounded Rectangular Callout 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F213F5B-A78A-4802-8033-189BAE7B0B97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2076451" y="12172949"/>
+          <a:ext cx="1143000" cy="733425"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 109482"/>
+            <a:gd name="adj2" fmla="val -7420"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="900"/>
+            <a:t>nếu người dùng không nhập cmd trong quá trình đợi</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="34" name="Straight Arrow Connector 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B73EEDE3-A5A1-0154-6BD1-9DF9F2E0A904}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4114800" y="12725400"/>
+          <a:ext cx="5486400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="35" name="Straight Arrow Connector 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05800E4F-FB03-4AE9-8572-222D7C63DAFA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="4114800" y="13449300"/>
+          <a:ext cx="5486400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="Rounded Rectangular Callout 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EB3144D-5D64-46EC-BF2E-C551A840A82B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2057400" y="13449300"/>
+          <a:ext cx="1143000" cy="704850"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 109482"/>
+            <a:gd name="adj2" fmla="val -7420"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="900"/>
+            <a:t>nếu người dùng nhập cmd trong quá trình đợi</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="38" name="Straight Arrow Connector 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{363FEE12-7C07-4F0C-8050-0C6061383761}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4114800" y="14354175"/>
+          <a:ext cx="5486400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="39" name="Straight Arrow Connector 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87C538E1-3296-4196-A7B6-BAF43CC34147}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="4114800" y="15078075"/>
+          <a:ext cx="5486400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>58</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>104776</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="Rounded Rectangular Callout 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F0557E7-9953-4974-90C5-491160DDE530}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11887200" y="11820525"/>
+          <a:ext cx="1495425" cy="647701"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -151647"/>
+            <a:gd name="adj2" fmla="val 64029"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="1050"/>
+            <a:t>thực hiện chuỗi cmd để boot image</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1050">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>58</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>76201</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="Rounded Rectangular Callout 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F65F379B-E659-4041-92B5-E4A7F82549B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11887200" y="13420725"/>
+          <a:ext cx="1495425" cy="647701"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -151647"/>
+            <a:gd name="adj2" fmla="val 64029"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="1050"/>
+            <a:t>thực hiện chuỗi cmd do user nhập</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1050">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>59</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Arrow Connector 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DD715EB-7538-2DFA-1FF3-DC3D43804652}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10058400" y="13268325"/>
+          <a:ext cx="3429000" cy="9525"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>50</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>66674</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Rounded Rectangular Callout 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{921613FF-909F-4A83-8444-4143113820EB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9829800" y="8372475"/>
+          <a:ext cx="1781175" cy="619124"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -96827"/>
+            <a:gd name="adj2" fmla="val 98435"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="900"/>
+            <a:t>bảng băm chứa tham số môi trường được khởi tọa ở third stage boot loader</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Arrow Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5855EE18-38C0-5F7C-6B6A-E7DF91E02E10}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2286000" y="5286375"/>
+          <a:ext cx="1828800" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="Straight Arrow Connector 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33EA3214-6386-65F1-C858-0DBBA6E6C85F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4572000" y="5829300"/>
+          <a:ext cx="1371600" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Rounded Rectangular Callout 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22DC00F2-6058-467C-A904-977E1942C370}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7543800" y="5267325"/>
+          <a:ext cx="1600200" cy="495300"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -94180"/>
+            <a:gd name="adj2" fmla="val 137495"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="900"/>
+            <a:t>Duyệt qua danh sách driver theo thứ tự ưu tiên</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="Straight Arrow Connector 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDD89D0E-2879-F5A8-0F8A-440F286CDBB0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="6629400" y="8362950"/>
+          <a:ext cx="457200" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>50</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Rounded Rectangular Callout 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{199E4532-524D-450D-84F9-237E32ED1C2C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9344025" y="7753350"/>
+          <a:ext cx="2085975" cy="1085850"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -76918"/>
+            <a:gd name="adj2" fmla="val -22120"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>static enum env_location env_locations[] = {</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#ifdef CONFIG_ENV_IS_IN_EEPROM</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>    ENVL_EEPROM,</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#endif</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#ifdef CONFIG_ENV_IS_IN_EXT4</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>    ENVL_EXT4,</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#endif</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#ifdef CONFIG_ENV_IS_IN_FAT</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>    ENVL_FAT,</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#endif</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#ifdef CONFIG_ENV_IS_IN_FLASH</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>    ENVL_FLASH,</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#endif</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#ifdef CONFIG_ENV_IS_IN_MMC</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>    ENVL_MMC,</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#endif</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#ifdef CONFIG_ENV_IS_IN_NAND</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>    ENVL_NAND,</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#endif</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#ifdef CONFIG_ENV_IS_IN_NVRAM</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>    ENVL_NVRAM,</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#endif</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#ifdef CONFIG_ENV_IS_IN_REMOTE</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>    ENVL_REMOTE,</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#endif</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#ifdef CONFIG_ENV_IS_IN_SATA</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>    ENVL_ESATA,</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#endif</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#ifdef CONFIG_ENV_IS_IN_SPI_FLASH</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>    ENVL_SPI_FLASH,</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#endif</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#ifdef CONFIG_ENV_IS_IN_UBI</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>    ENVL_UBI,</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#endif</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#ifdef CONFIG_ENV_IS_NOWHERE</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>    ENVL_NOWHERE,</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>#endif</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>};</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>50</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Rounded Rectangular Callout 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53D27148-997B-4708-A334-7D424E9D7E28}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9296400" y="8953500"/>
+          <a:ext cx="2133600" cy="495300"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -93436"/>
+            <a:gd name="adj2" fmla="val -102890"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="900"/>
+            <a:t>tìm một env_driver tương ứng với vị trí lưu trữ environment được chỉ định</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3338,7 +6933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E7"/>
+  <dimension ref="B2:E11"/>
   <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="2" spans="2:5">
@@ -3369,6 +6964,26 @@
     <row r="7" spans="2:5">
       <c r="E7" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="E8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="E9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="E10" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="E11" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -3446,6 +7061,11 @@
     <row r="41" spans="1:3" s="2" customFormat="1" ht="15" thickBot="1">
       <c r="A41" s="1" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -3879,7 +7499,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:CC64"/>
+  <dimension ref="A1:BZ64"/>
   <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:57">
@@ -4203,51 +7823,51 @@
       <c r="G34" s="21"/>
     </row>
     <row r="36" spans="2:64">
-      <c r="N36" s="41" t="s">
+      <c r="N36" s="82" t="s">
         <v>89</v>
       </c>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="42"/>
-      <c r="R36" s="42"/>
-      <c r="S36" s="42"/>
-      <c r="T36" s="42"/>
-      <c r="U36" s="42"/>
-      <c r="V36" s="42"/>
-      <c r="W36" s="43"/>
-      <c r="Z36" s="41" t="s">
+      <c r="O36" s="83"/>
+      <c r="P36" s="83"/>
+      <c r="Q36" s="83"/>
+      <c r="R36" s="83"/>
+      <c r="S36" s="83"/>
+      <c r="T36" s="83"/>
+      <c r="U36" s="83"/>
+      <c r="V36" s="83"/>
+      <c r="W36" s="84"/>
+      <c r="Z36" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="AA36" s="42"/>
-      <c r="AB36" s="42"/>
-      <c r="AC36" s="42"/>
-      <c r="AD36" s="42"/>
-      <c r="AE36" s="42"/>
-      <c r="AF36" s="42"/>
-      <c r="AG36" s="43"/>
-      <c r="AO36" s="41" t="s">
+      <c r="AA36" s="83"/>
+      <c r="AB36" s="83"/>
+      <c r="AC36" s="83"/>
+      <c r="AD36" s="83"/>
+      <c r="AE36" s="83"/>
+      <c r="AF36" s="83"/>
+      <c r="AG36" s="84"/>
+      <c r="AO36" s="82" t="s">
         <v>101</v>
       </c>
-      <c r="AP36" s="42"/>
-      <c r="AQ36" s="42"/>
-      <c r="AR36" s="42"/>
-      <c r="AS36" s="42"/>
-      <c r="AT36" s="42"/>
-      <c r="AU36" s="42"/>
-      <c r="AV36" s="42"/>
-      <c r="AW36" s="42"/>
-      <c r="AX36" s="42"/>
-      <c r="AY36" s="42"/>
-      <c r="AZ36" s="42"/>
-      <c r="BA36" s="43"/>
-      <c r="BG36" s="41" t="s">
+      <c r="AP36" s="83"/>
+      <c r="AQ36" s="83"/>
+      <c r="AR36" s="83"/>
+      <c r="AS36" s="83"/>
+      <c r="AT36" s="83"/>
+      <c r="AU36" s="83"/>
+      <c r="AV36" s="83"/>
+      <c r="AW36" s="83"/>
+      <c r="AX36" s="83"/>
+      <c r="AY36" s="83"/>
+      <c r="AZ36" s="83"/>
+      <c r="BA36" s="84"/>
+      <c r="BG36" s="82" t="s">
         <v>109</v>
       </c>
-      <c r="BH36" s="42"/>
-      <c r="BI36" s="42"/>
-      <c r="BJ36" s="42"/>
-      <c r="BK36" s="42"/>
-      <c r="BL36" s="43"/>
+      <c r="BH36" s="83"/>
+      <c r="BI36" s="83"/>
+      <c r="BJ36" s="83"/>
+      <c r="BK36" s="83"/>
+      <c r="BL36" s="84"/>
     </row>
     <row r="37" spans="2:64">
       <c r="R37" s="8"/>
@@ -4373,7 +7993,7 @@
       <c r="AX48" s="14"/>
       <c r="BI48" s="8"/>
     </row>
-    <row r="49" spans="18:81">
+    <row r="49" spans="18:78">
       <c r="R49" s="8"/>
       <c r="AC49" s="8"/>
       <c r="AE49" s="8"/>
@@ -4382,7 +8002,7 @@
       <c r="AV49" s="6"/>
       <c r="BI49" s="8"/>
     </row>
-    <row r="50" spans="18:81">
+    <row r="50" spans="18:78">
       <c r="R50" s="8"/>
       <c r="AC50" s="8"/>
       <c r="AE50" t="s">
@@ -4394,7 +8014,7 @@
       </c>
       <c r="BI50" s="8"/>
     </row>
-    <row r="51" spans="18:81">
+    <row r="51" spans="18:78">
       <c r="R51" s="8"/>
       <c r="AC51" s="8"/>
       <c r="AE51" s="8"/>
@@ -4404,7 +8024,7 @@
       </c>
       <c r="BI51" s="8"/>
     </row>
-    <row r="52" spans="18:81">
+    <row r="52" spans="18:78">
       <c r="R52" s="8"/>
       <c r="AC52" s="8"/>
       <c r="AE52" s="8"/>
@@ -4414,7 +8034,7 @@
       </c>
       <c r="BI52" s="8"/>
     </row>
-    <row r="53" spans="18:81">
+    <row r="53" spans="18:78">
       <c r="R53" s="8"/>
       <c r="AC53" s="8"/>
       <c r="AE53" s="8"/>
@@ -4424,7 +8044,7 @@
       </c>
       <c r="BI53" s="8"/>
     </row>
-    <row r="54" spans="18:81">
+    <row r="54" spans="18:78">
       <c r="R54" s="8"/>
       <c r="AC54" s="8"/>
       <c r="AE54" s="8"/>
@@ -4433,7 +8053,7 @@
       <c r="AV54" s="11"/>
       <c r="BI54" s="8"/>
     </row>
-    <row r="55" spans="18:81">
+    <row r="55" spans="18:78">
       <c r="R55" s="8"/>
       <c r="AC55" s="8"/>
       <c r="AE55" s="8" t="s">
@@ -4445,7 +8065,7 @@
       </c>
       <c r="BI55" s="8"/>
     </row>
-    <row r="56" spans="18:81">
+    <row r="56" spans="18:78">
       <c r="R56" s="8"/>
       <c r="AC56" s="8"/>
       <c r="AE56" s="8"/>
@@ -4456,7 +8076,7 @@
       <c r="BL56" s="13"/>
       <c r="BM56" s="14"/>
     </row>
-    <row r="57" spans="18:81">
+    <row r="57" spans="18:78">
       <c r="R57" s="8"/>
       <c r="AC57" s="8"/>
       <c r="AT57" s="8"/>
@@ -4464,7 +8084,7 @@
       <c r="BJ57" s="4"/>
       <c r="BK57" s="6"/>
     </row>
-    <row r="58" spans="18:81">
+    <row r="58" spans="18:78">
       <c r="R58" s="8"/>
       <c r="AC58" s="8"/>
       <c r="AT58" s="8"/>
@@ -4474,7 +8094,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="59" spans="18:81">
+    <row r="59" spans="18:78">
       <c r="R59" s="8"/>
       <c r="AC59" s="8"/>
       <c r="AT59" s="8"/>
@@ -4483,17 +8103,17 @@
       <c r="BK59" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="BW59" s="36" t="s">
+      <c r="BT59" s="36" t="s">
         <v>113</v>
       </c>
+      <c r="BU59" s="37"/>
+      <c r="BV59" s="37"/>
+      <c r="BW59" s="37"/>
       <c r="BX59" s="37"/>
       <c r="BY59" s="37"/>
-      <c r="BZ59" s="37"/>
-      <c r="CA59" s="37"/>
-      <c r="CB59" s="37"/>
-      <c r="CC59" s="38"/>
-    </row>
-    <row r="60" spans="18:81">
+      <c r="BZ59" s="38"/>
+    </row>
+    <row r="60" spans="18:78">
       <c r="R60" s="8"/>
       <c r="AC60" s="8"/>
       <c r="AT60" s="8"/>
@@ -4501,25 +8121,25 @@
       <c r="BJ60" s="9"/>
       <c r="BK60" s="11"/>
     </row>
-    <row r="61" spans="18:81">
+    <row r="61" spans="18:78">
       <c r="R61" s="8"/>
       <c r="AC61" s="8"/>
       <c r="AT61" s="8"/>
       <c r="BI61" s="8"/>
     </row>
-    <row r="62" spans="18:81">
+    <row r="62" spans="18:78">
       <c r="R62" s="8"/>
       <c r="AC62" s="8"/>
       <c r="AT62" s="8"/>
       <c r="BI62" s="8"/>
     </row>
-    <row r="63" spans="18:81">
+    <row r="63" spans="18:78">
       <c r="R63" s="8"/>
       <c r="AC63" s="8"/>
       <c r="AT63" s="8"/>
       <c r="BI63" s="8"/>
     </row>
-    <row r="64" spans="18:81">
+    <row r="64" spans="18:78">
       <c r="R64" s="8"/>
       <c r="AC64" s="8"/>
       <c r="AT64" s="8"/>
@@ -4540,11 +8160,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:BS44"/>
+  <dimension ref="A1:CJ81"/>
   <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:70" ht="15" thickBot="1"/>
-    <row r="2" spans="1:70" ht="15" thickBot="1">
+    <row r="1" spans="1:83" ht="15" thickBot="1"/>
+    <row r="2" spans="1:83" ht="15" thickBot="1">
       <c r="B2" s="32" t="s">
         <v>83</v>
       </c>
@@ -4553,29 +8173,29 @@
       <c r="E2" s="33"/>
       <c r="F2" s="33"/>
       <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-    </row>
-    <row r="3" spans="1:70">
+      <c r="H2" s="34"/>
+    </row>
+    <row r="3" spans="1:83">
       <c r="C3" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:70">
+    <row r="4" spans="1:83">
       <c r="C4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:70">
+    <row r="5" spans="1:83">
       <c r="C5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:70">
+    <row r="6" spans="1:83">
       <c r="C6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:70" ht="15">
+    <row r="8" spans="1:83" ht="15">
       <c r="D8" s="39" t="s">
         <v>115</v>
       </c>
@@ -4623,77 +8243,90 @@
       <c r="AT8" s="37"/>
       <c r="AU8" s="37"/>
       <c r="AV8" s="37"/>
-      <c r="AW8" s="36"/>
+      <c r="AW8" s="37"/>
       <c r="AX8" s="37"/>
       <c r="AY8" s="37"/>
-      <c r="AZ8" s="37"/>
-      <c r="BA8" s="37"/>
-      <c r="BB8" s="37"/>
-      <c r="BC8" s="37"/>
-      <c r="BD8" s="37"/>
-      <c r="BE8" s="38"/>
-    </row>
-    <row r="9" spans="1:70" ht="15" thickBot="1"/>
-    <row r="10" spans="1:70" s="30" customFormat="1" ht="15" thickBot="1">
+      <c r="AZ8" s="38"/>
+    </row>
+    <row r="9" spans="1:83" ht="15" thickBot="1"/>
+    <row r="10" spans="1:83" s="30" customFormat="1" ht="15" thickBot="1">
       <c r="A10" s="29"/>
     </row>
-    <row r="13" spans="1:70">
-      <c r="K13" s="41" t="s">
+    <row r="13" spans="1:83">
+      <c r="K13" s="82" t="s">
         <v>89</v>
       </c>
-      <c r="L13" s="42"/>
-      <c r="M13" s="42"/>
-      <c r="N13" s="42"/>
-      <c r="O13" s="42"/>
-      <c r="P13" s="42"/>
-      <c r="Q13" s="42"/>
-      <c r="R13" s="42"/>
-      <c r="S13" s="42"/>
-      <c r="T13" s="43"/>
-      <c r="W13" s="41" t="s">
+      <c r="L13" s="83"/>
+      <c r="M13" s="83"/>
+      <c r="N13" s="83"/>
+      <c r="O13" s="83"/>
+      <c r="P13" s="83"/>
+      <c r="Q13" s="83"/>
+      <c r="R13" s="83"/>
+      <c r="S13" s="83"/>
+      <c r="T13" s="84"/>
+      <c r="W13" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="X13" s="42"/>
-      <c r="Y13" s="42"/>
-      <c r="Z13" s="42"/>
-      <c r="AA13" s="42"/>
-      <c r="AB13" s="42"/>
-      <c r="AC13" s="42"/>
-      <c r="AD13" s="43"/>
+      <c r="X13" s="83"/>
+      <c r="Y13" s="83"/>
+      <c r="Z13" s="83"/>
+      <c r="AA13" s="83"/>
+      <c r="AB13" s="83"/>
+      <c r="AC13" s="83"/>
+      <c r="AD13" s="84"/>
       <c r="AJ13" s="8"/>
-      <c r="AK13" s="41" t="s">
+      <c r="AK13" s="82" t="s">
         <v>116</v>
       </c>
-      <c r="AL13" s="42"/>
-      <c r="AM13" s="42"/>
-      <c r="AN13" s="42"/>
-      <c r="AO13" s="42"/>
-      <c r="AP13" s="43"/>
-      <c r="BB13" s="41" t="s">
+      <c r="AL13" s="83"/>
+      <c r="AM13" s="83"/>
+      <c r="AN13" s="83"/>
+      <c r="AO13" s="83"/>
+      <c r="AP13" s="84"/>
+      <c r="AW13" s="82" t="s">
         <v>121</v>
       </c>
-      <c r="BC13" s="42"/>
-      <c r="BD13" s="42"/>
-      <c r="BE13" s="42"/>
-      <c r="BF13" s="42"/>
-      <c r="BG13" s="43"/>
-      <c r="BM13" s="41" t="s">
+      <c r="AX13" s="83"/>
+      <c r="AY13" s="83"/>
+      <c r="AZ13" s="83"/>
+      <c r="BA13" s="83"/>
+      <c r="BB13" s="84"/>
+      <c r="BH13" s="82" t="s">
         <v>124</v>
       </c>
-      <c r="BN13" s="42"/>
-      <c r="BO13" s="42"/>
-      <c r="BP13" s="42"/>
-      <c r="BQ13" s="42"/>
-      <c r="BR13" s="43"/>
-    </row>
-    <row r="14" spans="1:70">
+      <c r="BI13" s="83"/>
+      <c r="BJ13" s="83"/>
+      <c r="BK13" s="83"/>
+      <c r="BL13" s="83"/>
+      <c r="BM13" s="84"/>
+      <c r="BR13" s="82" t="s">
+        <v>130</v>
+      </c>
+      <c r="BS13" s="83"/>
+      <c r="BT13" s="83"/>
+      <c r="BU13" s="83"/>
+      <c r="BV13" s="83"/>
+      <c r="BW13" s="84"/>
+      <c r="BZ13" s="82" t="s">
+        <v>132</v>
+      </c>
+      <c r="CA13" s="83"/>
+      <c r="CB13" s="83"/>
+      <c r="CC13" s="83"/>
+      <c r="CD13" s="83"/>
+      <c r="CE13" s="84"/>
+    </row>
+    <row r="14" spans="1:83">
       <c r="O14" s="8"/>
       <c r="Z14" s="8"/>
       <c r="AM14" s="8"/>
-      <c r="BD14" s="6"/>
-      <c r="BO14" s="6"/>
-    </row>
-    <row r="15" spans="1:70">
+      <c r="AY14" s="6"/>
+      <c r="BJ14" s="6"/>
+      <c r="BT14" s="6"/>
+      <c r="CB14" s="6"/>
+    </row>
+    <row r="15" spans="1:83">
       <c r="B15" s="36" t="s">
         <v>114</v>
       </c>
@@ -4709,10 +8342,12 @@
       <c r="O15" s="8"/>
       <c r="Z15" s="8"/>
       <c r="AM15" s="8"/>
-      <c r="BD15" s="8"/>
-      <c r="BO15" s="8"/>
-    </row>
-    <row r="16" spans="1:70">
+      <c r="AY15" s="8"/>
+      <c r="BJ15" s="8"/>
+      <c r="BT15" s="8"/>
+      <c r="CB15" s="8"/>
+    </row>
+    <row r="16" spans="1:83">
       <c r="I16" t="s">
         <v>90</v>
       </c>
@@ -4722,30 +8357,36 @@
       </c>
       <c r="Z16" s="8"/>
       <c r="AM16" s="8"/>
-      <c r="BD16" s="8"/>
-      <c r="BO16" s="8"/>
-    </row>
-    <row r="17" spans="15:67">
+      <c r="AY16" s="8"/>
+      <c r="BJ16" s="8"/>
+      <c r="BT16" s="8"/>
+      <c r="CB16" s="8"/>
+    </row>
+    <row r="17" spans="15:80">
       <c r="O17" s="8"/>
       <c r="P17" t="s">
         <v>95</v>
       </c>
       <c r="Z17" s="8"/>
       <c r="AM17" s="8"/>
-      <c r="BD17" s="8"/>
-      <c r="BO17" s="8"/>
-    </row>
-    <row r="18" spans="15:67">
+      <c r="AY17" s="8"/>
+      <c r="BJ17" s="8"/>
+      <c r="BT17" s="8"/>
+      <c r="CB17" s="8"/>
+    </row>
+    <row r="18" spans="15:80">
       <c r="O18" s="8"/>
       <c r="P18" t="s">
         <v>93</v>
       </c>
       <c r="Z18" s="8"/>
       <c r="AM18" s="8"/>
-      <c r="BD18" s="8"/>
-      <c r="BO18" s="8"/>
-    </row>
-    <row r="19" spans="15:67">
+      <c r="AY18" s="8"/>
+      <c r="BJ18" s="8"/>
+      <c r="BT18" s="8"/>
+      <c r="CB18" s="8"/>
+    </row>
+    <row r="19" spans="15:80">
       <c r="O19" s="8"/>
       <c r="Q19" t="s">
         <v>94</v>
@@ -4755,10 +8396,12 @@
         <v>97</v>
       </c>
       <c r="AM19" s="8"/>
-      <c r="BD19" s="8"/>
-      <c r="BO19" s="8"/>
-    </row>
-    <row r="20" spans="15:67">
+      <c r="AY19" s="8"/>
+      <c r="BJ19" s="8"/>
+      <c r="BT19" s="8"/>
+      <c r="CB19" s="8"/>
+    </row>
+    <row r="20" spans="15:80">
       <c r="O20" s="8"/>
       <c r="Z20" s="8"/>
       <c r="AA20" s="12"/>
@@ -4766,38 +8409,46 @@
       <c r="AC20" s="13"/>
       <c r="AD20" s="14"/>
       <c r="AM20" s="8"/>
-      <c r="BD20" s="8"/>
-      <c r="BO20" s="8"/>
-    </row>
-    <row r="21" spans="15:67">
+      <c r="AY20" s="8"/>
+      <c r="BJ20" s="8"/>
+      <c r="BT20" s="8"/>
+      <c r="CB20" s="8"/>
+    </row>
+    <row r="21" spans="15:80">
       <c r="O21" s="8"/>
       <c r="Z21" s="8"/>
       <c r="AB21" s="6"/>
       <c r="AM21" s="8"/>
-      <c r="BD21" s="8"/>
-      <c r="BO21" s="8"/>
-    </row>
-    <row r="22" spans="15:67">
+      <c r="AY21" s="8"/>
+      <c r="BJ21" s="8"/>
+      <c r="BT21" s="8"/>
+      <c r="CB21" s="8"/>
+    </row>
+    <row r="22" spans="15:80">
       <c r="O22" s="8"/>
       <c r="Z22" s="8"/>
       <c r="AB22" t="s">
         <v>98</v>
       </c>
       <c r="AM22" s="8"/>
-      <c r="BD22" s="8"/>
-      <c r="BO22" s="8"/>
-    </row>
-    <row r="23" spans="15:67">
+      <c r="AY22" s="8"/>
+      <c r="BJ22" s="8"/>
+      <c r="BT22" s="8"/>
+      <c r="CB22" s="8"/>
+    </row>
+    <row r="23" spans="15:80">
       <c r="O23" s="8"/>
       <c r="Z23" s="8"/>
       <c r="AB23" t="s">
         <v>99</v>
       </c>
       <c r="AM23" s="8"/>
-      <c r="BD23" s="8"/>
-      <c r="BO23" s="8"/>
-    </row>
-    <row r="24" spans="15:67">
+      <c r="AY23" s="8"/>
+      <c r="BJ23" s="8"/>
+      <c r="BT23" s="8"/>
+      <c r="CB23" s="8"/>
+    </row>
+    <row r="24" spans="15:80">
       <c r="O24" s="8"/>
       <c r="Z24" s="8"/>
       <c r="AB24" t="s">
@@ -4807,10 +8458,12 @@
       <c r="AN24" t="s">
         <v>117</v>
       </c>
-      <c r="BD24" s="8"/>
-      <c r="BO24" s="8"/>
-    </row>
-    <row r="25" spans="15:67">
+      <c r="AY24" s="8"/>
+      <c r="BJ24" s="8"/>
+      <c r="BT24" s="8"/>
+      <c r="CB24" s="8"/>
+    </row>
+    <row r="25" spans="15:80">
       <c r="O25" s="8"/>
       <c r="Z25" s="8"/>
       <c r="AB25" s="8"/>
@@ -4819,20 +8472,24 @@
       <c r="AO25" s="13"/>
       <c r="AP25" s="13"/>
       <c r="AQ25" s="14"/>
-      <c r="BD25" s="8"/>
-      <c r="BO25" s="8"/>
-    </row>
-    <row r="26" spans="15:67">
+      <c r="AY25" s="8"/>
+      <c r="BJ25" s="8"/>
+      <c r="BT25" s="8"/>
+      <c r="CB25" s="8"/>
+    </row>
+    <row r="26" spans="15:80">
       <c r="O26" s="8"/>
       <c r="Z26" s="8"/>
       <c r="AB26" s="8"/>
       <c r="AM26" s="8"/>
       <c r="AN26" s="4"/>
       <c r="AO26" s="6"/>
-      <c r="BD26" s="8"/>
-      <c r="BO26" s="8"/>
-    </row>
-    <row r="27" spans="15:67">
+      <c r="AY26" s="8"/>
+      <c r="BJ26" s="8"/>
+      <c r="BT26" s="8"/>
+      <c r="CB26" s="8"/>
+    </row>
+    <row r="27" spans="15:80">
       <c r="O27" s="8"/>
       <c r="Z27" s="8"/>
       <c r="AB27" t="s">
@@ -4843,10 +8500,12 @@
         <v>118</v>
       </c>
       <c r="AO27" s="8"/>
-      <c r="BD27" s="8"/>
-      <c r="BO27" s="8"/>
-    </row>
-    <row r="28" spans="15:67">
+      <c r="AY27" s="8"/>
+      <c r="BJ27" s="8"/>
+      <c r="BT27" s="8"/>
+      <c r="CB27" s="8"/>
+    </row>
+    <row r="28" spans="15:80">
       <c r="O28" s="8"/>
       <c r="Z28" s="8"/>
       <c r="AB28" s="8"/>
@@ -4854,19 +8513,23 @@
       <c r="AO28" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="BD28" s="8"/>
-      <c r="BO28" s="8"/>
-    </row>
-    <row r="29" spans="15:67">
+      <c r="AY28" s="8"/>
+      <c r="BJ28" s="8"/>
+      <c r="BT28" s="8"/>
+      <c r="CB28" s="8"/>
+    </row>
+    <row r="29" spans="15:80">
       <c r="O29" s="8"/>
       <c r="Z29" s="8"/>
       <c r="AB29" s="8"/>
       <c r="AM29" s="8"/>
       <c r="AO29" s="8"/>
-      <c r="BD29" s="8"/>
-      <c r="BO29" s="8"/>
-    </row>
-    <row r="30" spans="15:67">
+      <c r="AY29" s="8"/>
+      <c r="BJ29" s="8"/>
+      <c r="BT29" s="8"/>
+      <c r="CB29" s="8"/>
+    </row>
+    <row r="30" spans="15:80">
       <c r="O30" s="8"/>
       <c r="Z30" s="8"/>
       <c r="AB30" s="8"/>
@@ -4875,10 +8538,12 @@
       <c r="AP30" t="s">
         <v>120</v>
       </c>
-      <c r="BD30" s="8"/>
-      <c r="BO30" s="8"/>
-    </row>
-    <row r="31" spans="15:67">
+      <c r="AY30" s="8"/>
+      <c r="BJ30" s="8"/>
+      <c r="BT30" s="8"/>
+      <c r="CB30" s="8"/>
+    </row>
+    <row r="31" spans="15:80">
       <c r="O31" s="8"/>
       <c r="Z31" s="8"/>
       <c r="AB31" s="8"/>
@@ -4887,10 +8552,12 @@
       <c r="AP31" t="s">
         <v>95</v>
       </c>
-      <c r="BD31" s="8"/>
-      <c r="BO31" s="8"/>
-    </row>
-    <row r="32" spans="15:67">
+      <c r="AY31" s="8"/>
+      <c r="BJ31" s="8"/>
+      <c r="BT31" s="8"/>
+      <c r="CB31" s="8"/>
+    </row>
+    <row r="32" spans="15:80">
       <c r="O32" s="8"/>
       <c r="Z32" s="8"/>
       <c r="AB32" s="8"/>
@@ -4900,147 +8567,2906 @@
       <c r="AQ32" s="13"/>
       <c r="AR32" s="13"/>
       <c r="AS32" s="14"/>
-      <c r="BD32" s="8"/>
-      <c r="BO32" s="8"/>
-    </row>
-    <row r="33" spans="15:71">
+      <c r="AY32" s="8"/>
+      <c r="BJ32" s="8"/>
+      <c r="BT32" s="8"/>
+      <c r="CB32" s="8"/>
+    </row>
+    <row r="33" spans="15:88">
       <c r="O33" s="8"/>
       <c r="Z33" s="8"/>
       <c r="AB33" s="8"/>
       <c r="AM33" s="8"/>
       <c r="AN33" s="9"/>
       <c r="AO33" s="11"/>
-      <c r="BD33" s="8"/>
-      <c r="BO33" s="8"/>
-    </row>
-    <row r="34" spans="15:71">
+      <c r="AY33" s="8"/>
+      <c r="BJ33" s="8"/>
+      <c r="BT33" s="8"/>
+      <c r="CB33" s="8"/>
+    </row>
+    <row r="34" spans="15:88">
       <c r="O34" s="8"/>
       <c r="Z34" s="8"/>
       <c r="AB34" s="8" t="s">
         <v>104</v>
       </c>
       <c r="AM34" s="8"/>
-      <c r="BB34" t="s">
+      <c r="AW34" t="s">
         <v>122</v>
       </c>
-      <c r="BD34" s="8"/>
-      <c r="BO34" s="8"/>
-    </row>
-    <row r="35" spans="15:71">
+      <c r="AY34" s="8"/>
+      <c r="BJ34" s="8"/>
+      <c r="BT34" s="8"/>
+      <c r="CB34" s="8"/>
+    </row>
+    <row r="35" spans="15:88">
       <c r="O35" s="8"/>
       <c r="Z35" s="8"/>
       <c r="AB35" s="8"/>
       <c r="AM35" s="8"/>
-      <c r="BD35" s="8"/>
-      <c r="BE35" s="12"/>
-      <c r="BF35" s="13"/>
-      <c r="BG35" s="13"/>
-      <c r="BH35" s="14"/>
-      <c r="BO35" s="8"/>
-    </row>
-    <row r="36" spans="15:71">
+      <c r="AY35" s="8"/>
+      <c r="AZ35" s="12"/>
+      <c r="BA35" s="13"/>
+      <c r="BB35" s="13"/>
+      <c r="BC35" s="14"/>
+      <c r="BJ35" s="8"/>
+      <c r="BT35" s="8"/>
+      <c r="CB35" s="8"/>
+    </row>
+    <row r="36" spans="15:88">
       <c r="O36" s="8"/>
       <c r="Z36" s="8"/>
       <c r="AM36" s="8"/>
-      <c r="BD36" s="8"/>
-      <c r="BE36" s="4"/>
-      <c r="BF36" s="6"/>
-      <c r="BO36" s="8"/>
-    </row>
-    <row r="37" spans="15:71">
+      <c r="AY36" s="8"/>
+      <c r="AZ36" s="4"/>
+      <c r="BA36" s="6"/>
+      <c r="BJ36" s="8"/>
+      <c r="BT36" s="8"/>
+      <c r="CB36" s="8"/>
+    </row>
+    <row r="37" spans="15:88">
       <c r="O37" s="8"/>
       <c r="Z37" s="8"/>
       <c r="AM37" s="8"/>
-      <c r="BD37" s="8"/>
-      <c r="BE37" s="7"/>
-      <c r="BF37" t="s">
+      <c r="AY37" s="8"/>
+      <c r="AZ37" s="7"/>
+      <c r="BA37" t="s">
         <v>123</v>
       </c>
-      <c r="BO37" s="8" t="s">
+      <c r="BJ37" s="8" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="38" spans="15:71">
+      <c r="BT37" s="8"/>
+      <c r="CB37" s="8"/>
+    </row>
+    <row r="38" spans="15:88">
       <c r="O38" s="8"/>
       <c r="Z38" s="8"/>
       <c r="AM38" s="8"/>
-      <c r="BD38" s="8"/>
-      <c r="BE38" s="7"/>
-      <c r="BF38" s="8"/>
-      <c r="BO38" s="8"/>
-      <c r="BP38" t="s">
+      <c r="AY38" s="8"/>
+      <c r="AZ38" s="7"/>
+      <c r="BA38" s="8"/>
+      <c r="BJ38" s="8"/>
+      <c r="BK38" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="39" spans="15:71">
+      <c r="BM38" s="10"/>
+      <c r="BN38" s="10"/>
+      <c r="BT38" s="8"/>
+      <c r="CB38" s="8"/>
+    </row>
+    <row r="39" spans="15:88">
       <c r="O39" s="8"/>
       <c r="Z39" s="8"/>
       <c r="AM39" s="8"/>
-      <c r="BD39" s="8"/>
-      <c r="BE39" s="7"/>
-      <c r="BF39" s="8"/>
-      <c r="BO39" s="8"/>
-      <c r="BP39" s="12"/>
-      <c r="BQ39" s="13"/>
-      <c r="BR39" s="13"/>
-      <c r="BS39" s="14"/>
-    </row>
-    <row r="40" spans="15:71">
+      <c r="AY39" s="8"/>
+      <c r="AZ39" s="7"/>
+      <c r="BA39" s="8"/>
+      <c r="BJ39" s="8"/>
+      <c r="BK39" s="12"/>
+      <c r="BL39" s="13"/>
+      <c r="BM39" s="10"/>
+      <c r="BN39" s="14"/>
+      <c r="BT39" s="8"/>
+      <c r="CB39" s="8"/>
+    </row>
+    <row r="40" spans="15:88">
       <c r="O40" s="8"/>
       <c r="Z40" s="8"/>
       <c r="AM40" s="8"/>
-      <c r="BD40" s="8"/>
-      <c r="BE40" s="7"/>
-      <c r="BF40" s="8"/>
-      <c r="BO40" s="8"/>
-      <c r="BQ40" s="6"/>
-    </row>
-    <row r="41" spans="15:71">
+      <c r="AY40" s="8"/>
+      <c r="AZ40" s="7"/>
+      <c r="BA40" s="8"/>
+      <c r="BJ40" s="8"/>
+      <c r="BL40" s="6"/>
+      <c r="BT40" s="8"/>
+      <c r="CB40" s="8"/>
+    </row>
+    <row r="41" spans="15:88">
       <c r="O41" s="8"/>
       <c r="Z41" s="8"/>
       <c r="AM41" s="8"/>
-      <c r="BD41" s="8"/>
-      <c r="BE41" s="7"/>
-      <c r="BF41" s="8"/>
-      <c r="BO41" s="8"/>
-      <c r="BQ41" s="8"/>
-    </row>
-    <row r="42" spans="15:71">
+      <c r="AY41" s="8"/>
+      <c r="AZ41" s="7"/>
+      <c r="BA41" s="8"/>
+      <c r="BJ41" s="8"/>
+      <c r="BL41" t="s">
+        <v>194</v>
+      </c>
+      <c r="BT41" s="8"/>
+      <c r="CB41" s="8"/>
+    </row>
+    <row r="42" spans="15:88">
       <c r="O42" s="8"/>
       <c r="Z42" s="8"/>
       <c r="AM42" s="8"/>
-      <c r="BD42" s="8"/>
-      <c r="BE42" s="7"/>
-      <c r="BF42" s="8"/>
-      <c r="BO42" s="8"/>
-      <c r="BQ42" s="8"/>
-    </row>
-    <row r="43" spans="15:71">
+      <c r="AY42" s="8"/>
+      <c r="AZ42" s="7"/>
+      <c r="BA42" s="8"/>
+      <c r="BJ42" s="8"/>
+      <c r="BL42" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="BT42" s="8"/>
+      <c r="CB42" s="8"/>
+    </row>
+    <row r="43" spans="15:88">
       <c r="O43" s="8"/>
       <c r="Z43" s="8"/>
       <c r="AM43" s="8"/>
-      <c r="BD43" s="8"/>
-      <c r="BE43" s="9"/>
-      <c r="BF43" s="11"/>
-      <c r="BO43" s="8"/>
-    </row>
-    <row r="44" spans="15:71">
+      <c r="AY43" s="8"/>
+      <c r="AZ43" s="7"/>
+      <c r="BA43" s="8"/>
+      <c r="BJ43" s="8"/>
+      <c r="BL43" s="8"/>
+      <c r="BM43" s="12"/>
+      <c r="BN43" s="13"/>
+      <c r="BO43" s="13"/>
+      <c r="BP43" s="14"/>
+      <c r="BT43" s="8"/>
+      <c r="CB43" s="8"/>
+    </row>
+    <row r="44" spans="15:88">
       <c r="O44" s="8"/>
       <c r="Z44" s="8"/>
       <c r="AM44" s="8"/>
-      <c r="BD44" s="8"/>
-      <c r="BO44" s="8"/>
+      <c r="AY44" s="8"/>
+      <c r="AZ44" s="7"/>
+      <c r="BA44" s="8"/>
+      <c r="BJ44" s="8"/>
+      <c r="BL44" s="8"/>
+      <c r="BT44" s="8"/>
+      <c r="CB44" s="8"/>
+    </row>
+    <row r="45" spans="15:88">
+      <c r="O45" s="8"/>
+      <c r="Z45" s="8"/>
+      <c r="AM45" s="8"/>
+      <c r="AY45" s="8"/>
+      <c r="AZ45" s="7"/>
+      <c r="BA45" s="8"/>
+      <c r="BJ45" s="8"/>
+      <c r="BL45" s="8"/>
+      <c r="BT45" s="8"/>
+      <c r="CB45" s="8"/>
+    </row>
+    <row r="46" spans="15:88">
+      <c r="O46" s="8"/>
+      <c r="Z46" s="8"/>
+      <c r="AM46" s="8"/>
+      <c r="AY46" s="8"/>
+      <c r="AZ46" s="7"/>
+      <c r="BA46" s="8"/>
+      <c r="BJ46" s="8"/>
+      <c r="BT46" s="8"/>
+      <c r="CB46" s="8"/>
+    </row>
+    <row r="47" spans="15:88" ht="15">
+      <c r="O47" s="8"/>
+      <c r="Z47" s="8"/>
+      <c r="AM47" s="8"/>
+      <c r="AW47" s="8"/>
+      <c r="AX47" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="AY47" s="42"/>
+      <c r="AZ47" s="43"/>
+      <c r="BA47" s="42"/>
+      <c r="BB47" s="44"/>
+      <c r="BC47" s="44"/>
+      <c r="BD47" s="44"/>
+      <c r="BE47" s="44"/>
+      <c r="BF47" s="44"/>
+      <c r="BG47" s="44"/>
+      <c r="BH47" s="44"/>
+      <c r="BI47" s="44"/>
+      <c r="BJ47" s="42"/>
+      <c r="BK47" s="44"/>
+      <c r="BL47" s="44"/>
+      <c r="BM47" s="44"/>
+      <c r="BN47" s="44"/>
+      <c r="BO47" s="44"/>
+      <c r="BP47" s="44"/>
+      <c r="BQ47" s="44"/>
+      <c r="BR47" s="44"/>
+      <c r="BS47" s="44"/>
+      <c r="BT47" s="42"/>
+      <c r="BU47" s="44"/>
+      <c r="BV47" s="44"/>
+      <c r="BW47" s="44"/>
+      <c r="BX47" s="44"/>
+      <c r="BY47" s="44"/>
+      <c r="BZ47" s="44"/>
+      <c r="CA47" s="44"/>
+      <c r="CB47" s="42"/>
+      <c r="CC47" s="44"/>
+      <c r="CD47" s="44"/>
+      <c r="CE47" s="44"/>
+      <c r="CF47" s="44"/>
+      <c r="CG47" s="44"/>
+      <c r="CH47" s="44"/>
+      <c r="CI47" s="44"/>
+      <c r="CJ47" s="42"/>
+    </row>
+    <row r="48" spans="15:88">
+      <c r="O48" s="8"/>
+      <c r="Z48" s="8"/>
+      <c r="AM48" s="8"/>
+      <c r="AW48" s="8"/>
+      <c r="AX48" s="45"/>
+      <c r="AY48" s="46"/>
+      <c r="AZ48" s="47"/>
+      <c r="BA48" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="BB48" s="48"/>
+      <c r="BC48" s="48"/>
+      <c r="BD48" s="45"/>
+      <c r="BE48" s="48"/>
+      <c r="BF48" s="45"/>
+      <c r="BG48" s="45"/>
+      <c r="BH48" s="45"/>
+      <c r="BI48" s="45"/>
+      <c r="BJ48" s="46"/>
+      <c r="BK48" s="45"/>
+      <c r="BL48" s="45"/>
+      <c r="BM48" s="45"/>
+      <c r="BN48" s="45"/>
+      <c r="BO48" s="45"/>
+      <c r="BP48" s="45"/>
+      <c r="BQ48" s="45"/>
+      <c r="BR48" s="45"/>
+      <c r="BS48" s="45"/>
+      <c r="BT48" s="46"/>
+      <c r="BU48" s="45"/>
+      <c r="BV48" s="45"/>
+      <c r="BW48" s="45"/>
+      <c r="BX48" s="45"/>
+      <c r="BY48" s="45"/>
+      <c r="BZ48" s="45"/>
+      <c r="CA48" s="45"/>
+      <c r="CB48" s="46"/>
+      <c r="CC48" s="45"/>
+      <c r="CD48" s="45"/>
+      <c r="CE48" s="45"/>
+      <c r="CF48" s="45"/>
+      <c r="CG48" s="45"/>
+      <c r="CH48" s="45"/>
+      <c r="CI48" s="45"/>
+      <c r="CJ48" s="46"/>
+    </row>
+    <row r="49" spans="15:88">
+      <c r="O49" s="8"/>
+      <c r="Z49" s="8"/>
+      <c r="AM49" s="8"/>
+      <c r="AW49" s="8"/>
+      <c r="AX49" s="45"/>
+      <c r="AY49" s="46"/>
+      <c r="AZ49" s="47"/>
+      <c r="BA49" s="46"/>
+      <c r="BB49" s="49"/>
+      <c r="BC49" s="50"/>
+      <c r="BD49" s="50"/>
+      <c r="BE49" s="51"/>
+      <c r="BF49" s="45"/>
+      <c r="BG49" s="45"/>
+      <c r="BH49" s="45"/>
+      <c r="BI49" s="45"/>
+      <c r="BJ49" s="46"/>
+      <c r="BK49" s="45"/>
+      <c r="BL49" s="45"/>
+      <c r="BM49" s="45"/>
+      <c r="BN49" s="45"/>
+      <c r="BO49" s="45"/>
+      <c r="BP49" s="45"/>
+      <c r="BQ49" s="45"/>
+      <c r="BR49" s="45"/>
+      <c r="BS49" s="45"/>
+      <c r="BT49" s="46"/>
+      <c r="BU49" s="45"/>
+      <c r="BV49" s="45"/>
+      <c r="BW49" s="45"/>
+      <c r="BX49" s="45"/>
+      <c r="BY49" s="45"/>
+      <c r="BZ49" s="45"/>
+      <c r="CA49" s="45"/>
+      <c r="CB49" s="46"/>
+      <c r="CC49" s="45"/>
+      <c r="CD49" s="45"/>
+      <c r="CE49" s="45"/>
+      <c r="CF49" s="45"/>
+      <c r="CG49" s="45"/>
+      <c r="CH49" s="45"/>
+      <c r="CI49" s="45"/>
+      <c r="CJ49" s="46"/>
+    </row>
+    <row r="50" spans="15:88">
+      <c r="O50" s="8"/>
+      <c r="Z50" s="8"/>
+      <c r="AM50" s="8"/>
+      <c r="AW50" s="8"/>
+      <c r="AX50" s="45"/>
+      <c r="AY50" s="46"/>
+      <c r="AZ50" s="47"/>
+      <c r="BA50" s="46"/>
+      <c r="BB50" s="43"/>
+      <c r="BC50" s="42"/>
+      <c r="BD50" s="45"/>
+      <c r="BE50" s="45"/>
+      <c r="BF50" s="45"/>
+      <c r="BG50" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="BH50" s="45"/>
+      <c r="BI50" s="45"/>
+      <c r="BJ50" s="46"/>
+      <c r="BK50" s="45"/>
+      <c r="BL50" s="45"/>
+      <c r="BM50" s="45"/>
+      <c r="BN50" s="45"/>
+      <c r="BO50" s="45"/>
+      <c r="BP50" s="45"/>
+      <c r="BQ50" s="45"/>
+      <c r="BR50" s="45"/>
+      <c r="BS50" s="45"/>
+      <c r="BT50" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="BU50" s="45"/>
+      <c r="BV50" s="45"/>
+      <c r="BW50" s="45"/>
+      <c r="BX50" s="45"/>
+      <c r="BY50" s="45"/>
+      <c r="BZ50" s="45"/>
+      <c r="CA50" s="45"/>
+      <c r="CB50" s="46"/>
+      <c r="CC50" s="45"/>
+      <c r="CD50" s="45"/>
+      <c r="CE50" s="45"/>
+      <c r="CF50" s="45"/>
+      <c r="CG50" s="45"/>
+      <c r="CH50" s="45"/>
+      <c r="CI50" s="45"/>
+      <c r="CJ50" s="46"/>
+    </row>
+    <row r="51" spans="15:88">
+      <c r="O51" s="8"/>
+      <c r="Z51" s="8"/>
+      <c r="AM51" s="8"/>
+      <c r="AW51" s="8"/>
+      <c r="AX51" s="45"/>
+      <c r="AY51" s="46"/>
+      <c r="AZ51" s="47"/>
+      <c r="BA51" s="46"/>
+      <c r="BB51" s="47"/>
+      <c r="BC51" s="46"/>
+      <c r="BD51" s="45"/>
+      <c r="BE51" s="45"/>
+      <c r="BF51" s="45"/>
+      <c r="BG51" s="45"/>
+      <c r="BH51" s="45"/>
+      <c r="BI51" s="45"/>
+      <c r="BJ51" s="46"/>
+      <c r="BK51" s="45"/>
+      <c r="BL51" s="45"/>
+      <c r="BM51" s="45"/>
+      <c r="BN51" s="45"/>
+      <c r="BO51" s="45"/>
+      <c r="BP51" s="45"/>
+      <c r="BQ51" s="45"/>
+      <c r="BR51" s="45"/>
+      <c r="BS51" s="45"/>
+      <c r="BT51" s="46"/>
+      <c r="BU51" s="49"/>
+      <c r="BV51" s="50"/>
+      <c r="BW51" s="50"/>
+      <c r="BX51" s="51"/>
+      <c r="BY51" s="45"/>
+      <c r="BZ51" s="45"/>
+      <c r="CA51" s="45"/>
+      <c r="CB51" s="46"/>
+      <c r="CC51" s="45"/>
+      <c r="CD51" s="45"/>
+      <c r="CE51" s="45"/>
+      <c r="CF51" s="45"/>
+      <c r="CG51" s="45"/>
+      <c r="CH51" s="45"/>
+      <c r="CI51" s="45"/>
+      <c r="CJ51" s="46"/>
+    </row>
+    <row r="52" spans="15:88">
+      <c r="O52" s="8"/>
+      <c r="Z52" s="8"/>
+      <c r="AM52" s="8"/>
+      <c r="AW52" s="8"/>
+      <c r="AX52" s="45"/>
+      <c r="AY52" s="46"/>
+      <c r="AZ52" s="47"/>
+      <c r="BA52" s="45"/>
+      <c r="BB52" s="47"/>
+      <c r="BC52" s="46"/>
+      <c r="BD52" s="45"/>
+      <c r="BE52" s="45"/>
+      <c r="BF52" s="45"/>
+      <c r="BG52" s="45"/>
+      <c r="BH52" s="45"/>
+      <c r="BI52" s="45"/>
+      <c r="BJ52" s="46"/>
+      <c r="BK52" s="45"/>
+      <c r="BL52" s="45"/>
+      <c r="BM52" s="45"/>
+      <c r="BN52" s="45"/>
+      <c r="BO52" s="45"/>
+      <c r="BP52" s="45"/>
+      <c r="BQ52" s="45"/>
+      <c r="BR52" s="45"/>
+      <c r="BS52" s="45"/>
+      <c r="BT52" s="46"/>
+      <c r="BU52" s="43"/>
+      <c r="BV52" s="42"/>
+      <c r="BW52" s="45"/>
+      <c r="BX52" s="45"/>
+      <c r="BY52" s="45"/>
+      <c r="BZ52" s="45"/>
+      <c r="CA52" s="45"/>
+      <c r="CB52" s="46"/>
+      <c r="CC52" s="45"/>
+      <c r="CD52" s="45"/>
+      <c r="CE52" s="45"/>
+      <c r="CF52" s="45"/>
+      <c r="CG52" s="45"/>
+      <c r="CH52" s="45"/>
+      <c r="CI52" s="45"/>
+      <c r="CJ52" s="46"/>
+    </row>
+    <row r="53" spans="15:88">
+      <c r="O53" s="8"/>
+      <c r="Z53" s="8"/>
+      <c r="AM53" s="8"/>
+      <c r="AW53" s="8"/>
+      <c r="AX53" s="45"/>
+      <c r="AY53" s="46"/>
+      <c r="AZ53" s="47"/>
+      <c r="BA53" s="45"/>
+      <c r="BB53" s="47"/>
+      <c r="BC53" s="46"/>
+      <c r="BD53" s="45"/>
+      <c r="BE53" s="45"/>
+      <c r="BF53" s="45"/>
+      <c r="BG53" s="45"/>
+      <c r="BH53" s="45"/>
+      <c r="BI53" s="45"/>
+      <c r="BJ53" s="46"/>
+      <c r="BK53" s="45"/>
+      <c r="BL53" s="45"/>
+      <c r="BM53" s="45"/>
+      <c r="BN53" s="45"/>
+      <c r="BO53" s="45"/>
+      <c r="BP53" s="45"/>
+      <c r="BQ53" s="45"/>
+      <c r="BR53" s="45"/>
+      <c r="BS53" s="45"/>
+      <c r="BT53" s="46"/>
+      <c r="BU53" s="47"/>
+      <c r="BV53" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="BW53" s="45"/>
+      <c r="BX53" s="45"/>
+      <c r="BY53" s="45"/>
+      <c r="BZ53" s="45"/>
+      <c r="CA53" s="45"/>
+      <c r="CB53" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="CC53" s="45"/>
+      <c r="CD53" s="45"/>
+      <c r="CE53" s="45"/>
+      <c r="CF53" s="45"/>
+      <c r="CG53" s="45"/>
+      <c r="CH53" s="45"/>
+      <c r="CI53" s="45"/>
+      <c r="CJ53" s="46"/>
+    </row>
+    <row r="54" spans="15:88">
+      <c r="O54" s="8"/>
+      <c r="Z54" s="8"/>
+      <c r="AM54" s="8"/>
+      <c r="AW54" s="8"/>
+      <c r="AX54" s="45"/>
+      <c r="AY54" s="46"/>
+      <c r="AZ54" s="47"/>
+      <c r="BA54" s="45"/>
+      <c r="BB54" s="47"/>
+      <c r="BC54" s="46"/>
+      <c r="BD54" s="45"/>
+      <c r="BE54" s="45"/>
+      <c r="BF54" s="45"/>
+      <c r="BG54" s="45"/>
+      <c r="BH54" s="45"/>
+      <c r="BI54" s="45"/>
+      <c r="BJ54" s="46"/>
+      <c r="BK54" s="45"/>
+      <c r="BL54" s="45"/>
+      <c r="BM54" s="45"/>
+      <c r="BN54" s="45"/>
+      <c r="BO54" s="45"/>
+      <c r="BP54" s="45"/>
+      <c r="BQ54" s="45"/>
+      <c r="BR54" s="45"/>
+      <c r="BS54" s="45"/>
+      <c r="BT54" s="46"/>
+      <c r="BU54" s="47"/>
+      <c r="BV54" s="46"/>
+      <c r="BW54" s="45"/>
+      <c r="BX54" s="45"/>
+      <c r="BY54" s="45"/>
+      <c r="BZ54" s="45"/>
+      <c r="CA54" s="45"/>
+      <c r="CB54" s="46"/>
+      <c r="CC54" s="49"/>
+      <c r="CD54" s="50"/>
+      <c r="CE54" s="50"/>
+      <c r="CF54" s="51"/>
+      <c r="CG54" s="45"/>
+      <c r="CH54" s="45"/>
+      <c r="CI54" s="45"/>
+      <c r="CJ54" s="46"/>
+    </row>
+    <row r="55" spans="15:88">
+      <c r="O55" s="8"/>
+      <c r="Z55" s="8"/>
+      <c r="AM55" s="8"/>
+      <c r="AW55" s="8"/>
+      <c r="AX55" s="45"/>
+      <c r="AY55" s="46"/>
+      <c r="AZ55" s="47"/>
+      <c r="BA55" s="45"/>
+      <c r="BB55" s="47"/>
+      <c r="BC55" s="46"/>
+      <c r="BD55" s="45"/>
+      <c r="BE55" s="45"/>
+      <c r="BF55" s="45"/>
+      <c r="BG55" s="45"/>
+      <c r="BH55" s="45"/>
+      <c r="BI55" s="45"/>
+      <c r="BJ55" s="46"/>
+      <c r="BK55" s="45"/>
+      <c r="BL55" s="45"/>
+      <c r="BM55" s="45"/>
+      <c r="BN55" s="45"/>
+      <c r="BO55" s="45"/>
+      <c r="BP55" s="45"/>
+      <c r="BQ55" s="45"/>
+      <c r="BR55" s="45"/>
+      <c r="BS55" s="45"/>
+      <c r="BT55" s="46"/>
+      <c r="BU55" s="47"/>
+      <c r="BV55" s="46"/>
+      <c r="BW55" s="45"/>
+      <c r="BX55" s="45"/>
+      <c r="BY55" s="45"/>
+      <c r="BZ55" s="45"/>
+      <c r="CA55" s="45"/>
+      <c r="CB55" s="46"/>
+      <c r="CC55" s="43"/>
+      <c r="CD55" s="42"/>
+      <c r="CE55" s="45"/>
+      <c r="CF55" s="45"/>
+      <c r="CG55" s="45"/>
+      <c r="CH55" s="45"/>
+      <c r="CI55" s="45"/>
+      <c r="CJ55" s="46"/>
+    </row>
+    <row r="56" spans="15:88">
+      <c r="O56" s="8"/>
+      <c r="Z56" s="8"/>
+      <c r="AM56" s="8"/>
+      <c r="AW56" s="8"/>
+      <c r="AX56" s="45"/>
+      <c r="AY56" s="46"/>
+      <c r="AZ56" s="47"/>
+      <c r="BA56" s="45"/>
+      <c r="BB56" s="47"/>
+      <c r="BC56" s="46"/>
+      <c r="BD56" s="45"/>
+      <c r="BE56" s="45"/>
+      <c r="BF56" s="45"/>
+      <c r="BG56" s="45"/>
+      <c r="BH56" s="45"/>
+      <c r="BI56" s="45"/>
+      <c r="BJ56" s="46"/>
+      <c r="BK56" s="45"/>
+      <c r="BL56" s="45"/>
+      <c r="BM56" s="45"/>
+      <c r="BN56" s="45"/>
+      <c r="BO56" s="45"/>
+      <c r="BP56" s="45"/>
+      <c r="BQ56" s="45"/>
+      <c r="BR56" s="45"/>
+      <c r="BS56" s="45"/>
+      <c r="BT56" s="46"/>
+      <c r="BU56" s="47"/>
+      <c r="BV56" s="46"/>
+      <c r="BW56" s="45"/>
+      <c r="BX56" s="45"/>
+      <c r="BY56" s="45"/>
+      <c r="BZ56" s="45"/>
+      <c r="CA56" s="45"/>
+      <c r="CB56" s="46"/>
+      <c r="CC56" s="47"/>
+      <c r="CD56" s="46"/>
+      <c r="CE56" s="45" t="s">
+        <v>156</v>
+      </c>
+      <c r="CF56" s="45"/>
+      <c r="CG56" s="45"/>
+      <c r="CH56" s="45"/>
+      <c r="CI56" s="45"/>
+      <c r="CJ56" s="46"/>
+    </row>
+    <row r="57" spans="15:88">
+      <c r="O57" s="8"/>
+      <c r="Z57" s="8"/>
+      <c r="AM57" s="8"/>
+      <c r="AW57" s="8"/>
+      <c r="AX57" s="45"/>
+      <c r="AY57" s="46"/>
+      <c r="AZ57" s="47"/>
+      <c r="BA57" s="45"/>
+      <c r="BB57" s="47"/>
+      <c r="BC57" s="46"/>
+      <c r="BD57" s="45"/>
+      <c r="BE57" s="45"/>
+      <c r="BF57" s="45"/>
+      <c r="BG57" s="45"/>
+      <c r="BH57" s="45"/>
+      <c r="BI57" s="45"/>
+      <c r="BJ57" s="46"/>
+      <c r="BK57" s="45"/>
+      <c r="BL57" s="45"/>
+      <c r="BM57" s="45"/>
+      <c r="BN57" s="45"/>
+      <c r="BO57" s="45"/>
+      <c r="BP57" s="45"/>
+      <c r="BQ57" s="45"/>
+      <c r="BR57" s="45"/>
+      <c r="BS57" s="45"/>
+      <c r="BT57" s="46"/>
+      <c r="BU57" s="47"/>
+      <c r="BV57" s="46"/>
+      <c r="BW57" s="45"/>
+      <c r="BX57" s="45"/>
+      <c r="BY57" s="45"/>
+      <c r="BZ57" s="45"/>
+      <c r="CA57" s="45"/>
+      <c r="CB57" s="46"/>
+      <c r="CC57" s="53"/>
+      <c r="CD57" s="54"/>
+      <c r="CE57" s="45"/>
+      <c r="CF57" s="45"/>
+      <c r="CG57" s="45"/>
+      <c r="CH57" s="45"/>
+      <c r="CI57" s="45"/>
+      <c r="CJ57" s="46"/>
+    </row>
+    <row r="58" spans="15:88">
+      <c r="O58" s="8"/>
+      <c r="Z58" s="8"/>
+      <c r="AM58" s="8"/>
+      <c r="AW58" s="8"/>
+      <c r="AX58" s="45"/>
+      <c r="AY58" s="46"/>
+      <c r="AZ58" s="47"/>
+      <c r="BA58" s="45"/>
+      <c r="BB58" s="47"/>
+      <c r="BC58" s="46"/>
+      <c r="BD58" s="45"/>
+      <c r="BE58" s="45"/>
+      <c r="BF58" s="45"/>
+      <c r="BG58" s="45"/>
+      <c r="BH58" s="45"/>
+      <c r="BI58" s="45"/>
+      <c r="BJ58" s="46"/>
+      <c r="BK58" s="45"/>
+      <c r="BL58" s="45"/>
+      <c r="BM58" s="45"/>
+      <c r="BN58" s="45"/>
+      <c r="BO58" s="45"/>
+      <c r="BP58" s="45"/>
+      <c r="BQ58" s="45"/>
+      <c r="BR58" s="45"/>
+      <c r="BS58" s="45"/>
+      <c r="BT58" s="46"/>
+      <c r="BU58" s="47"/>
+      <c r="BV58" s="46"/>
+      <c r="BW58" s="45"/>
+      <c r="BX58" s="45"/>
+      <c r="BY58" s="45"/>
+      <c r="BZ58" s="45"/>
+      <c r="CA58" s="45"/>
+      <c r="CB58" s="46"/>
+      <c r="CC58" s="45"/>
+      <c r="CD58" s="45"/>
+      <c r="CE58" s="45"/>
+      <c r="CF58" s="45"/>
+      <c r="CG58" s="45"/>
+      <c r="CH58" s="45"/>
+      <c r="CI58" s="45"/>
+      <c r="CJ58" s="46"/>
+    </row>
+    <row r="59" spans="15:88">
+      <c r="O59" s="8"/>
+      <c r="Z59" s="8"/>
+      <c r="AM59" s="8"/>
+      <c r="AW59" s="8"/>
+      <c r="AX59" s="45"/>
+      <c r="AY59" s="46"/>
+      <c r="AZ59" s="47"/>
+      <c r="BA59" s="45"/>
+      <c r="BB59" s="47"/>
+      <c r="BC59" s="46"/>
+      <c r="BD59" s="45"/>
+      <c r="BE59" s="45"/>
+      <c r="BF59" s="45"/>
+      <c r="BG59" s="45"/>
+      <c r="BH59" s="45"/>
+      <c r="BI59" s="45"/>
+      <c r="BJ59" s="46"/>
+      <c r="BK59" s="45"/>
+      <c r="BL59" s="45"/>
+      <c r="BM59" s="45"/>
+      <c r="BN59" s="45"/>
+      <c r="BO59" s="45"/>
+      <c r="BP59" s="45"/>
+      <c r="BQ59" s="45"/>
+      <c r="BR59" s="45"/>
+      <c r="BS59" s="45"/>
+      <c r="BT59" s="46"/>
+      <c r="BU59" s="47"/>
+      <c r="BV59" s="46"/>
+      <c r="BW59" s="45"/>
+      <c r="BX59" s="45"/>
+      <c r="BY59" s="45"/>
+      <c r="BZ59" s="45"/>
+      <c r="CA59" s="45"/>
+      <c r="CB59" s="46"/>
+      <c r="CC59" s="45"/>
+      <c r="CD59" s="45"/>
+      <c r="CE59" s="45"/>
+      <c r="CF59" s="45"/>
+      <c r="CG59" s="45"/>
+      <c r="CH59" s="45"/>
+      <c r="CI59" s="45"/>
+      <c r="CJ59" s="46"/>
+    </row>
+    <row r="60" spans="15:88">
+      <c r="O60" s="8"/>
+      <c r="Z60" s="8"/>
+      <c r="AM60" s="8"/>
+      <c r="AW60" s="8"/>
+      <c r="AX60" s="45"/>
+      <c r="AY60" s="46"/>
+      <c r="AZ60" s="47"/>
+      <c r="BA60" s="45"/>
+      <c r="BB60" s="47"/>
+      <c r="BC60" s="46"/>
+      <c r="BD60" s="45"/>
+      <c r="BE60" s="45"/>
+      <c r="BF60" s="45"/>
+      <c r="BG60" s="45"/>
+      <c r="BH60" s="45"/>
+      <c r="BI60" s="45"/>
+      <c r="BJ60" s="46"/>
+      <c r="BK60" s="45"/>
+      <c r="BL60" s="45"/>
+      <c r="BM60" s="45"/>
+      <c r="BN60" s="45"/>
+      <c r="BO60" s="45"/>
+      <c r="BP60" s="45"/>
+      <c r="BQ60" s="45"/>
+      <c r="BR60" s="45"/>
+      <c r="BS60" s="45"/>
+      <c r="BT60" s="46"/>
+      <c r="BU60" s="47"/>
+      <c r="BV60" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="BW60" s="45"/>
+      <c r="BX60" s="45"/>
+      <c r="BY60" s="45"/>
+      <c r="BZ60" s="45"/>
+      <c r="CA60" s="45"/>
+      <c r="CB60" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="CC60" s="45"/>
+      <c r="CD60" s="45"/>
+      <c r="CE60" s="45"/>
+      <c r="CF60" s="45"/>
+      <c r="CG60" s="45"/>
+      <c r="CH60" s="45"/>
+      <c r="CI60" s="45"/>
+      <c r="CJ60" s="46"/>
+    </row>
+    <row r="61" spans="15:88">
+      <c r="O61" s="8"/>
+      <c r="Z61" s="8"/>
+      <c r="AM61" s="8"/>
+      <c r="AW61" s="8"/>
+      <c r="AX61" s="45"/>
+      <c r="AY61" s="46"/>
+      <c r="AZ61" s="47"/>
+      <c r="BA61" s="45"/>
+      <c r="BB61" s="47"/>
+      <c r="BC61" s="46"/>
+      <c r="BD61" s="45"/>
+      <c r="BE61" s="45"/>
+      <c r="BF61" s="45"/>
+      <c r="BG61" s="45"/>
+      <c r="BH61" s="45"/>
+      <c r="BI61" s="45"/>
+      <c r="BJ61" s="46"/>
+      <c r="BK61" s="45"/>
+      <c r="BL61" s="45"/>
+      <c r="BM61" s="45"/>
+      <c r="BN61" s="45"/>
+      <c r="BO61" s="45"/>
+      <c r="BP61" s="45"/>
+      <c r="BQ61" s="45"/>
+      <c r="BR61" s="45"/>
+      <c r="BS61" s="45"/>
+      <c r="BT61" s="46"/>
+      <c r="BU61" s="47"/>
+      <c r="BV61" s="46"/>
+      <c r="BW61" s="45"/>
+      <c r="BX61" s="45"/>
+      <c r="BY61" s="45"/>
+      <c r="BZ61" s="45"/>
+      <c r="CA61" s="45"/>
+      <c r="CB61" s="46"/>
+      <c r="CC61" s="49"/>
+      <c r="CD61" s="50"/>
+      <c r="CE61" s="50"/>
+      <c r="CF61" s="51"/>
+      <c r="CG61" s="45"/>
+      <c r="CH61" s="45"/>
+      <c r="CI61" s="45"/>
+      <c r="CJ61" s="46"/>
+    </row>
+    <row r="62" spans="15:88">
+      <c r="O62" s="8"/>
+      <c r="Z62" s="8"/>
+      <c r="AM62" s="8"/>
+      <c r="AW62" s="8"/>
+      <c r="AX62" s="45"/>
+      <c r="AY62" s="46"/>
+      <c r="AZ62" s="47"/>
+      <c r="BA62" s="45"/>
+      <c r="BB62" s="47"/>
+      <c r="BC62" s="46"/>
+      <c r="BD62" s="45"/>
+      <c r="BE62" s="45"/>
+      <c r="BF62" s="45"/>
+      <c r="BG62" s="45"/>
+      <c r="BH62" s="45"/>
+      <c r="BI62" s="45"/>
+      <c r="BJ62" s="46"/>
+      <c r="BK62" s="45"/>
+      <c r="BL62" s="45"/>
+      <c r="BM62" s="45"/>
+      <c r="BN62" s="45"/>
+      <c r="BO62" s="45"/>
+      <c r="BP62" s="45"/>
+      <c r="BQ62" s="45"/>
+      <c r="BR62" s="45"/>
+      <c r="BS62" s="45"/>
+      <c r="BT62" s="46"/>
+      <c r="BU62" s="47"/>
+      <c r="BV62" s="46"/>
+      <c r="BW62" s="45"/>
+      <c r="BX62" s="45"/>
+      <c r="BY62" s="45"/>
+      <c r="BZ62" s="45"/>
+      <c r="CA62" s="45"/>
+      <c r="CB62" s="46"/>
+      <c r="CC62" s="43"/>
+      <c r="CD62" s="44"/>
+      <c r="CE62" s="43"/>
+      <c r="CF62" s="45"/>
+      <c r="CG62" s="45"/>
+      <c r="CH62" s="45"/>
+      <c r="CI62" s="45"/>
+      <c r="CJ62" s="46"/>
+    </row>
+    <row r="63" spans="15:88">
+      <c r="O63" s="8"/>
+      <c r="Z63" s="8"/>
+      <c r="AM63" s="8"/>
+      <c r="AW63" s="8"/>
+      <c r="AX63" s="45"/>
+      <c r="AY63" s="46"/>
+      <c r="AZ63" s="47"/>
+      <c r="BA63" s="45"/>
+      <c r="BB63" s="47"/>
+      <c r="BC63" s="46"/>
+      <c r="BD63" s="45"/>
+      <c r="BE63" s="45"/>
+      <c r="BF63" s="45"/>
+      <c r="BG63" s="45"/>
+      <c r="BH63" s="45"/>
+      <c r="BI63" s="45"/>
+      <c r="BJ63" s="46"/>
+      <c r="BK63" s="45"/>
+      <c r="BL63" s="45"/>
+      <c r="BM63" s="45"/>
+      <c r="BN63" s="45"/>
+      <c r="BO63" s="45"/>
+      <c r="BP63" s="45"/>
+      <c r="BQ63" s="45"/>
+      <c r="BR63" s="45"/>
+      <c r="BS63" s="45"/>
+      <c r="BT63" s="46"/>
+      <c r="BU63" s="47"/>
+      <c r="BV63" s="46"/>
+      <c r="BW63" s="45"/>
+      <c r="BX63" s="45"/>
+      <c r="BY63" s="45"/>
+      <c r="BZ63" s="45"/>
+      <c r="CA63" s="45"/>
+      <c r="CB63" s="46"/>
+      <c r="CC63" s="52" t="s">
+        <v>135</v>
+      </c>
+      <c r="CD63" s="45"/>
+      <c r="CE63" s="45"/>
+      <c r="CF63" s="45"/>
+      <c r="CG63" s="45"/>
+      <c r="CH63" s="45"/>
+      <c r="CI63" s="45"/>
+      <c r="CJ63" s="46"/>
+    </row>
+    <row r="64" spans="15:88">
+      <c r="O64" s="8"/>
+      <c r="Z64" s="8"/>
+      <c r="AM64" s="8"/>
+      <c r="AW64" s="8"/>
+      <c r="AX64" s="45"/>
+      <c r="AY64" s="46"/>
+      <c r="AZ64" s="47"/>
+      <c r="BA64" s="45"/>
+      <c r="BB64" s="47"/>
+      <c r="BC64" s="46"/>
+      <c r="BD64" s="45"/>
+      <c r="BE64" s="45"/>
+      <c r="BF64" s="45"/>
+      <c r="BG64" s="45"/>
+      <c r="BH64" s="45"/>
+      <c r="BI64" s="45"/>
+      <c r="BJ64" s="46"/>
+      <c r="BK64" s="45"/>
+      <c r="BL64" s="45"/>
+      <c r="BM64" s="45"/>
+      <c r="BN64" s="45"/>
+      <c r="BO64" s="45"/>
+      <c r="BP64" s="45"/>
+      <c r="BQ64" s="45"/>
+      <c r="BR64" s="45"/>
+      <c r="BS64" s="45"/>
+      <c r="BT64" s="46"/>
+      <c r="BU64" s="47"/>
+      <c r="BV64" s="46"/>
+      <c r="BW64" s="45"/>
+      <c r="BX64" s="45"/>
+      <c r="BY64" s="45"/>
+      <c r="BZ64" s="45"/>
+      <c r="CA64" s="45"/>
+      <c r="CB64" s="46"/>
+      <c r="CC64" s="53"/>
+      <c r="CD64" s="54"/>
+      <c r="CE64" s="45"/>
+      <c r="CF64" s="45"/>
+      <c r="CG64" s="45"/>
+      <c r="CH64" s="45"/>
+      <c r="CI64" s="45"/>
+      <c r="CJ64" s="46"/>
+    </row>
+    <row r="65" spans="15:88">
+      <c r="O65" s="8"/>
+      <c r="Z65" s="8"/>
+      <c r="AM65" s="8"/>
+      <c r="AW65" s="8"/>
+      <c r="AX65" s="45"/>
+      <c r="AY65" s="46"/>
+      <c r="AZ65" s="47"/>
+      <c r="BA65" s="46"/>
+      <c r="BB65" s="47"/>
+      <c r="BC65" s="46"/>
+      <c r="BD65" s="45"/>
+      <c r="BE65" s="45"/>
+      <c r="BF65" s="45"/>
+      <c r="BG65" s="45"/>
+      <c r="BH65" s="45"/>
+      <c r="BI65" s="45"/>
+      <c r="BJ65" s="46"/>
+      <c r="BK65" s="45"/>
+      <c r="BL65" s="45"/>
+      <c r="BM65" s="45"/>
+      <c r="BN65" s="45"/>
+      <c r="BO65" s="45"/>
+      <c r="BP65" s="45"/>
+      <c r="BQ65" s="45"/>
+      <c r="BR65" s="45"/>
+      <c r="BS65" s="45"/>
+      <c r="BT65" s="46"/>
+      <c r="BU65" s="53"/>
+      <c r="BV65" s="54"/>
+      <c r="BW65" s="45"/>
+      <c r="BX65" s="45"/>
+      <c r="BY65" s="45"/>
+      <c r="BZ65" s="45"/>
+      <c r="CA65" s="45"/>
+      <c r="CB65" s="46"/>
+      <c r="CC65" s="45"/>
+      <c r="CD65" s="45"/>
+      <c r="CE65" s="45"/>
+      <c r="CF65" s="45"/>
+      <c r="CG65" s="45"/>
+      <c r="CH65" s="45"/>
+      <c r="CI65" s="45"/>
+      <c r="CJ65" s="46"/>
+    </row>
+    <row r="66" spans="15:88">
+      <c r="O66" s="8"/>
+      <c r="Z66" s="8"/>
+      <c r="AM66" s="8"/>
+      <c r="AW66" s="8"/>
+      <c r="AX66" s="45"/>
+      <c r="AY66" s="46"/>
+      <c r="AZ66" s="47"/>
+      <c r="BA66" s="46"/>
+      <c r="BB66" s="47"/>
+      <c r="BC66" s="46"/>
+      <c r="BD66" s="45"/>
+      <c r="BE66" s="45"/>
+      <c r="BF66" s="45"/>
+      <c r="BG66" s="45"/>
+      <c r="BH66" s="45"/>
+      <c r="BI66" s="45"/>
+      <c r="BJ66" s="46"/>
+      <c r="BK66" s="45"/>
+      <c r="BL66" s="45"/>
+      <c r="BM66" s="45"/>
+      <c r="BN66" s="45"/>
+      <c r="BO66" s="45"/>
+      <c r="BP66" s="45"/>
+      <c r="BQ66" s="45"/>
+      <c r="BR66" s="45"/>
+      <c r="BS66" s="45"/>
+      <c r="BT66" s="46"/>
+      <c r="BU66" s="45"/>
+      <c r="BV66" s="45"/>
+      <c r="BW66" s="45"/>
+      <c r="BX66" s="45"/>
+      <c r="BY66" s="45"/>
+      <c r="BZ66" s="45"/>
+      <c r="CA66" s="45"/>
+      <c r="CB66" s="46"/>
+      <c r="CC66" s="45"/>
+      <c r="CD66" s="45"/>
+      <c r="CE66" s="45"/>
+      <c r="CF66" s="45"/>
+      <c r="CG66" s="45"/>
+      <c r="CH66" s="45"/>
+      <c r="CI66" s="45"/>
+      <c r="CJ66" s="46"/>
+    </row>
+    <row r="67" spans="15:88">
+      <c r="O67" s="8"/>
+      <c r="Z67" s="8"/>
+      <c r="AM67" s="8"/>
+      <c r="AW67" s="8"/>
+      <c r="AX67" s="45"/>
+      <c r="AY67" s="46"/>
+      <c r="AZ67" s="47"/>
+      <c r="BA67" s="46"/>
+      <c r="BB67" s="48"/>
+      <c r="BC67" s="54"/>
+      <c r="BD67" s="45"/>
+      <c r="BE67" s="45"/>
+      <c r="BF67" s="45"/>
+      <c r="BG67" s="45"/>
+      <c r="BH67" s="45"/>
+      <c r="BI67" s="45"/>
+      <c r="BJ67" s="46"/>
+      <c r="BK67" s="45"/>
+      <c r="BL67" s="45"/>
+      <c r="BM67" s="45"/>
+      <c r="BN67" s="45"/>
+      <c r="BO67" s="45"/>
+      <c r="BP67" s="45"/>
+      <c r="BQ67" s="45"/>
+      <c r="BR67" s="45"/>
+      <c r="BS67" s="45"/>
+      <c r="BT67" s="46"/>
+      <c r="BU67" s="45"/>
+      <c r="BV67" s="45"/>
+      <c r="BW67" s="45"/>
+      <c r="BX67" s="45"/>
+      <c r="BY67" s="45"/>
+      <c r="BZ67" s="45"/>
+      <c r="CA67" s="45"/>
+      <c r="CB67" s="46"/>
+      <c r="CC67" s="45"/>
+      <c r="CD67" s="45"/>
+      <c r="CE67" s="45"/>
+      <c r="CF67" s="45"/>
+      <c r="CG67" s="45"/>
+      <c r="CH67" s="45"/>
+      <c r="CI67" s="45"/>
+      <c r="CJ67" s="46"/>
+    </row>
+    <row r="68" spans="15:88">
+      <c r="O68" s="8"/>
+      <c r="Z68" s="8"/>
+      <c r="AM68" s="8"/>
+      <c r="AW68" s="8"/>
+      <c r="AX68" s="45"/>
+      <c r="AY68" s="54"/>
+      <c r="AZ68" s="53"/>
+      <c r="BA68" s="54"/>
+      <c r="BB68" s="48"/>
+      <c r="BC68" s="48"/>
+      <c r="BD68" s="48"/>
+      <c r="BE68" s="48"/>
+      <c r="BF68" s="48"/>
+      <c r="BG68" s="48"/>
+      <c r="BH68" s="48"/>
+      <c r="BI68" s="48"/>
+      <c r="BJ68" s="54"/>
+      <c r="BK68" s="48"/>
+      <c r="BL68" s="48"/>
+      <c r="BM68" s="48"/>
+      <c r="BN68" s="48"/>
+      <c r="BO68" s="48"/>
+      <c r="BP68" s="48"/>
+      <c r="BQ68" s="48"/>
+      <c r="BR68" s="48"/>
+      <c r="BS68" s="48"/>
+      <c r="BT68" s="54"/>
+      <c r="BU68" s="48"/>
+      <c r="BV68" s="48"/>
+      <c r="BW68" s="48"/>
+      <c r="BX68" s="48"/>
+      <c r="BY68" s="48"/>
+      <c r="BZ68" s="48"/>
+      <c r="CA68" s="48"/>
+      <c r="CB68" s="54"/>
+      <c r="CC68" s="48"/>
+      <c r="CD68" s="48"/>
+      <c r="CE68" s="48"/>
+      <c r="CF68" s="48"/>
+      <c r="CG68" s="48"/>
+      <c r="CH68" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="CI68" s="48"/>
+      <c r="CJ68" s="54"/>
+    </row>
+    <row r="69" spans="15:88">
+      <c r="O69" s="8"/>
+      <c r="Z69" s="8"/>
+      <c r="AM69" s="8"/>
+      <c r="AX69" s="5"/>
+      <c r="AY69" s="8"/>
+      <c r="AZ69" s="9"/>
+      <c r="BA69" s="11"/>
+      <c r="BJ69" s="8"/>
+      <c r="BT69" s="8"/>
+      <c r="CB69" s="8"/>
+    </row>
+    <row r="70" spans="15:88">
+      <c r="O70" s="8"/>
+      <c r="Z70" s="8"/>
+      <c r="AM70" s="8"/>
+      <c r="AY70" s="8"/>
+      <c r="BJ70" s="8"/>
+      <c r="BT70" s="8"/>
+      <c r="CB70" s="8"/>
+    </row>
+    <row r="71" spans="15:88">
+      <c r="O71" s="8"/>
+      <c r="Z71" s="8"/>
+      <c r="AM71" s="8"/>
+      <c r="AY71" s="8"/>
+      <c r="BJ71" s="8"/>
+      <c r="BT71" s="8"/>
+      <c r="CB71" s="8"/>
+    </row>
+    <row r="72" spans="15:88">
+      <c r="O72" s="8"/>
+      <c r="Z72" s="8"/>
+      <c r="AM72" s="8"/>
+      <c r="AY72" s="8"/>
+      <c r="BJ72" s="8"/>
+      <c r="BT72" s="8"/>
+      <c r="CB72" s="8"/>
+    </row>
+    <row r="73" spans="15:88">
+      <c r="O73" s="8"/>
+      <c r="Z73" s="8"/>
+      <c r="AM73" s="8"/>
+      <c r="AY73" s="8"/>
+      <c r="BJ73" s="8"/>
+      <c r="BT73" s="8"/>
+      <c r="CB73" s="8"/>
+    </row>
+    <row r="74" spans="15:88">
+      <c r="O74" s="8"/>
+      <c r="Z74" s="8"/>
+      <c r="AM74" s="8"/>
+      <c r="AY74" s="8"/>
+      <c r="BJ74" s="8"/>
+      <c r="BT74" s="8"/>
+      <c r="CB74" s="8"/>
+    </row>
+    <row r="75" spans="15:88">
+      <c r="O75" s="8"/>
+      <c r="Z75" s="8"/>
+      <c r="AM75" s="8"/>
+      <c r="AY75" s="8"/>
+      <c r="BJ75" s="8"/>
+      <c r="BT75" s="8"/>
+      <c r="CB75" s="8"/>
+    </row>
+    <row r="76" spans="15:88">
+      <c r="O76" s="8"/>
+      <c r="Z76" s="8"/>
+      <c r="AM76" s="8"/>
+      <c r="AY76" s="8"/>
+      <c r="BJ76" s="8"/>
+      <c r="BT76" s="8"/>
+      <c r="CB76" s="8"/>
+    </row>
+    <row r="77" spans="15:88">
+      <c r="O77" s="8"/>
+      <c r="Z77" s="8"/>
+      <c r="AM77" s="8"/>
+      <c r="AY77" s="8"/>
+      <c r="BJ77" s="8"/>
+      <c r="BT77" s="8"/>
+      <c r="CB77" s="8"/>
+    </row>
+    <row r="78" spans="15:88">
+      <c r="O78" s="8"/>
+      <c r="Z78" s="8"/>
+      <c r="AM78" s="8"/>
+      <c r="AY78" s="8"/>
+      <c r="BJ78" s="8"/>
+      <c r="BT78" s="8"/>
+      <c r="CB78" s="8"/>
+    </row>
+    <row r="79" spans="15:88">
+      <c r="O79" s="8"/>
+      <c r="Z79" s="8"/>
+      <c r="AM79" s="8"/>
+      <c r="AY79" s="8"/>
+      <c r="BJ79" s="8"/>
+      <c r="BT79" s="8"/>
+      <c r="CB79" s="8"/>
+    </row>
+    <row r="80" spans="15:88">
+      <c r="O80" s="8"/>
+      <c r="Z80" s="8"/>
+      <c r="AM80" s="8"/>
+      <c r="AY80" s="8"/>
+      <c r="BJ80" s="8"/>
+      <c r="BT80" s="8"/>
+      <c r="CB80" s="8"/>
+    </row>
+    <row r="81" spans="15:80">
+      <c r="O81" s="8"/>
+      <c r="Z81" s="8"/>
+      <c r="AM81" s="8"/>
+      <c r="AY81" s="8"/>
+      <c r="BJ81" s="8"/>
+      <c r="BT81" s="8"/>
+      <c r="CB81" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="BR13:BW13"/>
+    <mergeCell ref="BZ13:CE13"/>
     <mergeCell ref="K13:T13"/>
     <mergeCell ref="W13:AD13"/>
-    <mergeCell ref="BB13:BG13"/>
+    <mergeCell ref="AW13:BB13"/>
     <mergeCell ref="AK13:AP13"/>
-    <mergeCell ref="BM13:BR13"/>
+    <mergeCell ref="BH13:BM13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88332979-A2FD-4E58-B6E8-B4E152EFAC60}">
+  <dimension ref="B20:BM96"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="20" spans="2:15">
+      <c r="B20" s="55" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15">
+      <c r="B21" s="56" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15">
+      <c r="B22" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15">
+      <c r="C24" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="57"/>
+    </row>
+    <row r="25" spans="2:15">
+      <c r="C25" s="58" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="59"/>
+      <c r="K25" s="59"/>
+      <c r="L25" s="59"/>
+      <c r="M25" s="59"/>
+      <c r="N25" s="59"/>
+      <c r="O25" s="60"/>
+    </row>
+    <row r="26" spans="2:15">
+      <c r="C26" s="58" t="s">
+        <v>145</v>
+      </c>
+      <c r="D26" s="59"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="59"/>
+      <c r="K26" s="59"/>
+      <c r="L26" s="59"/>
+      <c r="M26" s="59"/>
+      <c r="N26" s="59"/>
+      <c r="O26" s="60"/>
+    </row>
+    <row r="27" spans="2:15">
+      <c r="C27" s="58" t="s">
+        <v>146</v>
+      </c>
+      <c r="D27" s="59"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="59"/>
+      <c r="K27" s="59"/>
+      <c r="L27" s="59"/>
+      <c r="M27" s="59"/>
+      <c r="N27" s="59"/>
+      <c r="O27" s="60"/>
+    </row>
+    <row r="28" spans="2:15">
+      <c r="C28" s="58" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="59"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="59"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="59"/>
+      <c r="K28" s="59"/>
+      <c r="L28" s="59"/>
+      <c r="M28" s="59"/>
+      <c r="N28" s="59"/>
+      <c r="O28" s="60"/>
+    </row>
+    <row r="29" spans="2:15">
+      <c r="C29" s="58" t="s">
+        <v>148</v>
+      </c>
+      <c r="D29" s="59"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="59"/>
+      <c r="J29" s="59"/>
+      <c r="K29" s="59"/>
+      <c r="L29" s="59"/>
+      <c r="M29" s="59"/>
+      <c r="N29" s="59"/>
+      <c r="O29" s="60"/>
+    </row>
+    <row r="30" spans="2:15">
+      <c r="C30" s="58" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" s="59"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="59"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="59"/>
+      <c r="J30" s="59"/>
+      <c r="K30" s="59"/>
+      <c r="L30" s="59"/>
+      <c r="M30" s="59"/>
+      <c r="N30" s="59"/>
+      <c r="O30" s="60"/>
+    </row>
+    <row r="31" spans="2:15">
+      <c r="C31" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="19"/>
+      <c r="O31" s="61"/>
+    </row>
+    <row r="33" spans="2:44">
+      <c r="B33" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="34" spans="2:44" ht="18">
+      <c r="B34" s="62" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="37" spans="2:44">
+      <c r="F37" s="82" t="s">
+        <v>130</v>
+      </c>
+      <c r="G37" s="83"/>
+      <c r="H37" s="83"/>
+      <c r="I37" s="83"/>
+      <c r="J37" s="83"/>
+      <c r="K37" s="84"/>
+      <c r="N37" s="82" t="s">
+        <v>132</v>
+      </c>
+      <c r="O37" s="83"/>
+      <c r="P37" s="83"/>
+      <c r="Q37" s="83"/>
+      <c r="R37" s="83"/>
+      <c r="S37" s="84"/>
+      <c r="Y37" s="12"/>
+      <c r="Z37" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA37" s="13"/>
+      <c r="AB37" s="13"/>
+      <c r="AC37" s="13"/>
+      <c r="AD37" s="14"/>
+      <c r="AO37" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="AP37" s="13"/>
+      <c r="AQ37" s="13"/>
+      <c r="AR37" s="14"/>
+    </row>
+    <row r="38" spans="2:44">
+      <c r="H38" s="6"/>
+      <c r="P38" s="6"/>
+      <c r="AA38" s="6"/>
+      <c r="AP38" s="6"/>
+    </row>
+    <row r="39" spans="2:44">
+      <c r="H39" s="8"/>
+      <c r="P39" s="8"/>
+      <c r="AA39" s="8"/>
+      <c r="AP39" s="8"/>
+    </row>
+    <row r="40" spans="2:44">
+      <c r="C40" s="63" t="s">
+        <v>129</v>
+      </c>
+      <c r="D40" s="64"/>
+      <c r="E40" s="64"/>
+      <c r="F40" s="65"/>
+      <c r="H40" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="P40" s="8"/>
+      <c r="AA40" s="8"/>
+      <c r="AP40" s="8"/>
+    </row>
+    <row r="41" spans="2:44">
+      <c r="H41" s="8"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="14"/>
+      <c r="P41" s="8"/>
+      <c r="AA41" s="8"/>
+      <c r="AP41" s="8"/>
+    </row>
+    <row r="42" spans="2:44">
+      <c r="H42" s="8"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="6"/>
+      <c r="P42" s="8"/>
+      <c r="AA42" s="8"/>
+      <c r="AP42" s="8"/>
+    </row>
+    <row r="43" spans="2:44">
+      <c r="H43" s="8"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="P43" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="AA43" s="8"/>
+      <c r="AP43" s="8"/>
+    </row>
+    <row r="44" spans="2:44">
+      <c r="H44" s="8"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="8"/>
+      <c r="P44" s="8"/>
+      <c r="Q44" s="12"/>
+      <c r="R44" s="13"/>
+      <c r="S44" s="13"/>
+      <c r="T44" s="14"/>
+      <c r="AA44" s="8"/>
+      <c r="AP44" s="8"/>
+    </row>
+    <row r="45" spans="2:44">
+      <c r="H45" s="8"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="8"/>
+      <c r="P45" s="8"/>
+      <c r="Q45" s="4"/>
+      <c r="R45" s="6"/>
+      <c r="AA45" s="8"/>
+      <c r="AP45" s="8"/>
+    </row>
+    <row r="46" spans="2:44">
+      <c r="H46" s="8"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="8"/>
+      <c r="P46" s="8"/>
+      <c r="Q46" s="7"/>
+      <c r="R46" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="AA46" s="8"/>
+      <c r="AP46" s="8"/>
+    </row>
+    <row r="47" spans="2:44">
+      <c r="H47" s="8"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="8"/>
+      <c r="P47" s="8"/>
+      <c r="Q47" s="7"/>
+      <c r="R47" s="8"/>
+      <c r="AA47" s="8"/>
+      <c r="AP47" s="8"/>
+    </row>
+    <row r="48" spans="2:44" ht="15">
+      <c r="H48" s="8"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="8"/>
+      <c r="P48" s="8"/>
+      <c r="Q48" s="7"/>
+      <c r="R48" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA48" s="66" t="s">
+        <v>160</v>
+      </c>
+      <c r="AP48" s="8"/>
+    </row>
+    <row r="49" spans="8:42">
+      <c r="H49" s="8"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="8"/>
+      <c r="P49" s="8"/>
+      <c r="Q49" s="7"/>
+      <c r="R49" s="8"/>
+      <c r="AA49" s="8"/>
+      <c r="AB49" s="12"/>
+      <c r="AC49" s="13"/>
+      <c r="AD49" s="13"/>
+      <c r="AE49" s="14"/>
+      <c r="AP49" s="8"/>
+    </row>
+    <row r="50" spans="8:42">
+      <c r="H50" s="8"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="8"/>
+      <c r="P50" s="8"/>
+      <c r="Q50" s="7"/>
+      <c r="R50" s="8"/>
+      <c r="AA50" s="8"/>
+      <c r="AB50" s="4"/>
+      <c r="AC50" s="6"/>
+      <c r="AP50" s="8"/>
+    </row>
+    <row r="51" spans="8:42">
+      <c r="H51" s="8"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="8"/>
+      <c r="P51" s="8"/>
+      <c r="Q51" s="7"/>
+      <c r="R51" s="8"/>
+      <c r="AA51" s="8"/>
+      <c r="AB51" s="7"/>
+      <c r="AC51" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="AP51" s="8"/>
+    </row>
+    <row r="52" spans="8:42">
+      <c r="H52" s="8"/>
+      <c r="I52" s="7"/>
+      <c r="J52" s="8"/>
+      <c r="P52" s="8"/>
+      <c r="Q52" s="7"/>
+      <c r="R52" s="8"/>
+      <c r="AA52" s="8"/>
+      <c r="AB52" s="7"/>
+      <c r="AC52" s="8"/>
+      <c r="AD52" t="s">
+        <v>164</v>
+      </c>
+      <c r="AP52" s="8"/>
+    </row>
+    <row r="53" spans="8:42">
+      <c r="H53" s="8"/>
+      <c r="I53" s="7"/>
+      <c r="J53" s="8"/>
+      <c r="P53" s="8"/>
+      <c r="Q53" s="7"/>
+      <c r="R53" s="8"/>
+      <c r="AA53" s="8"/>
+      <c r="AB53" s="7"/>
+      <c r="AC53" s="8"/>
+      <c r="AD53" t="s">
+        <v>165</v>
+      </c>
+      <c r="AP53" s="8"/>
+    </row>
+    <row r="54" spans="8:42">
+      <c r="H54" s="8"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="8"/>
+      <c r="P54" s="8"/>
+      <c r="Q54" s="7"/>
+      <c r="R54" s="8"/>
+      <c r="AA54" s="8"/>
+      <c r="AB54" s="7"/>
+      <c r="AC54" s="8"/>
+      <c r="AP54" s="8"/>
+    </row>
+    <row r="55" spans="8:42">
+      <c r="H55" s="8"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="8"/>
+      <c r="P55" s="8"/>
+      <c r="Q55" s="7"/>
+      <c r="R55" s="8"/>
+      <c r="AA55" s="8"/>
+      <c r="AB55" s="7"/>
+      <c r="AC55" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="AP55" s="8"/>
+    </row>
+    <row r="56" spans="8:42">
+      <c r="H56" s="8"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="8"/>
+      <c r="P56" s="8"/>
+      <c r="Q56" s="7"/>
+      <c r="R56" s="8"/>
+      <c r="AA56" s="8"/>
+      <c r="AB56" s="7"/>
+      <c r="AC56" s="8"/>
+      <c r="AD56" t="s">
+        <v>163</v>
+      </c>
+      <c r="AP56" s="8"/>
+    </row>
+    <row r="57" spans="8:42">
+      <c r="H57" s="8"/>
+      <c r="I57" s="7"/>
+      <c r="J57" s="8"/>
+      <c r="P57" s="8"/>
+      <c r="Q57" s="7"/>
+      <c r="R57" s="8"/>
+      <c r="AA57" s="8"/>
+      <c r="AB57" s="9"/>
+      <c r="AC57" s="11"/>
+      <c r="AP57" s="8"/>
+    </row>
+    <row r="58" spans="8:42">
+      <c r="H58" s="8"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="8"/>
+      <c r="P58" s="8"/>
+      <c r="Q58" s="7"/>
+      <c r="R58" s="8"/>
+      <c r="AA58" s="8"/>
+      <c r="AP58" s="8"/>
+    </row>
+    <row r="59" spans="8:42">
+      <c r="H59" s="8"/>
+      <c r="I59" s="7"/>
+      <c r="J59" s="8"/>
+      <c r="P59" s="8"/>
+      <c r="Q59" s="7"/>
+      <c r="R59" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="AA59" s="8"/>
+      <c r="AP59" s="8"/>
+    </row>
+    <row r="60" spans="8:42">
+      <c r="H60" s="8"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="8"/>
+      <c r="P60" s="8"/>
+      <c r="Q60" s="7"/>
+      <c r="R60" s="40" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA60" s="8"/>
+      <c r="AP60" s="8"/>
+    </row>
+    <row r="61" spans="8:42">
+      <c r="H61" s="8"/>
+      <c r="I61" s="7"/>
+      <c r="J61" s="8"/>
+      <c r="P61" s="8"/>
+      <c r="Q61" s="7"/>
+      <c r="R61" s="8"/>
+      <c r="AA61" s="8"/>
+      <c r="AP61" s="8"/>
+    </row>
+    <row r="62" spans="8:42">
+      <c r="H62" s="8"/>
+      <c r="I62" s="7"/>
+      <c r="J62" s="8"/>
+      <c r="P62" s="8"/>
+      <c r="Q62" s="9"/>
+      <c r="R62" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA62" s="8"/>
+      <c r="AP62" s="8"/>
+    </row>
+    <row r="63" spans="8:42">
+      <c r="H63" s="8"/>
+      <c r="I63" s="7"/>
+      <c r="J63" s="8"/>
+      <c r="P63" s="8"/>
+      <c r="AA63" s="8"/>
+      <c r="AP63" s="8"/>
+    </row>
+    <row r="64" spans="8:42">
+      <c r="H64" s="8"/>
+      <c r="I64" s="7"/>
+      <c r="J64" s="8"/>
+      <c r="P64" s="8"/>
+      <c r="AA64" s="8"/>
+      <c r="AP64" s="8"/>
+    </row>
+    <row r="65" spans="8:65">
+      <c r="H65" s="8"/>
+      <c r="I65" s="7"/>
+      <c r="J65" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="P65" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="AA65" s="8"/>
+      <c r="AP65" s="8"/>
+    </row>
+    <row r="66" spans="8:65">
+      <c r="H66" s="8"/>
+      <c r="I66" s="7"/>
+      <c r="J66" s="8"/>
+      <c r="P66" s="8"/>
+      <c r="Q66" s="12"/>
+      <c r="R66" s="13"/>
+      <c r="S66" s="13"/>
+      <c r="T66" s="14"/>
+      <c r="AA66" s="8"/>
+      <c r="AP66" s="8"/>
+    </row>
+    <row r="67" spans="8:65">
+      <c r="H67" s="8"/>
+      <c r="I67" s="7"/>
+      <c r="J67" s="8"/>
+      <c r="P67" s="8"/>
+      <c r="Q67" s="4"/>
+      <c r="R67" s="5"/>
+      <c r="S67" s="4"/>
+      <c r="AA67" s="8"/>
+      <c r="AP67" s="8"/>
+    </row>
+    <row r="68" spans="8:65">
+      <c r="H68" s="8"/>
+      <c r="I68" s="7"/>
+      <c r="J68" s="8"/>
+      <c r="P68" s="8"/>
+      <c r="Q68" s="3"/>
+      <c r="R68" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA68" s="8"/>
+      <c r="AP68" s="8"/>
+    </row>
+    <row r="69" spans="8:65">
+      <c r="H69" s="8"/>
+      <c r="I69" s="7"/>
+      <c r="J69" s="8"/>
+      <c r="P69" s="8"/>
+      <c r="Q69" s="3"/>
+      <c r="R69" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="AA69" s="8"/>
+      <c r="AP69" s="8"/>
+    </row>
+    <row r="70" spans="8:65">
+      <c r="H70" s="8"/>
+      <c r="I70" s="7"/>
+      <c r="J70" s="8"/>
+      <c r="P70" s="8"/>
+      <c r="Q70" s="3"/>
+      <c r="R70" s="8"/>
+      <c r="S70" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="AA70" s="8"/>
+      <c r="AP70" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="71" spans="8:65">
+      <c r="H71" s="8"/>
+      <c r="I71" s="7"/>
+      <c r="J71" s="8"/>
+      <c r="P71" s="8"/>
+      <c r="Q71" s="3"/>
+      <c r="R71" s="8"/>
+      <c r="AA71" s="8"/>
+      <c r="AP71" s="8"/>
+      <c r="AQ71" s="12"/>
+      <c r="AR71" s="13"/>
+      <c r="AS71" s="13"/>
+      <c r="AT71" s="14"/>
+    </row>
+    <row r="72" spans="8:65" ht="15" thickBot="1">
+      <c r="H72" s="8"/>
+      <c r="I72" s="7"/>
+      <c r="J72" s="8"/>
+      <c r="P72" s="8"/>
+      <c r="Q72" s="3"/>
+      <c r="R72" s="8"/>
+      <c r="AA72" s="8"/>
+      <c r="AP72" s="8"/>
+      <c r="AQ72" s="4"/>
+      <c r="AR72" s="6"/>
+    </row>
+    <row r="73" spans="8:65" ht="15.75" thickBot="1">
+      <c r="H73" s="8"/>
+      <c r="I73" s="7"/>
+      <c r="J73" s="8"/>
+      <c r="P73" s="8"/>
+      <c r="Q73" s="3"/>
+      <c r="R73" s="8"/>
+      <c r="AA73" s="8"/>
+      <c r="AP73" s="8"/>
+      <c r="AQ73" s="7"/>
+      <c r="AR73" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="BH73" s="67" t="s">
+        <v>193</v>
+      </c>
+      <c r="BI73" s="68"/>
+      <c r="BJ73" s="68"/>
+      <c r="BK73" s="68"/>
+      <c r="BL73" s="68"/>
+      <c r="BM73" s="69"/>
+    </row>
+    <row r="74" spans="8:65">
+      <c r="H74" s="8"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="8"/>
+      <c r="P74" s="8"/>
+      <c r="Q74" s="3"/>
+      <c r="R74" s="8"/>
+      <c r="AA74" s="8"/>
+      <c r="AP74" s="8"/>
+      <c r="AQ74" s="9"/>
+      <c r="AR74" s="11"/>
+    </row>
+    <row r="75" spans="8:65">
+      <c r="H75" s="8"/>
+      <c r="I75" s="7"/>
+      <c r="J75" s="8"/>
+      <c r="P75" s="8"/>
+      <c r="Q75" s="3"/>
+      <c r="R75" s="8"/>
+      <c r="AA75" s="8"/>
+      <c r="AP75" s="8"/>
+    </row>
+    <row r="76" spans="8:65">
+      <c r="H76" s="8"/>
+      <c r="I76" s="7"/>
+      <c r="J76" s="8"/>
+      <c r="P76" s="8"/>
+      <c r="Q76" s="3"/>
+      <c r="R76" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA76" s="8"/>
+      <c r="AP76" s="8"/>
+    </row>
+    <row r="77" spans="8:65">
+      <c r="H77" s="8"/>
+      <c r="I77" s="7"/>
+      <c r="J77" s="8"/>
+      <c r="P77" s="8"/>
+      <c r="Q77" s="3"/>
+      <c r="S77" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="AA77" s="8"/>
+      <c r="AP77" s="8"/>
+    </row>
+    <row r="78" spans="8:65">
+      <c r="H78" s="8"/>
+      <c r="I78" s="7"/>
+      <c r="J78" s="8"/>
+      <c r="P78" s="8"/>
+      <c r="Q78" s="3"/>
+      <c r="R78" s="8"/>
+      <c r="S78" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="AA78" s="8"/>
+      <c r="AP78" s="8"/>
+    </row>
+    <row r="79" spans="8:65">
+      <c r="H79" s="8"/>
+      <c r="I79" s="7"/>
+      <c r="J79" s="8"/>
+      <c r="P79" s="8"/>
+      <c r="Q79" s="3"/>
+      <c r="R79" s="8"/>
+      <c r="S79" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="AA79" s="8"/>
+      <c r="AP79" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="80" spans="8:65">
+      <c r="H80" s="8"/>
+      <c r="I80" s="7"/>
+      <c r="J80" s="8"/>
+      <c r="P80" s="8"/>
+      <c r="Q80" s="3"/>
+      <c r="R80" s="8"/>
+      <c r="AA80" s="8"/>
+      <c r="AP80" s="8"/>
+      <c r="AQ80" s="12"/>
+      <c r="AR80" s="13"/>
+      <c r="AS80" s="13"/>
+      <c r="AT80" s="14"/>
+    </row>
+    <row r="81" spans="8:44">
+      <c r="H81" s="8"/>
+      <c r="I81" s="7"/>
+      <c r="J81" s="8"/>
+      <c r="P81" s="8"/>
+      <c r="Q81" s="3"/>
+      <c r="R81" s="8"/>
+      <c r="AA81" s="8"/>
+      <c r="AP81" s="8"/>
+      <c r="AQ81" s="4"/>
+      <c r="AR81" s="6"/>
+    </row>
+    <row r="82" spans="8:44">
+      <c r="H82" s="8"/>
+      <c r="I82" s="7"/>
+      <c r="J82" s="8"/>
+      <c r="P82" s="8"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="8"/>
+      <c r="AA82" s="8"/>
+      <c r="AP82" s="8"/>
+      <c r="AQ82" s="7"/>
+      <c r="AR82" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="83" spans="8:44">
+      <c r="H83" s="8"/>
+      <c r="I83" s="7"/>
+      <c r="J83" s="8"/>
+      <c r="P83" s="8"/>
+      <c r="Q83" s="3"/>
+      <c r="R83" s="8"/>
+      <c r="AA83" s="8"/>
+      <c r="AP83" s="8"/>
+      <c r="AQ83" s="9"/>
+      <c r="AR83" s="11"/>
+    </row>
+    <row r="84" spans="8:44">
+      <c r="H84" s="8"/>
+      <c r="I84" s="7"/>
+      <c r="J84" s="8"/>
+      <c r="P84" s="8"/>
+      <c r="Q84" s="9"/>
+      <c r="R84" s="11"/>
+      <c r="AA84" s="8"/>
+      <c r="AP84" s="8"/>
+    </row>
+    <row r="85" spans="8:44">
+      <c r="H85" s="8"/>
+      <c r="I85" s="9"/>
+      <c r="J85" s="11"/>
+      <c r="P85" s="8"/>
+      <c r="AA85" s="8"/>
+      <c r="AP85" s="8"/>
+    </row>
+    <row r="86" spans="8:44">
+      <c r="H86" s="8"/>
+      <c r="P86" s="8"/>
+      <c r="AA86" s="8"/>
+      <c r="AP86" s="8"/>
+    </row>
+    <row r="87" spans="8:44">
+      <c r="H87" s="8"/>
+      <c r="P87" s="8"/>
+      <c r="AA87" s="8"/>
+      <c r="AP87" s="8"/>
+    </row>
+    <row r="88" spans="8:44">
+      <c r="H88" s="8"/>
+      <c r="P88" s="8"/>
+      <c r="V88" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA88" s="8"/>
+      <c r="AP88" s="8"/>
+    </row>
+    <row r="89" spans="8:44">
+      <c r="H89" s="8"/>
+      <c r="P89" s="8"/>
+      <c r="AA89" s="8"/>
+      <c r="AP89" s="8"/>
+    </row>
+    <row r="90" spans="8:44">
+      <c r="H90" s="8"/>
+      <c r="P90" s="8"/>
+      <c r="AA90" s="8"/>
+      <c r="AP90" s="8"/>
+    </row>
+    <row r="91" spans="8:44">
+      <c r="H91" s="8"/>
+      <c r="P91" s="8"/>
+      <c r="AA91" s="8"/>
+      <c r="AP91" s="8"/>
+    </row>
+    <row r="92" spans="8:44">
+      <c r="H92" s="8"/>
+      <c r="P92" s="8"/>
+      <c r="AA92" s="8"/>
+      <c r="AP92" s="8"/>
+    </row>
+    <row r="93" spans="8:44">
+      <c r="H93" s="8"/>
+      <c r="P93" s="8"/>
+      <c r="AA93" s="8"/>
+      <c r="AP93" s="8"/>
+    </row>
+    <row r="94" spans="8:44">
+      <c r="H94" s="8"/>
+      <c r="P94" s="8"/>
+      <c r="AA94" s="8"/>
+      <c r="AP94" s="8"/>
+    </row>
+    <row r="95" spans="8:44">
+      <c r="H95" s="8"/>
+      <c r="P95" s="8"/>
+      <c r="AA95" s="8"/>
+      <c r="AP95" s="8"/>
+    </row>
+    <row r="96" spans="8:44">
+      <c r="H96" s="8"/>
+      <c r="P96" s="8"/>
+      <c r="AA96" s="8"/>
+      <c r="AP96" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F37:K37"/>
+    <mergeCell ref="N37:S37"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B97659E-0B8C-451B-B9D6-7BDEA7E84F0C}">
+  <dimension ref="A2:AY57"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="2" spans="1:51" ht="23.25">
+      <c r="B2" s="71" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="6"/>
+      <c r="AA2" s="71" t="s">
+        <v>204</v>
+      </c>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="5"/>
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="5"/>
+      <c r="AJ2" s="5"/>
+      <c r="AK2" s="5"/>
+      <c r="AL2" s="5"/>
+      <c r="AM2" s="5"/>
+      <c r="AN2" s="5"/>
+      <c r="AO2" s="5"/>
+      <c r="AP2" s="5"/>
+      <c r="AQ2" s="5"/>
+      <c r="AR2" s="5"/>
+      <c r="AS2" s="5"/>
+      <c r="AT2" s="5"/>
+      <c r="AU2" s="5"/>
+      <c r="AV2" s="5"/>
+      <c r="AW2" s="5"/>
+      <c r="AX2" s="5"/>
+      <c r="AY2" s="6"/>
+    </row>
+    <row r="3" spans="1:51" ht="15">
+      <c r="B3" s="75" t="s">
+        <v>197</v>
+      </c>
+      <c r="Y3" s="8"/>
+      <c r="AA3" s="72" t="s">
+        <v>205</v>
+      </c>
+      <c r="AY3" s="8"/>
+    </row>
+    <row r="4" spans="1:51" ht="15">
+      <c r="B4" s="76" t="s">
+        <v>198</v>
+      </c>
+      <c r="Y4" s="8"/>
+      <c r="AA4" s="72" t="s">
+        <v>206</v>
+      </c>
+      <c r="AY4" s="8"/>
+    </row>
+    <row r="5" spans="1:51" ht="15">
+      <c r="B5" s="76" t="s">
+        <v>199</v>
+      </c>
+      <c r="Y5" s="8"/>
+      <c r="AA5" s="72" t="s">
+        <v>207</v>
+      </c>
+      <c r="AY5" s="8"/>
+    </row>
+    <row r="6" spans="1:51" ht="15">
+      <c r="B6" s="76" t="s">
+        <v>200</v>
+      </c>
+      <c r="Y6" s="8"/>
+      <c r="AA6" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="AY6" s="8"/>
+    </row>
+    <row r="7" spans="1:51" ht="15">
+      <c r="B7" s="75" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y7" s="8"/>
+      <c r="AA7" s="73" t="s">
+        <v>209</v>
+      </c>
+      <c r="AY7" s="8"/>
+    </row>
+    <row r="8" spans="1:51">
+      <c r="B8" s="76" t="s">
+        <v>202</v>
+      </c>
+      <c r="Y8" s="8"/>
+      <c r="AA8" s="74" t="s">
+        <v>210</v>
+      </c>
+      <c r="AY8" s="8"/>
+    </row>
+    <row r="9" spans="1:51">
+      <c r="B9" s="76" t="s">
+        <v>203</v>
+      </c>
+      <c r="Y9" s="8"/>
+      <c r="AA9" s="73" t="s">
+        <v>211</v>
+      </c>
+      <c r="AY9" s="8"/>
+    </row>
+    <row r="10" spans="1:51">
+      <c r="B10" s="87" t="s">
+        <v>227</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="11"/>
+      <c r="AA10" s="9"/>
+      <c r="AB10" s="10"/>
+      <c r="AC10" s="10"/>
+      <c r="AD10" s="10"/>
+      <c r="AE10" s="10"/>
+      <c r="AF10" s="10"/>
+      <c r="AG10" s="10"/>
+      <c r="AH10" s="10"/>
+      <c r="AI10" s="10"/>
+      <c r="AJ10" s="10"/>
+      <c r="AK10" s="10"/>
+      <c r="AL10" s="10"/>
+      <c r="AM10" s="10"/>
+      <c r="AN10" s="10"/>
+      <c r="AO10" s="10"/>
+      <c r="AP10" s="10"/>
+      <c r="AQ10" s="10"/>
+      <c r="AR10" s="10"/>
+      <c r="AS10" s="10"/>
+      <c r="AT10" s="10"/>
+      <c r="AU10" s="10"/>
+      <c r="AV10" s="10"/>
+      <c r="AW10" s="10"/>
+      <c r="AX10" s="10"/>
+      <c r="AY10" s="11"/>
+    </row>
+    <row r="12" spans="1:51" ht="15">
+      <c r="B12" s="70" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="13" spans="1:51" ht="15" thickBot="1"/>
+    <row r="14" spans="1:51" s="68" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A14" s="77"/>
+      <c r="B14" s="78" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="15" spans="1:51" ht="15" thickBot="1"/>
+    <row r="16" spans="1:51" ht="15" thickBot="1">
+      <c r="C16" s="79" t="s">
+        <v>214</v>
+      </c>
+      <c r="D16" s="80"/>
+      <c r="E16" s="80"/>
+      <c r="F16" s="80"/>
+      <c r="G16" s="80"/>
+      <c r="H16" s="80"/>
+      <c r="I16" s="80"/>
+      <c r="J16" s="80"/>
+      <c r="K16" s="80"/>
+      <c r="L16" s="80"/>
+      <c r="M16" s="80"/>
+      <c r="N16" s="80"/>
+      <c r="O16" s="81"/>
+    </row>
+    <row r="18" spans="4:29">
+      <c r="D18" s="12"/>
+      <c r="E18" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="14"/>
+      <c r="P18" s="82" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q18" s="83"/>
+      <c r="R18" s="83"/>
+      <c r="S18" s="83"/>
+      <c r="T18" s="83"/>
+      <c r="U18" s="84"/>
+      <c r="X18" s="82" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y18" s="83"/>
+      <c r="Z18" s="83"/>
+      <c r="AA18" s="84"/>
+    </row>
+    <row r="19" spans="4:29">
+      <c r="F19" s="6"/>
+      <c r="R19" s="6"/>
+      <c r="Y19" s="6"/>
+    </row>
+    <row r="20" spans="4:29">
+      <c r="F20" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="R20" s="8"/>
+      <c r="Y20" s="8"/>
+    </row>
+    <row r="21" spans="4:29">
+      <c r="F21" s="8"/>
+      <c r="G21" t="s">
+        <v>126</v>
+      </c>
+      <c r="R21" s="8"/>
+      <c r="Y21" s="8"/>
+    </row>
+    <row r="22" spans="4:29">
+      <c r="F22" s="8"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="14"/>
+      <c r="R22" s="8"/>
+      <c r="Y22" s="8"/>
+    </row>
+    <row r="23" spans="4:29">
+      <c r="F23" s="8"/>
+      <c r="H23" s="6"/>
+      <c r="R23" s="8"/>
+      <c r="Y23" s="8"/>
+    </row>
+    <row r="24" spans="4:29">
+      <c r="F24" s="8"/>
+      <c r="H24" t="s">
+        <v>194</v>
+      </c>
+      <c r="R24" s="8"/>
+      <c r="Y24" s="8"/>
+    </row>
+    <row r="25" spans="4:29">
+      <c r="F25" s="8"/>
+      <c r="H25" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="R25" s="8"/>
+      <c r="Y25" s="8"/>
+    </row>
+    <row r="26" spans="4:29">
+      <c r="F26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="14"/>
+      <c r="R26" s="8"/>
+      <c r="Y26" s="8"/>
+    </row>
+    <row r="27" spans="4:29">
+      <c r="F27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="J27" s="6"/>
+      <c r="R27" s="8"/>
+      <c r="Y27" s="8"/>
+    </row>
+    <row r="28" spans="4:29">
+      <c r="F28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="J28" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="R28" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="Y28" s="8"/>
+    </row>
+    <row r="29" spans="4:29">
+      <c r="F29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="R29" s="8"/>
+      <c r="S29" s="12"/>
+      <c r="T29" s="13"/>
+      <c r="U29" s="13"/>
+      <c r="V29" s="14"/>
+      <c r="Y29" s="8"/>
+    </row>
+    <row r="30" spans="4:29">
+      <c r="F30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="R30" s="8"/>
+      <c r="S30" s="4"/>
+      <c r="T30" s="6"/>
+      <c r="Y30" s="8"/>
+    </row>
+    <row r="31" spans="4:29">
+      <c r="F31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="R31" s="8"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y31" s="8" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="32" spans="4:29">
+      <c r="F32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="R32" s="8"/>
+      <c r="S32" s="9"/>
+      <c r="T32" s="11"/>
+      <c r="Y32" s="8"/>
+      <c r="Z32" s="12"/>
+      <c r="AA32" s="13"/>
+      <c r="AB32" s="13"/>
+      <c r="AC32" s="14"/>
+    </row>
+    <row r="33" spans="6:33">
+      <c r="F33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="R33" s="8"/>
+      <c r="Y33" s="8"/>
+      <c r="AA33" s="6"/>
+    </row>
+    <row r="34" spans="6:33">
+      <c r="F34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="R34" s="8"/>
+      <c r="Y34" s="8"/>
+      <c r="AA34" s="8" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="35" spans="6:33">
+      <c r="F35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="R35" s="8"/>
+      <c r="Y35" s="8"/>
+      <c r="AA35" s="8"/>
+    </row>
+    <row r="36" spans="6:33">
+      <c r="F36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="R36" s="8"/>
+      <c r="Y36" s="8"/>
+      <c r="AA36" s="8" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="37" spans="6:33">
+      <c r="F37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="R37" s="8"/>
+      <c r="Y37" s="8"/>
+      <c r="AA37" s="8"/>
+      <c r="AB37" s="12"/>
+      <c r="AC37" s="13"/>
+      <c r="AD37" s="13"/>
+      <c r="AE37" s="14"/>
+    </row>
+    <row r="38" spans="6:33">
+      <c r="F38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="R38" s="8"/>
+      <c r="Y38" s="8"/>
+      <c r="AA38" s="8"/>
+      <c r="AC38" s="6"/>
+    </row>
+    <row r="39" spans="6:33">
+      <c r="F39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="R39" s="8"/>
+      <c r="Y39" s="8"/>
+      <c r="AA39" s="8"/>
+      <c r="AC39" s="8" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="40" spans="6:33">
+      <c r="F40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="R40" s="8"/>
+      <c r="Y40" s="8"/>
+      <c r="AA40" s="8"/>
+      <c r="AC40" s="8"/>
+    </row>
+    <row r="41" spans="6:33">
+      <c r="F41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="R41" s="8"/>
+      <c r="Y41" s="8"/>
+      <c r="AA41" s="8"/>
+      <c r="AC41" s="8" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="42" spans="6:33">
+      <c r="F42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="J42" s="8"/>
+      <c r="R42" s="8"/>
+      <c r="Y42" s="8"/>
+      <c r="AA42" s="8"/>
+      <c r="AC42" s="8"/>
+      <c r="AD42" s="12"/>
+      <c r="AE42" s="13"/>
+      <c r="AF42" s="13"/>
+      <c r="AG42" s="14"/>
+    </row>
+    <row r="43" spans="6:33">
+      <c r="F43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="R43" s="8"/>
+      <c r="Y43" s="8"/>
+      <c r="AA43" s="8"/>
+      <c r="AC43" s="8"/>
+      <c r="AE43" s="6"/>
+    </row>
+    <row r="44" spans="6:33">
+      <c r="F44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="R44" s="8"/>
+      <c r="Y44" s="8"/>
+      <c r="AA44" s="8"/>
+      <c r="AC44" s="8"/>
+      <c r="AE44" s="8" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="45" spans="6:33">
+      <c r="F45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="R45" s="8"/>
+      <c r="Y45" s="8"/>
+      <c r="AA45" s="8"/>
+      <c r="AC45" s="8"/>
+      <c r="AE45" s="8"/>
+      <c r="AF45" s="85"/>
+      <c r="AG45" s="86" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="46" spans="6:33">
+      <c r="F46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="J46" s="8"/>
+      <c r="R46" s="8"/>
+      <c r="Y46" s="8"/>
+      <c r="AA46" s="8"/>
+      <c r="AC46" s="8"/>
+    </row>
+    <row r="47" spans="6:33">
+      <c r="F47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="R47" s="8"/>
+      <c r="Y47" s="8"/>
+      <c r="AA47" s="8"/>
+      <c r="AC47" s="8" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="48" spans="6:33">
+      <c r="F48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="J48" s="8"/>
+      <c r="R48" s="8"/>
+      <c r="Y48" s="8"/>
+      <c r="AA48" s="8"/>
+      <c r="AC48" s="8"/>
+    </row>
+    <row r="49" spans="6:41">
+      <c r="F49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="J49" s="8"/>
+      <c r="R49" s="8"/>
+      <c r="Y49" s="8"/>
+      <c r="AA49" s="8"/>
+      <c r="AC49" s="8"/>
+    </row>
+    <row r="50" spans="6:41">
+      <c r="F50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="R50" s="8"/>
+      <c r="Y50" s="8"/>
+      <c r="AA50" s="8"/>
+      <c r="AC50" s="8"/>
+    </row>
+    <row r="51" spans="6:41">
+      <c r="F51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="R51" s="8"/>
+      <c r="Y51" s="8"/>
+      <c r="AA51" s="8"/>
+      <c r="AC51" s="8"/>
+    </row>
+    <row r="52" spans="6:41">
+      <c r="F52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="R52" s="8"/>
+      <c r="Y52" s="8"/>
+      <c r="AA52" s="8"/>
+      <c r="AC52" s="8"/>
+    </row>
+    <row r="53" spans="6:41">
+      <c r="F53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="R53" s="8"/>
+      <c r="Y53" s="8"/>
+      <c r="AA53" s="8"/>
+      <c r="AC53" s="8"/>
+      <c r="AO53" s="85"/>
+    </row>
+    <row r="54" spans="6:41">
+      <c r="F54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="J54" s="8"/>
+      <c r="R54" s="8"/>
+      <c r="Y54" s="8"/>
+      <c r="AA54" s="8"/>
+      <c r="AC54" s="8"/>
+    </row>
+    <row r="55" spans="6:41">
+      <c r="F55" s="8"/>
+      <c r="H55" s="8"/>
+      <c r="J55" s="8"/>
+      <c r="R55" s="8"/>
+      <c r="Y55" s="8"/>
+      <c r="AA55" s="8"/>
+      <c r="AC55" s="8"/>
+    </row>
+    <row r="56" spans="6:41">
+      <c r="F56" s="8"/>
+      <c r="H56" s="8"/>
+      <c r="J56" s="8"/>
+      <c r="R56" s="8"/>
+      <c r="Y56" s="8"/>
+      <c r="AA56" s="8"/>
+      <c r="AC56" s="8"/>
+    </row>
+    <row r="57" spans="6:41">
+      <c r="F57" s="8"/>
+      <c r="H57" s="8"/>
+      <c r="J57" s="8"/>
+      <c r="R57" s="8"/>
+      <c r="Y57" s="8"/>
+      <c r="AA57" s="8"/>
+      <c r="AC57" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="P18:U18"/>
+    <mergeCell ref="X18:AA18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D37D8AE1-203C-42DF-8D3A-6A86DDA0335D}">
+  <dimension ref="C2:C17"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="2" spans="3:3">
+      <c r="C2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3">
+      <c r="C4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3">
+      <c r="C7" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3">
+      <c r="C8" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3">
+      <c r="C14" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="15" spans="3:3">
+      <c r="C15" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3">
+      <c r="C16" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>192</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/unit12_Uboot/unit12_Uboot.xlsx
+++ b/unit12_Uboot/unit12_Uboot.xlsx
@@ -3,18 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720DC19B-37DC-4851-A63C-8A6B316EEADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975110F8-0427-4F7A-BD63-E31B08697ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="First stage boot loader" sheetId="2" r:id="rId2"/>
-    <sheet name="Second stage boot loader." sheetId="3" r:id="rId3"/>
-    <sheet name="Third stage boot loader" sheetId="4" r:id="rId4"/>
-    <sheet name="command line" sheetId="5" r:id="rId5"/>
-    <sheet name="load Linux kernel" sheetId="7" r:id="rId6"/>
-    <sheet name=" source code" sheetId="6" r:id="rId7"/>
+    <sheet name="Second stage boot loader." sheetId="3" r:id="rId2"/>
+    <sheet name="Third stage boot loader" sheetId="4" r:id="rId3"/>
+    <sheet name="command line" sheetId="5" r:id="rId4"/>
+    <sheet name="load Linux kernel" sheetId="7" r:id="rId5"/>
+    <sheet name=" source code" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,183 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="171">
   <si>
     <t>protocall driver cho nokia 5110</t>
   </si>
   <si>
     <t>controler driver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">first stage -romcode (Chip) </t>
-  </si>
-  <si>
-    <t>third stage boot loader:  second + third stage =&gt; uboot</t>
-  </si>
-  <si>
-    <t>second stage boot loader (bo nho ngoai- emmc, sdcard ...)</t>
-  </si>
-  <si>
-    <t>Linux kernel (sdcard, ethernet, serial)</t>
-  </si>
-  <si>
-    <t>root file system (applications …)</t>
-  </si>
-  <si>
-    <t>Uboot.img</t>
-  </si>
-  <si>
-    <t>Boot rom</t>
-  </si>
-  <si>
-    <t>Là chương trình được lưu trong vùng nhớ Rom của SoC, nằm tại địa chỉ 0x20000.</t>
-  </si>
-  <si>
-    <t>Ngay sau khi power on, CPU sẽ thực thi chương trình này.</t>
-  </si>
-  <si>
-    <t>SYSBOOT Configuration Pins</t>
-  </si>
-  <si>
-    <t>Bao gồm 15 chân Pin. Giá trị điện áp tại mỗi chân Pin sẽ quyết định 1 thuộc tính khi boot.</t>
-  </si>
-  <si>
-    <t>Crystal Frequency.</t>
-  </si>
-  <si>
-    <t>Pinmuxing.</t>
-  </si>
-  <si>
-    <t>Boot sequence.</t>
-  </si>
-  <si>
-    <t>Do đặc thù kích thước nhỏ và không thể ghi đè lại. Nên chương trình boot ROM thường sẽ làm rất đơn giản. Tuy nhiên ngày nay, có nhu cầu về những cách thức boot phức tạp hơn. Ví dụ như cho phép boot OS từ ethernet, serial, hiển thị logo, boot song song nhiều OS…</t>
-  </si>
-  <si>
-    <t>Do đó cần phải có 1 chương trình boot loader phức tạp hơn. Chương trình sẽ được lưu ở bộ nhớ ngoài với kích thước lớn hơn. Uboot ra đời.</t>
-  </si>
-  <si>
-    <t>Uboot được xây dựng với tư tưởng như sau:</t>
-  </si>
-  <si>
-    <t>Tầng thấp nhất là các device driver. Chúng làm nhiệm vụ điều khiển phần cứng. Chức năng sẽ tập chung vào cấu hình clock, power, pinmuxing, đọc ghi dữ liệu từ thiết bị nhớ.</t>
-  </si>
-  <si>
-    <t>Tầng thư viện: Là các library với những API như printf, debug_log, read(), write()…</t>
-  </si>
-  <si>
-    <t>Tầng application: Là các command line. Như read, load, bootm…</t>
-  </si>
-  <si>
-    <t>Mục đich cuối cùng của uboot là thực hiện boot script. Boot script sẽ gọi 1 loạt các command line để thực hiện việc boot hệ điều hành.</t>
-  </si>
-  <si>
-    <t>Uboot source code</t>
-  </si>
-  <si>
-    <t>Device tree.</t>
-  </si>
-  <si>
-    <t>Syntax về device tree trong uboot follow theo đúng với Linux.</t>
-  </si>
-  <si>
-    <t>Device driver</t>
-  </si>
-  <si>
-    <t>Template về driver của uboot khá giống với Linux.</t>
-  </si>
-  <si>
-    <t>Command line</t>
-  </si>
-  <si>
-    <t>Uboot device tree</t>
-  </si>
-  <si>
-    <t>Uboot cũng sử dụng device tree tương tự như kernel. Tuy nhiên, các ngoại vi cần sử dụng trước khi device tree được khởi tạo thì sẽ được hardcode về hardware.</t>
-  </si>
-  <si>
-    <t>Device tree trong uboot được đính kèm trong file uboot.img chứ không được build riêng ra file dtb.</t>
-  </si>
-  <si>
-    <t>Uboot command line</t>
-  </si>
-  <si>
-    <t>Command line trong uboot giống như hệ thống application trên Linux.</t>
-  </si>
-  <si>
-    <t>Toàn bộ quá trình hoạt động sẽ theo 1 luồng gọi giữa các command line.</t>
-  </si>
-  <si>
-    <t>uEnv.txt</t>
-  </si>
-  <si>
-    <t>SPL/MLO file có thể được load thông qua uart, sdcard hoặc eMMC.</t>
-  </si>
-  <si>
-    <t>Khởi tạo 1 số clock quan trọng, static ram, 1 số ngoại vi như serial…</t>
-  </si>
-  <si>
-    <t>Boot trap loader – start.S</t>
-  </si>
-  <si>
-    <t>board_init_f</t>
-  </si>
-  <si>
-    <t>board_init_r</t>
-  </si>
-  <si>
-    <t>Khởi tạo tài nguyên hệ thống để load kernel image.</t>
-  </si>
-  <si>
-    <t>Peripheral: Ethernet, uart, graphic, dram,…</t>
-  </si>
-  <si>
-    <t>Tài nguyên: malloc, stdio, file system,…</t>
-  </si>
-  <si>
-    <t>Uboot sẽ thực thi 1 loạt các câu lệnh bao gồm:</t>
-  </si>
-  <si>
-    <t>Setup environment.</t>
-  </si>
-  <si>
-    <t>Load kernel image từ flash vào ram.</t>
-  </si>
-  <si>
-    <t>Jump để boot trap loader của Linux kernel (kernel_entry call head.S)</t>
-  </si>
-  <si>
-    <t>Kernel parameter???</t>
-  </si>
-  <si>
-    <t>uboot reference manual</t>
-  </si>
-  <si>
-    <t>uboot script</t>
-  </si>
-  <si>
-    <t>trái tim của uboot</t>
-  </si>
-  <si>
-    <t>/include/config</t>
-  </si>
-  <si>
-    <t>viết cmd line của uboot để bật tắt led</t>
-  </si>
-  <si>
-    <t>viết driver, dt, makefile của uboot để điều khiển led</t>
-  </si>
-  <si>
-    <t>Kconfig, Makefile</t>
-  </si>
-  <si>
-    <t>khởi tạo những tài nguyên tối thiểu như 1 core của CPU, static ram, sdcard (nếu như uboot được lưu trữ trên sdcard)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhiệm vụ: </t>
-  </si>
-  <si>
-    <t>Khởi tạo 1 số clock, pin muxing, disable watchdog… Đọc giá trị của SYSBOOT_PIN để load second stage boot loader.</t>
   </si>
   <si>
     <t>1.2 Uboot basic</t>
@@ -1153,9 +981,6 @@
       </rPr>
       <t>include/configs/omap3_beagle.h</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -1508,10 +1333,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -1524,7 +1347,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1619,6 +1441,11 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1627,11 +1454,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1651,583 +1473,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>133523</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="209550" y="190500"/>
-          <a:ext cx="4114973" cy="2019300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>123824</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>119484</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>115291</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="57150" y="3952874"/>
-          <a:ext cx="4462884" cy="3610967"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>42611</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>43</xdr:col>
-      <xdr:colOff>39082</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>172155</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4652711" y="4086225"/>
-          <a:ext cx="4397021" cy="3153480"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>43</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>91978</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>73</xdr:col>
-      <xdr:colOff>163423</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>181805</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9115425" y="3730528"/>
-          <a:ext cx="6345148" cy="3518827"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>74</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>57358</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>97</xdr:col>
-      <xdr:colOff>67651</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>730</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15630525" y="3695908"/>
-          <a:ext cx="4763476" cy="3562872"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>114299</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>168354</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>56</xdr:col>
-      <xdr:colOff>68094</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>104185</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8286749" y="168354"/>
-          <a:ext cx="3516145" cy="2031331"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>45</xdr:col>
-      <xdr:colOff>1287</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>133395</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="209550" y="17202150"/>
-          <a:ext cx="9221487" cy="323895"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>95644</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>124002</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="209550" y="17583150"/>
-          <a:ext cx="2819794" cy="1267002"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>29573</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>47658</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="209550" y="18916650"/>
-          <a:ext cx="7154273" cy="238158"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>181644</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>162081</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="209550" y="19297650"/>
-          <a:ext cx="4791744" cy="1114581"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>104</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>162416</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>162027</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="209550" y="20440650"/>
-          <a:ext cx="3515216" cy="733527"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>64</xdr:col>
-      <xdr:colOff>77428</xdr:colOff>
-      <xdr:row>147</xdr:row>
-      <xdr:rowOff>182094</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4686300" y="20793075"/>
-          <a:ext cx="8802328" cy="8021169"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>112</xdr:row>
-      <xdr:rowOff>76201</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>105530</xdr:colOff>
-      <xdr:row>114</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="190500" y="22040851"/>
-          <a:ext cx="4315580" cy="447674"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2895,7 +2140,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -4281,7 +3526,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -5782,7 +5027,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -6934,7 +6179,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:E11"/>
-  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="13.8"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" t="s">
@@ -6948,42 +6193,42 @@
     </row>
     <row r="4" spans="2:5">
       <c r="D4" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="D5" t="s">
-        <v>59</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="E6" t="s">
-        <v>60</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="E7" t="s">
-        <v>61</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="E8" t="s">
-        <v>137</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="E9" t="s">
-        <v>138</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="E10" t="s">
-        <v>152</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="E11" t="s">
-        <v>153</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -6992,839 +6237,333 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A5:BV112"/>
-  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
-  <sheetData>
-    <row r="5" spans="1:45">
-      <c r="Y5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:45">
-      <c r="Y6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:45" ht="15" thickBot="1"/>
-    <row r="13" spans="1:45" s="2" customFormat="1" ht="15" thickBot="1">
-      <c r="A13" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:45">
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:45">
-      <c r="C15" t="s">
-        <v>9</v>
-      </c>
-      <c r="AR15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:45">
-      <c r="C16" t="s">
-        <v>10</v>
-      </c>
-      <c r="AS16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="3:46">
-      <c r="C17" t="s">
-        <v>57</v>
-      </c>
-      <c r="AT17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="3:46">
-      <c r="D18" t="s">
-        <v>56</v>
-      </c>
-      <c r="AT18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="3:46">
-      <c r="D19" t="s">
-        <v>58</v>
-      </c>
-      <c r="AT19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="15" thickBot="1"/>
-    <row r="41" spans="1:3" s="2" customFormat="1" ht="15" thickBot="1">
-      <c r="A41" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="B44" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="B46" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="C47" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="C48" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="C49" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="B50" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="C52" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="C53" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="C54" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="C55" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="C56" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="15" thickBot="1">
-      <c r="B58" s="3"/>
-    </row>
-    <row r="59" spans="1:4" s="2" customFormat="1" ht="15" thickBot="1">
-      <c r="A59" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="B60" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="C61" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="D62" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="D63" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="D64" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="65" spans="2:74">
-      <c r="D65" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="67" spans="2:74">
-      <c r="C67" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="68" spans="2:74">
-      <c r="D68" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="69" spans="2:74">
-      <c r="D69" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="70" spans="2:74">
-      <c r="D70" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="71" spans="2:74">
-      <c r="D71" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="74" spans="2:74">
-      <c r="B74" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5"/>
-      <c r="J74" s="5"/>
-      <c r="K74" s="5"/>
-      <c r="L74" s="5"/>
-      <c r="M74" s="5"/>
-      <c r="N74" s="5"/>
-      <c r="O74" s="5"/>
-      <c r="P74" s="5"/>
-      <c r="Q74" s="5"/>
-      <c r="R74" s="5"/>
-      <c r="S74" s="5"/>
-      <c r="T74" s="5"/>
-      <c r="U74" s="5"/>
-      <c r="V74" s="6"/>
-      <c r="AB74" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC74" s="5"/>
-      <c r="AD74" s="5"/>
-      <c r="AE74" s="5"/>
-      <c r="AF74" s="5"/>
-      <c r="AG74" s="5"/>
-      <c r="AH74" s="5"/>
-      <c r="AI74" s="5"/>
-      <c r="AJ74" s="5"/>
-      <c r="AK74" s="5"/>
-      <c r="AL74" s="5"/>
-      <c r="AM74" s="5"/>
-      <c r="AN74" s="5"/>
-      <c r="AO74" s="5"/>
-      <c r="AP74" s="5"/>
-      <c r="AQ74" s="5"/>
-      <c r="AR74" s="5"/>
-      <c r="AS74" s="5"/>
-      <c r="AT74" s="5"/>
-      <c r="AU74" s="5"/>
-      <c r="AV74" s="5"/>
-      <c r="AW74" s="5"/>
-      <c r="AX74" s="5"/>
-      <c r="AY74" s="5"/>
-      <c r="AZ74" s="5"/>
-      <c r="BA74" s="5"/>
-      <c r="BB74" s="5"/>
-      <c r="BC74" s="5"/>
-      <c r="BD74" s="5"/>
-      <c r="BE74" s="5"/>
-      <c r="BF74" s="5"/>
-      <c r="BG74" s="5"/>
-      <c r="BH74" s="5"/>
-      <c r="BI74" s="5"/>
-      <c r="BJ74" s="5"/>
-      <c r="BK74" s="5"/>
-      <c r="BL74" s="5"/>
-      <c r="BM74" s="5"/>
-      <c r="BN74" s="5"/>
-      <c r="BO74" s="5"/>
-      <c r="BP74" s="5"/>
-      <c r="BQ74" s="5"/>
-      <c r="BR74" s="5"/>
-      <c r="BS74" s="5"/>
-      <c r="BT74" s="5"/>
-      <c r="BU74" s="5"/>
-      <c r="BV74" s="6"/>
-    </row>
-    <row r="75" spans="2:74">
-      <c r="B75" s="7"/>
-      <c r="C75" t="s">
-        <v>24</v>
-      </c>
-      <c r="V75" s="8"/>
-      <c r="AB75" s="7"/>
-      <c r="AC75" t="s">
-        <v>30</v>
-      </c>
-      <c r="BV75" s="8"/>
-    </row>
-    <row r="76" spans="2:74">
-      <c r="B76" s="7"/>
-      <c r="D76" t="s">
-        <v>25</v>
-      </c>
-      <c r="V76" s="8"/>
-      <c r="AB76" s="7"/>
-      <c r="AC76" t="s">
-        <v>31</v>
-      </c>
-      <c r="BV76" s="8"/>
-    </row>
-    <row r="77" spans="2:74">
-      <c r="B77" s="7"/>
-      <c r="C77" t="s">
-        <v>26</v>
-      </c>
-      <c r="V77" s="8"/>
-      <c r="AB77" s="7"/>
-      <c r="BV77" s="8"/>
-    </row>
-    <row r="78" spans="2:74">
-      <c r="B78" s="7"/>
-      <c r="D78" t="s">
-        <v>27</v>
-      </c>
-      <c r="V78" s="8"/>
-      <c r="AB78" s="7"/>
-      <c r="BV78" s="8"/>
-    </row>
-    <row r="79" spans="2:74">
-      <c r="B79" s="9"/>
-      <c r="C79" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D79" s="10"/>
-      <c r="E79" s="10"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="10"/>
-      <c r="H79" s="10"/>
-      <c r="I79" s="10"/>
-      <c r="J79" s="10"/>
-      <c r="K79" s="10"/>
-      <c r="L79" s="10"/>
-      <c r="M79" s="10"/>
-      <c r="N79" s="10"/>
-      <c r="O79" s="10"/>
-      <c r="P79" s="10"/>
-      <c r="Q79" s="10"/>
-      <c r="R79" s="10"/>
-      <c r="S79" s="10"/>
-      <c r="T79" s="10"/>
-      <c r="U79" s="10"/>
-      <c r="V79" s="11"/>
-      <c r="AB79" s="9"/>
-      <c r="AC79" s="10"/>
-      <c r="AD79" s="10"/>
-      <c r="AE79" s="10"/>
-      <c r="AF79" s="10"/>
-      <c r="AG79" s="10"/>
-      <c r="AH79" s="10"/>
-      <c r="AI79" s="10"/>
-      <c r="AJ79" s="10"/>
-      <c r="AK79" s="10"/>
-      <c r="AL79" s="10"/>
-      <c r="AM79" s="10"/>
-      <c r="AN79" s="10"/>
-      <c r="AO79" s="10"/>
-      <c r="AP79" s="10"/>
-      <c r="AQ79" s="10"/>
-      <c r="AR79" s="10"/>
-      <c r="AS79" s="10"/>
-      <c r="AT79" s="10"/>
-      <c r="AU79" s="10"/>
-      <c r="AV79" s="10"/>
-      <c r="AW79" s="10"/>
-      <c r="AX79" s="10"/>
-      <c r="AY79" s="10"/>
-      <c r="AZ79" s="10"/>
-      <c r="BA79" s="10"/>
-      <c r="BB79" s="10"/>
-      <c r="BC79" s="10"/>
-      <c r="BD79" s="10"/>
-      <c r="BE79" s="10"/>
-      <c r="BF79" s="10"/>
-      <c r="BG79" s="10"/>
-      <c r="BH79" s="10"/>
-      <c r="BI79" s="10"/>
-      <c r="BJ79" s="10"/>
-      <c r="BK79" s="10"/>
-      <c r="BL79" s="10"/>
-      <c r="BM79" s="10"/>
-      <c r="BN79" s="10"/>
-      <c r="BO79" s="10"/>
-      <c r="BP79" s="10"/>
-      <c r="BQ79" s="10"/>
-      <c r="BR79" s="10"/>
-      <c r="BS79" s="10"/>
-      <c r="BT79" s="10"/>
-      <c r="BU79" s="10"/>
-      <c r="BV79" s="11"/>
-    </row>
-    <row r="81" spans="2:34">
-      <c r="B81" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C81" s="5"/>
-      <c r="D81" s="5"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="5"/>
-      <c r="G81" s="5"/>
-      <c r="H81" s="5"/>
-      <c r="I81" s="5"/>
-      <c r="J81" s="5"/>
-      <c r="K81" s="5"/>
-      <c r="L81" s="5"/>
-      <c r="M81" s="5"/>
-      <c r="N81" s="5"/>
-      <c r="O81" s="5"/>
-      <c r="P81" s="5"/>
-      <c r="Q81" s="5"/>
-      <c r="R81" s="5"/>
-      <c r="S81" s="5"/>
-      <c r="T81" s="5"/>
-      <c r="U81" s="5"/>
-      <c r="V81" s="5"/>
-      <c r="W81" s="6"/>
-      <c r="AB81" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC81" s="13"/>
-      <c r="AD81" s="13"/>
-      <c r="AE81" s="13"/>
-      <c r="AF81" s="13"/>
-      <c r="AG81" s="13"/>
-      <c r="AH81" s="14"/>
-    </row>
-    <row r="82" spans="2:34">
-      <c r="B82" s="7"/>
-      <c r="C82" t="s">
-        <v>33</v>
-      </c>
-      <c r="W82" s="8"/>
-    </row>
-    <row r="83" spans="2:34">
-      <c r="B83" s="7"/>
-      <c r="C83" t="s">
-        <v>34</v>
-      </c>
-      <c r="W83" s="8"/>
-      <c r="AB83" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="AC83" s="13"/>
-      <c r="AD83" s="13"/>
-      <c r="AE83" s="14"/>
-      <c r="AG83" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="84" spans="2:34">
-      <c r="B84" s="7"/>
-      <c r="C84" t="s">
-        <v>35</v>
-      </c>
-      <c r="W84" s="8"/>
-      <c r="AC84" s="15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="85" spans="2:34">
-      <c r="B85" s="7"/>
-      <c r="W85" s="8"/>
-    </row>
-    <row r="86" spans="2:34">
-      <c r="B86" s="9"/>
-      <c r="C86" s="10"/>
-      <c r="D86" s="10"/>
-      <c r="E86" s="10"/>
-      <c r="F86" s="10"/>
-      <c r="G86" s="10"/>
-      <c r="H86" s="10"/>
-      <c r="I86" s="10"/>
-      <c r="J86" s="10"/>
-      <c r="K86" s="10"/>
-      <c r="L86" s="10"/>
-      <c r="M86" s="10"/>
-      <c r="N86" s="10"/>
-      <c r="O86" s="10"/>
-      <c r="P86" s="10"/>
-      <c r="Q86" s="10"/>
-      <c r="R86" s="10"/>
-      <c r="S86" s="10"/>
-      <c r="T86" s="10"/>
-      <c r="U86" s="10"/>
-      <c r="V86" s="10"/>
-      <c r="W86" s="11"/>
-    </row>
-    <row r="110" spans="2:3">
-      <c r="B110" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="111" spans="2:3">
-      <c r="B111" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="112" spans="2:3">
-      <c r="C112" t="s">
-        <v>55</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:BZ64"/>
-  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="13.8"/>
   <sheetData>
     <row r="1" spans="1:57">
       <c r="B1" t="s">
-        <v>63</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:57">
       <c r="B3" t="s">
-        <v>66</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:57">
-      <c r="C4" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="17"/>
-      <c r="U4" s="17"/>
-      <c r="V4" s="17"/>
-      <c r="W4" s="17"/>
-      <c r="X4" s="17"/>
+      <c r="C4" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="14"/>
+      <c r="W4" s="14"/>
+      <c r="X4" s="14"/>
     </row>
     <row r="5" spans="1:57">
-      <c r="C5" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="19"/>
-      <c r="S5" s="19"/>
-      <c r="T5" s="19"/>
-      <c r="U5" s="19"/>
-      <c r="V5" s="19"/>
-      <c r="W5" s="19"/>
-      <c r="X5" s="19"/>
+      <c r="C5" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="16"/>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
     </row>
     <row r="6" spans="1:57">
       <c r="B6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:57" ht="15" thickBot="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:57" ht="14.4" thickBot="1">
       <c r="B7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:57" s="30" customFormat="1" ht="15" thickBot="1">
-      <c r="A8" s="29"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-    </row>
-    <row r="9" spans="1:57" ht="15" thickBot="1"/>
-    <row r="10" spans="1:57" ht="15" thickBot="1">
-      <c r="B10" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="34"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:57" s="27" customFormat="1" ht="14.4" thickBot="1">
+      <c r="A8" s="26"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+    </row>
+    <row r="9" spans="1:57" ht="14.4" thickBot="1"/>
+    <row r="10" spans="1:57" ht="14.4" thickBot="1">
+      <c r="B10" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="31"/>
     </row>
     <row r="11" spans="1:57">
       <c r="C11" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:57">
       <c r="C12" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:57">
       <c r="C13" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:57">
       <c r="C14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:57" ht="15">
-      <c r="D16" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="37"/>
-      <c r="L16" s="37"/>
-      <c r="M16" s="37"/>
-      <c r="N16" s="37"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="37"/>
-      <c r="R16" s="37"/>
-      <c r="S16" s="37"/>
-      <c r="T16" s="37"/>
-      <c r="U16" s="37"/>
-      <c r="V16" s="37"/>
-      <c r="W16" s="37"/>
-      <c r="X16" s="37"/>
-      <c r="Y16" s="37"/>
-      <c r="Z16" s="37"/>
-      <c r="AA16" s="37"/>
-      <c r="AB16" s="37"/>
-      <c r="AC16" s="37"/>
-      <c r="AD16" s="37"/>
-      <c r="AE16" s="37"/>
-      <c r="AF16" s="37"/>
-      <c r="AG16" s="37"/>
-      <c r="AH16" s="37"/>
-      <c r="AI16" s="37"/>
-      <c r="AJ16" s="37"/>
-      <c r="AK16" s="37"/>
-      <c r="AL16" s="37"/>
-      <c r="AM16" s="37"/>
-      <c r="AN16" s="37"/>
-      <c r="AO16" s="37"/>
-      <c r="AP16" s="37"/>
-      <c r="AQ16" s="37"/>
-      <c r="AR16" s="37"/>
-      <c r="AS16" s="37"/>
-      <c r="AT16" s="37"/>
-      <c r="AU16" s="37"/>
-      <c r="AV16" s="37"/>
-      <c r="AW16" s="37"/>
-      <c r="AX16" s="37"/>
-      <c r="AY16" s="37"/>
-      <c r="AZ16" s="37"/>
-      <c r="BA16" s="37"/>
-      <c r="BB16" s="37"/>
-      <c r="BC16" s="37"/>
-      <c r="BD16" s="37"/>
-      <c r="BE16" s="38"/>
-    </row>
-    <row r="17" spans="1:53" ht="15" thickBot="1"/>
-    <row r="18" spans="1:53" s="30" customFormat="1" ht="15" thickBot="1">
-      <c r="A18" s="29"/>
-    </row>
-    <row r="19" spans="1:53" ht="16.5">
-      <c r="C19" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-    </row>
-    <row r="20" spans="1:53" ht="21">
-      <c r="C20" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-    </row>
-    <row r="21" spans="1:53" ht="16.5">
-      <c r="H21" s="23" t="s">
-        <v>70</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:57">
+      <c r="D16" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
+      <c r="P16" s="34"/>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="34"/>
+      <c r="S16" s="34"/>
+      <c r="T16" s="34"/>
+      <c r="U16" s="34"/>
+      <c r="V16" s="34"/>
+      <c r="W16" s="34"/>
+      <c r="X16" s="34"/>
+      <c r="Y16" s="34"/>
+      <c r="Z16" s="34"/>
+      <c r="AA16" s="34"/>
+      <c r="AB16" s="34"/>
+      <c r="AC16" s="34"/>
+      <c r="AD16" s="34"/>
+      <c r="AE16" s="34"/>
+      <c r="AF16" s="34"/>
+      <c r="AG16" s="34"/>
+      <c r="AH16" s="34"/>
+      <c r="AI16" s="34"/>
+      <c r="AJ16" s="34"/>
+      <c r="AK16" s="34"/>
+      <c r="AL16" s="34"/>
+      <c r="AM16" s="34"/>
+      <c r="AN16" s="34"/>
+      <c r="AO16" s="34"/>
+      <c r="AP16" s="34"/>
+      <c r="AQ16" s="34"/>
+      <c r="AR16" s="34"/>
+      <c r="AS16" s="34"/>
+      <c r="AT16" s="34"/>
+      <c r="AU16" s="34"/>
+      <c r="AV16" s="34"/>
+      <c r="AW16" s="34"/>
+      <c r="AX16" s="34"/>
+      <c r="AY16" s="34"/>
+      <c r="AZ16" s="34"/>
+      <c r="BA16" s="34"/>
+      <c r="BB16" s="34"/>
+      <c r="BC16" s="34"/>
+      <c r="BD16" s="34"/>
+      <c r="BE16" s="35"/>
+    </row>
+    <row r="17" spans="1:53" ht="14.4" thickBot="1"/>
+    <row r="18" spans="1:53" s="27" customFormat="1" ht="14.4" thickBot="1">
+      <c r="A18" s="26"/>
+    </row>
+    <row r="19" spans="1:53" ht="16.8">
+      <c r="C19" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+    </row>
+    <row r="20" spans="1:53" ht="20.399999999999999">
+      <c r="C20" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+    </row>
+    <row r="21" spans="1:53" ht="16.8">
+      <c r="H21" s="20" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:53">
-      <c r="H22" s="24" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:53" ht="16.5">
-      <c r="H23" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="AM23" s="35" t="s">
-        <v>88</v>
-      </c>
-      <c r="AN23" s="28"/>
-      <c r="AO23" s="28"/>
-      <c r="AP23" s="28"/>
-      <c r="AQ23" s="28"/>
-      <c r="AR23" s="28"/>
-      <c r="AS23" s="28"/>
-      <c r="AT23" s="28"/>
-      <c r="AU23" s="28"/>
-      <c r="AV23" s="28"/>
-      <c r="AW23" s="28"/>
-      <c r="AX23" s="28"/>
-      <c r="AY23" s="28"/>
-      <c r="AZ23" s="28"/>
-      <c r="BA23" s="28"/>
+      <c r="H22" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:53" ht="16.8">
+      <c r="H23" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM23" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN23" s="25"/>
+      <c r="AO23" s="25"/>
+      <c r="AP23" s="25"/>
+      <c r="AQ23" s="25"/>
+      <c r="AR23" s="25"/>
+      <c r="AS23" s="25"/>
+      <c r="AT23" s="25"/>
+      <c r="AU23" s="25"/>
+      <c r="AV23" s="25"/>
+      <c r="AW23" s="25"/>
+      <c r="AX23" s="25"/>
+      <c r="AY23" s="25"/>
+      <c r="AZ23" s="25"/>
+      <c r="BA23" s="25"/>
     </row>
     <row r="24" spans="1:53">
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-    </row>
-    <row r="25" spans="1:53" ht="21">
-      <c r="C25" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-    </row>
-    <row r="26" spans="1:53" ht="16.5">
-      <c r="C26" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-    </row>
-    <row r="27" spans="1:53" ht="16.5">
-      <c r="C27" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-    </row>
-    <row r="28" spans="1:53" ht="16.5">
-      <c r="C28" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-    </row>
-    <row r="29" spans="1:53" ht="16.5">
-      <c r="C29" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-    </row>
-    <row r="30" spans="1:53" ht="16.5">
-      <c r="C30" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-    </row>
-    <row r="31" spans="1:53" ht="16.5">
-      <c r="C31" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+    </row>
+    <row r="25" spans="1:53" ht="20.399999999999999">
+      <c r="C25" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+    </row>
+    <row r="26" spans="1:53" ht="16.8">
+      <c r="C26" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+    </row>
+    <row r="27" spans="1:53" ht="16.8">
+      <c r="C27" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+    </row>
+    <row r="28" spans="1:53" ht="16.8">
+      <c r="C28" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+    </row>
+    <row r="29" spans="1:53" ht="16.8">
+      <c r="C29" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+    </row>
+    <row r="30" spans="1:53" ht="16.8">
+      <c r="C30" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+    </row>
+    <row r="31" spans="1:53" ht="16.8">
+      <c r="C31" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
     </row>
     <row r="32" spans="1:53">
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-    </row>
-    <row r="33" spans="2:64" ht="21">
-      <c r="C33" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-    </row>
-    <row r="34" spans="2:64" ht="16.5">
-      <c r="C34" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+    </row>
+    <row r="33" spans="2:64" ht="20.399999999999999">
+      <c r="C33" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+    </row>
+    <row r="34" spans="2:64" ht="16.8">
+      <c r="C34" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
     </row>
     <row r="36" spans="2:64">
       <c r="N36" s="82" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="O36" s="83"/>
       <c r="P36" s="83"/>
@@ -7836,7 +6575,7 @@
       <c r="V36" s="83"/>
       <c r="W36" s="84"/>
       <c r="Z36" s="82" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="AA36" s="83"/>
       <c r="AB36" s="83"/>
@@ -7846,7 +6585,7 @@
       <c r="AF36" s="83"/>
       <c r="AG36" s="84"/>
       <c r="AO36" s="82" t="s">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="AP36" s="83"/>
       <c r="AQ36" s="83"/>
@@ -7861,7 +6600,7 @@
       <c r="AZ36" s="83"/>
       <c r="BA36" s="84"/>
       <c r="BG36" s="82" t="s">
-        <v>109</v>
+        <v>52</v>
       </c>
       <c r="BH36" s="83"/>
       <c r="BI36" s="83"/>
@@ -7870,280 +6609,280 @@
       <c r="BL36" s="84"/>
     </row>
     <row r="37" spans="2:64">
-      <c r="R37" s="8"/>
-      <c r="AC37" s="8"/>
-      <c r="AT37" s="8"/>
-      <c r="BI37" s="6"/>
+      <c r="R37" s="6"/>
+      <c r="AC37" s="6"/>
+      <c r="AT37" s="6"/>
+      <c r="BI37" s="4"/>
     </row>
     <row r="38" spans="2:64">
-      <c r="B38" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="C38" s="37"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="37"/>
-      <c r="H38" s="38"/>
+      <c r="B38" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" s="34"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="34"/>
+      <c r="G38" s="34"/>
+      <c r="H38" s="35"/>
       <c r="J38" t="s">
-        <v>91</v>
-      </c>
-      <c r="R38" s="8"/>
-      <c r="AC38" s="8"/>
-      <c r="AT38" s="8"/>
-      <c r="BI38" s="8"/>
+        <v>34</v>
+      </c>
+      <c r="R38" s="6"/>
+      <c r="AC38" s="6"/>
+      <c r="AT38" s="6"/>
+      <c r="BI38" s="6"/>
     </row>
     <row r="39" spans="2:64">
       <c r="J39" t="s">
-        <v>90</v>
-      </c>
-      <c r="R39" s="8"/>
+        <v>33</v>
+      </c>
+      <c r="R39" s="6"/>
       <c r="S39" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC39" s="8"/>
-      <c r="AT39" s="8"/>
-      <c r="BI39" s="8"/>
+        <v>35</v>
+      </c>
+      <c r="AC39" s="6"/>
+      <c r="AT39" s="6"/>
+      <c r="BI39" s="6"/>
     </row>
     <row r="40" spans="2:64">
-      <c r="R40" s="8"/>
+      <c r="R40" s="6"/>
       <c r="S40" t="s">
-        <v>95</v>
-      </c>
-      <c r="AC40" s="8"/>
-      <c r="AT40" s="8"/>
-      <c r="BI40" s="8"/>
+        <v>38</v>
+      </c>
+      <c r="AC40" s="6"/>
+      <c r="AT40" s="6"/>
+      <c r="BI40" s="6"/>
     </row>
     <row r="41" spans="2:64">
-      <c r="R41" s="8"/>
+      <c r="R41" s="6"/>
       <c r="S41" t="s">
-        <v>93</v>
-      </c>
-      <c r="AC41" s="8"/>
-      <c r="AT41" s="8"/>
-      <c r="BI41" s="8"/>
+        <v>36</v>
+      </c>
+      <c r="AC41" s="6"/>
+      <c r="AT41" s="6"/>
+      <c r="BI41" s="6"/>
     </row>
     <row r="42" spans="2:64">
-      <c r="R42" s="8"/>
+      <c r="R42" s="6"/>
       <c r="T42" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC42" s="8"/>
+        <v>37</v>
+      </c>
+      <c r="AC42" s="6"/>
       <c r="AD42" t="s">
-        <v>97</v>
-      </c>
-      <c r="AT42" s="8"/>
-      <c r="BI42" s="8"/>
+        <v>40</v>
+      </c>
+      <c r="AT42" s="6"/>
+      <c r="BI42" s="6"/>
     </row>
     <row r="43" spans="2:64">
-      <c r="R43" s="8"/>
-      <c r="AC43" s="8"/>
-      <c r="AD43" s="12"/>
-      <c r="AE43" s="13"/>
-      <c r="AF43" s="13"/>
-      <c r="AG43" s="14"/>
-      <c r="AT43" s="8"/>
-      <c r="BI43" s="8"/>
+      <c r="R43" s="6"/>
+      <c r="AC43" s="6"/>
+      <c r="AD43" s="10"/>
+      <c r="AE43" s="11"/>
+      <c r="AF43" s="11"/>
+      <c r="AG43" s="12"/>
+      <c r="AT43" s="6"/>
+      <c r="BI43" s="6"/>
     </row>
     <row r="44" spans="2:64">
-      <c r="R44" s="8"/>
-      <c r="AC44" s="8"/>
-      <c r="AE44" s="6"/>
-      <c r="AT44" s="8"/>
-      <c r="BI44" s="8"/>
+      <c r="R44" s="6"/>
+      <c r="AC44" s="6"/>
+      <c r="AE44" s="4"/>
+      <c r="AT44" s="6"/>
+      <c r="BI44" s="6"/>
     </row>
     <row r="45" spans="2:64">
-      <c r="R45" s="8"/>
-      <c r="AC45" s="8"/>
+      <c r="R45" s="6"/>
+      <c r="AC45" s="6"/>
       <c r="AE45" t="s">
-        <v>98</v>
-      </c>
-      <c r="AT45" s="8"/>
-      <c r="BI45" s="8"/>
+        <v>41</v>
+      </c>
+      <c r="AT45" s="6"/>
+      <c r="BI45" s="6"/>
     </row>
     <row r="46" spans="2:64">
-      <c r="R46" s="8"/>
-      <c r="AC46" s="8"/>
+      <c r="R46" s="6"/>
+      <c r="AC46" s="6"/>
       <c r="AE46" t="s">
-        <v>99</v>
-      </c>
-      <c r="AT46" s="8"/>
-      <c r="BI46" s="8"/>
+        <v>42</v>
+      </c>
+      <c r="AT46" s="6"/>
+      <c r="BI46" s="6"/>
     </row>
     <row r="47" spans="2:64">
-      <c r="R47" s="8"/>
-      <c r="AC47" s="8"/>
+      <c r="R47" s="6"/>
+      <c r="AC47" s="6"/>
       <c r="AE47" t="s">
-        <v>100</v>
-      </c>
-      <c r="AT47" s="8"/>
+        <v>43</v>
+      </c>
+      <c r="AT47" s="6"/>
       <c r="AU47" t="s">
-        <v>102</v>
-      </c>
-      <c r="BI47" s="8"/>
+        <v>45</v>
+      </c>
+      <c r="BI47" s="6"/>
     </row>
     <row r="48" spans="2:64">
-      <c r="R48" s="8"/>
-      <c r="AC48" s="8"/>
-      <c r="AE48" s="8"/>
-      <c r="AT48" s="8"/>
-      <c r="AU48" s="12"/>
-      <c r="AV48" s="13"/>
-      <c r="AW48" s="13"/>
-      <c r="AX48" s="14"/>
-      <c r="BI48" s="8"/>
+      <c r="R48" s="6"/>
+      <c r="AC48" s="6"/>
+      <c r="AE48" s="6"/>
+      <c r="AT48" s="6"/>
+      <c r="AU48" s="10"/>
+      <c r="AV48" s="11"/>
+      <c r="AW48" s="11"/>
+      <c r="AX48" s="12"/>
+      <c r="BI48" s="6"/>
     </row>
     <row r="49" spans="18:78">
-      <c r="R49" s="8"/>
-      <c r="AC49" s="8"/>
-      <c r="AE49" s="8"/>
-      <c r="AT49" s="8"/>
-      <c r="AU49" s="4"/>
-      <c r="AV49" s="6"/>
-      <c r="BI49" s="8"/>
+      <c r="R49" s="6"/>
+      <c r="AC49" s="6"/>
+      <c r="AE49" s="6"/>
+      <c r="AT49" s="6"/>
+      <c r="AU49" s="2"/>
+      <c r="AV49" s="4"/>
+      <c r="BI49" s="6"/>
     </row>
     <row r="50" spans="18:78">
-      <c r="R50" s="8"/>
-      <c r="AC50" s="8"/>
+      <c r="R50" s="6"/>
+      <c r="AC50" s="6"/>
       <c r="AE50" t="s">
-        <v>103</v>
-      </c>
-      <c r="AT50" s="8"/>
-      <c r="AV50" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="BI50" s="8"/>
+        <v>46</v>
+      </c>
+      <c r="AT50" s="6"/>
+      <c r="AV50" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="BI50" s="6"/>
     </row>
     <row r="51" spans="18:78">
-      <c r="R51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AE51" s="8"/>
-      <c r="AT51" s="8"/>
-      <c r="AV51" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="BI51" s="8"/>
+      <c r="R51" s="6"/>
+      <c r="AC51" s="6"/>
+      <c r="AE51" s="6"/>
+      <c r="AT51" s="6"/>
+      <c r="AV51" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="BI51" s="6"/>
     </row>
     <row r="52" spans="18:78">
-      <c r="R52" s="8"/>
-      <c r="AC52" s="8"/>
-      <c r="AE52" s="8"/>
-      <c r="AT52" s="8"/>
-      <c r="AV52" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="BI52" s="8"/>
+      <c r="R52" s="6"/>
+      <c r="AC52" s="6"/>
+      <c r="AE52" s="6"/>
+      <c r="AT52" s="6"/>
+      <c r="AV52" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI52" s="6"/>
     </row>
     <row r="53" spans="18:78">
-      <c r="R53" s="8"/>
-      <c r="AC53" s="8"/>
-      <c r="AE53" s="8"/>
-      <c r="AT53" s="8"/>
+      <c r="R53" s="6"/>
+      <c r="AC53" s="6"/>
+      <c r="AE53" s="6"/>
+      <c r="AT53" s="6"/>
       <c r="AV53" t="s">
-        <v>108</v>
-      </c>
-      <c r="BI53" s="8"/>
+        <v>51</v>
+      </c>
+      <c r="BI53" s="6"/>
     </row>
     <row r="54" spans="18:78">
-      <c r="R54" s="8"/>
-      <c r="AC54" s="8"/>
-      <c r="AE54" s="8"/>
-      <c r="AT54" s="8"/>
-      <c r="AU54" s="9"/>
-      <c r="AV54" s="11"/>
-      <c r="BI54" s="8"/>
+      <c r="R54" s="6"/>
+      <c r="AC54" s="6"/>
+      <c r="AE54" s="6"/>
+      <c r="AT54" s="6"/>
+      <c r="AU54" s="7"/>
+      <c r="AV54" s="9"/>
+      <c r="BI54" s="6"/>
     </row>
     <row r="55" spans="18:78">
-      <c r="R55" s="8"/>
-      <c r="AC55" s="8"/>
-      <c r="AE55" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="AT55" s="8"/>
+      <c r="R55" s="6"/>
+      <c r="AC55" s="6"/>
+      <c r="AE55" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT55" s="6"/>
       <c r="BG55" t="s">
-        <v>110</v>
-      </c>
-      <c r="BI55" s="8"/>
+        <v>53</v>
+      </c>
+      <c r="BI55" s="6"/>
     </row>
     <row r="56" spans="18:78">
-      <c r="R56" s="8"/>
-      <c r="AC56" s="8"/>
-      <c r="AE56" s="8"/>
-      <c r="AT56" s="8"/>
-      <c r="BI56" s="8"/>
-      <c r="BJ56" s="12"/>
-      <c r="BK56" s="13"/>
-      <c r="BL56" s="13"/>
-      <c r="BM56" s="14"/>
+      <c r="R56" s="6"/>
+      <c r="AC56" s="6"/>
+      <c r="AE56" s="6"/>
+      <c r="AT56" s="6"/>
+      <c r="BI56" s="6"/>
+      <c r="BJ56" s="10"/>
+      <c r="BK56" s="11"/>
+      <c r="BL56" s="11"/>
+      <c r="BM56" s="12"/>
     </row>
     <row r="57" spans="18:78">
-      <c r="R57" s="8"/>
-      <c r="AC57" s="8"/>
-      <c r="AT57" s="8"/>
-      <c r="BI57" s="8"/>
-      <c r="BJ57" s="4"/>
-      <c r="BK57" s="6"/>
+      <c r="R57" s="6"/>
+      <c r="AC57" s="6"/>
+      <c r="AT57" s="6"/>
+      <c r="BI57" s="6"/>
+      <c r="BJ57" s="2"/>
+      <c r="BK57" s="4"/>
     </row>
     <row r="58" spans="18:78">
-      <c r="R58" s="8"/>
-      <c r="AC58" s="8"/>
-      <c r="AT58" s="8"/>
-      <c r="BI58" s="8"/>
-      <c r="BJ58" s="7"/>
+      <c r="R58" s="6"/>
+      <c r="AC58" s="6"/>
+      <c r="AT58" s="6"/>
+      <c r="BI58" s="6"/>
+      <c r="BJ58" s="5"/>
       <c r="BK58" t="s">
-        <v>112</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="18:78">
-      <c r="R59" s="8"/>
-      <c r="AC59" s="8"/>
-      <c r="AT59" s="8"/>
-      <c r="BI59" s="8"/>
-      <c r="BJ59" s="7"/>
-      <c r="BK59" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="BT59" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="BU59" s="37"/>
-      <c r="BV59" s="37"/>
-      <c r="BW59" s="37"/>
-      <c r="BX59" s="37"/>
-      <c r="BY59" s="37"/>
-      <c r="BZ59" s="38"/>
+      <c r="R59" s="6"/>
+      <c r="AC59" s="6"/>
+      <c r="AT59" s="6"/>
+      <c r="BI59" s="6"/>
+      <c r="BJ59" s="5"/>
+      <c r="BK59" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="BT59" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="BU59" s="34"/>
+      <c r="BV59" s="34"/>
+      <c r="BW59" s="34"/>
+      <c r="BX59" s="34"/>
+      <c r="BY59" s="34"/>
+      <c r="BZ59" s="35"/>
     </row>
     <row r="60" spans="18:78">
-      <c r="R60" s="8"/>
-      <c r="AC60" s="8"/>
-      <c r="AT60" s="8"/>
-      <c r="BI60" s="8"/>
-      <c r="BJ60" s="9"/>
-      <c r="BK60" s="11"/>
+      <c r="R60" s="6"/>
+      <c r="AC60" s="6"/>
+      <c r="AT60" s="6"/>
+      <c r="BI60" s="6"/>
+      <c r="BJ60" s="7"/>
+      <c r="BK60" s="9"/>
     </row>
     <row r="61" spans="18:78">
-      <c r="R61" s="8"/>
-      <c r="AC61" s="8"/>
-      <c r="AT61" s="8"/>
-      <c r="BI61" s="8"/>
+      <c r="R61" s="6"/>
+      <c r="AC61" s="6"/>
+      <c r="AT61" s="6"/>
+      <c r="BI61" s="6"/>
     </row>
     <row r="62" spans="18:78">
-      <c r="R62" s="8"/>
-      <c r="AC62" s="8"/>
-      <c r="AT62" s="8"/>
-      <c r="BI62" s="8"/>
+      <c r="R62" s="6"/>
+      <c r="AC62" s="6"/>
+      <c r="AT62" s="6"/>
+      <c r="BI62" s="6"/>
     </row>
     <row r="63" spans="18:78">
-      <c r="R63" s="8"/>
-      <c r="AC63" s="8"/>
-      <c r="AT63" s="8"/>
-      <c r="BI63" s="8"/>
+      <c r="R63" s="6"/>
+      <c r="AC63" s="6"/>
+      <c r="AT63" s="6"/>
+      <c r="BI63" s="6"/>
     </row>
     <row r="64" spans="18:78">
-      <c r="R64" s="8"/>
-      <c r="AC64" s="8"/>
-      <c r="AT64" s="8"/>
-      <c r="BI64" s="8"/>
+      <c r="R64" s="6"/>
+      <c r="AC64" s="6"/>
+      <c r="AT64" s="6"/>
+      <c r="BI64" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -8158,103 +6897,103 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:CJ81"/>
-  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="13.8"/>
   <sheetData>
-    <row r="1" spans="1:83" ht="15" thickBot="1"/>
-    <row r="2" spans="1:83" ht="15" thickBot="1">
-      <c r="B2" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="34"/>
+    <row r="1" spans="1:83" ht="14.4" thickBot="1"/>
+    <row r="2" spans="1:83" ht="14.4" thickBot="1">
+      <c r="B2" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
     </row>
     <row r="3" spans="1:83">
       <c r="C3" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:83">
       <c r="C4" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:83">
       <c r="C5" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:83">
       <c r="C6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:83" ht="15">
-      <c r="D8" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="37"/>
-      <c r="S8" s="37"/>
-      <c r="T8" s="37"/>
-      <c r="U8" s="37"/>
-      <c r="V8" s="37"/>
-      <c r="W8" s="37"/>
-      <c r="X8" s="37"/>
-      <c r="Y8" s="37"/>
-      <c r="Z8" s="37"/>
-      <c r="AA8" s="37"/>
-      <c r="AB8" s="37"/>
-      <c r="AC8" s="37"/>
-      <c r="AD8" s="37"/>
-      <c r="AE8" s="37"/>
-      <c r="AF8" s="37"/>
-      <c r="AG8" s="37"/>
-      <c r="AH8" s="37"/>
-      <c r="AI8" s="37"/>
-      <c r="AJ8" s="37"/>
-      <c r="AK8" s="37"/>
-      <c r="AL8" s="37"/>
-      <c r="AM8" s="37"/>
-      <c r="AN8" s="37"/>
-      <c r="AO8" s="37"/>
-      <c r="AP8" s="37"/>
-      <c r="AQ8" s="37"/>
-      <c r="AR8" s="37"/>
-      <c r="AS8" s="37"/>
-      <c r="AT8" s="37"/>
-      <c r="AU8" s="37"/>
-      <c r="AV8" s="37"/>
-      <c r="AW8" s="37"/>
-      <c r="AX8" s="37"/>
-      <c r="AY8" s="37"/>
-      <c r="AZ8" s="38"/>
-    </row>
-    <row r="9" spans="1:83" ht="15" thickBot="1"/>
-    <row r="10" spans="1:83" s="30" customFormat="1" ht="15" thickBot="1">
-      <c r="A10" s="29"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:83">
+      <c r="D8" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
+      <c r="P8" s="34"/>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="34"/>
+      <c r="S8" s="34"/>
+      <c r="T8" s="34"/>
+      <c r="U8" s="34"/>
+      <c r="V8" s="34"/>
+      <c r="W8" s="34"/>
+      <c r="X8" s="34"/>
+      <c r="Y8" s="34"/>
+      <c r="Z8" s="34"/>
+      <c r="AA8" s="34"/>
+      <c r="AB8" s="34"/>
+      <c r="AC8" s="34"/>
+      <c r="AD8" s="34"/>
+      <c r="AE8" s="34"/>
+      <c r="AF8" s="34"/>
+      <c r="AG8" s="34"/>
+      <c r="AH8" s="34"/>
+      <c r="AI8" s="34"/>
+      <c r="AJ8" s="34"/>
+      <c r="AK8" s="34"/>
+      <c r="AL8" s="34"/>
+      <c r="AM8" s="34"/>
+      <c r="AN8" s="34"/>
+      <c r="AO8" s="34"/>
+      <c r="AP8" s="34"/>
+      <c r="AQ8" s="34"/>
+      <c r="AR8" s="34"/>
+      <c r="AS8" s="34"/>
+      <c r="AT8" s="34"/>
+      <c r="AU8" s="34"/>
+      <c r="AV8" s="34"/>
+      <c r="AW8" s="34"/>
+      <c r="AX8" s="34"/>
+      <c r="AY8" s="34"/>
+      <c r="AZ8" s="35"/>
+    </row>
+    <row r="9" spans="1:83" ht="14.4" thickBot="1"/>
+    <row r="10" spans="1:83" s="27" customFormat="1" ht="14.4" thickBot="1">
+      <c r="A10" s="26"/>
     </row>
     <row r="13" spans="1:83">
       <c r="K13" s="82" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="L13" s="83"/>
       <c r="M13" s="83"/>
@@ -8266,7 +7005,7 @@
       <c r="S13" s="83"/>
       <c r="T13" s="84"/>
       <c r="W13" s="82" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="X13" s="83"/>
       <c r="Y13" s="83"/>
@@ -8275,9 +7014,9 @@
       <c r="AB13" s="83"/>
       <c r="AC13" s="83"/>
       <c r="AD13" s="84"/>
-      <c r="AJ13" s="8"/>
+      <c r="AJ13" s="6"/>
       <c r="AK13" s="82" t="s">
-        <v>116</v>
+        <v>59</v>
       </c>
       <c r="AL13" s="83"/>
       <c r="AM13" s="83"/>
@@ -8285,7 +7024,7 @@
       <c r="AO13" s="83"/>
       <c r="AP13" s="84"/>
       <c r="AW13" s="82" t="s">
-        <v>121</v>
+        <v>64</v>
       </c>
       <c r="AX13" s="83"/>
       <c r="AY13" s="83"/>
@@ -8293,7 +7032,7 @@
       <c r="BA13" s="83"/>
       <c r="BB13" s="84"/>
       <c r="BH13" s="82" t="s">
-        <v>124</v>
+        <v>67</v>
       </c>
       <c r="BI13" s="83"/>
       <c r="BJ13" s="83"/>
@@ -8301,7 +7040,7 @@
       <c r="BL13" s="83"/>
       <c r="BM13" s="84"/>
       <c r="BR13" s="82" t="s">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="BS13" s="83"/>
       <c r="BT13" s="83"/>
@@ -8309,7 +7048,7 @@
       <c r="BV13" s="83"/>
       <c r="BW13" s="84"/>
       <c r="BZ13" s="82" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="CA13" s="83"/>
       <c r="CB13" s="83"/>
@@ -8318,1580 +7057,1580 @@
       <c r="CE13" s="84"/>
     </row>
     <row r="14" spans="1:83">
-      <c r="O14" s="8"/>
-      <c r="Z14" s="8"/>
-      <c r="AM14" s="8"/>
-      <c r="AY14" s="6"/>
-      <c r="BJ14" s="6"/>
-      <c r="BT14" s="6"/>
-      <c r="CB14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="Z14" s="6"/>
+      <c r="AM14" s="6"/>
+      <c r="AY14" s="4"/>
+      <c r="BJ14" s="4"/>
+      <c r="BT14" s="4"/>
+      <c r="CB14" s="4"/>
     </row>
     <row r="15" spans="1:83">
-      <c r="B15" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="38"/>
+      <c r="B15" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="35"/>
       <c r="I15" t="s">
-        <v>91</v>
-      </c>
-      <c r="O15" s="8"/>
-      <c r="Z15" s="8"/>
-      <c r="AM15" s="8"/>
-      <c r="AY15" s="8"/>
-      <c r="BJ15" s="8"/>
-      <c r="BT15" s="8"/>
-      <c r="CB15" s="8"/>
+        <v>34</v>
+      </c>
+      <c r="O15" s="6"/>
+      <c r="Z15" s="6"/>
+      <c r="AM15" s="6"/>
+      <c r="AY15" s="6"/>
+      <c r="BJ15" s="6"/>
+      <c r="BT15" s="6"/>
+      <c r="CB15" s="6"/>
     </row>
     <row r="16" spans="1:83">
       <c r="I16" t="s">
-        <v>90</v>
-      </c>
-      <c r="O16" s="8"/>
+        <v>33</v>
+      </c>
+      <c r="O16" s="6"/>
       <c r="P16" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z16" s="8"/>
-      <c r="AM16" s="8"/>
-      <c r="AY16" s="8"/>
-      <c r="BJ16" s="8"/>
-      <c r="BT16" s="8"/>
-      <c r="CB16" s="8"/>
+        <v>35</v>
+      </c>
+      <c r="Z16" s="6"/>
+      <c r="AM16" s="6"/>
+      <c r="AY16" s="6"/>
+      <c r="BJ16" s="6"/>
+      <c r="BT16" s="6"/>
+      <c r="CB16" s="6"/>
     </row>
     <row r="17" spans="15:80">
-      <c r="O17" s="8"/>
+      <c r="O17" s="6"/>
       <c r="P17" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z17" s="8"/>
-      <c r="AM17" s="8"/>
-      <c r="AY17" s="8"/>
-      <c r="BJ17" s="8"/>
-      <c r="BT17" s="8"/>
-      <c r="CB17" s="8"/>
+        <v>38</v>
+      </c>
+      <c r="Z17" s="6"/>
+      <c r="AM17" s="6"/>
+      <c r="AY17" s="6"/>
+      <c r="BJ17" s="6"/>
+      <c r="BT17" s="6"/>
+      <c r="CB17" s="6"/>
     </row>
     <row r="18" spans="15:80">
-      <c r="O18" s="8"/>
+      <c r="O18" s="6"/>
       <c r="P18" t="s">
-        <v>93</v>
-      </c>
-      <c r="Z18" s="8"/>
-      <c r="AM18" s="8"/>
-      <c r="AY18" s="8"/>
-      <c r="BJ18" s="8"/>
-      <c r="BT18" s="8"/>
-      <c r="CB18" s="8"/>
+        <v>36</v>
+      </c>
+      <c r="Z18" s="6"/>
+      <c r="AM18" s="6"/>
+      <c r="AY18" s="6"/>
+      <c r="BJ18" s="6"/>
+      <c r="BT18" s="6"/>
+      <c r="CB18" s="6"/>
     </row>
     <row r="19" spans="15:80">
-      <c r="O19" s="8"/>
+      <c r="O19" s="6"/>
       <c r="Q19" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z19" s="8"/>
+        <v>37</v>
+      </c>
+      <c r="Z19" s="6"/>
       <c r="AA19" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM19" s="6"/>
+      <c r="AY19" s="6"/>
+      <c r="BJ19" s="6"/>
+      <c r="BT19" s="6"/>
+      <c r="CB19" s="6"/>
+    </row>
+    <row r="20" spans="15:80">
+      <c r="O20" s="6"/>
+      <c r="Z20" s="6"/>
+      <c r="AA20" s="10"/>
+      <c r="AB20" s="11"/>
+      <c r="AC20" s="11"/>
+      <c r="AD20" s="12"/>
+      <c r="AM20" s="6"/>
+      <c r="AY20" s="6"/>
+      <c r="BJ20" s="6"/>
+      <c r="BT20" s="6"/>
+      <c r="CB20" s="6"/>
+    </row>
+    <row r="21" spans="15:80">
+      <c r="O21" s="6"/>
+      <c r="Z21" s="6"/>
+      <c r="AB21" s="4"/>
+      <c r="AM21" s="6"/>
+      <c r="AY21" s="6"/>
+      <c r="BJ21" s="6"/>
+      <c r="BT21" s="6"/>
+      <c r="CB21" s="6"/>
+    </row>
+    <row r="22" spans="15:80">
+      <c r="O22" s="6"/>
+      <c r="Z22" s="6"/>
+      <c r="AB22" t="s">
+        <v>41</v>
+      </c>
+      <c r="AM22" s="6"/>
+      <c r="AY22" s="6"/>
+      <c r="BJ22" s="6"/>
+      <c r="BT22" s="6"/>
+      <c r="CB22" s="6"/>
+    </row>
+    <row r="23" spans="15:80">
+      <c r="O23" s="6"/>
+      <c r="Z23" s="6"/>
+      <c r="AB23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM23" s="6"/>
+      <c r="AY23" s="6"/>
+      <c r="BJ23" s="6"/>
+      <c r="BT23" s="6"/>
+      <c r="CB23" s="6"/>
+    </row>
+    <row r="24" spans="15:80">
+      <c r="O24" s="6"/>
+      <c r="Z24" s="6"/>
+      <c r="AB24" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM24" s="6"/>
+      <c r="AN24" t="s">
+        <v>60</v>
+      </c>
+      <c r="AY24" s="6"/>
+      <c r="BJ24" s="6"/>
+      <c r="BT24" s="6"/>
+      <c r="CB24" s="6"/>
+    </row>
+    <row r="25" spans="15:80">
+      <c r="O25" s="6"/>
+      <c r="Z25" s="6"/>
+      <c r="AB25" s="6"/>
+      <c r="AM25" s="6"/>
+      <c r="AN25" s="10"/>
+      <c r="AO25" s="11"/>
+      <c r="AP25" s="11"/>
+      <c r="AQ25" s="12"/>
+      <c r="AY25" s="6"/>
+      <c r="BJ25" s="6"/>
+      <c r="BT25" s="6"/>
+      <c r="CB25" s="6"/>
+    </row>
+    <row r="26" spans="15:80">
+      <c r="O26" s="6"/>
+      <c r="Z26" s="6"/>
+      <c r="AB26" s="6"/>
+      <c r="AM26" s="6"/>
+      <c r="AN26" s="2"/>
+      <c r="AO26" s="4"/>
+      <c r="AY26" s="6"/>
+      <c r="BJ26" s="6"/>
+      <c r="BT26" s="6"/>
+      <c r="CB26" s="6"/>
+    </row>
+    <row r="27" spans="15:80">
+      <c r="O27" s="6"/>
+      <c r="Z27" s="6"/>
+      <c r="AB27" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM27" s="6"/>
+      <c r="AN27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO27" s="6"/>
+      <c r="AY27" s="6"/>
+      <c r="BJ27" s="6"/>
+      <c r="BT27" s="6"/>
+      <c r="CB27" s="6"/>
+    </row>
+    <row r="28" spans="15:80">
+      <c r="O28" s="6"/>
+      <c r="Z28" s="6"/>
+      <c r="AB28" s="6"/>
+      <c r="AM28" s="6"/>
+      <c r="AO28" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="AY28" s="6"/>
+      <c r="BJ28" s="6"/>
+      <c r="BT28" s="6"/>
+      <c r="CB28" s="6"/>
+    </row>
+    <row r="29" spans="15:80">
+      <c r="O29" s="6"/>
+      <c r="Z29" s="6"/>
+      <c r="AB29" s="6"/>
+      <c r="AM29" s="6"/>
+      <c r="AO29" s="6"/>
+      <c r="AY29" s="6"/>
+      <c r="BJ29" s="6"/>
+      <c r="BT29" s="6"/>
+      <c r="CB29" s="6"/>
+    </row>
+    <row r="30" spans="15:80">
+      <c r="O30" s="6"/>
+      <c r="Z30" s="6"/>
+      <c r="AB30" s="6"/>
+      <c r="AM30" s="6"/>
+      <c r="AO30" s="6"/>
+      <c r="AP30" t="s">
+        <v>63</v>
+      </c>
+      <c r="AY30" s="6"/>
+      <c r="BJ30" s="6"/>
+      <c r="BT30" s="6"/>
+      <c r="CB30" s="6"/>
+    </row>
+    <row r="31" spans="15:80">
+      <c r="O31" s="6"/>
+      <c r="Z31" s="6"/>
+      <c r="AB31" s="6"/>
+      <c r="AM31" s="6"/>
+      <c r="AO31" s="6"/>
+      <c r="AP31" t="s">
+        <v>38</v>
+      </c>
+      <c r="AY31" s="6"/>
+      <c r="BJ31" s="6"/>
+      <c r="BT31" s="6"/>
+      <c r="CB31" s="6"/>
+    </row>
+    <row r="32" spans="15:80">
+      <c r="O32" s="6"/>
+      <c r="Z32" s="6"/>
+      <c r="AB32" s="6"/>
+      <c r="AM32" s="6"/>
+      <c r="AO32" s="6"/>
+      <c r="AP32" s="10"/>
+      <c r="AQ32" s="11"/>
+      <c r="AR32" s="11"/>
+      <c r="AS32" s="12"/>
+      <c r="AY32" s="6"/>
+      <c r="BJ32" s="6"/>
+      <c r="BT32" s="6"/>
+      <c r="CB32" s="6"/>
+    </row>
+    <row r="33" spans="15:88">
+      <c r="O33" s="6"/>
+      <c r="Z33" s="6"/>
+      <c r="AB33" s="6"/>
+      <c r="AM33" s="6"/>
+      <c r="AN33" s="7"/>
+      <c r="AO33" s="9"/>
+      <c r="AY33" s="6"/>
+      <c r="BJ33" s="6"/>
+      <c r="BT33" s="6"/>
+      <c r="CB33" s="6"/>
+    </row>
+    <row r="34" spans="15:88">
+      <c r="O34" s="6"/>
+      <c r="Z34" s="6"/>
+      <c r="AB34" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AM34" s="6"/>
+      <c r="AW34" t="s">
+        <v>65</v>
+      </c>
+      <c r="AY34" s="6"/>
+      <c r="BJ34" s="6"/>
+      <c r="BT34" s="6"/>
+      <c r="CB34" s="6"/>
+    </row>
+    <row r="35" spans="15:88">
+      <c r="O35" s="6"/>
+      <c r="Z35" s="6"/>
+      <c r="AB35" s="6"/>
+      <c r="AM35" s="6"/>
+      <c r="AY35" s="6"/>
+      <c r="AZ35" s="10"/>
+      <c r="BA35" s="11"/>
+      <c r="BB35" s="11"/>
+      <c r="BC35" s="12"/>
+      <c r="BJ35" s="6"/>
+      <c r="BT35" s="6"/>
+      <c r="CB35" s="6"/>
+    </row>
+    <row r="36" spans="15:88">
+      <c r="O36" s="6"/>
+      <c r="Z36" s="6"/>
+      <c r="AM36" s="6"/>
+      <c r="AY36" s="6"/>
+      <c r="AZ36" s="2"/>
+      <c r="BA36" s="4"/>
+      <c r="BJ36" s="6"/>
+      <c r="BT36" s="6"/>
+      <c r="CB36" s="6"/>
+    </row>
+    <row r="37" spans="15:88">
+      <c r="O37" s="6"/>
+      <c r="Z37" s="6"/>
+      <c r="AM37" s="6"/>
+      <c r="AY37" s="6"/>
+      <c r="AZ37" s="5"/>
+      <c r="BA37" t="s">
+        <v>66</v>
+      </c>
+      <c r="BJ37" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="BT37" s="6"/>
+      <c r="CB37" s="6"/>
+    </row>
+    <row r="38" spans="15:88">
+      <c r="O38" s="6"/>
+      <c r="Z38" s="6"/>
+      <c r="AM38" s="6"/>
+      <c r="AY38" s="6"/>
+      <c r="AZ38" s="5"/>
+      <c r="BA38" s="6"/>
+      <c r="BJ38" s="6"/>
+      <c r="BK38" t="s">
+        <v>69</v>
+      </c>
+      <c r="BM38" s="8"/>
+      <c r="BN38" s="8"/>
+      <c r="BT38" s="6"/>
+      <c r="CB38" s="6"/>
+    </row>
+    <row r="39" spans="15:88">
+      <c r="O39" s="6"/>
+      <c r="Z39" s="6"/>
+      <c r="AM39" s="6"/>
+      <c r="AY39" s="6"/>
+      <c r="AZ39" s="5"/>
+      <c r="BA39" s="6"/>
+      <c r="BJ39" s="6"/>
+      <c r="BK39" s="10"/>
+      <c r="BL39" s="11"/>
+      <c r="BM39" s="8"/>
+      <c r="BN39" s="12"/>
+      <c r="BT39" s="6"/>
+      <c r="CB39" s="6"/>
+    </row>
+    <row r="40" spans="15:88">
+      <c r="O40" s="6"/>
+      <c r="Z40" s="6"/>
+      <c r="AM40" s="6"/>
+      <c r="AY40" s="6"/>
+      <c r="AZ40" s="5"/>
+      <c r="BA40" s="6"/>
+      <c r="BJ40" s="6"/>
+      <c r="BL40" s="4"/>
+      <c r="BT40" s="6"/>
+      <c r="CB40" s="6"/>
+    </row>
+    <row r="41" spans="15:88">
+      <c r="O41" s="6"/>
+      <c r="Z41" s="6"/>
+      <c r="AM41" s="6"/>
+      <c r="AY41" s="6"/>
+      <c r="AZ41" s="5"/>
+      <c r="BA41" s="6"/>
+      <c r="BJ41" s="6"/>
+      <c r="BL41" t="s">
+        <v>137</v>
+      </c>
+      <c r="BT41" s="6"/>
+      <c r="CB41" s="6"/>
+    </row>
+    <row r="42" spans="15:88">
+      <c r="O42" s="6"/>
+      <c r="Z42" s="6"/>
+      <c r="AM42" s="6"/>
+      <c r="AY42" s="6"/>
+      <c r="AZ42" s="5"/>
+      <c r="BA42" s="6"/>
+      <c r="BJ42" s="6"/>
+      <c r="BL42" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="BT42" s="6"/>
+      <c r="CB42" s="6"/>
+    </row>
+    <row r="43" spans="15:88">
+      <c r="O43" s="6"/>
+      <c r="Z43" s="6"/>
+      <c r="AM43" s="6"/>
+      <c r="AY43" s="6"/>
+      <c r="AZ43" s="5"/>
+      <c r="BA43" s="6"/>
+      <c r="BJ43" s="6"/>
+      <c r="BL43" s="6"/>
+      <c r="BM43" s="10"/>
+      <c r="BN43" s="11"/>
+      <c r="BO43" s="11"/>
+      <c r="BP43" s="12"/>
+      <c r="BT43" s="6"/>
+      <c r="CB43" s="6"/>
+    </row>
+    <row r="44" spans="15:88">
+      <c r="O44" s="6"/>
+      <c r="Z44" s="6"/>
+      <c r="AM44" s="6"/>
+      <c r="AY44" s="6"/>
+      <c r="AZ44" s="5"/>
+      <c r="BA44" s="6"/>
+      <c r="BJ44" s="6"/>
+      <c r="BL44" s="6"/>
+      <c r="BT44" s="6"/>
+      <c r="CB44" s="6"/>
+    </row>
+    <row r="45" spans="15:88">
+      <c r="O45" s="6"/>
+      <c r="Z45" s="6"/>
+      <c r="AM45" s="6"/>
+      <c r="AY45" s="6"/>
+      <c r="AZ45" s="5"/>
+      <c r="BA45" s="6"/>
+      <c r="BJ45" s="6"/>
+      <c r="BL45" s="6"/>
+      <c r="BT45" s="6"/>
+      <c r="CB45" s="6"/>
+    </row>
+    <row r="46" spans="15:88">
+      <c r="O46" s="6"/>
+      <c r="Z46" s="6"/>
+      <c r="AM46" s="6"/>
+      <c r="AY46" s="6"/>
+      <c r="AZ46" s="5"/>
+      <c r="BA46" s="6"/>
+      <c r="BJ46" s="6"/>
+      <c r="BT46" s="6"/>
+      <c r="CB46" s="6"/>
+    </row>
+    <row r="47" spans="15:88">
+      <c r="O47" s="6"/>
+      <c r="Z47" s="6"/>
+      <c r="AM47" s="6"/>
+      <c r="AW47" s="6"/>
+      <c r="AX47" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="AY47" s="39"/>
+      <c r="AZ47" s="40"/>
+      <c r="BA47" s="39"/>
+      <c r="BB47" s="41"/>
+      <c r="BC47" s="41"/>
+      <c r="BD47" s="41"/>
+      <c r="BE47" s="41"/>
+      <c r="BF47" s="41"/>
+      <c r="BG47" s="41"/>
+      <c r="BH47" s="41"/>
+      <c r="BI47" s="41"/>
+      <c r="BJ47" s="39"/>
+      <c r="BK47" s="41"/>
+      <c r="BL47" s="41"/>
+      <c r="BM47" s="41"/>
+      <c r="BN47" s="41"/>
+      <c r="BO47" s="41"/>
+      <c r="BP47" s="41"/>
+      <c r="BQ47" s="41"/>
+      <c r="BR47" s="41"/>
+      <c r="BS47" s="41"/>
+      <c r="BT47" s="39"/>
+      <c r="BU47" s="41"/>
+      <c r="BV47" s="41"/>
+      <c r="BW47" s="41"/>
+      <c r="BX47" s="41"/>
+      <c r="BY47" s="41"/>
+      <c r="BZ47" s="41"/>
+      <c r="CA47" s="41"/>
+      <c r="CB47" s="39"/>
+      <c r="CC47" s="41"/>
+      <c r="CD47" s="41"/>
+      <c r="CE47" s="41"/>
+      <c r="CF47" s="41"/>
+      <c r="CG47" s="41"/>
+      <c r="CH47" s="41"/>
+      <c r="CI47" s="41"/>
+      <c r="CJ47" s="39"/>
+    </row>
+    <row r="48" spans="15:88">
+      <c r="O48" s="6"/>
+      <c r="Z48" s="6"/>
+      <c r="AM48" s="6"/>
+      <c r="AW48" s="6"/>
+      <c r="AX48" s="42"/>
+      <c r="AY48" s="43"/>
+      <c r="AZ48" s="44"/>
+      <c r="BA48" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="BB48" s="45"/>
+      <c r="BC48" s="45"/>
+      <c r="BD48" s="42"/>
+      <c r="BE48" s="45"/>
+      <c r="BF48" s="42"/>
+      <c r="BG48" s="42"/>
+      <c r="BH48" s="42"/>
+      <c r="BI48" s="42"/>
+      <c r="BJ48" s="43"/>
+      <c r="BK48" s="42"/>
+      <c r="BL48" s="42"/>
+      <c r="BM48" s="42"/>
+      <c r="BN48" s="42"/>
+      <c r="BO48" s="42"/>
+      <c r="BP48" s="42"/>
+      <c r="BQ48" s="42"/>
+      <c r="BR48" s="42"/>
+      <c r="BS48" s="42"/>
+      <c r="BT48" s="43"/>
+      <c r="BU48" s="42"/>
+      <c r="BV48" s="42"/>
+      <c r="BW48" s="42"/>
+      <c r="BX48" s="42"/>
+      <c r="BY48" s="42"/>
+      <c r="BZ48" s="42"/>
+      <c r="CA48" s="42"/>
+      <c r="CB48" s="43"/>
+      <c r="CC48" s="42"/>
+      <c r="CD48" s="42"/>
+      <c r="CE48" s="42"/>
+      <c r="CF48" s="42"/>
+      <c r="CG48" s="42"/>
+      <c r="CH48" s="42"/>
+      <c r="CI48" s="42"/>
+      <c r="CJ48" s="43"/>
+    </row>
+    <row r="49" spans="15:88">
+      <c r="O49" s="6"/>
+      <c r="Z49" s="6"/>
+      <c r="AM49" s="6"/>
+      <c r="AW49" s="6"/>
+      <c r="AX49" s="42"/>
+      <c r="AY49" s="43"/>
+      <c r="AZ49" s="44"/>
+      <c r="BA49" s="43"/>
+      <c r="BB49" s="46"/>
+      <c r="BC49" s="47"/>
+      <c r="BD49" s="47"/>
+      <c r="BE49" s="48"/>
+      <c r="BF49" s="42"/>
+      <c r="BG49" s="42"/>
+      <c r="BH49" s="42"/>
+      <c r="BI49" s="42"/>
+      <c r="BJ49" s="43"/>
+      <c r="BK49" s="42"/>
+      <c r="BL49" s="42"/>
+      <c r="BM49" s="42"/>
+      <c r="BN49" s="42"/>
+      <c r="BO49" s="42"/>
+      <c r="BP49" s="42"/>
+      <c r="BQ49" s="42"/>
+      <c r="BR49" s="42"/>
+      <c r="BS49" s="42"/>
+      <c r="BT49" s="43"/>
+      <c r="BU49" s="42"/>
+      <c r="BV49" s="42"/>
+      <c r="BW49" s="42"/>
+      <c r="BX49" s="42"/>
+      <c r="BY49" s="42"/>
+      <c r="BZ49" s="42"/>
+      <c r="CA49" s="42"/>
+      <c r="CB49" s="43"/>
+      <c r="CC49" s="42"/>
+      <c r="CD49" s="42"/>
+      <c r="CE49" s="42"/>
+      <c r="CF49" s="42"/>
+      <c r="CG49" s="42"/>
+      <c r="CH49" s="42"/>
+      <c r="CI49" s="42"/>
+      <c r="CJ49" s="43"/>
+    </row>
+    <row r="50" spans="15:88">
+      <c r="O50" s="6"/>
+      <c r="Z50" s="6"/>
+      <c r="AM50" s="6"/>
+      <c r="AW50" s="6"/>
+      <c r="AX50" s="42"/>
+      <c r="AY50" s="43"/>
+      <c r="AZ50" s="44"/>
+      <c r="BA50" s="43"/>
+      <c r="BB50" s="40"/>
+      <c r="BC50" s="39"/>
+      <c r="BD50" s="42"/>
+      <c r="BE50" s="42"/>
+      <c r="BF50" s="42"/>
+      <c r="BG50" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="BH50" s="42"/>
+      <c r="BI50" s="42"/>
+      <c r="BJ50" s="43"/>
+      <c r="BK50" s="42"/>
+      <c r="BL50" s="42"/>
+      <c r="BM50" s="42"/>
+      <c r="BN50" s="42"/>
+      <c r="BO50" s="42"/>
+      <c r="BP50" s="42"/>
+      <c r="BQ50" s="42"/>
+      <c r="BR50" s="42"/>
+      <c r="BS50" s="42"/>
+      <c r="BT50" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="BU50" s="42"/>
+      <c r="BV50" s="42"/>
+      <c r="BW50" s="42"/>
+      <c r="BX50" s="42"/>
+      <c r="BY50" s="42"/>
+      <c r="BZ50" s="42"/>
+      <c r="CA50" s="42"/>
+      <c r="CB50" s="43"/>
+      <c r="CC50" s="42"/>
+      <c r="CD50" s="42"/>
+      <c r="CE50" s="42"/>
+      <c r="CF50" s="42"/>
+      <c r="CG50" s="42"/>
+      <c r="CH50" s="42"/>
+      <c r="CI50" s="42"/>
+      <c r="CJ50" s="43"/>
+    </row>
+    <row r="51" spans="15:88">
+      <c r="O51" s="6"/>
+      <c r="Z51" s="6"/>
+      <c r="AM51" s="6"/>
+      <c r="AW51" s="6"/>
+      <c r="AX51" s="42"/>
+      <c r="AY51" s="43"/>
+      <c r="AZ51" s="44"/>
+      <c r="BA51" s="43"/>
+      <c r="BB51" s="44"/>
+      <c r="BC51" s="43"/>
+      <c r="BD51" s="42"/>
+      <c r="BE51" s="42"/>
+      <c r="BF51" s="42"/>
+      <c r="BG51" s="42"/>
+      <c r="BH51" s="42"/>
+      <c r="BI51" s="42"/>
+      <c r="BJ51" s="43"/>
+      <c r="BK51" s="42"/>
+      <c r="BL51" s="42"/>
+      <c r="BM51" s="42"/>
+      <c r="BN51" s="42"/>
+      <c r="BO51" s="42"/>
+      <c r="BP51" s="42"/>
+      <c r="BQ51" s="42"/>
+      <c r="BR51" s="42"/>
+      <c r="BS51" s="42"/>
+      <c r="BT51" s="43"/>
+      <c r="BU51" s="46"/>
+      <c r="BV51" s="47"/>
+      <c r="BW51" s="47"/>
+      <c r="BX51" s="48"/>
+      <c r="BY51" s="42"/>
+      <c r="BZ51" s="42"/>
+      <c r="CA51" s="42"/>
+      <c r="CB51" s="43"/>
+      <c r="CC51" s="42"/>
+      <c r="CD51" s="42"/>
+      <c r="CE51" s="42"/>
+      <c r="CF51" s="42"/>
+      <c r="CG51" s="42"/>
+      <c r="CH51" s="42"/>
+      <c r="CI51" s="42"/>
+      <c r="CJ51" s="43"/>
+    </row>
+    <row r="52" spans="15:88">
+      <c r="O52" s="6"/>
+      <c r="Z52" s="6"/>
+      <c r="AM52" s="6"/>
+      <c r="AW52" s="6"/>
+      <c r="AX52" s="42"/>
+      <c r="AY52" s="43"/>
+      <c r="AZ52" s="44"/>
+      <c r="BA52" s="42"/>
+      <c r="BB52" s="44"/>
+      <c r="BC52" s="43"/>
+      <c r="BD52" s="42"/>
+      <c r="BE52" s="42"/>
+      <c r="BF52" s="42"/>
+      <c r="BG52" s="42"/>
+      <c r="BH52" s="42"/>
+      <c r="BI52" s="42"/>
+      <c r="BJ52" s="43"/>
+      <c r="BK52" s="42"/>
+      <c r="BL52" s="42"/>
+      <c r="BM52" s="42"/>
+      <c r="BN52" s="42"/>
+      <c r="BO52" s="42"/>
+      <c r="BP52" s="42"/>
+      <c r="BQ52" s="42"/>
+      <c r="BR52" s="42"/>
+      <c r="BS52" s="42"/>
+      <c r="BT52" s="43"/>
+      <c r="BU52" s="40"/>
+      <c r="BV52" s="39"/>
+      <c r="BW52" s="42"/>
+      <c r="BX52" s="42"/>
+      <c r="BY52" s="42"/>
+      <c r="BZ52" s="42"/>
+      <c r="CA52" s="42"/>
+      <c r="CB52" s="43"/>
+      <c r="CC52" s="42"/>
+      <c r="CD52" s="42"/>
+      <c r="CE52" s="42"/>
+      <c r="CF52" s="42"/>
+      <c r="CG52" s="42"/>
+      <c r="CH52" s="42"/>
+      <c r="CI52" s="42"/>
+      <c r="CJ52" s="43"/>
+    </row>
+    <row r="53" spans="15:88">
+      <c r="O53" s="6"/>
+      <c r="Z53" s="6"/>
+      <c r="AM53" s="6"/>
+      <c r="AW53" s="6"/>
+      <c r="AX53" s="42"/>
+      <c r="AY53" s="43"/>
+      <c r="AZ53" s="44"/>
+      <c r="BA53" s="42"/>
+      <c r="BB53" s="44"/>
+      <c r="BC53" s="43"/>
+      <c r="BD53" s="42"/>
+      <c r="BE53" s="42"/>
+      <c r="BF53" s="42"/>
+      <c r="BG53" s="42"/>
+      <c r="BH53" s="42"/>
+      <c r="BI53" s="42"/>
+      <c r="BJ53" s="43"/>
+      <c r="BK53" s="42"/>
+      <c r="BL53" s="42"/>
+      <c r="BM53" s="42"/>
+      <c r="BN53" s="42"/>
+      <c r="BO53" s="42"/>
+      <c r="BP53" s="42"/>
+      <c r="BQ53" s="42"/>
+      <c r="BR53" s="42"/>
+      <c r="BS53" s="42"/>
+      <c r="BT53" s="43"/>
+      <c r="BU53" s="44"/>
+      <c r="BV53" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="AM19" s="8"/>
-      <c r="AY19" s="8"/>
-      <c r="BJ19" s="8"/>
-      <c r="BT19" s="8"/>
-      <c r="CB19" s="8"/>
-    </row>
-    <row r="20" spans="15:80">
-      <c r="O20" s="8"/>
-      <c r="Z20" s="8"/>
-      <c r="AA20" s="12"/>
-      <c r="AB20" s="13"/>
-      <c r="AC20" s="13"/>
-      <c r="AD20" s="14"/>
-      <c r="AM20" s="8"/>
-      <c r="AY20" s="8"/>
-      <c r="BJ20" s="8"/>
-      <c r="BT20" s="8"/>
-      <c r="CB20" s="8"/>
-    </row>
-    <row r="21" spans="15:80">
-      <c r="O21" s="8"/>
-      <c r="Z21" s="8"/>
-      <c r="AB21" s="6"/>
-      <c r="AM21" s="8"/>
-      <c r="AY21" s="8"/>
-      <c r="BJ21" s="8"/>
-      <c r="BT21" s="8"/>
-      <c r="CB21" s="8"/>
-    </row>
-    <row r="22" spans="15:80">
-      <c r="O22" s="8"/>
-      <c r="Z22" s="8"/>
-      <c r="AB22" t="s">
+      <c r="BW53" s="42"/>
+      <c r="BX53" s="42"/>
+      <c r="BY53" s="42"/>
+      <c r="BZ53" s="42"/>
+      <c r="CA53" s="42"/>
+      <c r="CB53" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="AM22" s="8"/>
-      <c r="AY22" s="8"/>
-      <c r="BJ22" s="8"/>
-      <c r="BT22" s="8"/>
-      <c r="CB22" s="8"/>
-    </row>
-    <row r="23" spans="15:80">
-      <c r="O23" s="8"/>
-      <c r="Z23" s="8"/>
-      <c r="AB23" t="s">
+      <c r="CC53" s="42"/>
+      <c r="CD53" s="42"/>
+      <c r="CE53" s="42"/>
+      <c r="CF53" s="42"/>
+      <c r="CG53" s="42"/>
+      <c r="CH53" s="42"/>
+      <c r="CI53" s="42"/>
+      <c r="CJ53" s="43"/>
+    </row>
+    <row r="54" spans="15:88">
+      <c r="O54" s="6"/>
+      <c r="Z54" s="6"/>
+      <c r="AM54" s="6"/>
+      <c r="AW54" s="6"/>
+      <c r="AX54" s="42"/>
+      <c r="AY54" s="43"/>
+      <c r="AZ54" s="44"/>
+      <c r="BA54" s="42"/>
+      <c r="BB54" s="44"/>
+      <c r="BC54" s="43"/>
+      <c r="BD54" s="42"/>
+      <c r="BE54" s="42"/>
+      <c r="BF54" s="42"/>
+      <c r="BG54" s="42"/>
+      <c r="BH54" s="42"/>
+      <c r="BI54" s="42"/>
+      <c r="BJ54" s="43"/>
+      <c r="BK54" s="42"/>
+      <c r="BL54" s="42"/>
+      <c r="BM54" s="42"/>
+      <c r="BN54" s="42"/>
+      <c r="BO54" s="42"/>
+      <c r="BP54" s="42"/>
+      <c r="BQ54" s="42"/>
+      <c r="BR54" s="42"/>
+      <c r="BS54" s="42"/>
+      <c r="BT54" s="43"/>
+      <c r="BU54" s="44"/>
+      <c r="BV54" s="43"/>
+      <c r="BW54" s="42"/>
+      <c r="BX54" s="42"/>
+      <c r="BY54" s="42"/>
+      <c r="BZ54" s="42"/>
+      <c r="CA54" s="42"/>
+      <c r="CB54" s="43"/>
+      <c r="CC54" s="46"/>
+      <c r="CD54" s="47"/>
+      <c r="CE54" s="47"/>
+      <c r="CF54" s="48"/>
+      <c r="CG54" s="42"/>
+      <c r="CH54" s="42"/>
+      <c r="CI54" s="42"/>
+      <c r="CJ54" s="43"/>
+    </row>
+    <row r="55" spans="15:88">
+      <c r="O55" s="6"/>
+      <c r="Z55" s="6"/>
+      <c r="AM55" s="6"/>
+      <c r="AW55" s="6"/>
+      <c r="AX55" s="42"/>
+      <c r="AY55" s="43"/>
+      <c r="AZ55" s="44"/>
+      <c r="BA55" s="42"/>
+      <c r="BB55" s="44"/>
+      <c r="BC55" s="43"/>
+      <c r="BD55" s="42"/>
+      <c r="BE55" s="42"/>
+      <c r="BF55" s="42"/>
+      <c r="BG55" s="42"/>
+      <c r="BH55" s="42"/>
+      <c r="BI55" s="42"/>
+      <c r="BJ55" s="43"/>
+      <c r="BK55" s="42"/>
+      <c r="BL55" s="42"/>
+      <c r="BM55" s="42"/>
+      <c r="BN55" s="42"/>
+      <c r="BO55" s="42"/>
+      <c r="BP55" s="42"/>
+      <c r="BQ55" s="42"/>
+      <c r="BR55" s="42"/>
+      <c r="BS55" s="42"/>
+      <c r="BT55" s="43"/>
+      <c r="BU55" s="44"/>
+      <c r="BV55" s="43"/>
+      <c r="BW55" s="42"/>
+      <c r="BX55" s="42"/>
+      <c r="BY55" s="42"/>
+      <c r="BZ55" s="42"/>
+      <c r="CA55" s="42"/>
+      <c r="CB55" s="43"/>
+      <c r="CC55" s="40"/>
+      <c r="CD55" s="39"/>
+      <c r="CE55" s="42"/>
+      <c r="CF55" s="42"/>
+      <c r="CG55" s="42"/>
+      <c r="CH55" s="42"/>
+      <c r="CI55" s="42"/>
+      <c r="CJ55" s="43"/>
+    </row>
+    <row r="56" spans="15:88">
+      <c r="O56" s="6"/>
+      <c r="Z56" s="6"/>
+      <c r="AM56" s="6"/>
+      <c r="AW56" s="6"/>
+      <c r="AX56" s="42"/>
+      <c r="AY56" s="43"/>
+      <c r="AZ56" s="44"/>
+      <c r="BA56" s="42"/>
+      <c r="BB56" s="44"/>
+      <c r="BC56" s="43"/>
+      <c r="BD56" s="42"/>
+      <c r="BE56" s="42"/>
+      <c r="BF56" s="42"/>
+      <c r="BG56" s="42"/>
+      <c r="BH56" s="42"/>
+      <c r="BI56" s="42"/>
+      <c r="BJ56" s="43"/>
+      <c r="BK56" s="42"/>
+      <c r="BL56" s="42"/>
+      <c r="BM56" s="42"/>
+      <c r="BN56" s="42"/>
+      <c r="BO56" s="42"/>
+      <c r="BP56" s="42"/>
+      <c r="BQ56" s="42"/>
+      <c r="BR56" s="42"/>
+      <c r="BS56" s="42"/>
+      <c r="BT56" s="43"/>
+      <c r="BU56" s="44"/>
+      <c r="BV56" s="43"/>
+      <c r="BW56" s="42"/>
+      <c r="BX56" s="42"/>
+      <c r="BY56" s="42"/>
+      <c r="BZ56" s="42"/>
+      <c r="CA56" s="42"/>
+      <c r="CB56" s="43"/>
+      <c r="CC56" s="44"/>
+      <c r="CD56" s="43"/>
+      <c r="CE56" s="42" t="s">
         <v>99</v>
       </c>
-      <c r="AM23" s="8"/>
-      <c r="AY23" s="8"/>
-      <c r="BJ23" s="8"/>
-      <c r="BT23" s="8"/>
-      <c r="CB23" s="8"/>
-    </row>
-    <row r="24" spans="15:80">
-      <c r="O24" s="8"/>
-      <c r="Z24" s="8"/>
-      <c r="AB24" t="s">
-        <v>100</v>
-      </c>
-      <c r="AM24" s="8"/>
-      <c r="AN24" t="s">
-        <v>117</v>
-      </c>
-      <c r="AY24" s="8"/>
-      <c r="BJ24" s="8"/>
-      <c r="BT24" s="8"/>
-      <c r="CB24" s="8"/>
-    </row>
-    <row r="25" spans="15:80">
-      <c r="O25" s="8"/>
-      <c r="Z25" s="8"/>
-      <c r="AB25" s="8"/>
-      <c r="AM25" s="8"/>
-      <c r="AN25" s="12"/>
-      <c r="AO25" s="13"/>
-      <c r="AP25" s="13"/>
-      <c r="AQ25" s="14"/>
-      <c r="AY25" s="8"/>
-      <c r="BJ25" s="8"/>
-      <c r="BT25" s="8"/>
-      <c r="CB25" s="8"/>
-    </row>
-    <row r="26" spans="15:80">
-      <c r="O26" s="8"/>
-      <c r="Z26" s="8"/>
-      <c r="AB26" s="8"/>
-      <c r="AM26" s="8"/>
-      <c r="AN26" s="4"/>
-      <c r="AO26" s="6"/>
-      <c r="AY26" s="8"/>
-      <c r="BJ26" s="8"/>
-      <c r="BT26" s="8"/>
-      <c r="CB26" s="8"/>
-    </row>
-    <row r="27" spans="15:80">
-      <c r="O27" s="8"/>
-      <c r="Z27" s="8"/>
-      <c r="AB27" t="s">
-        <v>103</v>
-      </c>
-      <c r="AM27" s="8"/>
-      <c r="AN27" t="s">
-        <v>118</v>
-      </c>
-      <c r="AO27" s="8"/>
-      <c r="AY27" s="8"/>
-      <c r="BJ27" s="8"/>
-      <c r="BT27" s="8"/>
-      <c r="CB27" s="8"/>
-    </row>
-    <row r="28" spans="15:80">
-      <c r="O28" s="8"/>
-      <c r="Z28" s="8"/>
-      <c r="AB28" s="8"/>
-      <c r="AM28" s="8"/>
-      <c r="AO28" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="AY28" s="8"/>
-      <c r="BJ28" s="8"/>
-      <c r="BT28" s="8"/>
-      <c r="CB28" s="8"/>
-    </row>
-    <row r="29" spans="15:80">
-      <c r="O29" s="8"/>
-      <c r="Z29" s="8"/>
-      <c r="AB29" s="8"/>
-      <c r="AM29" s="8"/>
-      <c r="AO29" s="8"/>
-      <c r="AY29" s="8"/>
-      <c r="BJ29" s="8"/>
-      <c r="BT29" s="8"/>
-      <c r="CB29" s="8"/>
-    </row>
-    <row r="30" spans="15:80">
-      <c r="O30" s="8"/>
-      <c r="Z30" s="8"/>
-      <c r="AB30" s="8"/>
-      <c r="AM30" s="8"/>
-      <c r="AO30" s="8"/>
-      <c r="AP30" t="s">
-        <v>120</v>
-      </c>
-      <c r="AY30" s="8"/>
-      <c r="BJ30" s="8"/>
-      <c r="BT30" s="8"/>
-      <c r="CB30" s="8"/>
-    </row>
-    <row r="31" spans="15:80">
-      <c r="O31" s="8"/>
-      <c r="Z31" s="8"/>
-      <c r="AB31" s="8"/>
-      <c r="AM31" s="8"/>
-      <c r="AO31" s="8"/>
-      <c r="AP31" t="s">
-        <v>95</v>
-      </c>
-      <c r="AY31" s="8"/>
-      <c r="BJ31" s="8"/>
-      <c r="BT31" s="8"/>
-      <c r="CB31" s="8"/>
-    </row>
-    <row r="32" spans="15:80">
-      <c r="O32" s="8"/>
-      <c r="Z32" s="8"/>
-      <c r="AB32" s="8"/>
-      <c r="AM32" s="8"/>
-      <c r="AO32" s="8"/>
-      <c r="AP32" s="12"/>
-      <c r="AQ32" s="13"/>
-      <c r="AR32" s="13"/>
-      <c r="AS32" s="14"/>
-      <c r="AY32" s="8"/>
-      <c r="BJ32" s="8"/>
-      <c r="BT32" s="8"/>
-      <c r="CB32" s="8"/>
-    </row>
-    <row r="33" spans="15:88">
-      <c r="O33" s="8"/>
-      <c r="Z33" s="8"/>
-      <c r="AB33" s="8"/>
-      <c r="AM33" s="8"/>
-      <c r="AN33" s="9"/>
-      <c r="AO33" s="11"/>
-      <c r="AY33" s="8"/>
-      <c r="BJ33" s="8"/>
-      <c r="BT33" s="8"/>
-      <c r="CB33" s="8"/>
-    </row>
-    <row r="34" spans="15:88">
-      <c r="O34" s="8"/>
-      <c r="Z34" s="8"/>
-      <c r="AB34" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="AM34" s="8"/>
-      <c r="AW34" t="s">
-        <v>122</v>
-      </c>
-      <c r="AY34" s="8"/>
-      <c r="BJ34" s="8"/>
-      <c r="BT34" s="8"/>
-      <c r="CB34" s="8"/>
-    </row>
-    <row r="35" spans="15:88">
-      <c r="O35" s="8"/>
-      <c r="Z35" s="8"/>
-      <c r="AB35" s="8"/>
-      <c r="AM35" s="8"/>
-      <c r="AY35" s="8"/>
-      <c r="AZ35" s="12"/>
-      <c r="BA35" s="13"/>
-      <c r="BB35" s="13"/>
-      <c r="BC35" s="14"/>
-      <c r="BJ35" s="8"/>
-      <c r="BT35" s="8"/>
-      <c r="CB35" s="8"/>
-    </row>
-    <row r="36" spans="15:88">
-      <c r="O36" s="8"/>
-      <c r="Z36" s="8"/>
-      <c r="AM36" s="8"/>
-      <c r="AY36" s="8"/>
-      <c r="AZ36" s="4"/>
-      <c r="BA36" s="6"/>
-      <c r="BJ36" s="8"/>
-      <c r="BT36" s="8"/>
-      <c r="CB36" s="8"/>
-    </row>
-    <row r="37" spans="15:88">
-      <c r="O37" s="8"/>
-      <c r="Z37" s="8"/>
-      <c r="AM37" s="8"/>
-      <c r="AY37" s="8"/>
-      <c r="AZ37" s="7"/>
-      <c r="BA37" t="s">
-        <v>123</v>
-      </c>
-      <c r="BJ37" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="BT37" s="8"/>
-      <c r="CB37" s="8"/>
-    </row>
-    <row r="38" spans="15:88">
-      <c r="O38" s="8"/>
-      <c r="Z38" s="8"/>
-      <c r="AM38" s="8"/>
-      <c r="AY38" s="8"/>
-      <c r="AZ38" s="7"/>
-      <c r="BA38" s="8"/>
-      <c r="BJ38" s="8"/>
-      <c r="BK38" t="s">
-        <v>126</v>
-      </c>
-      <c r="BM38" s="10"/>
-      <c r="BN38" s="10"/>
-      <c r="BT38" s="8"/>
-      <c r="CB38" s="8"/>
-    </row>
-    <row r="39" spans="15:88">
-      <c r="O39" s="8"/>
-      <c r="Z39" s="8"/>
-      <c r="AM39" s="8"/>
-      <c r="AY39" s="8"/>
-      <c r="AZ39" s="7"/>
-      <c r="BA39" s="8"/>
-      <c r="BJ39" s="8"/>
-      <c r="BK39" s="12"/>
-      <c r="BL39" s="13"/>
-      <c r="BM39" s="10"/>
-      <c r="BN39" s="14"/>
-      <c r="BT39" s="8"/>
-      <c r="CB39" s="8"/>
-    </row>
-    <row r="40" spans="15:88">
-      <c r="O40" s="8"/>
-      <c r="Z40" s="8"/>
-      <c r="AM40" s="8"/>
-      <c r="AY40" s="8"/>
-      <c r="AZ40" s="7"/>
-      <c r="BA40" s="8"/>
-      <c r="BJ40" s="8"/>
-      <c r="BL40" s="6"/>
-      <c r="BT40" s="8"/>
-      <c r="CB40" s="8"/>
-    </row>
-    <row r="41" spans="15:88">
-      <c r="O41" s="8"/>
-      <c r="Z41" s="8"/>
-      <c r="AM41" s="8"/>
-      <c r="AY41" s="8"/>
-      <c r="AZ41" s="7"/>
-      <c r="BA41" s="8"/>
-      <c r="BJ41" s="8"/>
-      <c r="BL41" t="s">
-        <v>194</v>
-      </c>
-      <c r="BT41" s="8"/>
-      <c r="CB41" s="8"/>
-    </row>
-    <row r="42" spans="15:88">
-      <c r="O42" s="8"/>
-      <c r="Z42" s="8"/>
-      <c r="AM42" s="8"/>
-      <c r="AY42" s="8"/>
-      <c r="AZ42" s="7"/>
-      <c r="BA42" s="8"/>
-      <c r="BJ42" s="8"/>
-      <c r="BL42" s="40" t="s">
-        <v>195</v>
-      </c>
-      <c r="BT42" s="8"/>
-      <c r="CB42" s="8"/>
-    </row>
-    <row r="43" spans="15:88">
-      <c r="O43" s="8"/>
-      <c r="Z43" s="8"/>
-      <c r="AM43" s="8"/>
-      <c r="AY43" s="8"/>
-      <c r="AZ43" s="7"/>
-      <c r="BA43" s="8"/>
-      <c r="BJ43" s="8"/>
-      <c r="BL43" s="8"/>
-      <c r="BM43" s="12"/>
-      <c r="BN43" s="13"/>
-      <c r="BO43" s="13"/>
-      <c r="BP43" s="14"/>
-      <c r="BT43" s="8"/>
-      <c r="CB43" s="8"/>
-    </row>
-    <row r="44" spans="15:88">
-      <c r="O44" s="8"/>
-      <c r="Z44" s="8"/>
-      <c r="AM44" s="8"/>
-      <c r="AY44" s="8"/>
-      <c r="AZ44" s="7"/>
-      <c r="BA44" s="8"/>
-      <c r="BJ44" s="8"/>
-      <c r="BL44" s="8"/>
-      <c r="BT44" s="8"/>
-      <c r="CB44" s="8"/>
-    </row>
-    <row r="45" spans="15:88">
-      <c r="O45" s="8"/>
-      <c r="Z45" s="8"/>
-      <c r="AM45" s="8"/>
-      <c r="AY45" s="8"/>
-      <c r="AZ45" s="7"/>
-      <c r="BA45" s="8"/>
-      <c r="BJ45" s="8"/>
-      <c r="BL45" s="8"/>
-      <c r="BT45" s="8"/>
-      <c r="CB45" s="8"/>
-    </row>
-    <row r="46" spans="15:88">
-      <c r="O46" s="8"/>
-      <c r="Z46" s="8"/>
-      <c r="AM46" s="8"/>
-      <c r="AY46" s="8"/>
-      <c r="AZ46" s="7"/>
-      <c r="BA46" s="8"/>
-      <c r="BJ46" s="8"/>
-      <c r="BT46" s="8"/>
-      <c r="CB46" s="8"/>
-    </row>
-    <row r="47" spans="15:88" ht="15">
-      <c r="O47" s="8"/>
-      <c r="Z47" s="8"/>
-      <c r="AM47" s="8"/>
-      <c r="AW47" s="8"/>
-      <c r="AX47" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="AY47" s="42"/>
-      <c r="AZ47" s="43"/>
-      <c r="BA47" s="42"/>
-      <c r="BB47" s="44"/>
-      <c r="BC47" s="44"/>
-      <c r="BD47" s="44"/>
-      <c r="BE47" s="44"/>
-      <c r="BF47" s="44"/>
-      <c r="BG47" s="44"/>
-      <c r="BH47" s="44"/>
-      <c r="BI47" s="44"/>
-      <c r="BJ47" s="42"/>
-      <c r="BK47" s="44"/>
-      <c r="BL47" s="44"/>
-      <c r="BM47" s="44"/>
-      <c r="BN47" s="44"/>
-      <c r="BO47" s="44"/>
-      <c r="BP47" s="44"/>
-      <c r="BQ47" s="44"/>
-      <c r="BR47" s="44"/>
-      <c r="BS47" s="44"/>
-      <c r="BT47" s="42"/>
-      <c r="BU47" s="44"/>
-      <c r="BV47" s="44"/>
-      <c r="BW47" s="44"/>
-      <c r="BX47" s="44"/>
-      <c r="BY47" s="44"/>
-      <c r="BZ47" s="44"/>
-      <c r="CA47" s="44"/>
-      <c r="CB47" s="42"/>
-      <c r="CC47" s="44"/>
-      <c r="CD47" s="44"/>
-      <c r="CE47" s="44"/>
-      <c r="CF47" s="44"/>
-      <c r="CG47" s="44"/>
-      <c r="CH47" s="44"/>
-      <c r="CI47" s="44"/>
-      <c r="CJ47" s="42"/>
-    </row>
-    <row r="48" spans="15:88">
-      <c r="O48" s="8"/>
-      <c r="Z48" s="8"/>
-      <c r="AM48" s="8"/>
-      <c r="AW48" s="8"/>
-      <c r="AX48" s="45"/>
-      <c r="AY48" s="46"/>
-      <c r="AZ48" s="47"/>
-      <c r="BA48" s="46" t="s">
-        <v>128</v>
-      </c>
-      <c r="BB48" s="48"/>
-      <c r="BC48" s="48"/>
-      <c r="BD48" s="45"/>
-      <c r="BE48" s="48"/>
-      <c r="BF48" s="45"/>
-      <c r="BG48" s="45"/>
-      <c r="BH48" s="45"/>
-      <c r="BI48" s="45"/>
-      <c r="BJ48" s="46"/>
-      <c r="BK48" s="45"/>
-      <c r="BL48" s="45"/>
-      <c r="BM48" s="45"/>
-      <c r="BN48" s="45"/>
-      <c r="BO48" s="45"/>
-      <c r="BP48" s="45"/>
-      <c r="BQ48" s="45"/>
-      <c r="BR48" s="45"/>
-      <c r="BS48" s="45"/>
-      <c r="BT48" s="46"/>
-      <c r="BU48" s="45"/>
-      <c r="BV48" s="45"/>
-      <c r="BW48" s="45"/>
-      <c r="BX48" s="45"/>
-      <c r="BY48" s="45"/>
-      <c r="BZ48" s="45"/>
-      <c r="CA48" s="45"/>
-      <c r="CB48" s="46"/>
-      <c r="CC48" s="45"/>
-      <c r="CD48" s="45"/>
-      <c r="CE48" s="45"/>
-      <c r="CF48" s="45"/>
-      <c r="CG48" s="45"/>
-      <c r="CH48" s="45"/>
-      <c r="CI48" s="45"/>
-      <c r="CJ48" s="46"/>
-    </row>
-    <row r="49" spans="15:88">
-      <c r="O49" s="8"/>
-      <c r="Z49" s="8"/>
-      <c r="AM49" s="8"/>
-      <c r="AW49" s="8"/>
-      <c r="AX49" s="45"/>
-      <c r="AY49" s="46"/>
-      <c r="AZ49" s="47"/>
-      <c r="BA49" s="46"/>
-      <c r="BB49" s="49"/>
-      <c r="BC49" s="50"/>
-      <c r="BD49" s="50"/>
-      <c r="BE49" s="51"/>
-      <c r="BF49" s="45"/>
-      <c r="BG49" s="45"/>
-      <c r="BH49" s="45"/>
-      <c r="BI49" s="45"/>
-      <c r="BJ49" s="46"/>
-      <c r="BK49" s="45"/>
-      <c r="BL49" s="45"/>
-      <c r="BM49" s="45"/>
-      <c r="BN49" s="45"/>
-      <c r="BO49" s="45"/>
-      <c r="BP49" s="45"/>
-      <c r="BQ49" s="45"/>
-      <c r="BR49" s="45"/>
-      <c r="BS49" s="45"/>
-      <c r="BT49" s="46"/>
-      <c r="BU49" s="45"/>
-      <c r="BV49" s="45"/>
-      <c r="BW49" s="45"/>
-      <c r="BX49" s="45"/>
-      <c r="BY49" s="45"/>
-      <c r="BZ49" s="45"/>
-      <c r="CA49" s="45"/>
-      <c r="CB49" s="46"/>
-      <c r="CC49" s="45"/>
-      <c r="CD49" s="45"/>
-      <c r="CE49" s="45"/>
-      <c r="CF49" s="45"/>
-      <c r="CG49" s="45"/>
-      <c r="CH49" s="45"/>
-      <c r="CI49" s="45"/>
-      <c r="CJ49" s="46"/>
-    </row>
-    <row r="50" spans="15:88">
-      <c r="O50" s="8"/>
-      <c r="Z50" s="8"/>
-      <c r="AM50" s="8"/>
-      <c r="AW50" s="8"/>
-      <c r="AX50" s="45"/>
-      <c r="AY50" s="46"/>
-      <c r="AZ50" s="47"/>
-      <c r="BA50" s="46"/>
-      <c r="BB50" s="43"/>
-      <c r="BC50" s="42"/>
-      <c r="BD50" s="45"/>
-      <c r="BE50" s="45"/>
-      <c r="BF50" s="45"/>
-      <c r="BG50" s="45" t="s">
-        <v>129</v>
-      </c>
-      <c r="BH50" s="45"/>
-      <c r="BI50" s="45"/>
-      <c r="BJ50" s="46"/>
-      <c r="BK50" s="45"/>
-      <c r="BL50" s="45"/>
-      <c r="BM50" s="45"/>
-      <c r="BN50" s="45"/>
-      <c r="BO50" s="45"/>
-      <c r="BP50" s="45"/>
-      <c r="BQ50" s="45"/>
-      <c r="BR50" s="45"/>
-      <c r="BS50" s="45"/>
-      <c r="BT50" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="BU50" s="45"/>
-      <c r="BV50" s="45"/>
-      <c r="BW50" s="45"/>
-      <c r="BX50" s="45"/>
-      <c r="BY50" s="45"/>
-      <c r="BZ50" s="45"/>
-      <c r="CA50" s="45"/>
-      <c r="CB50" s="46"/>
-      <c r="CC50" s="45"/>
-      <c r="CD50" s="45"/>
-      <c r="CE50" s="45"/>
-      <c r="CF50" s="45"/>
-      <c r="CG50" s="45"/>
-      <c r="CH50" s="45"/>
-      <c r="CI50" s="45"/>
-      <c r="CJ50" s="46"/>
-    </row>
-    <row r="51" spans="15:88">
-      <c r="O51" s="8"/>
-      <c r="Z51" s="8"/>
-      <c r="AM51" s="8"/>
-      <c r="AW51" s="8"/>
-      <c r="AX51" s="45"/>
-      <c r="AY51" s="46"/>
-      <c r="AZ51" s="47"/>
-      <c r="BA51" s="46"/>
-      <c r="BB51" s="47"/>
-      <c r="BC51" s="46"/>
-      <c r="BD51" s="45"/>
-      <c r="BE51" s="45"/>
-      <c r="BF51" s="45"/>
-      <c r="BG51" s="45"/>
-      <c r="BH51" s="45"/>
-      <c r="BI51" s="45"/>
-      <c r="BJ51" s="46"/>
-      <c r="BK51" s="45"/>
-      <c r="BL51" s="45"/>
-      <c r="BM51" s="45"/>
-      <c r="BN51" s="45"/>
-      <c r="BO51" s="45"/>
-      <c r="BP51" s="45"/>
-      <c r="BQ51" s="45"/>
-      <c r="BR51" s="45"/>
-      <c r="BS51" s="45"/>
-      <c r="BT51" s="46"/>
-      <c r="BU51" s="49"/>
-      <c r="BV51" s="50"/>
-      <c r="BW51" s="50"/>
-      <c r="BX51" s="51"/>
-      <c r="BY51" s="45"/>
-      <c r="BZ51" s="45"/>
-      <c r="CA51" s="45"/>
-      <c r="CB51" s="46"/>
-      <c r="CC51" s="45"/>
-      <c r="CD51" s="45"/>
-      <c r="CE51" s="45"/>
-      <c r="CF51" s="45"/>
-      <c r="CG51" s="45"/>
-      <c r="CH51" s="45"/>
-      <c r="CI51" s="45"/>
-      <c r="CJ51" s="46"/>
-    </row>
-    <row r="52" spans="15:88">
-      <c r="O52" s="8"/>
-      <c r="Z52" s="8"/>
-      <c r="AM52" s="8"/>
-      <c r="AW52" s="8"/>
-      <c r="AX52" s="45"/>
-      <c r="AY52" s="46"/>
-      <c r="AZ52" s="47"/>
-      <c r="BA52" s="45"/>
-      <c r="BB52" s="47"/>
-      <c r="BC52" s="46"/>
-      <c r="BD52" s="45"/>
-      <c r="BE52" s="45"/>
-      <c r="BF52" s="45"/>
-      <c r="BG52" s="45"/>
-      <c r="BH52" s="45"/>
-      <c r="BI52" s="45"/>
-      <c r="BJ52" s="46"/>
-      <c r="BK52" s="45"/>
-      <c r="BL52" s="45"/>
-      <c r="BM52" s="45"/>
-      <c r="BN52" s="45"/>
-      <c r="BO52" s="45"/>
-      <c r="BP52" s="45"/>
-      <c r="BQ52" s="45"/>
-      <c r="BR52" s="45"/>
-      <c r="BS52" s="45"/>
-      <c r="BT52" s="46"/>
-      <c r="BU52" s="43"/>
-      <c r="BV52" s="42"/>
-      <c r="BW52" s="45"/>
-      <c r="BX52" s="45"/>
-      <c r="BY52" s="45"/>
-      <c r="BZ52" s="45"/>
-      <c r="CA52" s="45"/>
-      <c r="CB52" s="46"/>
-      <c r="CC52" s="45"/>
-      <c r="CD52" s="45"/>
-      <c r="CE52" s="45"/>
-      <c r="CF52" s="45"/>
-      <c r="CG52" s="45"/>
-      <c r="CH52" s="45"/>
-      <c r="CI52" s="45"/>
-      <c r="CJ52" s="46"/>
-    </row>
-    <row r="53" spans="15:88">
-      <c r="O53" s="8"/>
-      <c r="Z53" s="8"/>
-      <c r="AM53" s="8"/>
-      <c r="AW53" s="8"/>
-      <c r="AX53" s="45"/>
-      <c r="AY53" s="46"/>
-      <c r="AZ53" s="47"/>
-      <c r="BA53" s="45"/>
-      <c r="BB53" s="47"/>
-      <c r="BC53" s="46"/>
-      <c r="BD53" s="45"/>
-      <c r="BE53" s="45"/>
-      <c r="BF53" s="45"/>
-      <c r="BG53" s="45"/>
-      <c r="BH53" s="45"/>
-      <c r="BI53" s="45"/>
-      <c r="BJ53" s="46"/>
-      <c r="BK53" s="45"/>
-      <c r="BL53" s="45"/>
-      <c r="BM53" s="45"/>
-      <c r="BN53" s="45"/>
-      <c r="BO53" s="45"/>
-      <c r="BP53" s="45"/>
-      <c r="BQ53" s="45"/>
-      <c r="BR53" s="45"/>
-      <c r="BS53" s="45"/>
-      <c r="BT53" s="46"/>
-      <c r="BU53" s="47"/>
-      <c r="BV53" s="46" t="s">
-        <v>154</v>
-      </c>
-      <c r="BW53" s="45"/>
-      <c r="BX53" s="45"/>
-      <c r="BY53" s="45"/>
-      <c r="BZ53" s="45"/>
-      <c r="CA53" s="45"/>
-      <c r="CB53" s="46" t="s">
-        <v>155</v>
-      </c>
-      <c r="CC53" s="45"/>
-      <c r="CD53" s="45"/>
-      <c r="CE53" s="45"/>
-      <c r="CF53" s="45"/>
-      <c r="CG53" s="45"/>
-      <c r="CH53" s="45"/>
-      <c r="CI53" s="45"/>
-      <c r="CJ53" s="46"/>
-    </row>
-    <row r="54" spans="15:88">
-      <c r="O54" s="8"/>
-      <c r="Z54" s="8"/>
-      <c r="AM54" s="8"/>
-      <c r="AW54" s="8"/>
-      <c r="AX54" s="45"/>
-      <c r="AY54" s="46"/>
-      <c r="AZ54" s="47"/>
-      <c r="BA54" s="45"/>
-      <c r="BB54" s="47"/>
-      <c r="BC54" s="46"/>
-      <c r="BD54" s="45"/>
-      <c r="BE54" s="45"/>
-      <c r="BF54" s="45"/>
-      <c r="BG54" s="45"/>
-      <c r="BH54" s="45"/>
-      <c r="BI54" s="45"/>
-      <c r="BJ54" s="46"/>
-      <c r="BK54" s="45"/>
-      <c r="BL54" s="45"/>
-      <c r="BM54" s="45"/>
-      <c r="BN54" s="45"/>
-      <c r="BO54" s="45"/>
-      <c r="BP54" s="45"/>
-      <c r="BQ54" s="45"/>
-      <c r="BR54" s="45"/>
-      <c r="BS54" s="45"/>
-      <c r="BT54" s="46"/>
-      <c r="BU54" s="47"/>
-      <c r="BV54" s="46"/>
-      <c r="BW54" s="45"/>
-      <c r="BX54" s="45"/>
-      <c r="BY54" s="45"/>
-      <c r="BZ54" s="45"/>
-      <c r="CA54" s="45"/>
-      <c r="CB54" s="46"/>
-      <c r="CC54" s="49"/>
-      <c r="CD54" s="50"/>
-      <c r="CE54" s="50"/>
-      <c r="CF54" s="51"/>
-      <c r="CG54" s="45"/>
-      <c r="CH54" s="45"/>
-      <c r="CI54" s="45"/>
-      <c r="CJ54" s="46"/>
-    </row>
-    <row r="55" spans="15:88">
-      <c r="O55" s="8"/>
-      <c r="Z55" s="8"/>
-      <c r="AM55" s="8"/>
-      <c r="AW55" s="8"/>
-      <c r="AX55" s="45"/>
-      <c r="AY55" s="46"/>
-      <c r="AZ55" s="47"/>
-      <c r="BA55" s="45"/>
-      <c r="BB55" s="47"/>
-      <c r="BC55" s="46"/>
-      <c r="BD55" s="45"/>
-      <c r="BE55" s="45"/>
-      <c r="BF55" s="45"/>
-      <c r="BG55" s="45"/>
-      <c r="BH55" s="45"/>
-      <c r="BI55" s="45"/>
-      <c r="BJ55" s="46"/>
-      <c r="BK55" s="45"/>
-      <c r="BL55" s="45"/>
-      <c r="BM55" s="45"/>
-      <c r="BN55" s="45"/>
-      <c r="BO55" s="45"/>
-      <c r="BP55" s="45"/>
-      <c r="BQ55" s="45"/>
-      <c r="BR55" s="45"/>
-      <c r="BS55" s="45"/>
-      <c r="BT55" s="46"/>
-      <c r="BU55" s="47"/>
-      <c r="BV55" s="46"/>
-      <c r="BW55" s="45"/>
-      <c r="BX55" s="45"/>
-      <c r="BY55" s="45"/>
-      <c r="BZ55" s="45"/>
-      <c r="CA55" s="45"/>
-      <c r="CB55" s="46"/>
-      <c r="CC55" s="43"/>
-      <c r="CD55" s="42"/>
-      <c r="CE55" s="45"/>
-      <c r="CF55" s="45"/>
-      <c r="CG55" s="45"/>
-      <c r="CH55" s="45"/>
-      <c r="CI55" s="45"/>
-      <c r="CJ55" s="46"/>
-    </row>
-    <row r="56" spans="15:88">
-      <c r="O56" s="8"/>
-      <c r="Z56" s="8"/>
-      <c r="AM56" s="8"/>
-      <c r="AW56" s="8"/>
-      <c r="AX56" s="45"/>
-      <c r="AY56" s="46"/>
-      <c r="AZ56" s="47"/>
-      <c r="BA56" s="45"/>
-      <c r="BB56" s="47"/>
-      <c r="BC56" s="46"/>
-      <c r="BD56" s="45"/>
-      <c r="BE56" s="45"/>
-      <c r="BF56" s="45"/>
-      <c r="BG56" s="45"/>
-      <c r="BH56" s="45"/>
-      <c r="BI56" s="45"/>
-      <c r="BJ56" s="46"/>
-      <c r="BK56" s="45"/>
-      <c r="BL56" s="45"/>
-      <c r="BM56" s="45"/>
-      <c r="BN56" s="45"/>
-      <c r="BO56" s="45"/>
-      <c r="BP56" s="45"/>
-      <c r="BQ56" s="45"/>
-      <c r="BR56" s="45"/>
-      <c r="BS56" s="45"/>
-      <c r="BT56" s="46"/>
-      <c r="BU56" s="47"/>
-      <c r="BV56" s="46"/>
-      <c r="BW56" s="45"/>
-      <c r="BX56" s="45"/>
-      <c r="BY56" s="45"/>
-      <c r="BZ56" s="45"/>
-      <c r="CA56" s="45"/>
-      <c r="CB56" s="46"/>
-      <c r="CC56" s="47"/>
-      <c r="CD56" s="46"/>
-      <c r="CE56" s="45" t="s">
-        <v>156</v>
-      </c>
-      <c r="CF56" s="45"/>
-      <c r="CG56" s="45"/>
-      <c r="CH56" s="45"/>
-      <c r="CI56" s="45"/>
-      <c r="CJ56" s="46"/>
+      <c r="CF56" s="42"/>
+      <c r="CG56" s="42"/>
+      <c r="CH56" s="42"/>
+      <c r="CI56" s="42"/>
+      <c r="CJ56" s="43"/>
     </row>
     <row r="57" spans="15:88">
-      <c r="O57" s="8"/>
-      <c r="Z57" s="8"/>
-      <c r="AM57" s="8"/>
-      <c r="AW57" s="8"/>
-      <c r="AX57" s="45"/>
-      <c r="AY57" s="46"/>
-      <c r="AZ57" s="47"/>
-      <c r="BA57" s="45"/>
-      <c r="BB57" s="47"/>
-      <c r="BC57" s="46"/>
-      <c r="BD57" s="45"/>
-      <c r="BE57" s="45"/>
-      <c r="BF57" s="45"/>
-      <c r="BG57" s="45"/>
-      <c r="BH57" s="45"/>
-      <c r="BI57" s="45"/>
-      <c r="BJ57" s="46"/>
-      <c r="BK57" s="45"/>
-      <c r="BL57" s="45"/>
-      <c r="BM57" s="45"/>
-      <c r="BN57" s="45"/>
-      <c r="BO57" s="45"/>
-      <c r="BP57" s="45"/>
-      <c r="BQ57" s="45"/>
-      <c r="BR57" s="45"/>
-      <c r="BS57" s="45"/>
-      <c r="BT57" s="46"/>
-      <c r="BU57" s="47"/>
-      <c r="BV57" s="46"/>
-      <c r="BW57" s="45"/>
-      <c r="BX57" s="45"/>
-      <c r="BY57" s="45"/>
-      <c r="BZ57" s="45"/>
-      <c r="CA57" s="45"/>
-      <c r="CB57" s="46"/>
-      <c r="CC57" s="53"/>
-      <c r="CD57" s="54"/>
-      <c r="CE57" s="45"/>
-      <c r="CF57" s="45"/>
-      <c r="CG57" s="45"/>
-      <c r="CH57" s="45"/>
-      <c r="CI57" s="45"/>
-      <c r="CJ57" s="46"/>
+      <c r="O57" s="6"/>
+      <c r="Z57" s="6"/>
+      <c r="AM57" s="6"/>
+      <c r="AW57" s="6"/>
+      <c r="AX57" s="42"/>
+      <c r="AY57" s="43"/>
+      <c r="AZ57" s="44"/>
+      <c r="BA57" s="42"/>
+      <c r="BB57" s="44"/>
+      <c r="BC57" s="43"/>
+      <c r="BD57" s="42"/>
+      <c r="BE57" s="42"/>
+      <c r="BF57" s="42"/>
+      <c r="BG57" s="42"/>
+      <c r="BH57" s="42"/>
+      <c r="BI57" s="42"/>
+      <c r="BJ57" s="43"/>
+      <c r="BK57" s="42"/>
+      <c r="BL57" s="42"/>
+      <c r="BM57" s="42"/>
+      <c r="BN57" s="42"/>
+      <c r="BO57" s="42"/>
+      <c r="BP57" s="42"/>
+      <c r="BQ57" s="42"/>
+      <c r="BR57" s="42"/>
+      <c r="BS57" s="42"/>
+      <c r="BT57" s="43"/>
+      <c r="BU57" s="44"/>
+      <c r="BV57" s="43"/>
+      <c r="BW57" s="42"/>
+      <c r="BX57" s="42"/>
+      <c r="BY57" s="42"/>
+      <c r="BZ57" s="42"/>
+      <c r="CA57" s="42"/>
+      <c r="CB57" s="43"/>
+      <c r="CC57" s="50"/>
+      <c r="CD57" s="51"/>
+      <c r="CE57" s="42"/>
+      <c r="CF57" s="42"/>
+      <c r="CG57" s="42"/>
+      <c r="CH57" s="42"/>
+      <c r="CI57" s="42"/>
+      <c r="CJ57" s="43"/>
     </row>
     <row r="58" spans="15:88">
-      <c r="O58" s="8"/>
-      <c r="Z58" s="8"/>
-      <c r="AM58" s="8"/>
-      <c r="AW58" s="8"/>
-      <c r="AX58" s="45"/>
-      <c r="AY58" s="46"/>
-      <c r="AZ58" s="47"/>
-      <c r="BA58" s="45"/>
-      <c r="BB58" s="47"/>
-      <c r="BC58" s="46"/>
-      <c r="BD58" s="45"/>
-      <c r="BE58" s="45"/>
-      <c r="BF58" s="45"/>
-      <c r="BG58" s="45"/>
-      <c r="BH58" s="45"/>
-      <c r="BI58" s="45"/>
-      <c r="BJ58" s="46"/>
-      <c r="BK58" s="45"/>
-      <c r="BL58" s="45"/>
-      <c r="BM58" s="45"/>
-      <c r="BN58" s="45"/>
-      <c r="BO58" s="45"/>
-      <c r="BP58" s="45"/>
-      <c r="BQ58" s="45"/>
-      <c r="BR58" s="45"/>
-      <c r="BS58" s="45"/>
-      <c r="BT58" s="46"/>
-      <c r="BU58" s="47"/>
-      <c r="BV58" s="46"/>
-      <c r="BW58" s="45"/>
-      <c r="BX58" s="45"/>
-      <c r="BY58" s="45"/>
-      <c r="BZ58" s="45"/>
-      <c r="CA58" s="45"/>
-      <c r="CB58" s="46"/>
-      <c r="CC58" s="45"/>
-      <c r="CD58" s="45"/>
-      <c r="CE58" s="45"/>
-      <c r="CF58" s="45"/>
-      <c r="CG58" s="45"/>
-      <c r="CH58" s="45"/>
-      <c r="CI58" s="45"/>
-      <c r="CJ58" s="46"/>
+      <c r="O58" s="6"/>
+      <c r="Z58" s="6"/>
+      <c r="AM58" s="6"/>
+      <c r="AW58" s="6"/>
+      <c r="AX58" s="42"/>
+      <c r="AY58" s="43"/>
+      <c r="AZ58" s="44"/>
+      <c r="BA58" s="42"/>
+      <c r="BB58" s="44"/>
+      <c r="BC58" s="43"/>
+      <c r="BD58" s="42"/>
+      <c r="BE58" s="42"/>
+      <c r="BF58" s="42"/>
+      <c r="BG58" s="42"/>
+      <c r="BH58" s="42"/>
+      <c r="BI58" s="42"/>
+      <c r="BJ58" s="43"/>
+      <c r="BK58" s="42"/>
+      <c r="BL58" s="42"/>
+      <c r="BM58" s="42"/>
+      <c r="BN58" s="42"/>
+      <c r="BO58" s="42"/>
+      <c r="BP58" s="42"/>
+      <c r="BQ58" s="42"/>
+      <c r="BR58" s="42"/>
+      <c r="BS58" s="42"/>
+      <c r="BT58" s="43"/>
+      <c r="BU58" s="44"/>
+      <c r="BV58" s="43"/>
+      <c r="BW58" s="42"/>
+      <c r="BX58" s="42"/>
+      <c r="BY58" s="42"/>
+      <c r="BZ58" s="42"/>
+      <c r="CA58" s="42"/>
+      <c r="CB58" s="43"/>
+      <c r="CC58" s="42"/>
+      <c r="CD58" s="42"/>
+      <c r="CE58" s="42"/>
+      <c r="CF58" s="42"/>
+      <c r="CG58" s="42"/>
+      <c r="CH58" s="42"/>
+      <c r="CI58" s="42"/>
+      <c r="CJ58" s="43"/>
     </row>
     <row r="59" spans="15:88">
-      <c r="O59" s="8"/>
-      <c r="Z59" s="8"/>
-      <c r="AM59" s="8"/>
-      <c r="AW59" s="8"/>
-      <c r="AX59" s="45"/>
-      <c r="AY59" s="46"/>
-      <c r="AZ59" s="47"/>
-      <c r="BA59" s="45"/>
-      <c r="BB59" s="47"/>
-      <c r="BC59" s="46"/>
-      <c r="BD59" s="45"/>
-      <c r="BE59" s="45"/>
-      <c r="BF59" s="45"/>
-      <c r="BG59" s="45"/>
-      <c r="BH59" s="45"/>
-      <c r="BI59" s="45"/>
-      <c r="BJ59" s="46"/>
-      <c r="BK59" s="45"/>
-      <c r="BL59" s="45"/>
-      <c r="BM59" s="45"/>
-      <c r="BN59" s="45"/>
-      <c r="BO59" s="45"/>
-      <c r="BP59" s="45"/>
-      <c r="BQ59" s="45"/>
-      <c r="BR59" s="45"/>
-      <c r="BS59" s="45"/>
-      <c r="BT59" s="46"/>
-      <c r="BU59" s="47"/>
-      <c r="BV59" s="46"/>
-      <c r="BW59" s="45"/>
-      <c r="BX59" s="45"/>
-      <c r="BY59" s="45"/>
-      <c r="BZ59" s="45"/>
-      <c r="CA59" s="45"/>
-      <c r="CB59" s="46"/>
-      <c r="CC59" s="45"/>
-      <c r="CD59" s="45"/>
-      <c r="CE59" s="45"/>
-      <c r="CF59" s="45"/>
-      <c r="CG59" s="45"/>
-      <c r="CH59" s="45"/>
-      <c r="CI59" s="45"/>
-      <c r="CJ59" s="46"/>
+      <c r="O59" s="6"/>
+      <c r="Z59" s="6"/>
+      <c r="AM59" s="6"/>
+      <c r="AW59" s="6"/>
+      <c r="AX59" s="42"/>
+      <c r="AY59" s="43"/>
+      <c r="AZ59" s="44"/>
+      <c r="BA59" s="42"/>
+      <c r="BB59" s="44"/>
+      <c r="BC59" s="43"/>
+      <c r="BD59" s="42"/>
+      <c r="BE59" s="42"/>
+      <c r="BF59" s="42"/>
+      <c r="BG59" s="42"/>
+      <c r="BH59" s="42"/>
+      <c r="BI59" s="42"/>
+      <c r="BJ59" s="43"/>
+      <c r="BK59" s="42"/>
+      <c r="BL59" s="42"/>
+      <c r="BM59" s="42"/>
+      <c r="BN59" s="42"/>
+      <c r="BO59" s="42"/>
+      <c r="BP59" s="42"/>
+      <c r="BQ59" s="42"/>
+      <c r="BR59" s="42"/>
+      <c r="BS59" s="42"/>
+      <c r="BT59" s="43"/>
+      <c r="BU59" s="44"/>
+      <c r="BV59" s="43"/>
+      <c r="BW59" s="42"/>
+      <c r="BX59" s="42"/>
+      <c r="BY59" s="42"/>
+      <c r="BZ59" s="42"/>
+      <c r="CA59" s="42"/>
+      <c r="CB59" s="43"/>
+      <c r="CC59" s="42"/>
+      <c r="CD59" s="42"/>
+      <c r="CE59" s="42"/>
+      <c r="CF59" s="42"/>
+      <c r="CG59" s="42"/>
+      <c r="CH59" s="42"/>
+      <c r="CI59" s="42"/>
+      <c r="CJ59" s="43"/>
     </row>
     <row r="60" spans="15:88">
-      <c r="O60" s="8"/>
-      <c r="Z60" s="8"/>
-      <c r="AM60" s="8"/>
-      <c r="AW60" s="8"/>
-      <c r="AX60" s="45"/>
-      <c r="AY60" s="46"/>
-      <c r="AZ60" s="47"/>
-      <c r="BA60" s="45"/>
-      <c r="BB60" s="47"/>
-      <c r="BC60" s="46"/>
-      <c r="BD60" s="45"/>
-      <c r="BE60" s="45"/>
-      <c r="BF60" s="45"/>
-      <c r="BG60" s="45"/>
-      <c r="BH60" s="45"/>
-      <c r="BI60" s="45"/>
-      <c r="BJ60" s="46"/>
-      <c r="BK60" s="45"/>
-      <c r="BL60" s="45"/>
-      <c r="BM60" s="45"/>
-      <c r="BN60" s="45"/>
-      <c r="BO60" s="45"/>
-      <c r="BP60" s="45"/>
-      <c r="BQ60" s="45"/>
-      <c r="BR60" s="45"/>
-      <c r="BS60" s="45"/>
-      <c r="BT60" s="46"/>
-      <c r="BU60" s="47"/>
-      <c r="BV60" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="BW60" s="45"/>
-      <c r="BX60" s="45"/>
-      <c r="BY60" s="45"/>
-      <c r="BZ60" s="45"/>
-      <c r="CA60" s="45"/>
-      <c r="CB60" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="CC60" s="45"/>
-      <c r="CD60" s="45"/>
-      <c r="CE60" s="45"/>
-      <c r="CF60" s="45"/>
-      <c r="CG60" s="45"/>
-      <c r="CH60" s="45"/>
-      <c r="CI60" s="45"/>
-      <c r="CJ60" s="46"/>
+      <c r="O60" s="6"/>
+      <c r="Z60" s="6"/>
+      <c r="AM60" s="6"/>
+      <c r="AW60" s="6"/>
+      <c r="AX60" s="42"/>
+      <c r="AY60" s="43"/>
+      <c r="AZ60" s="44"/>
+      <c r="BA60" s="42"/>
+      <c r="BB60" s="44"/>
+      <c r="BC60" s="43"/>
+      <c r="BD60" s="42"/>
+      <c r="BE60" s="42"/>
+      <c r="BF60" s="42"/>
+      <c r="BG60" s="42"/>
+      <c r="BH60" s="42"/>
+      <c r="BI60" s="42"/>
+      <c r="BJ60" s="43"/>
+      <c r="BK60" s="42"/>
+      <c r="BL60" s="42"/>
+      <c r="BM60" s="42"/>
+      <c r="BN60" s="42"/>
+      <c r="BO60" s="42"/>
+      <c r="BP60" s="42"/>
+      <c r="BQ60" s="42"/>
+      <c r="BR60" s="42"/>
+      <c r="BS60" s="42"/>
+      <c r="BT60" s="43"/>
+      <c r="BU60" s="44"/>
+      <c r="BV60" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="BW60" s="42"/>
+      <c r="BX60" s="42"/>
+      <c r="BY60" s="42"/>
+      <c r="BZ60" s="42"/>
+      <c r="CA60" s="42"/>
+      <c r="CB60" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="CC60" s="42"/>
+      <c r="CD60" s="42"/>
+      <c r="CE60" s="42"/>
+      <c r="CF60" s="42"/>
+      <c r="CG60" s="42"/>
+      <c r="CH60" s="42"/>
+      <c r="CI60" s="42"/>
+      <c r="CJ60" s="43"/>
     </row>
     <row r="61" spans="15:88">
-      <c r="O61" s="8"/>
-      <c r="Z61" s="8"/>
-      <c r="AM61" s="8"/>
-      <c r="AW61" s="8"/>
-      <c r="AX61" s="45"/>
-      <c r="AY61" s="46"/>
-      <c r="AZ61" s="47"/>
-      <c r="BA61" s="45"/>
-      <c r="BB61" s="47"/>
-      <c r="BC61" s="46"/>
-      <c r="BD61" s="45"/>
-      <c r="BE61" s="45"/>
-      <c r="BF61" s="45"/>
-      <c r="BG61" s="45"/>
-      <c r="BH61" s="45"/>
-      <c r="BI61" s="45"/>
-      <c r="BJ61" s="46"/>
-      <c r="BK61" s="45"/>
-      <c r="BL61" s="45"/>
-      <c r="BM61" s="45"/>
-      <c r="BN61" s="45"/>
-      <c r="BO61" s="45"/>
-      <c r="BP61" s="45"/>
-      <c r="BQ61" s="45"/>
-      <c r="BR61" s="45"/>
-      <c r="BS61" s="45"/>
-      <c r="BT61" s="46"/>
-      <c r="BU61" s="47"/>
-      <c r="BV61" s="46"/>
-      <c r="BW61" s="45"/>
-      <c r="BX61" s="45"/>
-      <c r="BY61" s="45"/>
-      <c r="BZ61" s="45"/>
-      <c r="CA61" s="45"/>
-      <c r="CB61" s="46"/>
-      <c r="CC61" s="49"/>
-      <c r="CD61" s="50"/>
-      <c r="CE61" s="50"/>
-      <c r="CF61" s="51"/>
-      <c r="CG61" s="45"/>
-      <c r="CH61" s="45"/>
-      <c r="CI61" s="45"/>
-      <c r="CJ61" s="46"/>
+      <c r="O61" s="6"/>
+      <c r="Z61" s="6"/>
+      <c r="AM61" s="6"/>
+      <c r="AW61" s="6"/>
+      <c r="AX61" s="42"/>
+      <c r="AY61" s="43"/>
+      <c r="AZ61" s="44"/>
+      <c r="BA61" s="42"/>
+      <c r="BB61" s="44"/>
+      <c r="BC61" s="43"/>
+      <c r="BD61" s="42"/>
+      <c r="BE61" s="42"/>
+      <c r="BF61" s="42"/>
+      <c r="BG61" s="42"/>
+      <c r="BH61" s="42"/>
+      <c r="BI61" s="42"/>
+      <c r="BJ61" s="43"/>
+      <c r="BK61" s="42"/>
+      <c r="BL61" s="42"/>
+      <c r="BM61" s="42"/>
+      <c r="BN61" s="42"/>
+      <c r="BO61" s="42"/>
+      <c r="BP61" s="42"/>
+      <c r="BQ61" s="42"/>
+      <c r="BR61" s="42"/>
+      <c r="BS61" s="42"/>
+      <c r="BT61" s="43"/>
+      <c r="BU61" s="44"/>
+      <c r="BV61" s="43"/>
+      <c r="BW61" s="42"/>
+      <c r="BX61" s="42"/>
+      <c r="BY61" s="42"/>
+      <c r="BZ61" s="42"/>
+      <c r="CA61" s="42"/>
+      <c r="CB61" s="43"/>
+      <c r="CC61" s="46"/>
+      <c r="CD61" s="47"/>
+      <c r="CE61" s="47"/>
+      <c r="CF61" s="48"/>
+      <c r="CG61" s="42"/>
+      <c r="CH61" s="42"/>
+      <c r="CI61" s="42"/>
+      <c r="CJ61" s="43"/>
     </row>
     <row r="62" spans="15:88">
-      <c r="O62" s="8"/>
-      <c r="Z62" s="8"/>
-      <c r="AM62" s="8"/>
-      <c r="AW62" s="8"/>
-      <c r="AX62" s="45"/>
-      <c r="AY62" s="46"/>
-      <c r="AZ62" s="47"/>
-      <c r="BA62" s="45"/>
-      <c r="BB62" s="47"/>
-      <c r="BC62" s="46"/>
-      <c r="BD62" s="45"/>
-      <c r="BE62" s="45"/>
-      <c r="BF62" s="45"/>
-      <c r="BG62" s="45"/>
-      <c r="BH62" s="45"/>
-      <c r="BI62" s="45"/>
-      <c r="BJ62" s="46"/>
-      <c r="BK62" s="45"/>
-      <c r="BL62" s="45"/>
-      <c r="BM62" s="45"/>
-      <c r="BN62" s="45"/>
-      <c r="BO62" s="45"/>
-      <c r="BP62" s="45"/>
-      <c r="BQ62" s="45"/>
-      <c r="BR62" s="45"/>
-      <c r="BS62" s="45"/>
-      <c r="BT62" s="46"/>
-      <c r="BU62" s="47"/>
-      <c r="BV62" s="46"/>
-      <c r="BW62" s="45"/>
-      <c r="BX62" s="45"/>
-      <c r="BY62" s="45"/>
-      <c r="BZ62" s="45"/>
-      <c r="CA62" s="45"/>
-      <c r="CB62" s="46"/>
-      <c r="CC62" s="43"/>
-      <c r="CD62" s="44"/>
-      <c r="CE62" s="43"/>
-      <c r="CF62" s="45"/>
-      <c r="CG62" s="45"/>
-      <c r="CH62" s="45"/>
-      <c r="CI62" s="45"/>
-      <c r="CJ62" s="46"/>
+      <c r="O62" s="6"/>
+      <c r="Z62" s="6"/>
+      <c r="AM62" s="6"/>
+      <c r="AW62" s="6"/>
+      <c r="AX62" s="42"/>
+      <c r="AY62" s="43"/>
+      <c r="AZ62" s="44"/>
+      <c r="BA62" s="42"/>
+      <c r="BB62" s="44"/>
+      <c r="BC62" s="43"/>
+      <c r="BD62" s="42"/>
+      <c r="BE62" s="42"/>
+      <c r="BF62" s="42"/>
+      <c r="BG62" s="42"/>
+      <c r="BH62" s="42"/>
+      <c r="BI62" s="42"/>
+      <c r="BJ62" s="43"/>
+      <c r="BK62" s="42"/>
+      <c r="BL62" s="42"/>
+      <c r="BM62" s="42"/>
+      <c r="BN62" s="42"/>
+      <c r="BO62" s="42"/>
+      <c r="BP62" s="42"/>
+      <c r="BQ62" s="42"/>
+      <c r="BR62" s="42"/>
+      <c r="BS62" s="42"/>
+      <c r="BT62" s="43"/>
+      <c r="BU62" s="44"/>
+      <c r="BV62" s="43"/>
+      <c r="BW62" s="42"/>
+      <c r="BX62" s="42"/>
+      <c r="BY62" s="42"/>
+      <c r="BZ62" s="42"/>
+      <c r="CA62" s="42"/>
+      <c r="CB62" s="43"/>
+      <c r="CC62" s="40"/>
+      <c r="CD62" s="41"/>
+      <c r="CE62" s="40"/>
+      <c r="CF62" s="42"/>
+      <c r="CG62" s="42"/>
+      <c r="CH62" s="42"/>
+      <c r="CI62" s="42"/>
+      <c r="CJ62" s="43"/>
     </row>
     <row r="63" spans="15:88">
-      <c r="O63" s="8"/>
-      <c r="Z63" s="8"/>
-      <c r="AM63" s="8"/>
-      <c r="AW63" s="8"/>
-      <c r="AX63" s="45"/>
-      <c r="AY63" s="46"/>
-      <c r="AZ63" s="47"/>
-      <c r="BA63" s="45"/>
-      <c r="BB63" s="47"/>
-      <c r="BC63" s="46"/>
-      <c r="BD63" s="45"/>
-      <c r="BE63" s="45"/>
-      <c r="BF63" s="45"/>
-      <c r="BG63" s="45"/>
-      <c r="BH63" s="45"/>
-      <c r="BI63" s="45"/>
-      <c r="BJ63" s="46"/>
-      <c r="BK63" s="45"/>
-      <c r="BL63" s="45"/>
-      <c r="BM63" s="45"/>
-      <c r="BN63" s="45"/>
-      <c r="BO63" s="45"/>
-      <c r="BP63" s="45"/>
-      <c r="BQ63" s="45"/>
-      <c r="BR63" s="45"/>
-      <c r="BS63" s="45"/>
-      <c r="BT63" s="46"/>
-      <c r="BU63" s="47"/>
-      <c r="BV63" s="46"/>
-      <c r="BW63" s="45"/>
-      <c r="BX63" s="45"/>
-      <c r="BY63" s="45"/>
-      <c r="BZ63" s="45"/>
-      <c r="CA63" s="45"/>
-      <c r="CB63" s="46"/>
-      <c r="CC63" s="52" t="s">
-        <v>135</v>
-      </c>
-      <c r="CD63" s="45"/>
-      <c r="CE63" s="45"/>
-      <c r="CF63" s="45"/>
-      <c r="CG63" s="45"/>
-      <c r="CH63" s="45"/>
-      <c r="CI63" s="45"/>
-      <c r="CJ63" s="46"/>
+      <c r="O63" s="6"/>
+      <c r="Z63" s="6"/>
+      <c r="AM63" s="6"/>
+      <c r="AW63" s="6"/>
+      <c r="AX63" s="42"/>
+      <c r="AY63" s="43"/>
+      <c r="AZ63" s="44"/>
+      <c r="BA63" s="42"/>
+      <c r="BB63" s="44"/>
+      <c r="BC63" s="43"/>
+      <c r="BD63" s="42"/>
+      <c r="BE63" s="42"/>
+      <c r="BF63" s="42"/>
+      <c r="BG63" s="42"/>
+      <c r="BH63" s="42"/>
+      <c r="BI63" s="42"/>
+      <c r="BJ63" s="43"/>
+      <c r="BK63" s="42"/>
+      <c r="BL63" s="42"/>
+      <c r="BM63" s="42"/>
+      <c r="BN63" s="42"/>
+      <c r="BO63" s="42"/>
+      <c r="BP63" s="42"/>
+      <c r="BQ63" s="42"/>
+      <c r="BR63" s="42"/>
+      <c r="BS63" s="42"/>
+      <c r="BT63" s="43"/>
+      <c r="BU63" s="44"/>
+      <c r="BV63" s="43"/>
+      <c r="BW63" s="42"/>
+      <c r="BX63" s="42"/>
+      <c r="BY63" s="42"/>
+      <c r="BZ63" s="42"/>
+      <c r="CA63" s="42"/>
+      <c r="CB63" s="43"/>
+      <c r="CC63" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="CD63" s="42"/>
+      <c r="CE63" s="42"/>
+      <c r="CF63" s="42"/>
+      <c r="CG63" s="42"/>
+      <c r="CH63" s="42"/>
+      <c r="CI63" s="42"/>
+      <c r="CJ63" s="43"/>
     </row>
     <row r="64" spans="15:88">
-      <c r="O64" s="8"/>
-      <c r="Z64" s="8"/>
-      <c r="AM64" s="8"/>
-      <c r="AW64" s="8"/>
-      <c r="AX64" s="45"/>
-      <c r="AY64" s="46"/>
-      <c r="AZ64" s="47"/>
-      <c r="BA64" s="45"/>
-      <c r="BB64" s="47"/>
-      <c r="BC64" s="46"/>
-      <c r="BD64" s="45"/>
-      <c r="BE64" s="45"/>
-      <c r="BF64" s="45"/>
-      <c r="BG64" s="45"/>
-      <c r="BH64" s="45"/>
-      <c r="BI64" s="45"/>
-      <c r="BJ64" s="46"/>
-      <c r="BK64" s="45"/>
-      <c r="BL64" s="45"/>
-      <c r="BM64" s="45"/>
-      <c r="BN64" s="45"/>
-      <c r="BO64" s="45"/>
-      <c r="BP64" s="45"/>
-      <c r="BQ64" s="45"/>
-      <c r="BR64" s="45"/>
-      <c r="BS64" s="45"/>
-      <c r="BT64" s="46"/>
-      <c r="BU64" s="47"/>
-      <c r="BV64" s="46"/>
-      <c r="BW64" s="45"/>
-      <c r="BX64" s="45"/>
-      <c r="BY64" s="45"/>
-      <c r="BZ64" s="45"/>
-      <c r="CA64" s="45"/>
-      <c r="CB64" s="46"/>
-      <c r="CC64" s="53"/>
-      <c r="CD64" s="54"/>
-      <c r="CE64" s="45"/>
-      <c r="CF64" s="45"/>
-      <c r="CG64" s="45"/>
-      <c r="CH64" s="45"/>
-      <c r="CI64" s="45"/>
-      <c r="CJ64" s="46"/>
+      <c r="O64" s="6"/>
+      <c r="Z64" s="6"/>
+      <c r="AM64" s="6"/>
+      <c r="AW64" s="6"/>
+      <c r="AX64" s="42"/>
+      <c r="AY64" s="43"/>
+      <c r="AZ64" s="44"/>
+      <c r="BA64" s="42"/>
+      <c r="BB64" s="44"/>
+      <c r="BC64" s="43"/>
+      <c r="BD64" s="42"/>
+      <c r="BE64" s="42"/>
+      <c r="BF64" s="42"/>
+      <c r="BG64" s="42"/>
+      <c r="BH64" s="42"/>
+      <c r="BI64" s="42"/>
+      <c r="BJ64" s="43"/>
+      <c r="BK64" s="42"/>
+      <c r="BL64" s="42"/>
+      <c r="BM64" s="42"/>
+      <c r="BN64" s="42"/>
+      <c r="BO64" s="42"/>
+      <c r="BP64" s="42"/>
+      <c r="BQ64" s="42"/>
+      <c r="BR64" s="42"/>
+      <c r="BS64" s="42"/>
+      <c r="BT64" s="43"/>
+      <c r="BU64" s="44"/>
+      <c r="BV64" s="43"/>
+      <c r="BW64" s="42"/>
+      <c r="BX64" s="42"/>
+      <c r="BY64" s="42"/>
+      <c r="BZ64" s="42"/>
+      <c r="CA64" s="42"/>
+      <c r="CB64" s="43"/>
+      <c r="CC64" s="50"/>
+      <c r="CD64" s="51"/>
+      <c r="CE64" s="42"/>
+      <c r="CF64" s="42"/>
+      <c r="CG64" s="42"/>
+      <c r="CH64" s="42"/>
+      <c r="CI64" s="42"/>
+      <c r="CJ64" s="43"/>
     </row>
     <row r="65" spans="15:88">
-      <c r="O65" s="8"/>
-      <c r="Z65" s="8"/>
-      <c r="AM65" s="8"/>
-      <c r="AW65" s="8"/>
-      <c r="AX65" s="45"/>
-      <c r="AY65" s="46"/>
-      <c r="AZ65" s="47"/>
-      <c r="BA65" s="46"/>
-      <c r="BB65" s="47"/>
-      <c r="BC65" s="46"/>
-      <c r="BD65" s="45"/>
-      <c r="BE65" s="45"/>
-      <c r="BF65" s="45"/>
-      <c r="BG65" s="45"/>
-      <c r="BH65" s="45"/>
-      <c r="BI65" s="45"/>
-      <c r="BJ65" s="46"/>
-      <c r="BK65" s="45"/>
-      <c r="BL65" s="45"/>
-      <c r="BM65" s="45"/>
-      <c r="BN65" s="45"/>
-      <c r="BO65" s="45"/>
-      <c r="BP65" s="45"/>
-      <c r="BQ65" s="45"/>
-      <c r="BR65" s="45"/>
-      <c r="BS65" s="45"/>
-      <c r="BT65" s="46"/>
-      <c r="BU65" s="53"/>
-      <c r="BV65" s="54"/>
-      <c r="BW65" s="45"/>
-      <c r="BX65" s="45"/>
-      <c r="BY65" s="45"/>
-      <c r="BZ65" s="45"/>
-      <c r="CA65" s="45"/>
-      <c r="CB65" s="46"/>
-      <c r="CC65" s="45"/>
-      <c r="CD65" s="45"/>
-      <c r="CE65" s="45"/>
-      <c r="CF65" s="45"/>
-      <c r="CG65" s="45"/>
-      <c r="CH65" s="45"/>
-      <c r="CI65" s="45"/>
-      <c r="CJ65" s="46"/>
+      <c r="O65" s="6"/>
+      <c r="Z65" s="6"/>
+      <c r="AM65" s="6"/>
+      <c r="AW65" s="6"/>
+      <c r="AX65" s="42"/>
+      <c r="AY65" s="43"/>
+      <c r="AZ65" s="44"/>
+      <c r="BA65" s="43"/>
+      <c r="BB65" s="44"/>
+      <c r="BC65" s="43"/>
+      <c r="BD65" s="42"/>
+      <c r="BE65" s="42"/>
+      <c r="BF65" s="42"/>
+      <c r="BG65" s="42"/>
+      <c r="BH65" s="42"/>
+      <c r="BI65" s="42"/>
+      <c r="BJ65" s="43"/>
+      <c r="BK65" s="42"/>
+      <c r="BL65" s="42"/>
+      <c r="BM65" s="42"/>
+      <c r="BN65" s="42"/>
+      <c r="BO65" s="42"/>
+      <c r="BP65" s="42"/>
+      <c r="BQ65" s="42"/>
+      <c r="BR65" s="42"/>
+      <c r="BS65" s="42"/>
+      <c r="BT65" s="43"/>
+      <c r="BU65" s="50"/>
+      <c r="BV65" s="51"/>
+      <c r="BW65" s="42"/>
+      <c r="BX65" s="42"/>
+      <c r="BY65" s="42"/>
+      <c r="BZ65" s="42"/>
+      <c r="CA65" s="42"/>
+      <c r="CB65" s="43"/>
+      <c r="CC65" s="42"/>
+      <c r="CD65" s="42"/>
+      <c r="CE65" s="42"/>
+      <c r="CF65" s="42"/>
+      <c r="CG65" s="42"/>
+      <c r="CH65" s="42"/>
+      <c r="CI65" s="42"/>
+      <c r="CJ65" s="43"/>
     </row>
     <row r="66" spans="15:88">
-      <c r="O66" s="8"/>
-      <c r="Z66" s="8"/>
-      <c r="AM66" s="8"/>
-      <c r="AW66" s="8"/>
-      <c r="AX66" s="45"/>
-      <c r="AY66" s="46"/>
-      <c r="AZ66" s="47"/>
-      <c r="BA66" s="46"/>
-      <c r="BB66" s="47"/>
-      <c r="BC66" s="46"/>
-      <c r="BD66" s="45"/>
-      <c r="BE66" s="45"/>
-      <c r="BF66" s="45"/>
-      <c r="BG66" s="45"/>
-      <c r="BH66" s="45"/>
-      <c r="BI66" s="45"/>
-      <c r="BJ66" s="46"/>
-      <c r="BK66" s="45"/>
-      <c r="BL66" s="45"/>
-      <c r="BM66" s="45"/>
-      <c r="BN66" s="45"/>
-      <c r="BO66" s="45"/>
-      <c r="BP66" s="45"/>
-      <c r="BQ66" s="45"/>
-      <c r="BR66" s="45"/>
-      <c r="BS66" s="45"/>
-      <c r="BT66" s="46"/>
-      <c r="BU66" s="45"/>
-      <c r="BV66" s="45"/>
-      <c r="BW66" s="45"/>
-      <c r="BX66" s="45"/>
-      <c r="BY66" s="45"/>
-      <c r="BZ66" s="45"/>
-      <c r="CA66" s="45"/>
-      <c r="CB66" s="46"/>
-      <c r="CC66" s="45"/>
-      <c r="CD66" s="45"/>
-      <c r="CE66" s="45"/>
-      <c r="CF66" s="45"/>
-      <c r="CG66" s="45"/>
-      <c r="CH66" s="45"/>
-      <c r="CI66" s="45"/>
-      <c r="CJ66" s="46"/>
+      <c r="O66" s="6"/>
+      <c r="Z66" s="6"/>
+      <c r="AM66" s="6"/>
+      <c r="AW66" s="6"/>
+      <c r="AX66" s="42"/>
+      <c r="AY66" s="43"/>
+      <c r="AZ66" s="44"/>
+      <c r="BA66" s="43"/>
+      <c r="BB66" s="44"/>
+      <c r="BC66" s="43"/>
+      <c r="BD66" s="42"/>
+      <c r="BE66" s="42"/>
+      <c r="BF66" s="42"/>
+      <c r="BG66" s="42"/>
+      <c r="BH66" s="42"/>
+      <c r="BI66" s="42"/>
+      <c r="BJ66" s="43"/>
+      <c r="BK66" s="42"/>
+      <c r="BL66" s="42"/>
+      <c r="BM66" s="42"/>
+      <c r="BN66" s="42"/>
+      <c r="BO66" s="42"/>
+      <c r="BP66" s="42"/>
+      <c r="BQ66" s="42"/>
+      <c r="BR66" s="42"/>
+      <c r="BS66" s="42"/>
+      <c r="BT66" s="43"/>
+      <c r="BU66" s="42"/>
+      <c r="BV66" s="42"/>
+      <c r="BW66" s="42"/>
+      <c r="BX66" s="42"/>
+      <c r="BY66" s="42"/>
+      <c r="BZ66" s="42"/>
+      <c r="CA66" s="42"/>
+      <c r="CB66" s="43"/>
+      <c r="CC66" s="42"/>
+      <c r="CD66" s="42"/>
+      <c r="CE66" s="42"/>
+      <c r="CF66" s="42"/>
+      <c r="CG66" s="42"/>
+      <c r="CH66" s="42"/>
+      <c r="CI66" s="42"/>
+      <c r="CJ66" s="43"/>
     </row>
     <row r="67" spans="15:88">
-      <c r="O67" s="8"/>
-      <c r="Z67" s="8"/>
-      <c r="AM67" s="8"/>
-      <c r="AW67" s="8"/>
-      <c r="AX67" s="45"/>
-      <c r="AY67" s="46"/>
-      <c r="AZ67" s="47"/>
-      <c r="BA67" s="46"/>
-      <c r="BB67" s="48"/>
-      <c r="BC67" s="54"/>
-      <c r="BD67" s="45"/>
-      <c r="BE67" s="45"/>
-      <c r="BF67" s="45"/>
-      <c r="BG67" s="45"/>
-      <c r="BH67" s="45"/>
-      <c r="BI67" s="45"/>
-      <c r="BJ67" s="46"/>
-      <c r="BK67" s="45"/>
-      <c r="BL67" s="45"/>
-      <c r="BM67" s="45"/>
-      <c r="BN67" s="45"/>
-      <c r="BO67" s="45"/>
-      <c r="BP67" s="45"/>
-      <c r="BQ67" s="45"/>
-      <c r="BR67" s="45"/>
-      <c r="BS67" s="45"/>
-      <c r="BT67" s="46"/>
-      <c r="BU67" s="45"/>
-      <c r="BV67" s="45"/>
-      <c r="BW67" s="45"/>
-      <c r="BX67" s="45"/>
-      <c r="BY67" s="45"/>
-      <c r="BZ67" s="45"/>
-      <c r="CA67" s="45"/>
-      <c r="CB67" s="46"/>
-      <c r="CC67" s="45"/>
-      <c r="CD67" s="45"/>
-      <c r="CE67" s="45"/>
-      <c r="CF67" s="45"/>
-      <c r="CG67" s="45"/>
-      <c r="CH67" s="45"/>
-      <c r="CI67" s="45"/>
-      <c r="CJ67" s="46"/>
+      <c r="O67" s="6"/>
+      <c r="Z67" s="6"/>
+      <c r="AM67" s="6"/>
+      <c r="AW67" s="6"/>
+      <c r="AX67" s="42"/>
+      <c r="AY67" s="43"/>
+      <c r="AZ67" s="44"/>
+      <c r="BA67" s="43"/>
+      <c r="BB67" s="45"/>
+      <c r="BC67" s="51"/>
+      <c r="BD67" s="42"/>
+      <c r="BE67" s="42"/>
+      <c r="BF67" s="42"/>
+      <c r="BG67" s="42"/>
+      <c r="BH67" s="42"/>
+      <c r="BI67" s="42"/>
+      <c r="BJ67" s="43"/>
+      <c r="BK67" s="42"/>
+      <c r="BL67" s="42"/>
+      <c r="BM67" s="42"/>
+      <c r="BN67" s="42"/>
+      <c r="BO67" s="42"/>
+      <c r="BP67" s="42"/>
+      <c r="BQ67" s="42"/>
+      <c r="BR67" s="42"/>
+      <c r="BS67" s="42"/>
+      <c r="BT67" s="43"/>
+      <c r="BU67" s="42"/>
+      <c r="BV67" s="42"/>
+      <c r="BW67" s="42"/>
+      <c r="BX67" s="42"/>
+      <c r="BY67" s="42"/>
+      <c r="BZ67" s="42"/>
+      <c r="CA67" s="42"/>
+      <c r="CB67" s="43"/>
+      <c r="CC67" s="42"/>
+      <c r="CD67" s="42"/>
+      <c r="CE67" s="42"/>
+      <c r="CF67" s="42"/>
+      <c r="CG67" s="42"/>
+      <c r="CH67" s="42"/>
+      <c r="CI67" s="42"/>
+      <c r="CJ67" s="43"/>
     </row>
     <row r="68" spans="15:88">
-      <c r="O68" s="8"/>
-      <c r="Z68" s="8"/>
-      <c r="AM68" s="8"/>
-      <c r="AW68" s="8"/>
-      <c r="AX68" s="45"/>
-      <c r="AY68" s="54"/>
-      <c r="AZ68" s="53"/>
-      <c r="BA68" s="54"/>
-      <c r="BB68" s="48"/>
-      <c r="BC68" s="48"/>
-      <c r="BD68" s="48"/>
-      <c r="BE68" s="48"/>
-      <c r="BF68" s="48"/>
-      <c r="BG68" s="48"/>
-      <c r="BH68" s="48"/>
-      <c r="BI68" s="48"/>
-      <c r="BJ68" s="54"/>
-      <c r="BK68" s="48"/>
-      <c r="BL68" s="48"/>
-      <c r="BM68" s="48"/>
-      <c r="BN68" s="48"/>
-      <c r="BO68" s="48"/>
-      <c r="BP68" s="48"/>
-      <c r="BQ68" s="48"/>
-      <c r="BR68" s="48"/>
-      <c r="BS68" s="48"/>
-      <c r="BT68" s="54"/>
-      <c r="BU68" s="48"/>
-      <c r="BV68" s="48"/>
-      <c r="BW68" s="48"/>
-      <c r="BX68" s="48"/>
-      <c r="BY68" s="48"/>
-      <c r="BZ68" s="48"/>
-      <c r="CA68" s="48"/>
-      <c r="CB68" s="54"/>
-      <c r="CC68" s="48"/>
-      <c r="CD68" s="48"/>
-      <c r="CE68" s="48"/>
-      <c r="CF68" s="48"/>
-      <c r="CG68" s="48"/>
-      <c r="CH68" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="CI68" s="48"/>
-      <c r="CJ68" s="54"/>
+      <c r="O68" s="6"/>
+      <c r="Z68" s="6"/>
+      <c r="AM68" s="6"/>
+      <c r="AW68" s="6"/>
+      <c r="AX68" s="42"/>
+      <c r="AY68" s="51"/>
+      <c r="AZ68" s="50"/>
+      <c r="BA68" s="51"/>
+      <c r="BB68" s="45"/>
+      <c r="BC68" s="45"/>
+      <c r="BD68" s="45"/>
+      <c r="BE68" s="45"/>
+      <c r="BF68" s="45"/>
+      <c r="BG68" s="45"/>
+      <c r="BH68" s="45"/>
+      <c r="BI68" s="45"/>
+      <c r="BJ68" s="51"/>
+      <c r="BK68" s="45"/>
+      <c r="BL68" s="45"/>
+      <c r="BM68" s="45"/>
+      <c r="BN68" s="45"/>
+      <c r="BO68" s="45"/>
+      <c r="BP68" s="45"/>
+      <c r="BQ68" s="45"/>
+      <c r="BR68" s="45"/>
+      <c r="BS68" s="45"/>
+      <c r="BT68" s="51"/>
+      <c r="BU68" s="45"/>
+      <c r="BV68" s="45"/>
+      <c r="BW68" s="45"/>
+      <c r="BX68" s="45"/>
+      <c r="BY68" s="45"/>
+      <c r="BZ68" s="45"/>
+      <c r="CA68" s="45"/>
+      <c r="CB68" s="51"/>
+      <c r="CC68" s="45"/>
+      <c r="CD68" s="45"/>
+      <c r="CE68" s="45"/>
+      <c r="CF68" s="45"/>
+      <c r="CG68" s="45"/>
+      <c r="CH68" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="CI68" s="45"/>
+      <c r="CJ68" s="51"/>
     </row>
     <row r="69" spans="15:88">
-      <c r="O69" s="8"/>
-      <c r="Z69" s="8"/>
-      <c r="AM69" s="8"/>
-      <c r="AX69" s="5"/>
-      <c r="AY69" s="8"/>
-      <c r="AZ69" s="9"/>
-      <c r="BA69" s="11"/>
-      <c r="BJ69" s="8"/>
-      <c r="BT69" s="8"/>
-      <c r="CB69" s="8"/>
+      <c r="O69" s="6"/>
+      <c r="Z69" s="6"/>
+      <c r="AM69" s="6"/>
+      <c r="AX69" s="3"/>
+      <c r="AY69" s="6"/>
+      <c r="AZ69" s="7"/>
+      <c r="BA69" s="9"/>
+      <c r="BJ69" s="6"/>
+      <c r="BT69" s="6"/>
+      <c r="CB69" s="6"/>
     </row>
     <row r="70" spans="15:88">
-      <c r="O70" s="8"/>
-      <c r="Z70" s="8"/>
-      <c r="AM70" s="8"/>
-      <c r="AY70" s="8"/>
-      <c r="BJ70" s="8"/>
-      <c r="BT70" s="8"/>
-      <c r="CB70" s="8"/>
+      <c r="O70" s="6"/>
+      <c r="Z70" s="6"/>
+      <c r="AM70" s="6"/>
+      <c r="AY70" s="6"/>
+      <c r="BJ70" s="6"/>
+      <c r="BT70" s="6"/>
+      <c r="CB70" s="6"/>
     </row>
     <row r="71" spans="15:88">
-      <c r="O71" s="8"/>
-      <c r="Z71" s="8"/>
-      <c r="AM71" s="8"/>
-      <c r="AY71" s="8"/>
-      <c r="BJ71" s="8"/>
-      <c r="BT71" s="8"/>
-      <c r="CB71" s="8"/>
+      <c r="O71" s="6"/>
+      <c r="Z71" s="6"/>
+      <c r="AM71" s="6"/>
+      <c r="AY71" s="6"/>
+      <c r="BJ71" s="6"/>
+      <c r="BT71" s="6"/>
+      <c r="CB71" s="6"/>
     </row>
     <row r="72" spans="15:88">
-      <c r="O72" s="8"/>
-      <c r="Z72" s="8"/>
-      <c r="AM72" s="8"/>
-      <c r="AY72" s="8"/>
-      <c r="BJ72" s="8"/>
-      <c r="BT72" s="8"/>
-      <c r="CB72" s="8"/>
+      <c r="O72" s="6"/>
+      <c r="Z72" s="6"/>
+      <c r="AM72" s="6"/>
+      <c r="AY72" s="6"/>
+      <c r="BJ72" s="6"/>
+      <c r="BT72" s="6"/>
+      <c r="CB72" s="6"/>
     </row>
     <row r="73" spans="15:88">
-      <c r="O73" s="8"/>
-      <c r="Z73" s="8"/>
-      <c r="AM73" s="8"/>
-      <c r="AY73" s="8"/>
-      <c r="BJ73" s="8"/>
-      <c r="BT73" s="8"/>
-      <c r="CB73" s="8"/>
+      <c r="O73" s="6"/>
+      <c r="Z73" s="6"/>
+      <c r="AM73" s="6"/>
+      <c r="AY73" s="6"/>
+      <c r="BJ73" s="6"/>
+      <c r="BT73" s="6"/>
+      <c r="CB73" s="6"/>
     </row>
     <row r="74" spans="15:88">
-      <c r="O74" s="8"/>
-      <c r="Z74" s="8"/>
-      <c r="AM74" s="8"/>
-      <c r="AY74" s="8"/>
-      <c r="BJ74" s="8"/>
-      <c r="BT74" s="8"/>
-      <c r="CB74" s="8"/>
+      <c r="O74" s="6"/>
+      <c r="Z74" s="6"/>
+      <c r="AM74" s="6"/>
+      <c r="AY74" s="6"/>
+      <c r="BJ74" s="6"/>
+      <c r="BT74" s="6"/>
+      <c r="CB74" s="6"/>
     </row>
     <row r="75" spans="15:88">
-      <c r="O75" s="8"/>
-      <c r="Z75" s="8"/>
-      <c r="AM75" s="8"/>
-      <c r="AY75" s="8"/>
-      <c r="BJ75" s="8"/>
-      <c r="BT75" s="8"/>
-      <c r="CB75" s="8"/>
+      <c r="O75" s="6"/>
+      <c r="Z75" s="6"/>
+      <c r="AM75" s="6"/>
+      <c r="AY75" s="6"/>
+      <c r="BJ75" s="6"/>
+      <c r="BT75" s="6"/>
+      <c r="CB75" s="6"/>
     </row>
     <row r="76" spans="15:88">
-      <c r="O76" s="8"/>
-      <c r="Z76" s="8"/>
-      <c r="AM76" s="8"/>
-      <c r="AY76" s="8"/>
-      <c r="BJ76" s="8"/>
-      <c r="BT76" s="8"/>
-      <c r="CB76" s="8"/>
+      <c r="O76" s="6"/>
+      <c r="Z76" s="6"/>
+      <c r="AM76" s="6"/>
+      <c r="AY76" s="6"/>
+      <c r="BJ76" s="6"/>
+      <c r="BT76" s="6"/>
+      <c r="CB76" s="6"/>
     </row>
     <row r="77" spans="15:88">
-      <c r="O77" s="8"/>
-      <c r="Z77" s="8"/>
-      <c r="AM77" s="8"/>
-      <c r="AY77" s="8"/>
-      <c r="BJ77" s="8"/>
-      <c r="BT77" s="8"/>
-      <c r="CB77" s="8"/>
+      <c r="O77" s="6"/>
+      <c r="Z77" s="6"/>
+      <c r="AM77" s="6"/>
+      <c r="AY77" s="6"/>
+      <c r="BJ77" s="6"/>
+      <c r="BT77" s="6"/>
+      <c r="CB77" s="6"/>
     </row>
     <row r="78" spans="15:88">
-      <c r="O78" s="8"/>
-      <c r="Z78" s="8"/>
-      <c r="AM78" s="8"/>
-      <c r="AY78" s="8"/>
-      <c r="BJ78" s="8"/>
-      <c r="BT78" s="8"/>
-      <c r="CB78" s="8"/>
+      <c r="O78" s="6"/>
+      <c r="Z78" s="6"/>
+      <c r="AM78" s="6"/>
+      <c r="AY78" s="6"/>
+      <c r="BJ78" s="6"/>
+      <c r="BT78" s="6"/>
+      <c r="CB78" s="6"/>
     </row>
     <row r="79" spans="15:88">
-      <c r="O79" s="8"/>
-      <c r="Z79" s="8"/>
-      <c r="AM79" s="8"/>
-      <c r="AY79" s="8"/>
-      <c r="BJ79" s="8"/>
-      <c r="BT79" s="8"/>
-      <c r="CB79" s="8"/>
+      <c r="O79" s="6"/>
+      <c r="Z79" s="6"/>
+      <c r="AM79" s="6"/>
+      <c r="AY79" s="6"/>
+      <c r="BJ79" s="6"/>
+      <c r="BT79" s="6"/>
+      <c r="CB79" s="6"/>
     </row>
     <row r="80" spans="15:88">
-      <c r="O80" s="8"/>
-      <c r="Z80" s="8"/>
-      <c r="AM80" s="8"/>
-      <c r="AY80" s="8"/>
-      <c r="BJ80" s="8"/>
-      <c r="BT80" s="8"/>
-      <c r="CB80" s="8"/>
+      <c r="O80" s="6"/>
+      <c r="Z80" s="6"/>
+      <c r="AM80" s="6"/>
+      <c r="AY80" s="6"/>
+      <c r="BJ80" s="6"/>
+      <c r="BT80" s="6"/>
+      <c r="CB80" s="6"/>
     </row>
     <row r="81" spans="15:80">
-      <c r="O81" s="8"/>
-      <c r="Z81" s="8"/>
-      <c r="AM81" s="8"/>
-      <c r="AY81" s="8"/>
-      <c r="BJ81" s="8"/>
-      <c r="BT81" s="8"/>
-      <c r="CB81" s="8"/>
+      <c r="O81" s="6"/>
+      <c r="Z81" s="6"/>
+      <c r="AM81" s="6"/>
+      <c r="AY81" s="6"/>
+      <c r="BJ81" s="6"/>
+      <c r="BT81" s="6"/>
+      <c r="CB81" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -9909,175 +8648,175 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88332979-A2FD-4E58-B6E8-B4E152EFAC60}">
   <dimension ref="B20:BM96"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="13.8"/>
   <sheetData>
     <row r="20" spans="2:15">
-      <c r="B20" s="55" t="s">
-        <v>139</v>
+      <c r="B20" s="52" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="2:15">
-      <c r="B21" s="56" t="s">
-        <v>140</v>
+      <c r="B21" s="53" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="2:15">
-      <c r="B22" s="3" t="s">
-        <v>141</v>
+      <c r="B22" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="2:15">
-      <c r="C24" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="57"/>
+      <c r="C24" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="54"/>
     </row>
     <row r="25" spans="2:15">
-      <c r="C25" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="59"/>
-      <c r="K25" s="59"/>
-      <c r="L25" s="59"/>
-      <c r="M25" s="59"/>
-      <c r="N25" s="59"/>
-      <c r="O25" s="60"/>
+      <c r="C25" s="55" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="56"/>
+      <c r="K25" s="56"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="56"/>
+      <c r="N25" s="56"/>
+      <c r="O25" s="57"/>
     </row>
     <row r="26" spans="2:15">
-      <c r="C26" s="58" t="s">
-        <v>145</v>
-      </c>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="59"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="59"/>
-      <c r="J26" s="59"/>
-      <c r="K26" s="59"/>
-      <c r="L26" s="59"/>
-      <c r="M26" s="59"/>
-      <c r="N26" s="59"/>
-      <c r="O26" s="60"/>
+      <c r="C26" s="55" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="56"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="56"/>
+      <c r="K26" s="56"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="56"/>
+      <c r="N26" s="56"/>
+      <c r="O26" s="57"/>
     </row>
     <row r="27" spans="2:15">
-      <c r="C27" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="D27" s="59"/>
-      <c r="E27" s="59"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="59"/>
-      <c r="J27" s="59"/>
-      <c r="K27" s="59"/>
-      <c r="L27" s="59"/>
-      <c r="M27" s="59"/>
-      <c r="N27" s="59"/>
-      <c r="O27" s="60"/>
+      <c r="C27" s="55" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="56"/>
+      <c r="K27" s="56"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="56"/>
+      <c r="N27" s="56"/>
+      <c r="O27" s="57"/>
     </row>
     <row r="28" spans="2:15">
-      <c r="C28" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="D28" s="59"/>
-      <c r="E28" s="59"/>
-      <c r="F28" s="59"/>
-      <c r="G28" s="59"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="59"/>
-      <c r="J28" s="59"/>
-      <c r="K28" s="59"/>
-      <c r="L28" s="59"/>
-      <c r="M28" s="59"/>
-      <c r="N28" s="59"/>
-      <c r="O28" s="60"/>
+      <c r="C28" s="55" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="56"/>
+      <c r="K28" s="56"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="56"/>
+      <c r="N28" s="56"/>
+      <c r="O28" s="57"/>
     </row>
     <row r="29" spans="2:15">
-      <c r="C29" s="58" t="s">
-        <v>148</v>
-      </c>
-      <c r="D29" s="59"/>
-      <c r="E29" s="59"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="59"/>
-      <c r="H29" s="59"/>
-      <c r="I29" s="59"/>
-      <c r="J29" s="59"/>
-      <c r="K29" s="59"/>
-      <c r="L29" s="59"/>
-      <c r="M29" s="59"/>
-      <c r="N29" s="59"/>
-      <c r="O29" s="60"/>
+      <c r="C29" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="56"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="56"/>
+      <c r="K29" s="56"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="56"/>
+      <c r="N29" s="56"/>
+      <c r="O29" s="57"/>
     </row>
     <row r="30" spans="2:15">
-      <c r="C30" s="58" t="s">
-        <v>149</v>
-      </c>
-      <c r="D30" s="59"/>
-      <c r="E30" s="59"/>
-      <c r="F30" s="59"/>
-      <c r="G30" s="59"/>
-      <c r="H30" s="59"/>
-      <c r="I30" s="59"/>
-      <c r="J30" s="59"/>
-      <c r="K30" s="59"/>
-      <c r="L30" s="59"/>
-      <c r="M30" s="59"/>
-      <c r="N30" s="59"/>
-      <c r="O30" s="60"/>
+      <c r="C30" s="55" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="56"/>
+      <c r="K30" s="56"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="56"/>
+      <c r="N30" s="56"/>
+      <c r="O30" s="57"/>
     </row>
     <row r="31" spans="2:15">
-      <c r="C31" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19"/>
-      <c r="O31" s="61"/>
+      <c r="C31" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16"/>
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
+      <c r="M31" s="16"/>
+      <c r="N31" s="16"/>
+      <c r="O31" s="58"/>
     </row>
     <row r="33" spans="2:44">
       <c r="B33" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="34" spans="2:44" ht="18">
-      <c r="B34" s="62" t="s">
-        <v>151</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="2:44" ht="17.399999999999999">
+      <c r="B34" s="59" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="37" spans="2:44">
       <c r="F37" s="82" t="s">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="G37" s="83"/>
       <c r="H37" s="83"/>
@@ -10085,671 +8824,671 @@
       <c r="J37" s="83"/>
       <c r="K37" s="84"/>
       <c r="N37" s="82" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="O37" s="83"/>
       <c r="P37" s="83"/>
       <c r="Q37" s="83"/>
       <c r="R37" s="83"/>
       <c r="S37" s="84"/>
-      <c r="Y37" s="12"/>
-      <c r="Z37" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="AA37" s="13"/>
-      <c r="AB37" s="13"/>
-      <c r="AC37" s="13"/>
-      <c r="AD37" s="14"/>
-      <c r="AO37" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="AP37" s="13"/>
-      <c r="AQ37" s="13"/>
-      <c r="AR37" s="14"/>
+      <c r="Y37" s="10"/>
+      <c r="Z37" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA37" s="11"/>
+      <c r="AB37" s="11"/>
+      <c r="AC37" s="11"/>
+      <c r="AD37" s="12"/>
+      <c r="AO37" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="AP37" s="11"/>
+      <c r="AQ37" s="11"/>
+      <c r="AR37" s="12"/>
     </row>
     <row r="38" spans="2:44">
-      <c r="H38" s="6"/>
-      <c r="P38" s="6"/>
-      <c r="AA38" s="6"/>
-      <c r="AP38" s="6"/>
+      <c r="H38" s="4"/>
+      <c r="P38" s="4"/>
+      <c r="AA38" s="4"/>
+      <c r="AP38" s="4"/>
     </row>
     <row r="39" spans="2:44">
-      <c r="H39" s="8"/>
-      <c r="P39" s="8"/>
-      <c r="AA39" s="8"/>
-      <c r="AP39" s="8"/>
+      <c r="H39" s="6"/>
+      <c r="P39" s="6"/>
+      <c r="AA39" s="6"/>
+      <c r="AP39" s="6"/>
     </row>
     <row r="40" spans="2:44">
-      <c r="C40" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="D40" s="64"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="65"/>
-      <c r="H40" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="P40" s="8"/>
-      <c r="AA40" s="8"/>
-      <c r="AP40" s="8"/>
+      <c r="C40" s="60" t="s">
+        <v>72</v>
+      </c>
+      <c r="D40" s="61"/>
+      <c r="E40" s="61"/>
+      <c r="F40" s="62"/>
+      <c r="H40" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="P40" s="6"/>
+      <c r="AA40" s="6"/>
+      <c r="AP40" s="6"/>
     </row>
     <row r="41" spans="2:44">
-      <c r="H41" s="8"/>
-      <c r="I41" s="12"/>
-      <c r="J41" s="13"/>
-      <c r="K41" s="13"/>
-      <c r="L41" s="14"/>
-      <c r="P41" s="8"/>
-      <c r="AA41" s="8"/>
-      <c r="AP41" s="8"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="12"/>
+      <c r="P41" s="6"/>
+      <c r="AA41" s="6"/>
+      <c r="AP41" s="6"/>
     </row>
     <row r="42" spans="2:44">
-      <c r="H42" s="8"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="6"/>
-      <c r="P42" s="8"/>
-      <c r="AA42" s="8"/>
-      <c r="AP42" s="8"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="4"/>
+      <c r="P42" s="6"/>
+      <c r="AA42" s="6"/>
+      <c r="AP42" s="6"/>
     </row>
     <row r="43" spans="2:44">
-      <c r="H43" s="8"/>
-      <c r="I43" s="7"/>
-      <c r="J43" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="P43" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA43" s="8"/>
-      <c r="AP43" s="8"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="P43" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA43" s="6"/>
+      <c r="AP43" s="6"/>
     </row>
     <row r="44" spans="2:44">
-      <c r="H44" s="8"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="8"/>
-      <c r="P44" s="8"/>
-      <c r="Q44" s="12"/>
-      <c r="R44" s="13"/>
-      <c r="S44" s="13"/>
-      <c r="T44" s="14"/>
-      <c r="AA44" s="8"/>
-      <c r="AP44" s="8"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="6"/>
+      <c r="P44" s="6"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="11"/>
+      <c r="S44" s="11"/>
+      <c r="T44" s="12"/>
+      <c r="AA44" s="6"/>
+      <c r="AP44" s="6"/>
     </row>
     <row r="45" spans="2:44">
-      <c r="H45" s="8"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="8"/>
-      <c r="P45" s="8"/>
-      <c r="Q45" s="4"/>
-      <c r="R45" s="6"/>
-      <c r="AA45" s="8"/>
-      <c r="AP45" s="8"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="6"/>
+      <c r="P45" s="6"/>
+      <c r="Q45" s="2"/>
+      <c r="R45" s="4"/>
+      <c r="AA45" s="6"/>
+      <c r="AP45" s="6"/>
     </row>
     <row r="46" spans="2:44">
-      <c r="H46" s="8"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="8"/>
-      <c r="P46" s="8"/>
-      <c r="Q46" s="7"/>
-      <c r="R46" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="AA46" s="8"/>
-      <c r="AP46" s="8"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="6"/>
+      <c r="P46" s="6"/>
+      <c r="Q46" s="5"/>
+      <c r="R46" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA46" s="6"/>
+      <c r="AP46" s="6"/>
     </row>
     <row r="47" spans="2:44">
-      <c r="H47" s="8"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="8"/>
-      <c r="P47" s="8"/>
-      <c r="Q47" s="7"/>
-      <c r="R47" s="8"/>
-      <c r="AA47" s="8"/>
-      <c r="AP47" s="8"/>
-    </row>
-    <row r="48" spans="2:44" ht="15">
-      <c r="H48" s="8"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="8"/>
-      <c r="P48" s="8"/>
-      <c r="Q48" s="7"/>
-      <c r="R48" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="AA48" s="66" t="s">
-        <v>160</v>
-      </c>
-      <c r="AP48" s="8"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="6"/>
+      <c r="P47" s="6"/>
+      <c r="Q47" s="5"/>
+      <c r="R47" s="6"/>
+      <c r="AA47" s="6"/>
+      <c r="AP47" s="6"/>
+    </row>
+    <row r="48" spans="2:44">
+      <c r="H48" s="6"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="6"/>
+      <c r="P48" s="6"/>
+      <c r="Q48" s="5"/>
+      <c r="R48" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA48" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="AP48" s="6"/>
     </row>
     <row r="49" spans="8:42">
-      <c r="H49" s="8"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="8"/>
-      <c r="P49" s="8"/>
-      <c r="Q49" s="7"/>
-      <c r="R49" s="8"/>
-      <c r="AA49" s="8"/>
-      <c r="AB49" s="12"/>
-      <c r="AC49" s="13"/>
-      <c r="AD49" s="13"/>
-      <c r="AE49" s="14"/>
-      <c r="AP49" s="8"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="6"/>
+      <c r="P49" s="6"/>
+      <c r="Q49" s="5"/>
+      <c r="R49" s="6"/>
+      <c r="AA49" s="6"/>
+      <c r="AB49" s="10"/>
+      <c r="AC49" s="11"/>
+      <c r="AD49" s="11"/>
+      <c r="AE49" s="12"/>
+      <c r="AP49" s="6"/>
     </row>
     <row r="50" spans="8:42">
-      <c r="H50" s="8"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="8"/>
-      <c r="P50" s="8"/>
-      <c r="Q50" s="7"/>
-      <c r="R50" s="8"/>
-      <c r="AA50" s="8"/>
-      <c r="AB50" s="4"/>
-      <c r="AC50" s="6"/>
-      <c r="AP50" s="8"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="6"/>
+      <c r="P50" s="6"/>
+      <c r="Q50" s="5"/>
+      <c r="R50" s="6"/>
+      <c r="AA50" s="6"/>
+      <c r="AB50" s="2"/>
+      <c r="AC50" s="4"/>
+      <c r="AP50" s="6"/>
     </row>
     <row r="51" spans="8:42">
-      <c r="H51" s="8"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="8"/>
-      <c r="P51" s="8"/>
-      <c r="Q51" s="7"/>
-      <c r="R51" s="8"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="7"/>
-      <c r="AC51" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="AP51" s="8"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="6"/>
+      <c r="P51" s="6"/>
+      <c r="Q51" s="5"/>
+      <c r="R51" s="6"/>
+      <c r="AA51" s="6"/>
+      <c r="AB51" s="5"/>
+      <c r="AC51" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="AP51" s="6"/>
     </row>
     <row r="52" spans="8:42">
-      <c r="H52" s="8"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="8"/>
-      <c r="P52" s="8"/>
-      <c r="Q52" s="7"/>
-      <c r="R52" s="8"/>
-      <c r="AA52" s="8"/>
-      <c r="AB52" s="7"/>
-      <c r="AC52" s="8"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="6"/>
+      <c r="P52" s="6"/>
+      <c r="Q52" s="5"/>
+      <c r="R52" s="6"/>
+      <c r="AA52" s="6"/>
+      <c r="AB52" s="5"/>
+      <c r="AC52" s="6"/>
       <c r="AD52" t="s">
-        <v>164</v>
-      </c>
-      <c r="AP52" s="8"/>
+        <v>107</v>
+      </c>
+      <c r="AP52" s="6"/>
     </row>
     <row r="53" spans="8:42">
-      <c r="H53" s="8"/>
-      <c r="I53" s="7"/>
-      <c r="J53" s="8"/>
-      <c r="P53" s="8"/>
-      <c r="Q53" s="7"/>
-      <c r="R53" s="8"/>
-      <c r="AA53" s="8"/>
-      <c r="AB53" s="7"/>
-      <c r="AC53" s="8"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="6"/>
+      <c r="P53" s="6"/>
+      <c r="Q53" s="5"/>
+      <c r="R53" s="6"/>
+      <c r="AA53" s="6"/>
+      <c r="AB53" s="5"/>
+      <c r="AC53" s="6"/>
       <c r="AD53" t="s">
-        <v>165</v>
-      </c>
-      <c r="AP53" s="8"/>
+        <v>108</v>
+      </c>
+      <c r="AP53" s="6"/>
     </row>
     <row r="54" spans="8:42">
-      <c r="H54" s="8"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="8"/>
-      <c r="P54" s="8"/>
-      <c r="Q54" s="7"/>
-      <c r="R54" s="8"/>
-      <c r="AA54" s="8"/>
-      <c r="AB54" s="7"/>
-      <c r="AC54" s="8"/>
-      <c r="AP54" s="8"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="6"/>
+      <c r="P54" s="6"/>
+      <c r="Q54" s="5"/>
+      <c r="R54" s="6"/>
+      <c r="AA54" s="6"/>
+      <c r="AB54" s="5"/>
+      <c r="AC54" s="6"/>
+      <c r="AP54" s="6"/>
     </row>
     <row r="55" spans="8:42">
-      <c r="H55" s="8"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="8"/>
-      <c r="P55" s="8"/>
-      <c r="Q55" s="7"/>
-      <c r="R55" s="8"/>
-      <c r="AA55" s="8"/>
-      <c r="AB55" s="7"/>
-      <c r="AC55" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="AP55" s="8"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="6"/>
+      <c r="P55" s="6"/>
+      <c r="Q55" s="5"/>
+      <c r="R55" s="6"/>
+      <c r="AA55" s="6"/>
+      <c r="AB55" s="5"/>
+      <c r="AC55" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AP55" s="6"/>
     </row>
     <row r="56" spans="8:42">
-      <c r="H56" s="8"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="8"/>
-      <c r="P56" s="8"/>
-      <c r="Q56" s="7"/>
-      <c r="R56" s="8"/>
-      <c r="AA56" s="8"/>
-      <c r="AB56" s="7"/>
-      <c r="AC56" s="8"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="6"/>
+      <c r="P56" s="6"/>
+      <c r="Q56" s="5"/>
+      <c r="R56" s="6"/>
+      <c r="AA56" s="6"/>
+      <c r="AB56" s="5"/>
+      <c r="AC56" s="6"/>
       <c r="AD56" t="s">
-        <v>163</v>
-      </c>
-      <c r="AP56" s="8"/>
+        <v>106</v>
+      </c>
+      <c r="AP56" s="6"/>
     </row>
     <row r="57" spans="8:42">
-      <c r="H57" s="8"/>
-      <c r="I57" s="7"/>
-      <c r="J57" s="8"/>
-      <c r="P57" s="8"/>
-      <c r="Q57" s="7"/>
-      <c r="R57" s="8"/>
-      <c r="AA57" s="8"/>
-      <c r="AB57" s="9"/>
-      <c r="AC57" s="11"/>
-      <c r="AP57" s="8"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="6"/>
+      <c r="P57" s="6"/>
+      <c r="Q57" s="5"/>
+      <c r="R57" s="6"/>
+      <c r="AA57" s="6"/>
+      <c r="AB57" s="7"/>
+      <c r="AC57" s="9"/>
+      <c r="AP57" s="6"/>
     </row>
     <row r="58" spans="8:42">
-      <c r="H58" s="8"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="8"/>
-      <c r="P58" s="8"/>
-      <c r="Q58" s="7"/>
-      <c r="R58" s="8"/>
-      <c r="AA58" s="8"/>
-      <c r="AP58" s="8"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="6"/>
+      <c r="P58" s="6"/>
+      <c r="Q58" s="5"/>
+      <c r="R58" s="6"/>
+      <c r="AA58" s="6"/>
+      <c r="AP58" s="6"/>
     </row>
     <row r="59" spans="8:42">
-      <c r="H59" s="8"/>
-      <c r="I59" s="7"/>
-      <c r="J59" s="8"/>
-      <c r="P59" s="8"/>
-      <c r="Q59" s="7"/>
-      <c r="R59" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="AA59" s="8"/>
-      <c r="AP59" s="8"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="5"/>
+      <c r="J59" s="6"/>
+      <c r="P59" s="6"/>
+      <c r="Q59" s="5"/>
+      <c r="R59" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA59" s="6"/>
+      <c r="AP59" s="6"/>
     </row>
     <row r="60" spans="8:42">
-      <c r="H60" s="8"/>
-      <c r="I60" s="7"/>
-      <c r="J60" s="8"/>
-      <c r="P60" s="8"/>
-      <c r="Q60" s="7"/>
-      <c r="R60" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="AA60" s="8"/>
-      <c r="AP60" s="8"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="6"/>
+      <c r="P60" s="6"/>
+      <c r="Q60" s="5"/>
+      <c r="R60" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA60" s="6"/>
+      <c r="AP60" s="6"/>
     </row>
     <row r="61" spans="8:42">
-      <c r="H61" s="8"/>
-      <c r="I61" s="7"/>
-      <c r="J61" s="8"/>
-      <c r="P61" s="8"/>
-      <c r="Q61" s="7"/>
-      <c r="R61" s="8"/>
-      <c r="AA61" s="8"/>
-      <c r="AP61" s="8"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="6"/>
+      <c r="P61" s="6"/>
+      <c r="Q61" s="5"/>
+      <c r="R61" s="6"/>
+      <c r="AA61" s="6"/>
+      <c r="AP61" s="6"/>
     </row>
     <row r="62" spans="8:42">
-      <c r="H62" s="8"/>
-      <c r="I62" s="7"/>
-      <c r="J62" s="8"/>
-      <c r="P62" s="8"/>
-      <c r="Q62" s="9"/>
-      <c r="R62" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA62" s="8"/>
-      <c r="AP62" s="8"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="6"/>
+      <c r="P62" s="6"/>
+      <c r="Q62" s="7"/>
+      <c r="R62" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA62" s="6"/>
+      <c r="AP62" s="6"/>
     </row>
     <row r="63" spans="8:42">
-      <c r="H63" s="8"/>
-      <c r="I63" s="7"/>
-      <c r="J63" s="8"/>
-      <c r="P63" s="8"/>
-      <c r="AA63" s="8"/>
-      <c r="AP63" s="8"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="6"/>
+      <c r="P63" s="6"/>
+      <c r="AA63" s="6"/>
+      <c r="AP63" s="6"/>
     </row>
     <row r="64" spans="8:42">
-      <c r="H64" s="8"/>
-      <c r="I64" s="7"/>
-      <c r="J64" s="8"/>
-      <c r="P64" s="8"/>
-      <c r="AA64" s="8"/>
-      <c r="AP64" s="8"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="6"/>
+      <c r="P64" s="6"/>
+      <c r="AA64" s="6"/>
+      <c r="AP64" s="6"/>
     </row>
     <row r="65" spans="8:65">
-      <c r="H65" s="8"/>
-      <c r="I65" s="7"/>
-      <c r="J65" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="P65" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="AA65" s="8"/>
-      <c r="AP65" s="8"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="P65" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA65" s="6"/>
+      <c r="AP65" s="6"/>
     </row>
     <row r="66" spans="8:65">
-      <c r="H66" s="8"/>
-      <c r="I66" s="7"/>
-      <c r="J66" s="8"/>
-      <c r="P66" s="8"/>
-      <c r="Q66" s="12"/>
-      <c r="R66" s="13"/>
-      <c r="S66" s="13"/>
-      <c r="T66" s="14"/>
-      <c r="AA66" s="8"/>
-      <c r="AP66" s="8"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="6"/>
+      <c r="P66" s="6"/>
+      <c r="Q66" s="10"/>
+      <c r="R66" s="11"/>
+      <c r="S66" s="11"/>
+      <c r="T66" s="12"/>
+      <c r="AA66" s="6"/>
+      <c r="AP66" s="6"/>
     </row>
     <row r="67" spans="8:65">
-      <c r="H67" s="8"/>
-      <c r="I67" s="7"/>
-      <c r="J67" s="8"/>
-      <c r="P67" s="8"/>
-      <c r="Q67" s="4"/>
-      <c r="R67" s="5"/>
-      <c r="S67" s="4"/>
-      <c r="AA67" s="8"/>
-      <c r="AP67" s="8"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="5"/>
+      <c r="J67" s="6"/>
+      <c r="P67" s="6"/>
+      <c r="Q67" s="2"/>
+      <c r="R67" s="3"/>
+      <c r="S67" s="2"/>
+      <c r="AA67" s="6"/>
+      <c r="AP67" s="6"/>
     </row>
     <row r="68" spans="8:65">
-      <c r="H68" s="8"/>
-      <c r="I68" s="7"/>
-      <c r="J68" s="8"/>
-      <c r="P68" s="8"/>
-      <c r="Q68" s="3"/>
-      <c r="R68" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA68" s="8"/>
-      <c r="AP68" s="8"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="6"/>
+      <c r="P68" s="6"/>
+      <c r="Q68" s="1"/>
+      <c r="R68" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA68" s="6"/>
+      <c r="AP68" s="6"/>
     </row>
     <row r="69" spans="8:65">
-      <c r="H69" s="8"/>
-      <c r="I69" s="7"/>
-      <c r="J69" s="8"/>
-      <c r="P69" s="8"/>
-      <c r="Q69" s="3"/>
-      <c r="R69" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="AA69" s="8"/>
-      <c r="AP69" s="8"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="6"/>
+      <c r="P69" s="6"/>
+      <c r="Q69" s="1"/>
+      <c r="R69" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA69" s="6"/>
+      <c r="AP69" s="6"/>
     </row>
     <row r="70" spans="8:65">
-      <c r="H70" s="8"/>
-      <c r="I70" s="7"/>
-      <c r="J70" s="8"/>
-      <c r="P70" s="8"/>
-      <c r="Q70" s="3"/>
-      <c r="R70" s="8"/>
-      <c r="S70" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="AA70" s="8"/>
-      <c r="AP70" s="8" t="s">
-        <v>172</v>
+      <c r="H70" s="6"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="6"/>
+      <c r="P70" s="6"/>
+      <c r="Q70" s="1"/>
+      <c r="R70" s="6"/>
+      <c r="S70" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA70" s="6"/>
+      <c r="AP70" s="6" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="71" spans="8:65">
-      <c r="H71" s="8"/>
-      <c r="I71" s="7"/>
-      <c r="J71" s="8"/>
-      <c r="P71" s="8"/>
-      <c r="Q71" s="3"/>
-      <c r="R71" s="8"/>
-      <c r="AA71" s="8"/>
-      <c r="AP71" s="8"/>
-      <c r="AQ71" s="12"/>
-      <c r="AR71" s="13"/>
-      <c r="AS71" s="13"/>
-      <c r="AT71" s="14"/>
-    </row>
-    <row r="72" spans="8:65" ht="15" thickBot="1">
-      <c r="H72" s="8"/>
-      <c r="I72" s="7"/>
-      <c r="J72" s="8"/>
-      <c r="P72" s="8"/>
-      <c r="Q72" s="3"/>
-      <c r="R72" s="8"/>
-      <c r="AA72" s="8"/>
-      <c r="AP72" s="8"/>
-      <c r="AQ72" s="4"/>
-      <c r="AR72" s="6"/>
-    </row>
-    <row r="73" spans="8:65" ht="15.75" thickBot="1">
-      <c r="H73" s="8"/>
-      <c r="I73" s="7"/>
-      <c r="J73" s="8"/>
-      <c r="P73" s="8"/>
-      <c r="Q73" s="3"/>
-      <c r="R73" s="8"/>
-      <c r="AA73" s="8"/>
-      <c r="AP73" s="8"/>
-      <c r="AQ73" s="7"/>
-      <c r="AR73" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="BH73" s="67" t="s">
-        <v>193</v>
-      </c>
-      <c r="BI73" s="68"/>
-      <c r="BJ73" s="68"/>
-      <c r="BK73" s="68"/>
-      <c r="BL73" s="68"/>
-      <c r="BM73" s="69"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="6"/>
+      <c r="P71" s="6"/>
+      <c r="Q71" s="1"/>
+      <c r="R71" s="6"/>
+      <c r="AA71" s="6"/>
+      <c r="AP71" s="6"/>
+      <c r="AQ71" s="10"/>
+      <c r="AR71" s="11"/>
+      <c r="AS71" s="11"/>
+      <c r="AT71" s="12"/>
+    </row>
+    <row r="72" spans="8:65" ht="14.4" thickBot="1">
+      <c r="H72" s="6"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="6"/>
+      <c r="P72" s="6"/>
+      <c r="Q72" s="1"/>
+      <c r="R72" s="6"/>
+      <c r="AA72" s="6"/>
+      <c r="AP72" s="6"/>
+      <c r="AQ72" s="2"/>
+      <c r="AR72" s="4"/>
+    </row>
+    <row r="73" spans="8:65" ht="14.4" thickBot="1">
+      <c r="H73" s="6"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="6"/>
+      <c r="P73" s="6"/>
+      <c r="Q73" s="1"/>
+      <c r="R73" s="6"/>
+      <c r="AA73" s="6"/>
+      <c r="AP73" s="6"/>
+      <c r="AQ73" s="5"/>
+      <c r="AR73" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="BH73" s="64" t="s">
+        <v>136</v>
+      </c>
+      <c r="BI73" s="65"/>
+      <c r="BJ73" s="65"/>
+      <c r="BK73" s="65"/>
+      <c r="BL73" s="65"/>
+      <c r="BM73" s="66"/>
     </row>
     <row r="74" spans="8:65">
-      <c r="H74" s="8"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="8"/>
-      <c r="P74" s="8"/>
-      <c r="Q74" s="3"/>
-      <c r="R74" s="8"/>
-      <c r="AA74" s="8"/>
-      <c r="AP74" s="8"/>
-      <c r="AQ74" s="9"/>
-      <c r="AR74" s="11"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="6"/>
+      <c r="P74" s="6"/>
+      <c r="Q74" s="1"/>
+      <c r="R74" s="6"/>
+      <c r="AA74" s="6"/>
+      <c r="AP74" s="6"/>
+      <c r="AQ74" s="7"/>
+      <c r="AR74" s="9"/>
     </row>
     <row r="75" spans="8:65">
-      <c r="H75" s="8"/>
-      <c r="I75" s="7"/>
-      <c r="J75" s="8"/>
-      <c r="P75" s="8"/>
-      <c r="Q75" s="3"/>
-      <c r="R75" s="8"/>
-      <c r="AA75" s="8"/>
-      <c r="AP75" s="8"/>
+      <c r="H75" s="6"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="6"/>
+      <c r="P75" s="6"/>
+      <c r="Q75" s="1"/>
+      <c r="R75" s="6"/>
+      <c r="AA75" s="6"/>
+      <c r="AP75" s="6"/>
     </row>
     <row r="76" spans="8:65">
-      <c r="H76" s="8"/>
-      <c r="I76" s="7"/>
-      <c r="J76" s="8"/>
-      <c r="P76" s="8"/>
-      <c r="Q76" s="3"/>
-      <c r="R76" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA76" s="8"/>
-      <c r="AP76" s="8"/>
+      <c r="H76" s="6"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="6"/>
+      <c r="P76" s="6"/>
+      <c r="Q76" s="1"/>
+      <c r="R76" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA76" s="6"/>
+      <c r="AP76" s="6"/>
     </row>
     <row r="77" spans="8:65">
-      <c r="H77" s="8"/>
-      <c r="I77" s="7"/>
-      <c r="J77" s="8"/>
-      <c r="P77" s="8"/>
-      <c r="Q77" s="3"/>
-      <c r="S77" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="AA77" s="8"/>
-      <c r="AP77" s="8"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="5"/>
+      <c r="J77" s="6"/>
+      <c r="P77" s="6"/>
+      <c r="Q77" s="1"/>
+      <c r="S77" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA77" s="6"/>
+      <c r="AP77" s="6"/>
     </row>
     <row r="78" spans="8:65">
-      <c r="H78" s="8"/>
-      <c r="I78" s="7"/>
-      <c r="J78" s="8"/>
-      <c r="P78" s="8"/>
-      <c r="Q78" s="3"/>
-      <c r="R78" s="8"/>
-      <c r="S78" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="AA78" s="8"/>
-      <c r="AP78" s="8"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="6"/>
+      <c r="P78" s="6"/>
+      <c r="Q78" s="1"/>
+      <c r="R78" s="6"/>
+      <c r="S78" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA78" s="6"/>
+      <c r="AP78" s="6"/>
     </row>
     <row r="79" spans="8:65">
-      <c r="H79" s="8"/>
-      <c r="I79" s="7"/>
-      <c r="J79" s="8"/>
-      <c r="P79" s="8"/>
-      <c r="Q79" s="3"/>
-      <c r="R79" s="8"/>
-      <c r="S79" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="AA79" s="8"/>
-      <c r="AP79" s="8" t="s">
-        <v>172</v>
+      <c r="H79" s="6"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="6"/>
+      <c r="P79" s="6"/>
+      <c r="Q79" s="1"/>
+      <c r="R79" s="6"/>
+      <c r="S79" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA79" s="6"/>
+      <c r="AP79" s="6" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="80" spans="8:65">
-      <c r="H80" s="8"/>
-      <c r="I80" s="7"/>
-      <c r="J80" s="8"/>
-      <c r="P80" s="8"/>
-      <c r="Q80" s="3"/>
-      <c r="R80" s="8"/>
-      <c r="AA80" s="8"/>
-      <c r="AP80" s="8"/>
-      <c r="AQ80" s="12"/>
-      <c r="AR80" s="13"/>
-      <c r="AS80" s="13"/>
-      <c r="AT80" s="14"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="6"/>
+      <c r="P80" s="6"/>
+      <c r="Q80" s="1"/>
+      <c r="R80" s="6"/>
+      <c r="AA80" s="6"/>
+      <c r="AP80" s="6"/>
+      <c r="AQ80" s="10"/>
+      <c r="AR80" s="11"/>
+      <c r="AS80" s="11"/>
+      <c r="AT80" s="12"/>
     </row>
     <row r="81" spans="8:44">
-      <c r="H81" s="8"/>
-      <c r="I81" s="7"/>
-      <c r="J81" s="8"/>
-      <c r="P81" s="8"/>
-      <c r="Q81" s="3"/>
-      <c r="R81" s="8"/>
-      <c r="AA81" s="8"/>
-      <c r="AP81" s="8"/>
-      <c r="AQ81" s="4"/>
-      <c r="AR81" s="6"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="5"/>
+      <c r="J81" s="6"/>
+      <c r="P81" s="6"/>
+      <c r="Q81" s="1"/>
+      <c r="R81" s="6"/>
+      <c r="AA81" s="6"/>
+      <c r="AP81" s="6"/>
+      <c r="AQ81" s="2"/>
+      <c r="AR81" s="4"/>
     </row>
     <row r="82" spans="8:44">
-      <c r="H82" s="8"/>
-      <c r="I82" s="7"/>
-      <c r="J82" s="8"/>
-      <c r="P82" s="8"/>
-      <c r="Q82" s="3"/>
-      <c r="R82" s="8"/>
-      <c r="AA82" s="8"/>
-      <c r="AP82" s="8"/>
-      <c r="AQ82" s="7"/>
-      <c r="AR82" s="8" t="s">
-        <v>173</v>
+      <c r="H82" s="6"/>
+      <c r="I82" s="5"/>
+      <c r="J82" s="6"/>
+      <c r="P82" s="6"/>
+      <c r="Q82" s="1"/>
+      <c r="R82" s="6"/>
+      <c r="AA82" s="6"/>
+      <c r="AP82" s="6"/>
+      <c r="AQ82" s="5"/>
+      <c r="AR82" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="8:44">
-      <c r="H83" s="8"/>
-      <c r="I83" s="7"/>
-      <c r="J83" s="8"/>
-      <c r="P83" s="8"/>
-      <c r="Q83" s="3"/>
-      <c r="R83" s="8"/>
-      <c r="AA83" s="8"/>
-      <c r="AP83" s="8"/>
-      <c r="AQ83" s="9"/>
-      <c r="AR83" s="11"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="5"/>
+      <c r="J83" s="6"/>
+      <c r="P83" s="6"/>
+      <c r="Q83" s="1"/>
+      <c r="R83" s="6"/>
+      <c r="AA83" s="6"/>
+      <c r="AP83" s="6"/>
+      <c r="AQ83" s="7"/>
+      <c r="AR83" s="9"/>
     </row>
     <row r="84" spans="8:44">
-      <c r="H84" s="8"/>
-      <c r="I84" s="7"/>
-      <c r="J84" s="8"/>
-      <c r="P84" s="8"/>
-      <c r="Q84" s="9"/>
-      <c r="R84" s="11"/>
-      <c r="AA84" s="8"/>
-      <c r="AP84" s="8"/>
+      <c r="H84" s="6"/>
+      <c r="I84" s="5"/>
+      <c r="J84" s="6"/>
+      <c r="P84" s="6"/>
+      <c r="Q84" s="7"/>
+      <c r="R84" s="9"/>
+      <c r="AA84" s="6"/>
+      <c r="AP84" s="6"/>
     </row>
     <row r="85" spans="8:44">
-      <c r="H85" s="8"/>
-      <c r="I85" s="9"/>
-      <c r="J85" s="11"/>
-      <c r="P85" s="8"/>
-      <c r="AA85" s="8"/>
-      <c r="AP85" s="8"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="7"/>
+      <c r="J85" s="9"/>
+      <c r="P85" s="6"/>
+      <c r="AA85" s="6"/>
+      <c r="AP85" s="6"/>
     </row>
     <row r="86" spans="8:44">
-      <c r="H86" s="8"/>
-      <c r="P86" s="8"/>
-      <c r="AA86" s="8"/>
-      <c r="AP86" s="8"/>
+      <c r="H86" s="6"/>
+      <c r="P86" s="6"/>
+      <c r="AA86" s="6"/>
+      <c r="AP86" s="6"/>
     </row>
     <row r="87" spans="8:44">
-      <c r="H87" s="8"/>
-      <c r="P87" s="8"/>
-      <c r="AA87" s="8"/>
-      <c r="AP87" s="8"/>
+      <c r="H87" s="6"/>
+      <c r="P87" s="6"/>
+      <c r="AA87" s="6"/>
+      <c r="AP87" s="6"/>
     </row>
     <row r="88" spans="8:44">
-      <c r="H88" s="8"/>
-      <c r="P88" s="8"/>
+      <c r="H88" s="6"/>
+      <c r="P88" s="6"/>
       <c r="V88" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA88" s="8"/>
-      <c r="AP88" s="8"/>
+        <v>70</v>
+      </c>
+      <c r="AA88" s="6"/>
+      <c r="AP88" s="6"/>
     </row>
     <row r="89" spans="8:44">
-      <c r="H89" s="8"/>
-      <c r="P89" s="8"/>
-      <c r="AA89" s="8"/>
-      <c r="AP89" s="8"/>
+      <c r="H89" s="6"/>
+      <c r="P89" s="6"/>
+      <c r="AA89" s="6"/>
+      <c r="AP89" s="6"/>
     </row>
     <row r="90" spans="8:44">
-      <c r="H90" s="8"/>
-      <c r="P90" s="8"/>
-      <c r="AA90" s="8"/>
-      <c r="AP90" s="8"/>
+      <c r="H90" s="6"/>
+      <c r="P90" s="6"/>
+      <c r="AA90" s="6"/>
+      <c r="AP90" s="6"/>
     </row>
     <row r="91" spans="8:44">
-      <c r="H91" s="8"/>
-      <c r="P91" s="8"/>
-      <c r="AA91" s="8"/>
-      <c r="AP91" s="8"/>
+      <c r="H91" s="6"/>
+      <c r="P91" s="6"/>
+      <c r="AA91" s="6"/>
+      <c r="AP91" s="6"/>
     </row>
     <row r="92" spans="8:44">
-      <c r="H92" s="8"/>
-      <c r="P92" s="8"/>
-      <c r="AA92" s="8"/>
-      <c r="AP92" s="8"/>
+      <c r="H92" s="6"/>
+      <c r="P92" s="6"/>
+      <c r="AA92" s="6"/>
+      <c r="AP92" s="6"/>
     </row>
     <row r="93" spans="8:44">
-      <c r="H93" s="8"/>
-      <c r="P93" s="8"/>
-      <c r="AA93" s="8"/>
-      <c r="AP93" s="8"/>
+      <c r="H93" s="6"/>
+      <c r="P93" s="6"/>
+      <c r="AA93" s="6"/>
+      <c r="AP93" s="6"/>
     </row>
     <row r="94" spans="8:44">
-      <c r="H94" s="8"/>
-      <c r="P94" s="8"/>
-      <c r="AA94" s="8"/>
-      <c r="AP94" s="8"/>
+      <c r="H94" s="6"/>
+      <c r="P94" s="6"/>
+      <c r="AA94" s="6"/>
+      <c r="AP94" s="6"/>
     </row>
     <row r="95" spans="8:44">
-      <c r="H95" s="8"/>
-      <c r="P95" s="8"/>
-      <c r="AA95" s="8"/>
-      <c r="AP95" s="8"/>
+      <c r="H95" s="6"/>
+      <c r="P95" s="6"/>
+      <c r="AA95" s="6"/>
+      <c r="AP95" s="6"/>
     </row>
     <row r="96" spans="8:44">
-      <c r="H96" s="8"/>
-      <c r="P96" s="8"/>
-      <c r="AA96" s="8"/>
-      <c r="AP96" s="8"/>
+      <c r="H96" s="6"/>
+      <c r="P96" s="6"/>
+      <c r="AA96" s="6"/>
+      <c r="AP96" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -10761,230 +9500,230 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B97659E-0B8C-451B-B9D6-7BDEA7E84F0C}">
   <dimension ref="A2:AY57"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="13.8"/>
   <sheetData>
-    <row r="2" spans="1:51" ht="23.25">
-      <c r="B2" s="71" t="s">
-        <v>196</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="6"/>
-      <c r="AA2" s="71" t="s">
-        <v>204</v>
-      </c>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
-      <c r="AF2" s="5"/>
-      <c r="AG2" s="5"/>
-      <c r="AH2" s="5"/>
-      <c r="AI2" s="5"/>
-      <c r="AJ2" s="5"/>
-      <c r="AK2" s="5"/>
-      <c r="AL2" s="5"/>
-      <c r="AM2" s="5"/>
-      <c r="AN2" s="5"/>
-      <c r="AO2" s="5"/>
-      <c r="AP2" s="5"/>
-      <c r="AQ2" s="5"/>
-      <c r="AR2" s="5"/>
-      <c r="AS2" s="5"/>
-      <c r="AT2" s="5"/>
-      <c r="AU2" s="5"/>
-      <c r="AV2" s="5"/>
-      <c r="AW2" s="5"/>
-      <c r="AX2" s="5"/>
-      <c r="AY2" s="6"/>
-    </row>
-    <row r="3" spans="1:51" ht="15">
-      <c r="B3" s="75" t="s">
-        <v>197</v>
-      </c>
-      <c r="Y3" s="8"/>
-      <c r="AA3" s="72" t="s">
-        <v>205</v>
-      </c>
-      <c r="AY3" s="8"/>
-    </row>
-    <row r="4" spans="1:51" ht="15">
-      <c r="B4" s="76" t="s">
-        <v>198</v>
-      </c>
-      <c r="Y4" s="8"/>
-      <c r="AA4" s="72" t="s">
-        <v>206</v>
-      </c>
-      <c r="AY4" s="8"/>
-    </row>
-    <row r="5" spans="1:51" ht="15">
-      <c r="B5" s="76" t="s">
-        <v>199</v>
-      </c>
-      <c r="Y5" s="8"/>
-      <c r="AA5" s="72" t="s">
-        <v>207</v>
-      </c>
-      <c r="AY5" s="8"/>
-    </row>
-    <row r="6" spans="1:51" ht="15">
-      <c r="B6" s="76" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y6" s="8"/>
-      <c r="AA6" s="72" t="s">
-        <v>208</v>
-      </c>
-      <c r="AY6" s="8"/>
-    </row>
-    <row r="7" spans="1:51" ht="15">
-      <c r="B7" s="75" t="s">
-        <v>201</v>
-      </c>
-      <c r="Y7" s="8"/>
-      <c r="AA7" s="73" t="s">
-        <v>209</v>
-      </c>
-      <c r="AY7" s="8"/>
+    <row r="2" spans="1:51" ht="22.8">
+      <c r="B2" s="68" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="4"/>
+      <c r="AA2" s="68" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="3"/>
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="3"/>
+      <c r="AK2" s="3"/>
+      <c r="AL2" s="3"/>
+      <c r="AM2" s="3"/>
+      <c r="AN2" s="3"/>
+      <c r="AO2" s="3"/>
+      <c r="AP2" s="3"/>
+      <c r="AQ2" s="3"/>
+      <c r="AR2" s="3"/>
+      <c r="AS2" s="3"/>
+      <c r="AT2" s="3"/>
+      <c r="AU2" s="3"/>
+      <c r="AV2" s="3"/>
+      <c r="AW2" s="3"/>
+      <c r="AX2" s="3"/>
+      <c r="AY2" s="4"/>
+    </row>
+    <row r="3" spans="1:51">
+      <c r="B3" s="72" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y3" s="6"/>
+      <c r="AA3" s="69" t="s">
+        <v>148</v>
+      </c>
+      <c r="AY3" s="6"/>
+    </row>
+    <row r="4" spans="1:51">
+      <c r="B4" s="73" t="s">
+        <v>141</v>
+      </c>
+      <c r="Y4" s="6"/>
+      <c r="AA4" s="69" t="s">
+        <v>149</v>
+      </c>
+      <c r="AY4" s="6"/>
+    </row>
+    <row r="5" spans="1:51">
+      <c r="B5" s="73" t="s">
+        <v>142</v>
+      </c>
+      <c r="Y5" s="6"/>
+      <c r="AA5" s="69" t="s">
+        <v>150</v>
+      </c>
+      <c r="AY5" s="6"/>
+    </row>
+    <row r="6" spans="1:51">
+      <c r="B6" s="73" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y6" s="6"/>
+      <c r="AA6" s="69" t="s">
+        <v>151</v>
+      </c>
+      <c r="AY6" s="6"/>
+    </row>
+    <row r="7" spans="1:51">
+      <c r="B7" s="72" t="s">
+        <v>144</v>
+      </c>
+      <c r="Y7" s="6"/>
+      <c r="AA7" s="70" t="s">
+        <v>152</v>
+      </c>
+      <c r="AY7" s="6"/>
     </row>
     <row r="8" spans="1:51">
-      <c r="B8" s="76" t="s">
-        <v>202</v>
-      </c>
-      <c r="Y8" s="8"/>
-      <c r="AA8" s="74" t="s">
-        <v>210</v>
-      </c>
-      <c r="AY8" s="8"/>
+      <c r="B8" s="73" t="s">
+        <v>145</v>
+      </c>
+      <c r="Y8" s="6"/>
+      <c r="AA8" s="71" t="s">
+        <v>153</v>
+      </c>
+      <c r="AY8" s="6"/>
     </row>
     <row r="9" spans="1:51">
-      <c r="B9" s="76" t="s">
-        <v>203</v>
-      </c>
-      <c r="Y9" s="8"/>
-      <c r="AA9" s="73" t="s">
-        <v>211</v>
-      </c>
-      <c r="AY9" s="8"/>
+      <c r="B9" s="73" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y9" s="6"/>
+      <c r="AA9" s="70" t="s">
+        <v>154</v>
+      </c>
+      <c r="AY9" s="6"/>
     </row>
     <row r="10" spans="1:51">
-      <c r="B10" s="87" t="s">
-        <v>227</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
-      <c r="U10" s="10"/>
-      <c r="V10" s="10"/>
-      <c r="W10" s="10"/>
-      <c r="X10" s="10"/>
-      <c r="Y10" s="11"/>
-      <c r="AA10" s="9"/>
-      <c r="AB10" s="10"/>
-      <c r="AC10" s="10"/>
-      <c r="AD10" s="10"/>
-      <c r="AE10" s="10"/>
-      <c r="AF10" s="10"/>
-      <c r="AG10" s="10"/>
-      <c r="AH10" s="10"/>
-      <c r="AI10" s="10"/>
-      <c r="AJ10" s="10"/>
-      <c r="AK10" s="10"/>
-      <c r="AL10" s="10"/>
-      <c r="AM10" s="10"/>
-      <c r="AN10" s="10"/>
-      <c r="AO10" s="10"/>
-      <c r="AP10" s="10"/>
-      <c r="AQ10" s="10"/>
-      <c r="AR10" s="10"/>
-      <c r="AS10" s="10"/>
-      <c r="AT10" s="10"/>
-      <c r="AU10" s="10"/>
-      <c r="AV10" s="10"/>
-      <c r="AW10" s="10"/>
-      <c r="AX10" s="10"/>
-      <c r="AY10" s="11"/>
-    </row>
-    <row r="12" spans="1:51" ht="15">
-      <c r="B12" s="70" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="13" spans="1:51" ht="15" thickBot="1"/>
-    <row r="14" spans="1:51" s="68" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A14" s="77"/>
-      <c r="B14" s="78" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="15" spans="1:51" ht="15" thickBot="1"/>
-    <row r="16" spans="1:51" ht="15" thickBot="1">
-      <c r="C16" s="79" t="s">
-        <v>214</v>
-      </c>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="80"/>
-      <c r="G16" s="80"/>
-      <c r="H16" s="80"/>
-      <c r="I16" s="80"/>
-      <c r="J16" s="80"/>
-      <c r="K16" s="80"/>
-      <c r="L16" s="80"/>
-      <c r="M16" s="80"/>
-      <c r="N16" s="80"/>
-      <c r="O16" s="81"/>
+      <c r="B10" s="81" t="s">
+        <v>170</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="9"/>
+      <c r="AA10" s="7"/>
+      <c r="AB10" s="8"/>
+      <c r="AC10" s="8"/>
+      <c r="AD10" s="8"/>
+      <c r="AE10" s="8"/>
+      <c r="AF10" s="8"/>
+      <c r="AG10" s="8"/>
+      <c r="AH10" s="8"/>
+      <c r="AI10" s="8"/>
+      <c r="AJ10" s="8"/>
+      <c r="AK10" s="8"/>
+      <c r="AL10" s="8"/>
+      <c r="AM10" s="8"/>
+      <c r="AN10" s="8"/>
+      <c r="AO10" s="8"/>
+      <c r="AP10" s="8"/>
+      <c r="AQ10" s="8"/>
+      <c r="AR10" s="8"/>
+      <c r="AS10" s="8"/>
+      <c r="AT10" s="8"/>
+      <c r="AU10" s="8"/>
+      <c r="AV10" s="8"/>
+      <c r="AW10" s="8"/>
+      <c r="AX10" s="8"/>
+      <c r="AY10" s="9"/>
+    </row>
+    <row r="12" spans="1:51">
+      <c r="B12" s="67" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="1:51" ht="14.4" thickBot="1"/>
+    <row r="14" spans="1:51" s="65" customFormat="1" ht="14.4" thickBot="1">
+      <c r="A14" s="74"/>
+      <c r="B14" s="75" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:51" ht="14.4" thickBot="1"/>
+    <row r="16" spans="1:51" ht="14.4" thickBot="1">
+      <c r="C16" s="76" t="s">
+        <v>157</v>
+      </c>
+      <c r="D16" s="77"/>
+      <c r="E16" s="77"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="77"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="77"/>
+      <c r="M16" s="77"/>
+      <c r="N16" s="77"/>
+      <c r="O16" s="78"/>
     </row>
     <row r="18" spans="4:29">
-      <c r="D18" s="12"/>
-      <c r="E18" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="14"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="12"/>
       <c r="P18" s="82" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="Q18" s="83"/>
       <c r="R18" s="83"/>
@@ -10992,384 +9731,384 @@
       <c r="T18" s="83"/>
       <c r="U18" s="84"/>
       <c r="X18" s="82" t="s">
-        <v>218</v>
+        <v>161</v>
       </c>
       <c r="Y18" s="83"/>
       <c r="Z18" s="83"/>
       <c r="AA18" s="84"/>
     </row>
     <row r="19" spans="4:29">
-      <c r="F19" s="6"/>
-      <c r="R19" s="6"/>
-      <c r="Y19" s="6"/>
+      <c r="F19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="Y19" s="4"/>
     </row>
     <row r="20" spans="4:29">
-      <c r="F20" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="R20" s="8"/>
-      <c r="Y20" s="8"/>
+      <c r="F20" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="R20" s="6"/>
+      <c r="Y20" s="6"/>
     </row>
     <row r="21" spans="4:29">
-      <c r="F21" s="8"/>
+      <c r="F21" s="6"/>
       <c r="G21" t="s">
-        <v>126</v>
-      </c>
-      <c r="R21" s="8"/>
-      <c r="Y21" s="8"/>
+        <v>69</v>
+      </c>
+      <c r="R21" s="6"/>
+      <c r="Y21" s="6"/>
     </row>
     <row r="22" spans="4:29">
-      <c r="F22" s="8"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="14"/>
-      <c r="R22" s="8"/>
-      <c r="Y22" s="8"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="12"/>
+      <c r="R22" s="6"/>
+      <c r="Y22" s="6"/>
     </row>
     <row r="23" spans="4:29">
-      <c r="F23" s="8"/>
-      <c r="H23" s="6"/>
-      <c r="R23" s="8"/>
-      <c r="Y23" s="8"/>
+      <c r="F23" s="6"/>
+      <c r="H23" s="4"/>
+      <c r="R23" s="6"/>
+      <c r="Y23" s="6"/>
     </row>
     <row r="24" spans="4:29">
-      <c r="F24" s="8"/>
+      <c r="F24" s="6"/>
       <c r="H24" t="s">
-        <v>194</v>
-      </c>
-      <c r="R24" s="8"/>
-      <c r="Y24" s="8"/>
+        <v>137</v>
+      </c>
+      <c r="R24" s="6"/>
+      <c r="Y24" s="6"/>
     </row>
     <row r="25" spans="4:29">
-      <c r="F25" s="8"/>
-      <c r="H25" s="40" t="s">
-        <v>195</v>
-      </c>
-      <c r="R25" s="8"/>
-      <c r="Y25" s="8"/>
+      <c r="F25" s="6"/>
+      <c r="H25" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="R25" s="6"/>
+      <c r="Y25" s="6"/>
     </row>
     <row r="26" spans="4:29">
-      <c r="F26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="14"/>
-      <c r="R26" s="8"/>
-      <c r="Y26" s="8"/>
+      <c r="F26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="12"/>
+      <c r="R26" s="6"/>
+      <c r="Y26" s="6"/>
     </row>
     <row r="27" spans="4:29">
-      <c r="F27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="J27" s="6"/>
-      <c r="R27" s="8"/>
-      <c r="Y27" s="8"/>
+      <c r="F27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="J27" s="4"/>
+      <c r="R27" s="6"/>
+      <c r="Y27" s="6"/>
     </row>
     <row r="28" spans="4:29">
-      <c r="F28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="J28" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="R28" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y28" s="8"/>
+      <c r="F28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="J28" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="R28" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y28" s="6"/>
     </row>
     <row r="29" spans="4:29">
-      <c r="F29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="R29" s="8"/>
-      <c r="S29" s="12"/>
-      <c r="T29" s="13"/>
-      <c r="U29" s="13"/>
-      <c r="V29" s="14"/>
-      <c r="Y29" s="8"/>
+      <c r="F29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="R29" s="6"/>
+      <c r="S29" s="10"/>
+      <c r="T29" s="11"/>
+      <c r="U29" s="11"/>
+      <c r="V29" s="12"/>
+      <c r="Y29" s="6"/>
     </row>
     <row r="30" spans="4:29">
-      <c r="F30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="R30" s="8"/>
-      <c r="S30" s="4"/>
-      <c r="T30" s="6"/>
-      <c r="Y30" s="8"/>
+      <c r="F30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="4"/>
+      <c r="Y30" s="6"/>
     </row>
     <row r="31" spans="4:29">
-      <c r="F31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="R31" s="8"/>
-      <c r="S31" s="7"/>
-      <c r="T31" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="Y31" s="8" t="s">
-        <v>219</v>
+      <c r="F31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="R31" s="6"/>
+      <c r="S31" s="5"/>
+      <c r="T31" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="Y31" s="6" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="4:29">
-      <c r="F32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="R32" s="8"/>
-      <c r="S32" s="9"/>
-      <c r="T32" s="11"/>
-      <c r="Y32" s="8"/>
-      <c r="Z32" s="12"/>
-      <c r="AA32" s="13"/>
-      <c r="AB32" s="13"/>
-      <c r="AC32" s="14"/>
+      <c r="F32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="R32" s="6"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="9"/>
+      <c r="Y32" s="6"/>
+      <c r="Z32" s="10"/>
+      <c r="AA32" s="11"/>
+      <c r="AB32" s="11"/>
+      <c r="AC32" s="12"/>
     </row>
     <row r="33" spans="6:33">
-      <c r="F33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="R33" s="8"/>
-      <c r="Y33" s="8"/>
-      <c r="AA33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="R33" s="6"/>
+      <c r="Y33" s="6"/>
+      <c r="AA33" s="4"/>
     </row>
     <row r="34" spans="6:33">
-      <c r="F34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="R34" s="8"/>
-      <c r="Y34" s="8"/>
-      <c r="AA34" s="8" t="s">
-        <v>220</v>
+      <c r="F34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="R34" s="6"/>
+      <c r="Y34" s="6"/>
+      <c r="AA34" s="6" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="35" spans="6:33">
-      <c r="F35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="J35" s="8"/>
-      <c r="R35" s="8"/>
-      <c r="Y35" s="8"/>
-      <c r="AA35" s="8"/>
+      <c r="F35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="R35" s="6"/>
+      <c r="Y35" s="6"/>
+      <c r="AA35" s="6"/>
     </row>
     <row r="36" spans="6:33">
-      <c r="F36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="Y36" s="8"/>
-      <c r="AA36" s="8" t="s">
-        <v>221</v>
+      <c r="F36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="R36" s="6"/>
+      <c r="Y36" s="6"/>
+      <c r="AA36" s="6" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="37" spans="6:33">
-      <c r="F37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="J37" s="8"/>
-      <c r="R37" s="8"/>
-      <c r="Y37" s="8"/>
-      <c r="AA37" s="8"/>
-      <c r="AB37" s="12"/>
-      <c r="AC37" s="13"/>
-      <c r="AD37" s="13"/>
-      <c r="AE37" s="14"/>
+      <c r="F37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="R37" s="6"/>
+      <c r="Y37" s="6"/>
+      <c r="AA37" s="6"/>
+      <c r="AB37" s="10"/>
+      <c r="AC37" s="11"/>
+      <c r="AD37" s="11"/>
+      <c r="AE37" s="12"/>
     </row>
     <row r="38" spans="6:33">
-      <c r="F38" s="8"/>
-      <c r="H38" s="8"/>
-      <c r="J38" s="8"/>
-      <c r="R38" s="8"/>
-      <c r="Y38" s="8"/>
-      <c r="AA38" s="8"/>
-      <c r="AC38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="R38" s="6"/>
+      <c r="Y38" s="6"/>
+      <c r="AA38" s="6"/>
+      <c r="AC38" s="4"/>
     </row>
     <row r="39" spans="6:33">
-      <c r="F39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="J39" s="8"/>
-      <c r="R39" s="8"/>
-      <c r="Y39" s="8"/>
-      <c r="AA39" s="8"/>
-      <c r="AC39" s="8" t="s">
-        <v>224</v>
+      <c r="F39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="R39" s="6"/>
+      <c r="Y39" s="6"/>
+      <c r="AA39" s="6"/>
+      <c r="AC39" s="6" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="40" spans="6:33">
-      <c r="F40" s="8"/>
-      <c r="H40" s="8"/>
-      <c r="J40" s="8"/>
-      <c r="R40" s="8"/>
-      <c r="Y40" s="8"/>
-      <c r="AA40" s="8"/>
-      <c r="AC40" s="8"/>
+      <c r="F40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="R40" s="6"/>
+      <c r="Y40" s="6"/>
+      <c r="AA40" s="6"/>
+      <c r="AC40" s="6"/>
     </row>
     <row r="41" spans="6:33">
-      <c r="F41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="J41" s="8"/>
-      <c r="R41" s="8"/>
-      <c r="Y41" s="8"/>
-      <c r="AA41" s="8"/>
-      <c r="AC41" s="8" t="s">
-        <v>222</v>
+      <c r="F41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="R41" s="6"/>
+      <c r="Y41" s="6"/>
+      <c r="AA41" s="6"/>
+      <c r="AC41" s="6" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="42" spans="6:33">
-      <c r="F42" s="8"/>
-      <c r="H42" s="8"/>
-      <c r="J42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="Y42" s="8"/>
-      <c r="AA42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="12"/>
-      <c r="AE42" s="13"/>
-      <c r="AF42" s="13"/>
-      <c r="AG42" s="14"/>
+      <c r="F42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="R42" s="6"/>
+      <c r="Y42" s="6"/>
+      <c r="AA42" s="6"/>
+      <c r="AC42" s="6"/>
+      <c r="AD42" s="10"/>
+      <c r="AE42" s="11"/>
+      <c r="AF42" s="11"/>
+      <c r="AG42" s="12"/>
     </row>
     <row r="43" spans="6:33">
-      <c r="F43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="R43" s="8"/>
-      <c r="Y43" s="8"/>
-      <c r="AA43" s="8"/>
-      <c r="AC43" s="8"/>
-      <c r="AE43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="R43" s="6"/>
+      <c r="Y43" s="6"/>
+      <c r="AA43" s="6"/>
+      <c r="AC43" s="6"/>
+      <c r="AE43" s="4"/>
     </row>
     <row r="44" spans="6:33">
-      <c r="F44" s="8"/>
-      <c r="H44" s="8"/>
-      <c r="J44" s="8"/>
-      <c r="R44" s="8"/>
-      <c r="Y44" s="8"/>
-      <c r="AA44" s="8"/>
-      <c r="AC44" s="8"/>
-      <c r="AE44" s="8" t="s">
-        <v>223</v>
+      <c r="F44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="R44" s="6"/>
+      <c r="Y44" s="6"/>
+      <c r="AA44" s="6"/>
+      <c r="AC44" s="6"/>
+      <c r="AE44" s="6" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="45" spans="6:33">
-      <c r="F45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="R45" s="8"/>
-      <c r="Y45" s="8"/>
-      <c r="AA45" s="8"/>
-      <c r="AC45" s="8"/>
-      <c r="AE45" s="8"/>
-      <c r="AF45" s="85"/>
-      <c r="AG45" s="86" t="s">
-        <v>226</v>
+      <c r="F45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="J45" s="6"/>
+      <c r="R45" s="6"/>
+      <c r="Y45" s="6"/>
+      <c r="AA45" s="6"/>
+      <c r="AC45" s="6"/>
+      <c r="AE45" s="6"/>
+      <c r="AF45" s="79"/>
+      <c r="AG45" s="80" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="6:33">
-      <c r="F46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="J46" s="8"/>
-      <c r="R46" s="8"/>
-      <c r="Y46" s="8"/>
-      <c r="AA46" s="8"/>
-      <c r="AC46" s="8"/>
+      <c r="F46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="R46" s="6"/>
+      <c r="Y46" s="6"/>
+      <c r="AA46" s="6"/>
+      <c r="AC46" s="6"/>
     </row>
     <row r="47" spans="6:33">
-      <c r="F47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="R47" s="8"/>
-      <c r="Y47" s="8"/>
-      <c r="AA47" s="8"/>
-      <c r="AC47" s="8" t="s">
-        <v>225</v>
+      <c r="F47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="J47" s="6"/>
+      <c r="R47" s="6"/>
+      <c r="Y47" s="6"/>
+      <c r="AA47" s="6"/>
+      <c r="AC47" s="6" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="48" spans="6:33">
-      <c r="F48" s="8"/>
-      <c r="H48" s="8"/>
-      <c r="J48" s="8"/>
-      <c r="R48" s="8"/>
-      <c r="Y48" s="8"/>
-      <c r="AA48" s="8"/>
-      <c r="AC48" s="8"/>
+      <c r="F48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="R48" s="6"/>
+      <c r="Y48" s="6"/>
+      <c r="AA48" s="6"/>
+      <c r="AC48" s="6"/>
     </row>
     <row r="49" spans="6:41">
-      <c r="F49" s="8"/>
-      <c r="H49" s="8"/>
-      <c r="J49" s="8"/>
-      <c r="R49" s="8"/>
-      <c r="Y49" s="8"/>
-      <c r="AA49" s="8"/>
-      <c r="AC49" s="8"/>
+      <c r="F49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="J49" s="6"/>
+      <c r="R49" s="6"/>
+      <c r="Y49" s="6"/>
+      <c r="AA49" s="6"/>
+      <c r="AC49" s="6"/>
     </row>
     <row r="50" spans="6:41">
-      <c r="F50" s="8"/>
-      <c r="H50" s="8"/>
-      <c r="J50" s="8"/>
-      <c r="R50" s="8"/>
-      <c r="Y50" s="8"/>
-      <c r="AA50" s="8"/>
-      <c r="AC50" s="8"/>
+      <c r="F50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="J50" s="6"/>
+      <c r="R50" s="6"/>
+      <c r="Y50" s="6"/>
+      <c r="AA50" s="6"/>
+      <c r="AC50" s="6"/>
     </row>
     <row r="51" spans="6:41">
-      <c r="F51" s="8"/>
-      <c r="H51" s="8"/>
-      <c r="J51" s="8"/>
-      <c r="R51" s="8"/>
-      <c r="Y51" s="8"/>
-      <c r="AA51" s="8"/>
-      <c r="AC51" s="8"/>
+      <c r="F51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="J51" s="6"/>
+      <c r="R51" s="6"/>
+      <c r="Y51" s="6"/>
+      <c r="AA51" s="6"/>
+      <c r="AC51" s="6"/>
     </row>
     <row r="52" spans="6:41">
-      <c r="F52" s="8"/>
-      <c r="H52" s="8"/>
-      <c r="J52" s="8"/>
-      <c r="R52" s="8"/>
-      <c r="Y52" s="8"/>
-      <c r="AA52" s="8"/>
-      <c r="AC52" s="8"/>
+      <c r="F52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="R52" s="6"/>
+      <c r="Y52" s="6"/>
+      <c r="AA52" s="6"/>
+      <c r="AC52" s="6"/>
     </row>
     <row r="53" spans="6:41">
-      <c r="F53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="J53" s="8"/>
-      <c r="R53" s="8"/>
-      <c r="Y53" s="8"/>
-      <c r="AA53" s="8"/>
-      <c r="AC53" s="8"/>
-      <c r="AO53" s="85"/>
+      <c r="F53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="J53" s="6"/>
+      <c r="R53" s="6"/>
+      <c r="Y53" s="6"/>
+      <c r="AA53" s="6"/>
+      <c r="AC53" s="6"/>
+      <c r="AO53" s="79"/>
     </row>
     <row r="54" spans="6:41">
-      <c r="F54" s="8"/>
-      <c r="H54" s="8"/>
-      <c r="J54" s="8"/>
-      <c r="R54" s="8"/>
-      <c r="Y54" s="8"/>
-      <c r="AA54" s="8"/>
-      <c r="AC54" s="8"/>
+      <c r="F54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="R54" s="6"/>
+      <c r="Y54" s="6"/>
+      <c r="AA54" s="6"/>
+      <c r="AC54" s="6"/>
     </row>
     <row r="55" spans="6:41">
-      <c r="F55" s="8"/>
-      <c r="H55" s="8"/>
-      <c r="J55" s="8"/>
-      <c r="R55" s="8"/>
-      <c r="Y55" s="8"/>
-      <c r="AA55" s="8"/>
-      <c r="AC55" s="8"/>
+      <c r="F55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="J55" s="6"/>
+      <c r="R55" s="6"/>
+      <c r="Y55" s="6"/>
+      <c r="AA55" s="6"/>
+      <c r="AC55" s="6"/>
     </row>
     <row r="56" spans="6:41">
-      <c r="F56" s="8"/>
-      <c r="H56" s="8"/>
-      <c r="J56" s="8"/>
-      <c r="R56" s="8"/>
-      <c r="Y56" s="8"/>
-      <c r="AA56" s="8"/>
-      <c r="AC56" s="8"/>
+      <c r="F56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="R56" s="6"/>
+      <c r="Y56" s="6"/>
+      <c r="AA56" s="6"/>
+      <c r="AC56" s="6"/>
     </row>
     <row r="57" spans="6:41">
-      <c r="F57" s="8"/>
-      <c r="H57" s="8"/>
-      <c r="J57" s="8"/>
-      <c r="R57" s="8"/>
-      <c r="Y57" s="8"/>
-      <c r="AA57" s="8"/>
-      <c r="AC57" s="8"/>
+      <c r="F57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="J57" s="6"/>
+      <c r="R57" s="6"/>
+      <c r="Y57" s="6"/>
+      <c r="AA57" s="6"/>
+      <c r="AC57" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -11381,89 +10120,89 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D37D8AE1-203C-42DF-8D3A-6A86DDA0335D}">
   <dimension ref="C2:C17"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="13.8"/>
   <sheetData>
     <row r="2" spans="3:3">
       <c r="C2" t="s">
-        <v>177</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>178</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="3:3">
       <c r="C4" t="s">
-        <v>179</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" t="s">
-        <v>180</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" t="s">
-        <v>182</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="3:3">
       <c r="C8" t="s">
-        <v>183</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" t="s">
-        <v>184</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="3:3">
       <c r="C10" t="s">
-        <v>185</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="3:3">
       <c r="C11" t="s">
-        <v>186</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="3:3">
       <c r="C12" t="s">
-        <v>187</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="3:3">
       <c r="C13" t="s">
-        <v>188</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="3:3">
       <c r="C14" t="s">
-        <v>189</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="3:3">
       <c r="C15" t="s">
-        <v>190</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="3:3">
       <c r="C16" t="s">
-        <v>191</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="3:3">
       <c r="C17" t="s">
-        <v>192</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
